--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -53640,6 +53640,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2317">
+      <c r="A2317" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2317" t="n">
+        <v>2450</v>
+      </c>
+      <c r="C2317" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -53663,6 +53663,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2318">
+      <c r="A2318" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2318" t="n">
+        <v>350</v>
+      </c>
+      <c r="C2318" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -53686,6 +53686,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2319">
+      <c r="A2319" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2319" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2319" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E2319" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F2319" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G2319" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -53709,6 +53709,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2320">
+      <c r="A2320" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2320" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C2320" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G2320" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -53550,22 +53550,22 @@
     </row>
     <row r="2313">
       <c r="A2313" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2313" t="n">
-        <v>350</v>
+        <v>6300</v>
       </c>
       <c r="C2313" t="n">
-        <v>1.20000004768372</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="D2313" t="n">
-        <v>1.20000004768372</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E2313" t="n">
         <v>1.20000004768372</v>
       </c>
       <c r="F2313" t="n">
-        <v>1.20000004768372</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="G2313" t="s">
         <v>7</v>
@@ -53573,13 +53573,13 @@
     </row>
     <row r="2314">
       <c r="A2314" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2314" t="n">
-        <v>3500</v>
+        <v>350</v>
       </c>
       <c r="C2314" t="n">
-        <v>1.23000001907349</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D2314" t="n">
         <v>1.20000004768372</v>
@@ -53596,13 +53596,13 @@
     </row>
     <row r="2315">
       <c r="A2315" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2315" t="n">
-        <v>1400</v>
+        <v>3500</v>
       </c>
       <c r="C2315" t="n">
-        <v>1.21000003814697</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="D2315" t="n">
         <v>1.20000004768372</v>
@@ -53611,7 +53611,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="F2315" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G2315" t="s">
         <v>7</v>
@@ -53619,22 +53619,22 @@
     </row>
     <row r="2316">
       <c r="A2316" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2316" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="C2316" t="n">
-        <v>1.17999994754791</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="D2316" t="n">
-        <v>1.16999995708466</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E2316" t="n">
-        <v>1.17999994754791</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F2316" t="n">
-        <v>1.17999994754791</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="G2316" t="s">
         <v>7</v>
@@ -53642,10 +53642,10 @@
     </row>
     <row r="2317">
       <c r="A2317" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2317" t="n">
-        <v>2450</v>
+        <v>1050</v>
       </c>
       <c r="C2317" t="n">
         <v>1.17999994754791</v>
@@ -53657,7 +53657,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="F2317" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="G2317" t="s">
         <v>7</v>
@@ -53665,22 +53665,22 @@
     </row>
     <row r="2318">
       <c r="A2318" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2318" t="n">
-        <v>350</v>
+        <v>2450</v>
       </c>
       <c r="C2318" t="n">
         <v>1.17999994754791</v>
       </c>
       <c r="D2318" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E2318" t="n">
         <v>1.17999994754791</v>
       </c>
       <c r="F2318" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="G2318" t="s">
         <v>7</v>
@@ -53688,22 +53688,22 @@
     </row>
     <row r="2319">
       <c r="A2319" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2319" t="n">
-        <v>1750</v>
+        <v>350</v>
       </c>
       <c r="C2319" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="D2319" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E2319" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="F2319" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="G2319" t="s">
         <v>7</v>
@@ -53711,10 +53711,10 @@
     </row>
     <row r="2320">
       <c r="A2320" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2320" t="n">
-        <v>4200</v>
+        <v>1750</v>
       </c>
       <c r="C2320" t="n">
         <v>1.16999995708466</v>
@@ -53729,6 +53729,29 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2320" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2321" t="n">
+        <v>700</v>
+      </c>
+      <c r="C2321" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G2321" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35906577110291</v>
+        <v>3.35906600952148</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178224563599</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245125770569</v>
+        <v>3.17245101928711</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206506729126</v>
+        <v>3.12206482887268</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.06981301307678</v>
+        <v>3.0698127746582</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178224563599</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389241218567</v>
+        <v>3.26389217376709</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.881587266922</v>
+        <v>3.88158750534058</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>4.01221799850464</v>
+        <v>4.01221752166748</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556353569031</v>
+        <v>3.96556377410889</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939910888672</v>
+        <v>4.07939958572388</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297533035278</v>
+        <v>4.64297485351562</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.76478481292725</v>
+        <v>6.7647852897644</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830642700195</v>
+        <v>6.08830738067627</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G42" t="n">
-        <v>6.82543468475342</v>
+        <v>6.82543516159058</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876251220703</v>
+        <v>6.84876203536987</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.91407680511475</v>
+        <v>6.9140772819519</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000364303589</v>
+        <v>7.18000316619873</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451351165771</v>
+        <v>7.7445125579834</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>8.02443599700928</v>
+        <v>8.02443504333496</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>8.36034202575684</v>
+        <v>8.36034297943115</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750999450684</v>
+        <v>8.95750904083252</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>6.6434850692749</v>
+        <v>6.64348554611206</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675428390503</v>
+        <v>6.87675380706787</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.5718936920166</v>
+        <v>7.57189416885376</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004287719727</v>
+        <v>7.04004240036011</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673442840576</v>
+        <v>6.94673490524292</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809278488159</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809278488159</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.81143951416016</v>
+        <v>6.811439037323</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75078916549683</v>
+        <v>6.75078964233398</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.783447265625</v>
+        <v>6.78344678878784</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279739379883</v>
+        <v>6.72279691696167</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094562530518</v>
+        <v>6.19094514846802</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287490844727</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962602615356</v>
+        <v>6.13962554931641</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828704833984</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.05564880371094</v>
+        <v>6.0556492805481</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175004959106</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301103591919</v>
+        <v>5.95301055908203</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175004959106</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.68242025375366</v>
+        <v>5.6824197769165</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81304979324341</v>
+        <v>5.81305027008057</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>5.32785177230835</v>
+        <v>5.32785224914551</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316654205322</v>
+        <v>5.39316749572754</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651327133179</v>
+        <v>5.34651279449463</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253700256348</v>
+        <v>5.26253652572632</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.333571434021</v>
+        <v>5.33357191085815</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043039321899</v>
+        <v>5.70043087005615</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212423324585</v>
+        <v>5.83212375640869</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102478027344</v>
+        <v>5.69102430343628</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729078292847</v>
+        <v>6.06729030609131</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891138076782</v>
+        <v>5.24891185760498</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" t="n">
-        <v>5.17365837097168</v>
+        <v>5.17365884780884</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.5</v>
       </c>
       <c r="G208" t="n">
-        <v>5.17365837097168</v>
+        <v>5.17365884780884</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>5.04196548461914</v>
+        <v>5.0419659614563</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077909469604</v>
+        <v>5.06077861785889</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.25</v>
       </c>
       <c r="G217" t="n">
-        <v>4.93849182128906</v>
+        <v>4.93849229812622</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.03255844116211</v>
+        <v>5.03255891799927</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.83501863479614</v>
+        <v>4.8350191116333</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442567825317</v>
+        <v>4.84442615509033</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51048994064331</v>
+        <v>4.51048946380615</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.12951993942261</v>
+        <v>4.12952041625977</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884052276611</v>
+        <v>4.29884004592896</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31295013427734</v>
+        <v>4.31294965744019</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G241" t="n">
-        <v>4.26121377944946</v>
+        <v>4.2612133026123</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22829008102417</v>
+        <v>4.22828960418701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.185959815979</v>
+        <v>4.18596029281616</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312376976013</v>
+        <v>3.99312329292297</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842024803162</v>
+        <v>3.9884204864502</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.75</v>
       </c>
       <c r="G255" t="n">
-        <v>3.52749443054199</v>
+        <v>3.52749466896057</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G264" t="n">
-        <v>3.57452774047852</v>
+        <v>3.57452750205994</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931772232056</v>
+        <v>3.41931796073914</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169121742249</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.41461491584778</v>
+        <v>3.4146146774292</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.75</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52749443054199</v>
+        <v>3.52749466896057</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.386394739151</v>
+        <v>3.38639450073242</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169121742249</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169121742249</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.75</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52749443054199</v>
+        <v>3.52749466896057</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092414855957</v>
+        <v>3.71092438697815</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813133239746</v>
+        <v>3.43813109397888</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.95368885993958</v>
+        <v>2.953688621521</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>3.27821803092957</v>
+        <v>3.27821826934814</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373208999634</v>
+        <v>2.87373232841492</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153270721436</v>
+        <v>2.59153294563293</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950672149658</v>
+        <v>1.98950695991516</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.0929799079895</v>
+        <v>2.09298014640808</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>1.98010039329529</v>
+        <v>1.98010015487671</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90484714508057</v>
+        <v>1.90484702587128</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G345" t="n">
-        <v>1.68755328655243</v>
+        <v>1.68755340576172</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G354" t="n">
-        <v>1.29435527324677</v>
+        <v>1.29435539245605</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.26049137115479</v>
+        <v>1.26049149036407</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209767818451</v>
+        <v>1.55209755897522</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928961753845</v>
+        <v>2.38928937911987</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089556694031</v>
+        <v>2.68089580535889</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>2.62915945053101</v>
+        <v>2.62915921211243</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983958244324</v>
+        <v>2.45983934402466</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.52098274230957</v>
+        <v>2.52098298072815</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216960906982</v>
+        <v>2.50216937065125</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750931739807</v>
+        <v>2.41750955581665</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G401" t="n">
-        <v>2.51627922058105</v>
+        <v>2.51627945899963</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047600746155</v>
+        <v>2.37047624588013</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056294441223</v>
+        <v>2.21056318283081</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31403636932373</v>
+        <v>2.31403660774231</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106967926025</v>
+        <v>2.36106944084167</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31403636932373</v>
+        <v>2.31403660774231</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>2.31403636932373</v>
+        <v>2.31403660774231</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421012401581</v>
+        <v>1.9942102432251</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421012401581</v>
+        <v>1.9942102432251</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421012401581</v>
+        <v>1.9942102432251</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G502" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196727275848</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G526" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434064865112</v>
+        <v>1.75434052944183</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196727275848</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196727275848</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G539" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G547" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421012401581</v>
+        <v>1.9942102432251</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G572" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196727275848</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196727275848</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71201062202454</v>
+        <v>1.71201074123383</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G586" t="n">
-        <v>1.71201062202454</v>
+        <v>1.71201074123383</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315378189087</v>
+        <v>1.77315390110016</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.70730745792389</v>
+        <v>1.7073073387146</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612059116364</v>
+        <v>1.72612071037292</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G594" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G597" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G625" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.625</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55680084228516</v>
+        <v>1.55680096149445</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620752811432</v>
+        <v>1.56620740890503</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.625</v>
       </c>
       <c r="G650" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803105831146</v>
+        <v>1.45803093910217</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.375</v>
       </c>
       <c r="G659" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>0.93125855922699</v>
+        <v>0.931258499622345</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G663" t="n">
-        <v>0.93125855922699</v>
+        <v>0.931258499622345</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G665" t="n">
-        <v>0.893631935119629</v>
+        <v>0.893631875514984</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G666" t="n">
-        <v>0.893631935119629</v>
+        <v>0.893631875514984</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775154590607</v>
+        <v>0.954775094985962</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106550693512</v>
+        <v>0.886106610298157</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970512390137</v>
+        <v>0.919970571994781</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089270591736</v>
+        <v>0.918089210987091</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021162033081</v>
+        <v>0.935021221637726</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.91432648897171</v>
+        <v>0.914326548576355</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G687" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>1.15701818466187</v>
+        <v>1.15701830387115</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409496307373</v>
+        <v>1.12409508228302</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.15701818466187</v>
+        <v>1.15701830387115</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G717" t="n">
-        <v>1.26049137115479</v>
+        <v>1.26049149036407</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875465869904</v>
+        <v>1.20875477790833</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G736" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G739" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.375</v>
       </c>
       <c r="G756" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.375</v>
       </c>
       <c r="G770" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G782" t="n">
-        <v>1.26049137115479</v>
+        <v>1.26049149036407</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G795" t="n">
-        <v>1.14290821552277</v>
+        <v>1.14290809631348</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G818" t="n">
-        <v>1.17112815380096</v>
+        <v>1.17112827301025</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G823" t="n">
-        <v>1.17112815380096</v>
+        <v>1.17112827301025</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G824" t="n">
-        <v>1.17112815380096</v>
+        <v>1.17112827301025</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G827" t="n">
-        <v>1.15701818466187</v>
+        <v>1.15701830387115</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510759830475</v>
+        <v>1.42510771751404</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G881" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.375</v>
       </c>
       <c r="G882" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.375</v>
       </c>
       <c r="G893" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.49095439910889</v>
+        <v>1.4909542798996</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G904" t="n">
-        <v>1.90014362335205</v>
+        <v>1.90014374256134</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G908" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.70260393619537</v>
+        <v>1.70260381698608</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.70260393619537</v>
+        <v>1.70260381698608</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361728668213</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777024745941</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946325302124</v>
+        <v>2.06946349143982</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361728668213</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361728668213</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827662467957</v>
+        <v>2.08827686309814</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.76555562019348</v>
+        <v>2.76555585861206</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.75</v>
       </c>
       <c r="G956" t="n">
-        <v>2.58682918548584</v>
+        <v>2.58682942390442</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.25</v>
       </c>
       <c r="G964" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224118232727</v>
+        <v>3.45224142074585</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G970" t="n">
-        <v>3.40520787239075</v>
+        <v>3.40520763397217</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G971" t="n">
-        <v>3.42402124404907</v>
+        <v>3.42402148246765</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.31114149093628</v>
+        <v>3.3111412525177</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.92546844482422</v>
+        <v>2.9254686832428</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.25</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.37698769569397</v>
+        <v>3.37698793411255</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630756378174</v>
+        <v>3.54630780220032</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.84732055664062</v>
+        <v>3.8473207950592</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.52749443054199</v>
+        <v>3.52749466896057</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.75</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.52749443054199</v>
+        <v>3.52749466896057</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.40520787239075</v>
+        <v>3.40520763397217</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.80969429016113</v>
+        <v>3.80969405174255</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562767028809</v>
+        <v>3.71562743186951</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.57452774047852</v>
+        <v>3.57452750205994</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.43342804908752</v>
+        <v>3.4334282875061</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046135902405</v>
+        <v>3.48046112060547</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.62507843971252</v>
+        <v>3.6250786781311</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794931411743</v>
+        <v>3.54794955253601</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436101913452</v>
+        <v>3.64436078071594</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579609870911</v>
+        <v>3.60579633712769</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687258720398</v>
+        <v>3.57687282562256</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.3262026309967</v>
+        <v>3.32620239257812</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31387996673584</v>
+        <v>2.31388020515442</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608028888702</v>
+        <v>1.98608016967773</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029167175293</v>
+        <v>2.41029143333435</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.29727911949158</v>
+        <v>3.297278881073</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512614250183</v>
+        <v>3.35512590408325</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871419906616</v>
+        <v>3.25871443748474</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -60770,6 +60770,32 @@
         <v>1.1599999666214</v>
       </c>
       <c r="H2323" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2324" t="n">
+        <v>3150</v>
+      </c>
+      <c r="C2324" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G2324" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H2324" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35906600952148</v>
+        <v>3.35906577110291</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671106338501</v>
+        <v>3.19671082496643</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206482887268</v>
+        <v>3.12206506729126</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389217376709</v>
+        <v>3.26389241218567</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G19" t="n">
-        <v>3.29375076293945</v>
+        <v>3.29375052452087</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556377410889</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830738067627</v>
+        <v>6.08830690383911</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876203536987</v>
+        <v>6.84876251220703</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>7.46459102630615</v>
+        <v>7.46459054946899</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>7.46459102630615</v>
+        <v>7.46459054946899</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451303482056</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435848236084</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>8.36034297943115</v>
+        <v>8.36034202575684</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866466522217</v>
+        <v>7.19866514205933</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061380386353</v>
+        <v>7.38061428070068</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059490203857</v>
+        <v>7.45059537887573</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004240036011</v>
+        <v>7.04004287719727</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75078964233398</v>
+        <v>6.75078916549683</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279691696167</v>
+        <v>6.72279739379883</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094514846802</v>
+        <v>6.19094562530518</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287490844727</v>
+        <v>6.44287538528442</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555191040039</v>
+        <v>6.40555143356323</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962554931641</v>
+        <v>6.13962602615356</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.0556492805481</v>
+        <v>6.05564880371094</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301055908203</v>
+        <v>5.95301103591919</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245853424072</v>
+        <v>5.54245901107788</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375875473022</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>5.45848178863525</v>
+        <v>5.4584813117981</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052877426147</v>
+        <v>5.29052925109863</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>5.32785224914551</v>
+        <v>5.32785177230835</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651279449463</v>
+        <v>5.34651327133179</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729030609131</v>
+        <v>6.06729078292847</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891185760498</v>
+        <v>5.24891138076782</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950529098511</v>
+        <v>5.23950481414795</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721897125244</v>
+        <v>5.11721849441528</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>5.0419659614563</v>
+        <v>5.04196548461914</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.25</v>
       </c>
       <c r="G217" t="n">
-        <v>4.93849229812622</v>
+        <v>4.93849182128906</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442615509033</v>
+        <v>4.84442567825317</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985256195068</v>
+        <v>4.59985303878784</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472995758057</v>
+        <v>4.28472948074341</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.24240016937256</v>
+        <v>4.2423996925354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.12952041625977</v>
+        <v>4.12951993942261</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884004592896</v>
+        <v>4.29884052276611</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G241" t="n">
-        <v>4.2612133026123</v>
+        <v>4.26121377944946</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22828960418701</v>
+        <v>4.22829008102417</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.18596029281616</v>
+        <v>4.185959815979</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.0636739730835</v>
+        <v>4.06367349624634</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312376976013</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.9884204864502</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G254" t="n">
-        <v>3.54160451889038</v>
+        <v>3.54160475730896</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.75</v>
       </c>
       <c r="G255" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.75</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.75</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092438697815</v>
+        <v>3.71092414855957</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>3.27821826934814</v>
+        <v>3.27821803092957</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153294563293</v>
+        <v>2.59153270721436</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G329" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.09298014640808</v>
+        <v>2.0929799079895</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>1.98010015487671</v>
+        <v>1.98010039329529</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90484702587128</v>
+        <v>1.90484714508057</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209755897522</v>
+        <v>1.55209767818451</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928937911987</v>
+        <v>2.38928961753845</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975264549255</v>
+        <v>2.61975240707397</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.52098298072815</v>
+        <v>2.52098274230957</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216937065125</v>
+        <v>2.50216960906982</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860948562622</v>
+        <v>2.55860924720764</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047624588013</v>
+        <v>2.37047600746155</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056318283081</v>
+        <v>2.21056294441223</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691612243652</v>
+        <v>2.4269163608551</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434052944183</v>
+        <v>1.75434064865112</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G586" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264752388</v>
+        <v>1.62264740467072</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387762069702</v>
+        <v>1.52387750148773</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798758983612</v>
+        <v>1.53798747062683</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620740890503</v>
+        <v>1.56620752811432</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378746509552</v>
+        <v>0.818378686904907</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775094985962</v>
+        <v>0.954775154590607</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089210987091</v>
+        <v>0.918089270591736</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326548576355</v>
+        <v>0.91432648897171</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591849327087</v>
+        <v>1.01591837406158</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G717" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G740" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G782" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G795" t="n">
-        <v>1.14290809631348</v>
+        <v>1.14290821552277</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G818" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G823" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G824" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G827" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G874" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.4909542798996</v>
+        <v>1.49095439910889</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G904" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G955" t="n">
-        <v>2.71852254867554</v>
+        <v>2.71852231025696</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>2.75614905357361</v>
+        <v>2.75614929199219</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.8690288066864</v>
+        <v>2.86902856826782</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G970" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G971" t="n">
-        <v>3.42402148246765</v>
+        <v>3.42402124404907</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3111412525177</v>
+        <v>3.31114149093628</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597517967224</v>
+        <v>3.07597494125366</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707510948181</v>
+        <v>3.21707487106323</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.77206778526306</v>
+        <v>3.77206754684448</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.75</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.80969405174255</v>
+        <v>3.80969429016113</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562743186951</v>
+        <v>3.71562767028809</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046112060547</v>
+        <v>3.48046135902405</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -60796,6 +60796,32 @@
         <v>1.13999998569489</v>
       </c>
       <c r="H2324" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2325" t="n">
+        <v>20300</v>
+      </c>
+      <c r="C2325" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2325" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="H2325" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671082496643</v>
+        <v>3.19671106338501</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245101928711</v>
+        <v>3.17245125770569</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G19" t="n">
-        <v>3.29375052452087</v>
+        <v>3.29375076293945</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501127243042</v>
+        <v>3.55501103401184</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.88158750534058</v>
+        <v>3.88158702850342</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105966567993</v>
+        <v>3.86105942726135</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556401252747</v>
+        <v>3.96556377410889</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939958572388</v>
+        <v>4.07939910888672</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615503311157</v>
+        <v>4.23615550994873</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30147075653076</v>
+        <v>4.3014702796936</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297485351562</v>
+        <v>4.64297533035278</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521352767944</v>
+        <v>5.22521305084229</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120506286621</v>
+        <v>7.65120553970337</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7647852897644</v>
+        <v>6.76478576660156</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092576980591</v>
+        <v>6.26092529296875</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761827468872</v>
+        <v>6.16761779785156</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G41" t="n">
-        <v>6.35423278808594</v>
+        <v>6.3542332649231</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>6.99338865280151</v>
+        <v>6.99338817596436</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939300537109</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000316619873</v>
+        <v>7.18000411987305</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>7.46459054946899</v>
+        <v>7.46459102630615</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>7.46459054946899</v>
+        <v>7.46459102630615</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451303482056</v>
+        <v>7.7445125579834</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435848236084</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>8.36034202575684</v>
+        <v>8.36034107208252</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750904083252</v>
+        <v>8.95750999450684</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424125671387</v>
+        <v>8.72424030303955</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303840637207</v>
+        <v>8.25303936004639</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175899505615</v>
+        <v>8.06175804138184</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866514205933</v>
+        <v>7.19866466522217</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002254486084</v>
+        <v>7.11002206802368</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675380706787</v>
+        <v>6.87675428390503</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>7.52524042129517</v>
+        <v>7.52523994445801</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252466201782</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858715057373</v>
+        <v>7.47858762741089</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059537887573</v>
+        <v>7.45059490203857</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.08669567108154</v>
+        <v>7.0866961479187</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>6.99338865280151</v>
+        <v>6.99338817596436</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474700927734</v>
+        <v>6.90474653244019</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939300537109</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405790328979</v>
+        <v>6.98405838012695</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004287719727</v>
+        <v>7.04004192352295</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673490524292</v>
+        <v>6.94673538208008</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>6.85809278488159</v>
+        <v>6.85809326171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466806411743</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>6.96539688110352</v>
+        <v>6.96539640426636</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85809278488159</v>
+        <v>6.85809326171875</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75078916549683</v>
+        <v>6.75078964233398</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279739379883</v>
+        <v>6.72279691696167</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817077636719</v>
+        <v>6.57817029953003</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094562530518</v>
+        <v>6.19094514846802</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555143356323</v>
+        <v>6.40555191040039</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828704833984</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.05564880371094</v>
+        <v>6.0556492805481</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75706577301025</v>
+        <v>5.7570652961731</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>6.37289476394653</v>
+        <v>6.37289428710938</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245901107788</v>
+        <v>5.54245853424072</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305027008057</v>
+        <v>5.81305074691772</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238054275513</v>
+        <v>5.82238101959229</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>5.4584813117981</v>
+        <v>5.45848178863525</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517477035522</v>
+        <v>5.36517429351807</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052925109863</v>
+        <v>5.29052877426147</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789052963257</v>
+        <v>5.18789100646973</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316701889038</v>
+        <v>5.39316749572754</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253652572632</v>
+        <v>5.26253700256348</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.73805713653564</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.73805713653564</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102478027344</v>
+        <v>5.69102430343628</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729078292847</v>
+        <v>6.06729030609131</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390453338623</v>
+        <v>5.80390405654907</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399099349976</v>
+        <v>5.64399147033691</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950481414795</v>
+        <v>5.23950576782227</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2206916809082</v>
+        <v>5.22069215774536</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.5</v>
       </c>
       <c r="G208" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721849441528</v>
+        <v>5.11721897125244</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959175109863</v>
+        <v>5.07959222793579</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.03255891799927</v>
+        <v>5.03255844116211</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>4.89145851135254</v>
+        <v>4.8914589881897</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G224" t="n">
-        <v>4.87264585494995</v>
+        <v>4.87264537811279</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472948074341</v>
+        <v>4.28472995758057</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.2423996925354</v>
+        <v>4.24240016937256</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884052276611</v>
+        <v>4.2988395690918</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22829008102417</v>
+        <v>4.22828960418701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.06367349624634</v>
+        <v>4.0636739730835</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312376976013</v>
+        <v>3.99312329292297</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842024803162</v>
+        <v>3.98842000961304</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147411346436</v>
+        <v>3.78147435188293</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G254" t="n">
-        <v>3.54160475730896</v>
+        <v>3.54160451889038</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.67329740524292</v>
+        <v>3.6732976436615</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G264" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.4146146774292</v>
+        <v>3.41461491584778</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G289" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>3.62156081199646</v>
+        <v>3.62156105041504</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813133239746</v>
+        <v>3.43813109397888</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.95368885993958</v>
+        <v>2.953688621521</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373208999634</v>
+        <v>2.87373232841492</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>2.1211998462677</v>
+        <v>2.12120008468628</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950695991516</v>
+        <v>1.98950672149658</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654003143311</v>
+        <v>2.03654026985168</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G329" t="n">
-        <v>2.1211998462677</v>
+        <v>2.12120008468628</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924653053284</v>
+        <v>1.81924641132355</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80983984470367</v>
+        <v>1.80983996391296</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G354" t="n">
-        <v>1.29435539245605</v>
+        <v>1.29435527324677</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209767818451</v>
+        <v>1.55209743976593</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928961753845</v>
+        <v>2.38928937911987</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089580535889</v>
+        <v>2.68089556694031</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975240707397</v>
+        <v>2.61975288391113</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983934402466</v>
+        <v>2.45983958244324</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G392" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216960906982</v>
+        <v>2.50216937065125</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860924720764</v>
+        <v>2.55860948562622</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G401" t="n">
-        <v>2.51627945899963</v>
+        <v>2.51627922058105</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047600746155</v>
+        <v>2.37047624588013</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056294441223</v>
+        <v>2.21056318283081</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.4269163608551</v>
+        <v>2.42691588401794</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13530993461609</v>
+        <v>2.13531017303467</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G460" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G502" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196715354919</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G522" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G526" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434064865112</v>
+        <v>1.75434052944183</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196715354919</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196715354919</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G539" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G547" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G553" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G572" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196715354919</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196715354919</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315390110016</v>
+        <v>1.77315378189087</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.7073073387146</v>
+        <v>1.70730745792389</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379068374634</v>
+        <v>1.68379056453705</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5191742181778</v>
+        <v>1.51917433738708</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264740467072</v>
+        <v>1.62264752388</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091081142426</v>
+        <v>1.57091093063354</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387750148773</v>
+        <v>1.52387762069702</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55680096149445</v>
+        <v>1.55680084228516</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798747062683</v>
+        <v>1.53798758983612</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625099658966</v>
+        <v>1.48625111579895</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447105407715</v>
+        <v>1.51447093486786</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.375</v>
       </c>
       <c r="G659" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G663" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G665" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G666" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106610298157</v>
+        <v>0.886106550693512</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089270591736</v>
+        <v>0.918089210987091</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.91432648897171</v>
+        <v>0.914326608181</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591837406158</v>
+        <v>1.01591849327087</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409496307373</v>
+        <v>1.12409508228302</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985435009003</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G723" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G728" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G733" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G737" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.375</v>
       </c>
       <c r="G756" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.375</v>
       </c>
       <c r="G770" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G780" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.1476114988327</v>
+        <v>1.14761161804199</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G791" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G816" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G826" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G828" t="n">
-        <v>1.15231490135193</v>
+        <v>1.15231478214264</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985435009003</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G863" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.35926115512848</v>
+        <v>1.35926127433777</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G874" t="n">
-        <v>1.35926115512848</v>
+        <v>1.35926127433777</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.33104121685028</v>
+        <v>1.33104133605957</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.375</v>
       </c>
       <c r="G882" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.375</v>
       </c>
       <c r="G893" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.49095439910889</v>
+        <v>1.4909542798996</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G902" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G913" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.15412330627441</v>
+        <v>2.15412306785583</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.97250199317932</v>
+        <v>2.9725022315979</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G955" t="n">
-        <v>2.71852231025696</v>
+        <v>2.71852254867554</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.75</v>
       </c>
       <c r="G956" t="n">
-        <v>2.58682942390442</v>
+        <v>2.58682918548584</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>2.75614929199219</v>
+        <v>2.75614905357361</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.86902856826782</v>
+        <v>2.8690288066864</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.31114149093628</v>
+        <v>3.3111412525177</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470161437988</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G989" t="n">
-        <v>3.30173468589783</v>
+        <v>3.30173492431641</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292179107666</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470161437988</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597494125366</v>
+        <v>3.07597517967224</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707487106323</v>
+        <v>3.21707510948181</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630780220032</v>
+        <v>3.54630756378174</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.77206754684448</v>
+        <v>3.77206778526306</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512093544006</v>
+        <v>3.56512117385864</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562767028809</v>
+        <v>3.71562743186951</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292179107666</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046135902405</v>
+        <v>3.48046112060547</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -60822,6 +60822,32 @@
         <v>1.08000004291534</v>
       </c>
       <c r="H2325" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2326" t="n">
+        <v>11550</v>
+      </c>
+      <c r="C2326" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2326" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249025344849</v>
+        <v>3.03249001502991</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15378975868225</v>
+        <v>3.15378952026367</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245125770569</v>
+        <v>3.17245101928711</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044326782227</v>
+        <v>3.20044350624084</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512802124023</v>
+        <v>3.13512825965881</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198707580566</v>
+        <v>3.40198683738708</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501103401184</v>
+        <v>3.55501127243042</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.88158702850342</v>
+        <v>3.881587266922</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105942726135</v>
+        <v>3.86105966567993</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>4.01221752166748</v>
+        <v>4.01221799850464</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556377410889</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615550994873</v>
+        <v>4.23615503311157</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3014702796936</v>
+        <v>4.30147123336792</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521305084229</v>
+        <v>5.2252140045166</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.76478576660156</v>
+        <v>6.7647852897644</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088653564453</v>
+        <v>6.40088701248169</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G41" t="n">
-        <v>6.3542332649231</v>
+        <v>6.35423231124878</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876251220703</v>
+        <v>6.84876203536987</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080854415894</v>
+        <v>6.68080806732178</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9140772819519</v>
+        <v>6.91407680511475</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000411987305</v>
+        <v>7.18000316619873</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451351165771</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>8.02443504333496</v>
+        <v>8.02443599700928</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435657501221</v>
+        <v>8.30435752868652</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>8.36034107208252</v>
+        <v>8.36034202575684</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424030303955</v>
+        <v>8.72424125671387</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303936004639</v>
+        <v>8.25303840637207</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726755142212</v>
+        <v>7.42726802825928</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061428070068</v>
+        <v>7.38061380386353</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002206802368</v>
+        <v>7.11002254486084</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675428390503</v>
+        <v>6.87675380706787</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252466201782</v>
+        <v>7.70252513885498</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858762741089</v>
+        <v>7.47858715057373</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.57189416885376</v>
+        <v>7.5718936920166</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.0866961479187</v>
+        <v>7.08669567108154</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474653244019</v>
+        <v>6.90474700927734</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405838012695</v>
+        <v>6.98405790328979</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004192352295</v>
+        <v>7.04004240036011</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541530609131</v>
+        <v>6.89541578292847</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673538208008</v>
+        <v>6.94673490524292</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809230804443</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809230804443</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>6.83943128585815</v>
+        <v>6.839430809021</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75078964233398</v>
+        <v>6.75078916549683</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279691696167</v>
+        <v>6.72279739379883</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817029953003</v>
+        <v>6.57817077636719</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419403076172</v>
+        <v>6.49419355392456</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.51285552978516</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287490844727</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555191040039</v>
+        <v>6.40555143356323</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.51285552978516</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G114" t="n">
-        <v>6.3075795173645</v>
+        <v>6.30757904052734</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828704833984</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561052322388</v>
+        <v>6.19561004638672</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G121" t="n">
-        <v>6.14895677566528</v>
+        <v>6.14895629882812</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.0556492805481</v>
+        <v>6.05564975738525</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7570652961731</v>
+        <v>5.75706624984741</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>6.37289428710938</v>
+        <v>6.37289476394653</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301103591919</v>
+        <v>5.95301151275635</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108127593994</v>
+        <v>5.7010817527771</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245853424072</v>
+        <v>5.54245901107788</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.6824197769165</v>
+        <v>5.68242073059082</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375875473022</v>
+        <v>5.66375827789307</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305074691772</v>
+        <v>5.81305027008057</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238101959229</v>
+        <v>5.82238054275513</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>5.71041202545166</v>
+        <v>5.71041250228882</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517429351807</v>
+        <v>5.36517524719238</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>5.32785177230835</v>
+        <v>5.32785224914551</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718299865723</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17856025695801</v>
+        <v>5.17856073379517</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789100646973</v>
+        <v>5.18789052963257</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718299865723</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.33357191085815</v>
+        <v>5.333571434021</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>5.45585823059082</v>
+        <v>5.45585870742798</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043087005615</v>
+        <v>5.70043134689331</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212375640869</v>
+        <v>5.83212423324585</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>5.45585823059082</v>
+        <v>5.45585870742798</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950576782227</v>
+        <v>5.23950529098511</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G202" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721897125244</v>
+        <v>5.11721849441528</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077861785889</v>
+        <v>5.06077909469604</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>4.97611904144287</v>
+        <v>4.97611856460571</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442567825317</v>
+        <v>4.84442520141602</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472995758057</v>
+        <v>4.28472948074341</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490383148193</v>
+        <v>3.96490359306335</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.2988395690918</v>
+        <v>4.29884004592896</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31294965744019</v>
+        <v>4.31295013427734</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.185959815979</v>
+        <v>4.18596029281616</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189319610596</v>
+        <v>4.09189367294312</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.0636739730835</v>
+        <v>4.06367349624634</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312353134155</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842000961304</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316699981689</v>
+        <v>3.91316723823547</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147435188293</v>
+        <v>3.78147411346436</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G252" t="n">
-        <v>3.74855065345764</v>
+        <v>3.74855041503906</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931796073914</v>
+        <v>3.41931819915771</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.41461491584778</v>
+        <v>3.4146146774292</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745120048523</v>
+        <v>3.60745096206665</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092414855957</v>
+        <v>3.71092391014099</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>3.01012873649597</v>
+        <v>3.01012849807739</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153270721436</v>
+        <v>2.59153246879578</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179304122925</v>
+        <v>2.11179327964783</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950672149658</v>
+        <v>1.98950695991516</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654026985168</v>
+        <v>2.03654003143311</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.0929799079895</v>
+        <v>2.09298014640808</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924641132355</v>
+        <v>1.81924653053284</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478907585144</v>
+        <v>1.79478919506073</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G348" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G349" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G353" t="n">
-        <v>1.29623663425446</v>
+        <v>1.29623651504517</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002808094025</v>
+        <v>1.68002796173096</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089556694031</v>
+        <v>2.68089580535889</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975288391113</v>
+        <v>2.61975264549255</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860948562622</v>
+        <v>2.55860924720764</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.40810298919678</v>
+        <v>2.4081027507782</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691588401794</v>
+        <v>2.42691612243652</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106944084167</v>
+        <v>2.36106967926025</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13531017303467</v>
+        <v>2.13530993461609</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G468" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658349990845</v>
+        <v>1.95658361911774</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G512" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539699077606</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G565" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.70730745792389</v>
+        <v>1.7073073387146</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.6649774312973</v>
+        <v>1.66497731208801</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379056453705</v>
+        <v>1.68379068374634</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.51917433738708</v>
+        <v>1.5191742181778</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264752388</v>
+        <v>1.62264740467072</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091093063354</v>
+        <v>1.57091081142426</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798758983612</v>
+        <v>1.53798747062683</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G642" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G644" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625111579895</v>
+        <v>1.48625099658966</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447093486786</v>
+        <v>1.51447081565857</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G648" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803093910217</v>
+        <v>1.45803105831146</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565768241882</v>
+        <v>1.49565756320953</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775154590607</v>
+        <v>0.954775214195251</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970571994781</v>
+        <v>0.919970512390137</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291749954224</v>
+        <v>0.978291809558868</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401719093323</v>
+        <v>0.992401659488678</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591849327087</v>
+        <v>1.01591837406158</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G755" t="n">
-        <v>1.32163453102112</v>
+        <v>1.32163465023041</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866784095764</v>
+        <v>1.36866796016693</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G841" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510771751404</v>
+        <v>1.42510783672333</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G851" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G860" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G861" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>1.32163453102112</v>
+        <v>1.32163465023041</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G900" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662696838379</v>
+        <v>1.87662708759308</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539699077606</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946349143982</v>
+        <v>2.06946325302124</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827686309814</v>
+        <v>2.08827662467957</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>2.72792911529541</v>
+        <v>2.72792935371399</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.02894186973572</v>
+        <v>3.02894163131714</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9725022315979</v>
+        <v>2.97250199317932</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>3.01012873649597</v>
+        <v>3.01012849807739</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.3581748008728</v>
+        <v>3.35817456245422</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597517967224</v>
+        <v>3.07597494125366</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.02894186973572</v>
+        <v>3.02894163131714</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325393676758</v>
+        <v>3.75325417518616</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512117385864</v>
+        <v>3.56512093544006</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.6250786781311</v>
+        <v>3.62507843971252</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794955253601</v>
+        <v>3.54794931411743</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436078071594</v>
+        <v>3.64436101913452</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579633712769</v>
+        <v>3.60579609870911</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687282562256</v>
+        <v>3.57687258720398</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32620239257812</v>
+        <v>3.3262026309967</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31388020515442</v>
+        <v>2.31387996673584</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608016967773</v>
+        <v>1.98608028888702</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029143333435</v>
+        <v>2.41029167175293</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.297278881073</v>
+        <v>3.29727911949158</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512590408325</v>
+        <v>3.35512614250183</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871443748474</v>
+        <v>3.25871419906616</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -60848,6 +60848,32 @@
         <v>1</v>
       </c>
       <c r="H2326" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2327" t="n">
+        <v>17150</v>
+      </c>
+      <c r="C2327" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G2327" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="H2327" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671106338501</v>
+        <v>3.19671130180359</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245101928711</v>
+        <v>3.17245125770569</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044326782227</v>
+        <v>3.20044350624084</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206482887268</v>
+        <v>3.12206506729126</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G17" t="n">
-        <v>3.18924641609192</v>
+        <v>3.1892466545105</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501127243042</v>
+        <v>3.555011510849</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.88158750534058</v>
+        <v>3.88158702850342</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939958572388</v>
+        <v>4.07939910888672</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30147075653076</v>
+        <v>4.3014702796936</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297485351562</v>
+        <v>4.64297533035278</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120506286621</v>
+        <v>7.65120601654053</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7647852897644</v>
+        <v>6.76478576660156</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088653564453</v>
+        <v>6.40088701248169</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G41" t="n">
-        <v>6.35423278808594</v>
+        <v>6.3542332649231</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>6.99338865280151</v>
+        <v>6.9933876991272</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401866912842</v>
+        <v>7.12401914596558</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080854415894</v>
+        <v>6.68080902099609</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9140772819519</v>
+        <v>6.91407775878906</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939300537109</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000316619873</v>
+        <v>7.18000364303589</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451351165771</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726755142212</v>
+        <v>7.42726802825928</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002254486084</v>
+        <v>7.110023021698</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>6.64348554611206</v>
+        <v>6.6434850692749</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>7.45525979995728</v>
+        <v>7.45526027679443</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059490203857</v>
+        <v>7.45059442520142</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>6.99338865280151</v>
+        <v>6.9933876991272</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939300537109</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405790328979</v>
+        <v>6.98405838012695</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004240036011</v>
+        <v>7.04004192352295</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673490524292</v>
+        <v>6.94673442840576</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>6.85809278488159</v>
+        <v>6.85809326171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.9607310295105</v>
+        <v>6.96073150634766</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>6.96539688110352</v>
+        <v>6.96539640426636</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85809278488159</v>
+        <v>6.85809326171875</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.811439037323</v>
+        <v>6.81143951416016</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>6.83943128585815</v>
+        <v>6.839430809021</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.78344678878784</v>
+        <v>6.78344631195068</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817077636719</v>
+        <v>6.57817125320435</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419403076172</v>
+        <v>6.49419450759888</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828800201416</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561052322388</v>
+        <v>6.19561004638672</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75706577301025</v>
+        <v>5.75706624984741</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>6.37289476394653</v>
+        <v>6.37289428710938</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301055908203</v>
+        <v>5.95301103591919</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G134" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375875473022</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238054275513</v>
+        <v>5.82238101959229</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>5.32785224914551</v>
+        <v>5.32785177230835</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17856025695801</v>
+        <v>5.17855978012085</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.33357191085815</v>
+        <v>5.333571434021</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043087005615</v>
+        <v>5.70043039321899</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212375640869</v>
+        <v>5.83212423324585</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729030609131</v>
+        <v>6.06729078292847</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891185760498</v>
+        <v>5.24891138076782</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.5</v>
       </c>
       <c r="G208" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>5.0419659614563</v>
+        <v>5.04196548461914</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>5.19247198104858</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077861785889</v>
+        <v>5.06077909469604</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.25</v>
       </c>
       <c r="G217" t="n">
-        <v>4.93849229812622</v>
+        <v>4.93849182128906</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.03255891799927</v>
+        <v>5.03255844116211</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.8350191116333</v>
+        <v>4.83501863479614</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442615509033</v>
+        <v>4.84442567825317</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51048946380615</v>
+        <v>4.51048994064331</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.12952041625977</v>
+        <v>4.12951993942261</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884004592896</v>
+        <v>4.29884052276611</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31294965744019</v>
+        <v>4.31295013427734</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G241" t="n">
-        <v>4.2612133026123</v>
+        <v>4.26121377944946</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22828960418701</v>
+        <v>4.22829008102417</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.18596029281616</v>
+        <v>4.185959815979</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312376976013</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.9884204864502</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.75</v>
       </c>
       <c r="G255" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G264" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931796073914</v>
+        <v>3.41931772232056</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.4146146774292</v>
+        <v>3.41461491584778</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.75</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.38639450073242</v>
+        <v>3.386394739151</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.75</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092438697815</v>
+        <v>3.71092414855957</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>3.27821826934814</v>
+        <v>3.27821803092957</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>2.77496242523193</v>
+        <v>2.77496218681335</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>2.77496242523193</v>
+        <v>2.77496218681335</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153294563293</v>
+        <v>2.59153270721436</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950695991516</v>
+        <v>1.98950672149658</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.09298014640808</v>
+        <v>2.0929799079895</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>1.98010015487671</v>
+        <v>1.98010039329529</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90484702587128</v>
+        <v>1.90484714508057</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G345" t="n">
-        <v>1.68755340576172</v>
+        <v>1.68755328655243</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G354" t="n">
-        <v>1.29435539245605</v>
+        <v>1.29435527324677</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209755897522</v>
+        <v>1.55209767818451</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928937911987</v>
+        <v>2.38928961753845</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089580535889</v>
+        <v>2.68089556694031</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>2.62915921211243</v>
+        <v>2.62915945053101</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983934402466</v>
+        <v>2.45983958244324</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.52098298072815</v>
+        <v>2.52098274230957</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216937065125</v>
+        <v>2.50216960906982</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750955581665</v>
+        <v>2.41750931739807</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G401" t="n">
-        <v>2.51627945899963</v>
+        <v>2.51627922058105</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047624588013</v>
+        <v>2.37047600746155</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056318283081</v>
+        <v>2.21056294441223</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106944084167</v>
+        <v>2.36106967926025</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G502" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G526" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434052944183</v>
+        <v>1.75434064865112</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G539" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G547" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G572" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G586" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315390110016</v>
+        <v>1.77315378189087</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.7073073387146</v>
+        <v>1.70730745792389</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612071037292</v>
+        <v>1.72612059116364</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G594" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G597" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G625" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.625</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52858090400696</v>
+        <v>1.52858102321625</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55680096149445</v>
+        <v>1.55680084228516</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620740890503</v>
+        <v>1.56620752811432</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.625</v>
       </c>
       <c r="G650" t="n">
-        <v>1.52858090400696</v>
+        <v>1.52858102321625</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803093910217</v>
+        <v>1.45803105831146</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.375</v>
       </c>
       <c r="G659" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G663" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G665" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G666" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775094985962</v>
+        <v>0.954775154590607</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106610298157</v>
+        <v>0.886106550693512</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970571994781</v>
+        <v>0.919970512390137</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089210987091</v>
+        <v>0.918089270591736</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021221637726</v>
+        <v>0.935021162033081</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326548576355</v>
+        <v>0.91432648897171</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G687" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G717" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875477790833</v>
+        <v>1.20875465869904</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G736" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G739" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.375</v>
       </c>
       <c r="G756" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.375</v>
       </c>
       <c r="G770" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G782" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G795" t="n">
-        <v>1.14290809631348</v>
+        <v>1.14290821552277</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G818" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G823" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G824" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G827" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.38277792930603</v>
+        <v>1.38277781009674</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510771751404</v>
+        <v>1.42510759830475</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.38277792930603</v>
+        <v>1.38277781009674</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G881" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.375</v>
       </c>
       <c r="G882" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.375</v>
       </c>
       <c r="G893" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.4909542798996</v>
+        <v>1.49095439910889</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G904" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G908" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777012825012</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946349143982</v>
+        <v>2.06946325302124</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827686309814</v>
+        <v>2.08827662467957</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.76555585861206</v>
+        <v>2.76555562019348</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.75</v>
       </c>
       <c r="G956" t="n">
-        <v>2.58682942390442</v>
+        <v>2.58682918548584</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.25</v>
       </c>
       <c r="G964" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224142074585</v>
+        <v>3.45224118232727</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G970" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G971" t="n">
-        <v>3.42402148246765</v>
+        <v>3.42402124404907</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3111412525177</v>
+        <v>3.31114149093628</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.9254686832428</v>
+        <v>2.92546844482422</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.25</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.37698793411255</v>
+        <v>3.37698769569397</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630780220032</v>
+        <v>3.54630756378174</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.8473207950592</v>
+        <v>3.84732055664062</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.75</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.80969405174255</v>
+        <v>3.80969429016113</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562743186951</v>
+        <v>3.71562767028809</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046112060547</v>
+        <v>3.48046135902405</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.6250786781311</v>
+        <v>3.62507843971252</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794955253601</v>
+        <v>3.54794931411743</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436078071594</v>
+        <v>3.64436101913452</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579633712769</v>
+        <v>3.60579609870911</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687282562256</v>
+        <v>3.57687258720398</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32620239257812</v>
+        <v>3.3262026309967</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31388020515442</v>
+        <v>2.31387996673584</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608016967773</v>
+        <v>1.98608028888702</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029143333435</v>
+        <v>2.41029167175293</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.297278881073</v>
+        <v>3.29727911949158</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512590408325</v>
+        <v>3.35512614250183</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871443748474</v>
+        <v>3.25871419906616</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -60926,6 +60926,32 @@
         <v>0.949999988079071</v>
       </c>
       <c r="H2329" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2330" t="n">
+        <v>35350</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>0.805000007152557</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="H2330" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -54024,8 +54024,31 @@
       <c r="E2333" t="n">
         <v>0.730000019073486</v>
       </c>
-      <c r="F2333"/>
+      <c r="F2333" t="n">
+        <v>0.670000016689301</v>
+      </c>
       <c r="G2333" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2334" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C2334" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="F2334"/>
+      <c r="G2334" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -54047,8 +54047,31 @@
       <c r="E2334" t="n">
         <v>0.639999985694885</v>
       </c>
-      <c r="F2334"/>
+      <c r="F2334" t="n">
+        <v>0.644999980926514</v>
+      </c>
       <c r="G2334" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2335" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="F2335"/>
+      <c r="G2335" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -54065,13 +54065,36 @@
         <v>0.649999976158142</v>
       </c>
       <c r="D2335" t="n">
-        <v>0.649999976158142</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="E2335" t="n">
         <v>0.649999976158142</v>
       </c>
-      <c r="F2335"/>
+      <c r="F2335" t="n">
+        <v>0.610000014305115</v>
+      </c>
       <c r="G2335" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2336" t="n">
+        <v>19950</v>
+      </c>
+      <c r="C2336" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F2336"/>
+      <c r="G2336" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -54093,8 +54093,31 @@
       <c r="E2336" t="n">
         <v>0.654999971389771</v>
       </c>
-      <c r="F2336"/>
+      <c r="F2336" t="n">
+        <v>0.699999988079071</v>
+      </c>
       <c r="G2336" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2337" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C2337" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F2337"/>
+      <c r="G2337" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -54123,6 +54123,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2338">
+      <c r="A2338" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2338" t="n">
+        <v>21700</v>
+      </c>
+      <c r="C2338" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F2338" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="G2338" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35906577110291</v>
+        <v>3.35906600952148</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249025344849</v>
+        <v>3.03249001502991</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G6" t="n">
-        <v>3.14445877075195</v>
+        <v>3.14445900917053</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044350624084</v>
+        <v>3.20044374465942</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512778282166</v>
+        <v>3.13512802124023</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G19" t="n">
-        <v>3.29375076293945</v>
+        <v>3.29375100135803</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198731422424</v>
+        <v>3.40198707580566</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3014702796936</v>
+        <v>4.30147075653076</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521352767944</v>
+        <v>5.22521305084229</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911275863647</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120506286621</v>
+        <v>7.65120553970337</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7647852897644</v>
+        <v>6.76478576660156</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>6.41954803466797</v>
+        <v>6.41954851150513</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092576980591</v>
+        <v>6.26092529296875</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088701248169</v>
+        <v>6.40088748931885</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G42" t="n">
-        <v>6.82543516159058</v>
+        <v>6.82543563842773</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451351165771</v>
+        <v>7.74451303482056</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424030303955</v>
+        <v>8.72424125671387</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>6.6434850692749</v>
+        <v>6.64348554611206</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252561569214</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541530609131</v>
+        <v>6.89541578292847</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673442840576</v>
+        <v>6.94673490524292</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809278488159</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>6.85809326171875</v>
+        <v>6.85809278488159</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>6.83943128585815</v>
+        <v>6.839430809021</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419450759888</v>
+        <v>6.49419403076172</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287490844727</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962554931641</v>
+        <v>6.13962602615356</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828800201416</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561052322388</v>
+        <v>6.19561004638672</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.05564880371094</v>
+        <v>6.0556492805481</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>5.79438829421997</v>
+        <v>5.79438877105713</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G134" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513505935669</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911275863647</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.6824197769165</v>
+        <v>5.68242025375366</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81304979324341</v>
+        <v>5.81305027008057</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.98100328445435</v>
+        <v>5.98100280761719</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513505935669</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513505935669</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316701889038</v>
+        <v>5.39316749572754</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651374816895</v>
+        <v>5.34651327133179</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043039321899</v>
+        <v>5.70043087005615</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.78509092330933</v>
+        <v>5.78509140014648</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729078292847</v>
+        <v>6.06729030609131</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390453338623</v>
+        <v>5.80390405654907</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399099349976</v>
+        <v>5.64399147033691</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G194" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G195" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891138076782</v>
+        <v>5.24891185760498</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>5.12662506103516</v>
+        <v>5.126624584198</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>5.05137205123901</v>
+        <v>5.05137157440186</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959175109863</v>
+        <v>5.07959222793579</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51048994064331</v>
+        <v>4.51048946380615</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>4.20007038116455</v>
+        <v>4.20006990432739</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490383148193</v>
+        <v>3.96490359306335</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22829008102417</v>
+        <v>4.22828960418701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189319610596</v>
+        <v>4.09189367294312</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312376976013</v>
+        <v>3.99312353134155</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316699981689</v>
+        <v>3.91316723823547</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931772232056</v>
+        <v>3.41931796073914</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745120048523</v>
+        <v>3.60745096206665</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.386394739151</v>
+        <v>3.38639450073242</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092414855957</v>
+        <v>3.71092391014099</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179304122925</v>
+        <v>2.11179327964783</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478907585144</v>
+        <v>1.79478919506073</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G345" t="n">
-        <v>1.68755328655243</v>
+        <v>1.68755340576172</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G350" t="n">
-        <v>1.24732208251953</v>
+        <v>1.24732196331024</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209767818451</v>
+        <v>1.55209755897522</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002808094025</v>
+        <v>1.68002796173096</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.56331253051758</v>
+        <v>2.563312292099</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>2.62915945053101</v>
+        <v>2.62915921211243</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983958244324</v>
+        <v>2.45983934402466</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.40810298919678</v>
+        <v>2.4081027507782</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047600746155</v>
+        <v>2.37047624588013</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.31873965263367</v>
+        <v>2.31873989105225</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658349990845</v>
+        <v>1.95658361911774</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315378189087</v>
+        <v>1.77315390110016</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G594" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G597" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.6649774312973</v>
+        <v>1.66497731208801</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>1.50976765155792</v>
+        <v>1.50976753234863</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G625" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.625</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387762069702</v>
+        <v>1.52387750148773</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620752811432</v>
+        <v>1.56620740890503</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447105407715</v>
+        <v>1.51447093486786</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.625</v>
       </c>
       <c r="G650" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565768241882</v>
+        <v>1.49565756320953</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775154590607</v>
+        <v>0.954775214195251</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106550693512</v>
+        <v>0.886106610298157</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089270591736</v>
+        <v>0.918089210987091</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.91432648897171</v>
+        <v>0.914326548576355</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291749954224</v>
+        <v>0.978291809558868</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401719093323</v>
+        <v>0.992401778697968</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G687" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G736" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G739" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G740" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.1476114988327</v>
+        <v>1.14761161804199</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G807" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G812" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866784095764</v>
+        <v>1.36866796016693</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G846" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510759830475</v>
+        <v>1.42510771751404</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G857" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G858" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G881" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.49095439910889</v>
+        <v>1.4909542798996</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G908" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662696838379</v>
+        <v>1.87662708759308</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946325302124</v>
+        <v>2.06946349143982</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.76555562019348</v>
+        <v>2.76555585861206</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>2.70911574363708</v>
+        <v>2.70911598205566</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.8690288066864</v>
+        <v>2.86902904510498</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.25</v>
       </c>
       <c r="G964" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.92546844482422</v>
+        <v>2.9254686832428</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>3.01953530311584</v>
+        <v>3.01953506469727</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292155265808</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.25</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.3581748008728</v>
+        <v>3.35817456245422</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707510948181</v>
+        <v>3.21707487106323</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.37698769569397</v>
+        <v>3.37698793411255</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630756378174</v>
+        <v>3.54630780220032</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.84732055664062</v>
+        <v>3.8473207950592</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325393676758</v>
+        <v>3.75325417518616</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292155265808</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -61212,6 +61212,32 @@
         <v>0.654999971389771</v>
       </c>
       <c r="H2340" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2341" t="n">
+        <v>7350</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G2341" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H2341" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -551,7 +551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044374465942</v>
+        <v>3.20044350624084</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512802124023</v>
+        <v>3.13512825965881</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389241218567</v>
+        <v>3.26389217376709</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198707580566</v>
+        <v>3.40198683738708</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.555011510849</v>
+        <v>3.55501127243042</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556401252747</v>
+        <v>3.96556353569031</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297580718994</v>
+        <v>4.64297533035278</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521305084229</v>
+        <v>5.22521352767944</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911180496216</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.76478576660156</v>
+        <v>6.7647852897644</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>6.41954851150513</v>
+        <v>6.41954803466797</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830690383911</v>
+        <v>6.08830642700195</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761779785156</v>
+        <v>6.16761827468872</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088748931885</v>
+        <v>6.40088701248169</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G41" t="n">
-        <v>6.3542332649231</v>
+        <v>6.35423278808594</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G42" t="n">
-        <v>6.82543563842773</v>
+        <v>6.82543516159058</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>6.99338817596436</v>
+        <v>6.99338865280151</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401914596558</v>
+        <v>7.12401866912842</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080902099609</v>
+        <v>6.68080854415894</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9140772819519</v>
+        <v>6.91407680511475</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939300537109</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435657501221</v>
+        <v>8.30435752868652</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750904083252</v>
+        <v>8.95750999450684</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866514205933</v>
+        <v>7.19866466522217</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061428070068</v>
+        <v>7.38061380386353</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.110023021698</v>
+        <v>7.11002254486084</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>6.83010053634644</v>
+        <v>6.83010101318359</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.0866961479187</v>
+        <v>7.08669567108154</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>6.99338817596436</v>
+        <v>6.99338865280151</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.83010053634644</v>
+        <v>6.83010101318359</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474653244019</v>
+        <v>6.90474700927734</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939300537109</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004240036011</v>
+        <v>7.04004287719727</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466806411743</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.96073150634766</v>
+        <v>6.9607310295105</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>6.96539640426636</v>
+        <v>6.96539688110352</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75078964233398</v>
+        <v>6.75078916549683</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.78344678878784</v>
+        <v>6.783447265625</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279691696167</v>
+        <v>6.72279739379883</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419403076172</v>
+        <v>6.49419355392456</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828800201416</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175004959106</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301151275635</v>
+        <v>5.95301103591919</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108079910278</v>
+        <v>5.70108127593994</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175004959106</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G134" t="n">
-        <v>5.50513505935669</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245901107788</v>
+        <v>5.54245853424072</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911180496216</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.68242025375366</v>
+        <v>5.68242073059082</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.50513505935669</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>5.50513505935669</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718299865723</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17855978012085</v>
+        <v>5.17856025695801</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718299865723</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651327133179</v>
+        <v>5.34651279449463</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -61220,7 +61220,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2341" t="n">
-        <v>7350</v>
+        <v>9450</v>
       </c>
       <c r="C2341" t="n">
         <v>0.680000007152557</v>
@@ -61238,6 +61238,32 @@
         <v>0.639999985694885</v>
       </c>
       <c r="H2341" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="G2342" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="H2342" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249025344849</v>
+        <v>3.03249001502991</v>
       </c>
       <c r="H3" t="n">
         <v>123200</v>
@@ -514,7 +514,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15378975868225</v>
+        <v>3.15378999710083</v>
       </c>
       <c r="H5" t="n">
         <v>82950</v>
@@ -572,7 +572,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H7" t="n">
         <v>6650</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245101928711</v>
+        <v>3.17245125770569</v>
       </c>
       <c r="H9" t="n">
         <v>5950</v>
@@ -688,7 +688,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H11" t="n">
         <v>3150</v>
@@ -746,7 +746,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H13" t="n">
         <v>1400</v>
@@ -833,7 +833,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H16" t="n">
         <v>17500</v>
@@ -891,7 +891,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389241218567</v>
+        <v>3.26389217376709</v>
       </c>
       <c r="H18" t="n">
         <v>19250</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105966567993</v>
+        <v>3.86105990409851</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1123,7 +1123,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939910888672</v>
+        <v>4.07939863204956</v>
       </c>
       <c r="H26" t="n">
         <v>28700</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911180496216</v>
       </c>
       <c r="H32" t="n">
         <v>60200</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120553970337</v>
+        <v>7.65120601654053</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1384,7 +1384,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7647852897644</v>
+        <v>6.76478576660156</v>
       </c>
       <c r="H35" t="n">
         <v>289450</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761827468872</v>
+        <v>6.16761875152588</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451351165771</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -2051,7 +2051,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303745269775</v>
+        <v>8.25303840637207</v>
       </c>
       <c r="H58" t="n">
         <v>105350</v>
@@ -2283,7 +2283,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H66" t="n">
         <v>14350</v>
@@ -2341,7 +2341,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>7.52523994445801</v>
+        <v>7.52524042129517</v>
       </c>
       <c r="H68" t="n">
         <v>49000</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252561569214</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2428,7 +2428,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>7.45525979995728</v>
+        <v>7.45526027679443</v>
       </c>
       <c r="H71" t="n">
         <v>10150</v>
@@ -2457,7 +2457,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.57189464569092</v>
+        <v>7.57189416885376</v>
       </c>
       <c r="H72" t="n">
         <v>15750</v>
@@ -2486,7 +2486,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059490203857</v>
+        <v>7.45059442520142</v>
       </c>
       <c r="H73" t="n">
         <v>20650</v>
@@ -2515,7 +2515,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H74" t="n">
         <v>15750</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.0866961479187</v>
+        <v>7.08669567108154</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2602,7 +2602,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H77" t="n">
         <v>12600</v>
@@ -2660,7 +2660,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.83010101318359</v>
+        <v>6.83010053634644</v>
       </c>
       <c r="H79" t="n">
         <v>5950</v>
@@ -2689,7 +2689,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474653244019</v>
+        <v>6.90474700927734</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673538208008</v>
+        <v>6.94673490524292</v>
       </c>
       <c r="H85" t="n">
         <v>3500</v>
@@ -2950,7 +2950,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H89" t="n">
         <v>7350</v>
@@ -2979,7 +2979,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.9607310295105</v>
+        <v>6.96073150634766</v>
       </c>
       <c r="H90" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.811439037323</v>
+        <v>6.81143951416016</v>
       </c>
       <c r="H93" t="n">
         <v>9800</v>
@@ -3095,7 +3095,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>6.83943176269531</v>
+        <v>6.83943128585815</v>
       </c>
       <c r="H94" t="n">
         <v>23100</v>
@@ -3153,7 +3153,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75079011917114</v>
+        <v>6.75078964233398</v>
       </c>
       <c r="H96" t="n">
         <v>3500</v>
@@ -3443,7 +3443,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H106" t="n">
         <v>9800</v>
@@ -3559,7 +3559,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490203857422</v>
+        <v>6.34490251541138</v>
       </c>
       <c r="H110" t="n">
         <v>1050</v>
@@ -3675,7 +3675,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G114" t="n">
-        <v>6.3075795173645</v>
+        <v>6.30757999420166</v>
       </c>
       <c r="H114" t="n">
         <v>4550</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828800201416</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561052322388</v>
+        <v>6.19561004638672</v>
       </c>
       <c r="H120" t="n">
         <v>5600</v>
@@ -3936,7 +3936,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H123" t="n">
         <v>8400</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4081,7 +4081,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75706577301025</v>
+        <v>5.75706624984741</v>
       </c>
       <c r="H128" t="n">
         <v>5250</v>
@@ -4168,7 +4168,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108079910278</v>
+        <v>5.70108127593994</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4197,7 +4197,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H132" t="n">
         <v>5600</v>
@@ -4313,7 +4313,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911180496216</v>
       </c>
       <c r="H136" t="n">
         <v>8750</v>
@@ -4342,7 +4342,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.68241930007935</v>
+        <v>5.6824197769165</v>
       </c>
       <c r="H137" t="n">
         <v>13300</v>
@@ -4371,7 +4371,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375923156738</v>
       </c>
       <c r="H138" t="n">
         <v>3850</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104299545288</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4458,7 +4458,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H141" t="n">
         <v>1400</v>
@@ -4487,7 +4487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238054275513</v>
+        <v>5.82238101959229</v>
       </c>
       <c r="H142" t="n">
         <v>3850</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4574,7 +4574,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.98100328445435</v>
+        <v>5.9810037612915</v>
       </c>
       <c r="H145" t="n">
         <v>39200</v>
@@ -4603,7 +4603,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H146" t="n">
         <v>8750</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104299545288</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4893,7 +4893,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517429351807</v>
+        <v>5.36517477035522</v>
       </c>
       <c r="H156" t="n">
         <v>5950</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052877426147</v>
+        <v>5.29052925109863</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -5038,7 +5038,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316654205322</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5154,7 +5154,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H165" t="n">
         <v>1750</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5618,7 +5618,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="n">
         <v>9100</v>
@@ -5647,7 +5647,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729030609131</v>
+        <v>6.06729078292847</v>
       </c>
       <c r="H182" t="n">
         <v>62650</v>
@@ -5850,7 +5850,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H189" t="n">
         <v>2450</v>
@@ -5879,7 +5879,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H190" t="n">
         <v>350</v>
@@ -6053,7 +6053,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891185760498</v>
+        <v>5.24891138076782</v>
       </c>
       <c r="H196" t="n">
         <v>25200</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950529098511</v>
+        <v>5.23950481414795</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6169,7 +6169,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H200" t="n">
         <v>5950</v>
@@ -6256,7 +6256,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H203" t="n">
         <v>12950</v>
@@ -6430,7 +6430,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721897125244</v>
+        <v>5.11721849441528</v>
       </c>
       <c r="H209" t="n">
         <v>5600</v>
@@ -6459,7 +6459,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>5.0419659614563</v>
+        <v>5.04196548461914</v>
       </c>
       <c r="H210" t="n">
         <v>8400</v>
@@ -6488,7 +6488,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H211" t="n">
         <v>4550</v>
@@ -6604,7 +6604,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6662,7 +6662,7 @@
         <v>5.25</v>
       </c>
       <c r="G217" t="n">
-        <v>4.93849229812622</v>
+        <v>4.93849182128906</v>
       </c>
       <c r="H217" t="n">
         <v>3850</v>
@@ -6778,7 +6778,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442615509033</v>
+        <v>4.84442567825317</v>
       </c>
       <c r="H221" t="n">
         <v>4550</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H227" t="n">
         <v>8400</v>
@@ -7039,7 +7039,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985256195068</v>
+        <v>4.59985303878784</v>
       </c>
       <c r="H230" t="n">
         <v>1750</v>
@@ -7097,7 +7097,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472995758057</v>
+        <v>4.28472948074341</v>
       </c>
       <c r="H232" t="n">
         <v>4900</v>
@@ -7126,7 +7126,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.24240016937256</v>
+        <v>4.2423996925354</v>
       </c>
       <c r="H233" t="n">
         <v>2450</v>
@@ -7184,7 +7184,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.12952041625977</v>
+        <v>4.12951993942261</v>
       </c>
       <c r="H235" t="n">
         <v>10150</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884004592896</v>
+        <v>4.29884052276611</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H238" t="n">
         <v>147350</v>
@@ -7358,7 +7358,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G241" t="n">
-        <v>4.2612133026123</v>
+        <v>4.26121377944946</v>
       </c>
       <c r="H241" t="n">
         <v>21350</v>
@@ -7387,7 +7387,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22828960418701</v>
+        <v>4.22829008102417</v>
       </c>
       <c r="H242" t="n">
         <v>7700</v>
@@ -7416,7 +7416,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.18596029281616</v>
+        <v>4.185959815979</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7474,7 +7474,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.0636739730835</v>
+        <v>4.06367349624634</v>
       </c>
       <c r="H245" t="n">
         <v>4550</v>
@@ -7503,7 +7503,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="n">
         <v>1050</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312376976013</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7590,7 +7590,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.9884204864502</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="n">
         <v>5250</v>
@@ -7735,7 +7735,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G254" t="n">
-        <v>3.54160451889038</v>
+        <v>3.54160475730896</v>
       </c>
       <c r="H254" t="n">
         <v>20300</v>
@@ -7764,7 +7764,7 @@
         <v>3.75</v>
       </c>
       <c r="G255" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7793,7 +7793,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7851,7 +7851,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="n">
         <v>73500</v>
@@ -7880,7 +7880,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="n">
         <v>77000</v>
@@ -7996,7 +7996,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H263" t="n">
         <v>3850</v>
@@ -8112,7 +8112,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H267" t="n">
         <v>1750</v>
@@ -8170,7 +8170,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H269" t="n">
         <v>3500</v>
@@ -8286,7 +8286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="n">
         <v>1050</v>
@@ -8402,7 +8402,7 @@
         <v>3.75</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H277" t="n">
         <v>3500</v>
@@ -8431,7 +8431,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H278" t="n">
         <v>1750</v>
@@ -8460,7 +8460,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H282" t="n">
         <v>5600</v>
@@ -8634,7 +8634,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H285" t="n">
         <v>12950</v>
@@ -8663,7 +8663,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H286" t="n">
         <v>10500</v>
@@ -8692,7 +8692,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169121742249</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H287" t="n">
         <v>2100</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="n">
         <v>17500</v>
@@ -8808,7 +8808,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="n">
         <v>4900</v>
@@ -8837,7 +8837,7 @@
         <v>3.75</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H292" t="n">
         <v>2800</v>
@@ -8924,7 +8924,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092438697815</v>
+        <v>3.71092414855957</v>
       </c>
       <c r="H295" t="n">
         <v>10500</v>
@@ -8953,7 +8953,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H296" t="n">
         <v>39900</v>
@@ -8982,7 +8982,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="n">
         <v>29400</v>
@@ -9040,7 +9040,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H299" t="n">
         <v>5950</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="n">
         <v>59850</v>
@@ -9127,7 +9127,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>3.27821826934814</v>
+        <v>3.27821803092957</v>
       </c>
       <c r="H302" t="n">
         <v>64750</v>
@@ -9214,7 +9214,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="n">
         <v>23450</v>
@@ -9388,7 +9388,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="n">
         <v>5950</v>
@@ -9417,7 +9417,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153294563293</v>
+        <v>2.59153270721436</v>
       </c>
       <c r="H312" t="n">
         <v>6650</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H316" t="n">
         <v>5600</v>
@@ -9562,7 +9562,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H317" t="n">
         <v>6650</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H318" t="n">
         <v>52850</v>
@@ -9678,7 +9678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H321" t="n">
         <v>5250</v>
@@ -9707,7 +9707,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H322" t="n">
         <v>3150</v>
@@ -9910,7 +9910,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G329" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H329" t="n">
         <v>12250</v>
@@ -9968,7 +9968,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.09298014640808</v>
+        <v>2.0929799079895</v>
       </c>
       <c r="H331" t="n">
         <v>10150</v>
@@ -10026,7 +10026,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>1.98010015487671</v>
+        <v>1.98010039329529</v>
       </c>
       <c r="H333" t="n">
         <v>10500</v>
@@ -10142,7 +10142,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90484702587128</v>
+        <v>1.90484714508057</v>
       </c>
       <c r="H337" t="n">
         <v>4200</v>
@@ -10258,7 +10258,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H341" t="n">
         <v>10500</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10548,7 +10548,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H351" t="n">
         <v>6650</v>
@@ -10664,7 +10664,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H355" t="n">
         <v>2100</v>
@@ -10780,7 +10780,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H359" t="n">
         <v>9100</v>
@@ -10809,7 +10809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="n">
         <v>9450</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209755897522</v>
+        <v>1.55209767818451</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -10925,7 +10925,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H364" t="n">
         <v>52500</v>
@@ -11012,7 +11012,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928937911987</v>
+        <v>2.38928961753845</v>
       </c>
       <c r="H367" t="n">
         <v>146300</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11302,7 +11302,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H377" t="n">
         <v>26600</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975264549255</v>
+        <v>2.61975240707397</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11476,7 +11476,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="n">
         <v>11200</v>
@@ -11650,7 +11650,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H389" t="n">
         <v>2800</v>
@@ -11708,7 +11708,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="n">
         <v>26250</v>
@@ -11795,7 +11795,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.52098298072815</v>
+        <v>2.52098274230957</v>
       </c>
       <c r="H394" t="n">
         <v>1400</v>
@@ -11824,7 +11824,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216937065125</v>
+        <v>2.50216960906982</v>
       </c>
       <c r="H395" t="n">
         <v>4900</v>
@@ -11853,7 +11853,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860948562622</v>
+        <v>2.55860924720764</v>
       </c>
       <c r="H396" t="n">
         <v>2100</v>
@@ -11882,7 +11882,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -12085,7 +12085,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H404" t="n">
         <v>5950</v>
@@ -12114,7 +12114,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H405" t="n">
         <v>1050</v>
@@ -12230,7 +12230,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047624588013</v>
+        <v>2.37047600746155</v>
       </c>
       <c r="H409" t="n">
         <v>6300</v>
@@ -12433,7 +12433,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H416" t="n">
         <v>22400</v>
@@ -12665,7 +12665,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H424" t="n">
         <v>3850</v>
@@ -12723,7 +12723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056318283081</v>
+        <v>2.21056294441223</v>
       </c>
       <c r="H426" t="n">
         <v>1750</v>
@@ -12752,7 +12752,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="n">
         <v>21000</v>
@@ -12781,7 +12781,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="n">
         <v>43400</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691612243652</v>
+        <v>2.4269163608551</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12868,7 +12868,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H431" t="n">
         <v>3850</v>
@@ -13013,7 +13013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H436" t="n">
         <v>7700</v>
@@ -13042,7 +13042,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H437" t="n">
         <v>2800</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="n">
         <v>350</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="n">
         <v>350</v>
@@ -13361,7 +13361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H448" t="n">
         <v>1750</v>
@@ -13390,7 +13390,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H449" t="n">
         <v>2800</v>
@@ -13448,7 +13448,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>2.31403660774231</v>
+        <v>2.31403636932373</v>
       </c>
       <c r="H451" t="n">
         <v>12950</v>
@@ -13622,7 +13622,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H457" t="n">
         <v>21350</v>
@@ -13651,7 +13651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="n">
         <v>14700</v>
@@ -13680,7 +13680,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H459" t="n">
         <v>12250</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H461" t="n">
         <v>1750</v>
@@ -13767,7 +13767,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H462" t="n">
         <v>7350</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13883,7 +13883,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H466" t="n">
         <v>5250</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -13999,7 +13999,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H470" t="n">
         <v>3850</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H478" t="n">
         <v>6650</v>
@@ -14260,7 +14260,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H479" t="n">
         <v>700</v>
@@ -14289,7 +14289,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H480" t="n">
         <v>5600</v>
@@ -14318,7 +14318,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H481" t="n">
         <v>1400</v>
@@ -14347,7 +14347,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="n">
         <v>1400</v>
@@ -14405,7 +14405,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="n">
         <v>1050</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14521,7 +14521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H488" t="n">
         <v>2450</v>
@@ -14579,7 +14579,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H490" t="n">
         <v>8750</v>
@@ -14608,7 +14608,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14811,7 +14811,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H498" t="n">
         <v>350</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H521" t="n">
         <v>1050</v>
@@ -15681,7 +15681,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434052944183</v>
+        <v>1.75434064865112</v>
       </c>
       <c r="H528" t="n">
         <v>1400</v>
@@ -15739,7 +15739,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H530" t="n">
         <v>3850</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16377,7 +16377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.9942102432251</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="n">
         <v>46200</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16725,7 +16725,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H564" t="n">
         <v>12250</v>
@@ -16841,7 +16841,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H568" t="n">
         <v>10150</v>
@@ -16899,7 +16899,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H570" t="n">
         <v>2100</v>
@@ -16986,7 +16986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H573" t="n">
         <v>7000</v>
@@ -17160,7 +17160,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H579" t="n">
         <v>8400</v>
@@ -17189,7 +17189,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H582" t="n">
         <v>350</v>
@@ -17334,7 +17334,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H585" t="n">
         <v>7700</v>
@@ -17363,7 +17363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G586" t="n">
-        <v>1.71201074123383</v>
+        <v>1.71201062202454</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H619" t="n">
         <v>2800</v>
@@ -18349,7 +18349,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H620" t="n">
         <v>10150</v>
@@ -18552,7 +18552,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264752388</v>
+        <v>1.62264740467072</v>
       </c>
       <c r="H627" t="n">
         <v>23800</v>
@@ -18639,7 +18639,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H630" t="n">
         <v>2100</v>
@@ -18755,7 +18755,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387762069702</v>
+        <v>1.52387750148773</v>
       </c>
       <c r="H634" t="n">
         <v>2450</v>
@@ -18842,7 +18842,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798758983612</v>
+        <v>1.53798747062683</v>
       </c>
       <c r="H637" t="n">
         <v>5950</v>
@@ -18871,7 +18871,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620740890503</v>
+        <v>1.56620752811432</v>
       </c>
       <c r="H638" t="n">
         <v>10500</v>
@@ -19074,7 +19074,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19625,7 +19625,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378746509552</v>
+        <v>0.818378686904907</v>
       </c>
       <c r="H664" t="n">
         <v>10850</v>
@@ -19712,7 +19712,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775094985962</v>
+        <v>0.954775154590607</v>
       </c>
       <c r="H667" t="n">
         <v>350</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19828,7 +19828,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089210987091</v>
+        <v>0.918089270591736</v>
       </c>
       <c r="H671" t="n">
         <v>3150</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326548576355</v>
+        <v>0.91432648897171</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20147,7 +20147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591849327087</v>
+        <v>1.01591837406158</v>
       </c>
       <c r="H682" t="n">
         <v>12950</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H684" t="n">
         <v>47250</v>
@@ -20234,7 +20234,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H685" t="n">
         <v>34650</v>
@@ -20263,7 +20263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H686" t="n">
         <v>6650</v>
@@ -20350,7 +20350,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H689" t="n">
         <v>23450</v>
@@ -20437,7 +20437,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H692" t="n">
         <v>4550</v>
@@ -20466,7 +20466,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H693" t="n">
         <v>17850</v>
@@ -20495,7 +20495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H694" t="n">
         <v>9800</v>
@@ -20524,7 +20524,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20611,7 +20611,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H698" t="n">
         <v>3850</v>
@@ -20640,7 +20640,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="n">
         <v>2450</v>
@@ -20843,7 +20843,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H706" t="n">
         <v>22400</v>
@@ -20872,7 +20872,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H707" t="n">
         <v>700</v>
@@ -20901,7 +20901,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H708" t="n">
         <v>13650</v>
@@ -20988,7 +20988,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="n">
         <v>1750</v>
@@ -21017,7 +21017,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H712" t="n">
         <v>10850</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H713" t="n">
         <v>2450</v>
@@ -21104,7 +21104,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H715" t="n">
         <v>128100</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21162,7 +21162,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G717" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H717" t="n">
         <v>350</v>
@@ -21278,7 +21278,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H721" t="n">
         <v>7700</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21365,7 +21365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="n">
         <v>21350</v>
@@ -21394,7 +21394,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H726" t="n">
         <v>13300</v>
@@ -21452,7 +21452,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H727" t="n">
         <v>2450</v>
@@ -21510,7 +21510,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H729" t="n">
         <v>1750</v>
@@ -21539,7 +21539,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H738" t="n">
         <v>22750</v>
@@ -21829,7 +21829,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G740" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H740" t="n">
         <v>7350</v>
@@ -21858,7 +21858,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H741" t="n">
         <v>38150</v>
@@ -21945,7 +21945,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H744" t="n">
         <v>1050</v>
@@ -22032,7 +22032,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H747" t="n">
         <v>1050</v>
@@ -22061,7 +22061,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H750" t="n">
         <v>350</v>
@@ -22148,7 +22148,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H765" t="n">
         <v>3150</v>
@@ -22612,7 +22612,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H767" t="n">
         <v>350</v>
@@ -23018,7 +23018,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="n">
         <v>14000</v>
@@ -23047,7 +23047,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G782" t="n">
-        <v>1.26049149036407</v>
+        <v>1.26049137115479</v>
       </c>
       <c r="H782" t="n">
         <v>2800</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H787" t="n">
         <v>700</v>
@@ -23279,7 +23279,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H790" t="n">
         <v>4200</v>
@@ -23424,7 +23424,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G795" t="n">
-        <v>1.14290809631348</v>
+        <v>1.14290821552277</v>
       </c>
       <c r="H795" t="n">
         <v>350</v>
@@ -23685,7 +23685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H804" t="n">
         <v>12600</v>
@@ -23714,7 +23714,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H805" t="n">
         <v>18550</v>
@@ -23830,7 +23830,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H809" t="n">
         <v>41300</v>
@@ -23946,7 +23946,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H813" t="n">
         <v>4200</v>
@@ -23975,7 +23975,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H814" t="n">
         <v>4550</v>
@@ -24091,7 +24091,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G818" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H818" t="n">
         <v>1050</v>
@@ -24149,7 +24149,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H820" t="n">
         <v>16100</v>
@@ -24178,7 +24178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H822" t="n">
         <v>3850</v>
@@ -24236,7 +24236,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G823" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H823" t="n">
         <v>16100</v>
@@ -24265,7 +24265,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G824" t="n">
-        <v>1.17112827301025</v>
+        <v>1.17112815380096</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G827" t="n">
-        <v>1.15701830387115</v>
+        <v>1.15701818466187</v>
       </c>
       <c r="H827" t="n">
         <v>3150</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24584,7 +24584,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H835" t="n">
         <v>9100</v>
@@ -24671,7 +24671,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="n">
         <v>13300</v>
@@ -24845,7 +24845,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="n">
         <v>129500</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -25483,7 +25483,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H866" t="n">
         <v>2800</v>
@@ -25686,7 +25686,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H873" t="n">
         <v>4550</v>
@@ -25715,7 +25715,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G874" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H874" t="n">
         <v>7350</v>
@@ -25802,7 +25802,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H877" t="n">
         <v>1400</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25976,7 +25976,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H883" t="n">
         <v>5950</v>
@@ -26005,7 +26005,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H884" t="n">
         <v>2800</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26121,7 +26121,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H888" t="n">
         <v>2450</v>
@@ -26208,7 +26208,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H891" t="n">
         <v>11900</v>
@@ -26237,7 +26237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="n">
         <v>7000</v>
@@ -26295,7 +26295,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H894" t="n">
         <v>14000</v>
@@ -26324,7 +26324,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H895" t="n">
         <v>10150</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26411,7 +26411,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.4909542798996</v>
+        <v>1.49095439910889</v>
       </c>
       <c r="H898" t="n">
         <v>172900</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H899" t="n">
         <v>51450</v>
@@ -26585,7 +26585,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G904" t="n">
-        <v>1.90014374256134</v>
+        <v>1.90014362335205</v>
       </c>
       <c r="H904" t="n">
         <v>367150</v>
@@ -26730,7 +26730,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H909" t="n">
         <v>4900</v>
@@ -26759,7 +26759,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.70260381698608</v>
+        <v>1.70260393619537</v>
       </c>
       <c r="H910" t="n">
         <v>4900</v>
@@ -27078,7 +27078,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H921" t="n">
         <v>352450</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27484,7 +27484,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H935" t="n">
         <v>40950</v>
@@ -27600,7 +27600,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H939" t="n">
         <v>46200</v>
@@ -27629,7 +27629,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361728668213</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H940" t="n">
         <v>2100</v>
@@ -28064,7 +28064,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G955" t="n">
-        <v>2.71852254867554</v>
+        <v>2.71852231025696</v>
       </c>
       <c r="H955" t="n">
         <v>15400</v>
@@ -28122,7 +28122,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>2.75614905357361</v>
+        <v>2.75614929199219</v>
       </c>
       <c r="H957" t="n">
         <v>51100</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.8690288066864</v>
+        <v>2.86902856826782</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28238,7 +28238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H961" t="n">
         <v>175000</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28470,7 +28470,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="n">
         <v>18550</v>
@@ -28499,7 +28499,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G970" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H970" t="n">
         <v>19600</v>
@@ -28528,7 +28528,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G971" t="n">
-        <v>3.42402148246765</v>
+        <v>3.42402124404907</v>
       </c>
       <c r="H971" t="n">
         <v>25200</v>
@@ -28557,7 +28557,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="n">
         <v>29400</v>
@@ -28586,7 +28586,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3111412525177</v>
+        <v>3.31114149093628</v>
       </c>
       <c r="H973" t="n">
         <v>20300</v>
@@ -28760,7 +28760,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H979" t="n">
         <v>12950</v>
@@ -28992,7 +28992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H987" t="n">
         <v>16800</v>
@@ -29021,7 +29021,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="n">
         <v>11550</v>
@@ -29079,7 +29079,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H990" t="n">
         <v>30450</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29253,7 +29253,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H996" t="n">
         <v>14700</v>
@@ -29369,7 +29369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H1000" t="n">
         <v>30100</v>
@@ -29427,7 +29427,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="n">
         <v>2450</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29630,7 +29630,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1009" t="n">
         <v>5250</v>
@@ -29688,7 +29688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1011" t="n">
         <v>2100</v>
@@ -29717,7 +29717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1012" t="n">
         <v>3500</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29891,7 +29891,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1018" t="n">
         <v>108150</v>
@@ -29920,7 +29920,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1019" t="n">
         <v>10500</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30036,7 +30036,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1023" t="n">
         <v>6650</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30123,7 +30123,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="n">
         <v>3500</v>
@@ -30181,7 +30181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1028" t="n">
         <v>2100</v>
@@ -30239,7 +30239,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1030" t="n">
         <v>6300</v>
@@ -30268,7 +30268,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="n">
         <v>1400</v>
@@ -30326,7 +30326,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="n">
         <v>6300</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30616,7 +30616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="n">
         <v>2800</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30877,7 +30877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597517967224</v>
+        <v>3.07597494125366</v>
       </c>
       <c r="H1052" t="n">
         <v>252000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31312,7 +31312,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="n">
         <v>21700</v>
@@ -31370,7 +31370,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707510948181</v>
+        <v>3.21707487106323</v>
       </c>
       <c r="H1069" t="n">
         <v>30450</v>
@@ -31457,7 +31457,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H1072" t="n">
         <v>64750</v>
@@ -31573,7 +31573,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.77206778526306</v>
+        <v>3.77206754684448</v>
       </c>
       <c r="H1076" t="n">
         <v>223300</v>
@@ -31718,7 +31718,7 @@
         <v>3.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1081" t="n">
         <v>52150</v>
@@ -31805,7 +31805,7 @@
         <v>3.75</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.52749466896057</v>
+        <v>3.52749443054199</v>
       </c>
       <c r="H1084" t="n">
         <v>55650</v>
@@ -31863,7 +31863,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1086" t="n">
         <v>16800</v>
@@ -31921,7 +31921,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1088" t="n">
         <v>14700</v>
@@ -31950,7 +31950,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.40520763397217</v>
+        <v>3.40520787239075</v>
       </c>
       <c r="H1089" t="n">
         <v>21000</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32037,7 +32037,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.80969405174255</v>
+        <v>3.80969429016113</v>
       </c>
       <c r="H1092" t="n">
         <v>31850</v>
@@ -32066,7 +32066,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562743186951</v>
+        <v>3.71562767028809</v>
       </c>
       <c r="H1093" t="n">
         <v>55300</v>
@@ -32182,7 +32182,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.4334282875061</v>
+        <v>3.43342804908752</v>
       </c>
       <c r="H1097" t="n">
         <v>32900</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -32298,7 +32298,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046112060547</v>
+        <v>3.48046135902405</v>
       </c>
       <c r="H1101" t="n">
         <v>45850</v>
@@ -68293,6 +68293,64 @@
         <v>2100</v>
       </c>
       <c r="I2342" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2343" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="G2343" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="H2343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2344" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="G2344" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="H2344" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I2344" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15378999710083</v>
+        <v>3.15378975868225</v>
       </c>
       <c r="H5" t="n">
         <v>82950</v>
@@ -659,7 +659,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044326782227</v>
+        <v>3.20044350624084</v>
       </c>
       <c r="H10" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512802124023</v>
+        <v>3.13512778282166</v>
       </c>
       <c r="H12" t="n">
         <v>5950</v>
@@ -862,7 +862,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1892466545105</v>
+        <v>3.18924641609192</v>
       </c>
       <c r="H17" t="n">
         <v>2450</v>
@@ -949,7 +949,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198707580566</v>
+        <v>3.40198731422424</v>
       </c>
       <c r="H20" t="n">
         <v>22050</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501127243042</v>
+        <v>3.555011510849</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1007,7 +1007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.88158702850342</v>
+        <v>3.881587266922</v>
       </c>
       <c r="H22" t="n">
         <v>75600</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105990409851</v>
+        <v>3.86105966567993</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1094,7 +1094,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556425094604</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H25" t="n">
         <v>38150</v>
@@ -1123,7 +1123,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939863204956</v>
+        <v>4.07939910888672</v>
       </c>
       <c r="H26" t="n">
         <v>28700</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911180496216</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H32" t="n">
         <v>60200</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120601654053</v>
+        <v>7.65120553970337</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761875152588</v>
+        <v>6.16761827468872</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1529,7 +1529,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088653564453</v>
+        <v>6.40088701248169</v>
       </c>
       <c r="H40" t="n">
         <v>82250</v>
@@ -1645,7 +1645,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401866912842</v>
+        <v>7.12401914596558</v>
       </c>
       <c r="H44" t="n">
         <v>91350</v>
@@ -1674,7 +1674,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876251220703</v>
+        <v>6.84876203536987</v>
       </c>
       <c r="H45" t="n">
         <v>72450</v>
@@ -1732,7 +1732,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9140772819519</v>
+        <v>6.91407775878906</v>
       </c>
       <c r="H47" t="n">
         <v>35350</v>
@@ -1761,7 +1761,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H48" t="n">
         <v>25200</v>
@@ -1790,7 +1790,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000316619873</v>
+        <v>7.18000364303589</v>
       </c>
       <c r="H49" t="n">
         <v>59850</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451351165771</v>
+        <v>7.74451398849487</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750999450684</v>
+        <v>8.95750904083252</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2022,7 +2022,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424125671387</v>
+        <v>8.72424030303955</v>
       </c>
       <c r="H57" t="n">
         <v>169750</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2138,7 +2138,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726755142212</v>
+        <v>7.42726802825928</v>
       </c>
       <c r="H61" t="n">
         <v>87500</v>
@@ -2167,7 +2167,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061428070068</v>
+        <v>7.38061380386353</v>
       </c>
       <c r="H62" t="n">
         <v>17150</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002254486084</v>
+        <v>7.110023021698</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2254,7 +2254,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675380706787</v>
+        <v>6.87675428390503</v>
       </c>
       <c r="H65" t="n">
         <v>99750</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252561569214</v>
+        <v>7.70252513885498</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2428,7 +2428,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>7.45526027679443</v>
+        <v>7.45525979995728</v>
       </c>
       <c r="H71" t="n">
         <v>10150</v>
@@ -2486,7 +2486,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059442520142</v>
+        <v>7.45059490203857</v>
       </c>
       <c r="H73" t="n">
         <v>20650</v>
@@ -2631,7 +2631,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H78" t="n">
         <v>8750</v>
@@ -2718,7 +2718,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H81" t="n">
         <v>11200</v>
@@ -2747,7 +2747,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405790328979</v>
+        <v>6.98405838012695</v>
       </c>
       <c r="H82" t="n">
         <v>10500</v>
@@ -2805,7 +2805,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541530609131</v>
+        <v>6.89541578292847</v>
       </c>
       <c r="H84" t="n">
         <v>2800</v>
@@ -2892,7 +2892,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H87" t="n">
         <v>30100</v>
@@ -2921,7 +2921,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H88" t="n">
         <v>7700</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145841598511</v>
+        <v>6.74145889282227</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817077636719</v>
+        <v>6.57817125320435</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3269,7 +3269,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419403076172</v>
+        <v>6.49419450759888</v>
       </c>
       <c r="H100" t="n">
         <v>8750</v>
@@ -3298,7 +3298,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094514846802</v>
+        <v>6.19094562530518</v>
       </c>
       <c r="H101" t="n">
         <v>40250</v>
@@ -3327,7 +3327,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.51285600662231</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H102" t="n">
         <v>24850</v>
@@ -3356,7 +3356,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287490844727</v>
       </c>
       <c r="H103" t="n">
         <v>5600</v>
@@ -3414,7 +3414,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.39155578613281</v>
+        <v>6.39155626296997</v>
       </c>
       <c r="H105" t="n">
         <v>2100</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3530,7 +3530,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.51285600662231</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H109" t="n">
         <v>2800</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3675,7 +3675,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G114" t="n">
-        <v>6.30757999420166</v>
+        <v>6.3075795173645</v>
       </c>
       <c r="H114" t="n">
         <v>4550</v>
@@ -3704,7 +3704,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H115" t="n">
         <v>10850</v>
@@ -3733,7 +3733,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H116" t="n">
         <v>1400</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828800201416</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -4052,7 +4052,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175004959106</v>
+        <v>5.69175100326538</v>
       </c>
       <c r="H127" t="n">
         <v>15750</v>
@@ -4081,7 +4081,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75706624984741</v>
+        <v>5.75706577301025</v>
       </c>
       <c r="H128" t="n">
         <v>5250</v>
@@ -4197,7 +4197,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H132" t="n">
         <v>5600</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175004959106</v>
+        <v>5.69175100326538</v>
       </c>
       <c r="H133" t="n">
         <v>16450</v>
@@ -4284,7 +4284,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245853424072</v>
+        <v>5.54245901107788</v>
       </c>
       <c r="H135" t="n">
         <v>20300</v>
@@ -4313,7 +4313,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911180496216</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H136" t="n">
         <v>8750</v>
@@ -4371,7 +4371,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375923156738</v>
+        <v>5.66375875473022</v>
       </c>
       <c r="H138" t="n">
         <v>3850</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305027008057</v>
+        <v>5.81304979324341</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4574,7 +4574,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.9810037612915</v>
+        <v>5.98100328445435</v>
       </c>
       <c r="H145" t="n">
         <v>39200</v>
@@ -4603,7 +4603,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H146" t="n">
         <v>8750</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4864,7 +4864,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>5.45848226547241</v>
+        <v>5.45848178863525</v>
       </c>
       <c r="H155" t="n">
         <v>7000</v>
@@ -4893,7 +4893,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517477035522</v>
+        <v>5.36517429351807</v>
       </c>
       <c r="H156" t="n">
         <v>5950</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052925109863</v>
+        <v>5.29052877426147</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5009,7 +5009,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>5.32785224914551</v>
+        <v>5.32785177230835</v>
       </c>
       <c r="H160" t="n">
         <v>5600</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316654205322</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -5270,7 +5270,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5357,7 +5357,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.33357191085815</v>
+        <v>5.333571434021</v>
       </c>
       <c r="H172" t="n">
         <v>4900</v>
@@ -5502,7 +5502,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.78509092330933</v>
+        <v>5.78509140014648</v>
       </c>
       <c r="H177" t="n">
         <v>8050</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.73805713653564</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5560,7 +5560,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212375640869</v>
+        <v>5.83212423324585</v>
       </c>
       <c r="H179" t="n">
         <v>14700</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.73805713653564</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5647,7 +5647,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729078292847</v>
+        <v>6.06729030609131</v>
       </c>
       <c r="H182" t="n">
         <v>62650</v>
@@ -5705,7 +5705,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390453338623</v>
+        <v>5.80390405654907</v>
       </c>
       <c r="H184" t="n">
         <v>16450</v>
@@ -5734,7 +5734,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399099349976</v>
+        <v>5.64399147033691</v>
       </c>
       <c r="H185" t="n">
         <v>4550</v>
@@ -5908,7 +5908,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H191" t="n">
         <v>2800</v>
@@ -5937,7 +5937,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H192" t="n">
         <v>5950</v>
@@ -5995,7 +5995,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G194" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H194" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G195" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H195" t="n">
         <v>2800</v>
@@ -6053,7 +6053,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891138076782</v>
+        <v>5.24891185760498</v>
       </c>
       <c r="H196" t="n">
         <v>25200</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950481414795</v>
+        <v>5.23950529098511</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6140,7 +6140,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H199" t="n">
         <v>1750</v>
@@ -6169,7 +6169,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H200" t="n">
         <v>5950</v>
@@ -6256,7 +6256,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H203" t="n">
         <v>12950</v>
@@ -6285,7 +6285,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>5.12662506103516</v>
+        <v>5.126624584198</v>
       </c>
       <c r="H204" t="n">
         <v>4900</v>
@@ -6372,7 +6372,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H207" t="n">
         <v>8050</v>
@@ -6401,7 +6401,7 @@
         <v>5.5</v>
       </c>
       <c r="G208" t="n">
-        <v>5.17365884780884</v>
+        <v>5.17365837097168</v>
       </c>
       <c r="H208" t="n">
         <v>9450</v>
@@ -6430,7 +6430,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721849441528</v>
+        <v>5.11721897125244</v>
       </c>
       <c r="H209" t="n">
         <v>5600</v>
@@ -6546,7 +6546,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077861785889</v>
+        <v>5.06077909469604</v>
       </c>
       <c r="H213" t="n">
         <v>10150</v>
@@ -6575,7 +6575,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>5.05137205123901</v>
+        <v>5.05137157440186</v>
       </c>
       <c r="H214" t="n">
         <v>1750</v>
@@ -6633,7 +6633,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959175109863</v>
+        <v>5.07959222793579</v>
       </c>
       <c r="H216" t="n">
         <v>2800</v>
@@ -6691,7 +6691,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.03255891799927</v>
+        <v>5.03255844116211</v>
       </c>
       <c r="H218" t="n">
         <v>25550</v>
@@ -6749,7 +6749,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.8350191116333</v>
+        <v>4.83501863479614</v>
       </c>
       <c r="H220" t="n">
         <v>10500</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H227" t="n">
         <v>8400</v>
@@ -7039,7 +7039,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985303878784</v>
+        <v>4.59985256195068</v>
       </c>
       <c r="H230" t="n">
         <v>1750</v>
@@ -7097,7 +7097,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472948074341</v>
+        <v>4.28472995758057</v>
       </c>
       <c r="H232" t="n">
         <v>4900</v>
@@ -7126,7 +7126,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.2423996925354</v>
+        <v>4.24240016937256</v>
       </c>
       <c r="H233" t="n">
         <v>2450</v>
@@ -7155,7 +7155,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>4.20007038116455</v>
+        <v>4.20006990432739</v>
       </c>
       <c r="H234" t="n">
         <v>6650</v>
@@ -7213,7 +7213,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490383148193</v>
+        <v>3.96490359306335</v>
       </c>
       <c r="H236" t="n">
         <v>12600</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H238" t="n">
         <v>147350</v>
@@ -7329,7 +7329,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31294965744019</v>
+        <v>4.31295013427734</v>
       </c>
       <c r="H240" t="n">
         <v>9100</v>
@@ -7387,7 +7387,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22829008102417</v>
+        <v>4.22828960418701</v>
       </c>
       <c r="H242" t="n">
         <v>7700</v>
@@ -7445,7 +7445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189319610596</v>
+        <v>4.09189367294312</v>
       </c>
       <c r="H244" t="n">
         <v>7700</v>
@@ -7474,7 +7474,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.06367349624634</v>
+        <v>4.0636739730835</v>
       </c>
       <c r="H245" t="n">
         <v>4550</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312376976013</v>
+        <v>3.99312353134155</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7619,7 +7619,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316699981689</v>
+        <v>3.91316723823547</v>
       </c>
       <c r="H250" t="n">
         <v>16450</v>
@@ -7735,7 +7735,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G254" t="n">
-        <v>3.54160475730896</v>
+        <v>3.54160451889038</v>
       </c>
       <c r="H254" t="n">
         <v>20300</v>
@@ -7793,7 +7793,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7996,7 +7996,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H263" t="n">
         <v>3850</v>
@@ -8025,7 +8025,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G264" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H264" t="n">
         <v>2450</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8199,7 +8199,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.4146146774292</v>
+        <v>3.41461491584778</v>
       </c>
       <c r="H270" t="n">
         <v>7350</v>
@@ -8315,7 +8315,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745120048523</v>
+        <v>3.60745096206665</v>
       </c>
       <c r="H274" t="n">
         <v>3500</v>
@@ -8634,7 +8634,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H285" t="n">
         <v>12950</v>
@@ -8779,7 +8779,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H290" t="n">
         <v>8750</v>
@@ -8924,7 +8924,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092414855957</v>
+        <v>3.71092391014099</v>
       </c>
       <c r="H295" t="n">
         <v>10500</v>
@@ -8953,7 +8953,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H296" t="n">
         <v>39900</v>
@@ -9011,7 +9011,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H298" t="n">
         <v>51800</v>
@@ -9040,7 +9040,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H299" t="n">
         <v>5950</v>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H301" t="n">
         <v>67900</v>
@@ -9156,7 +9156,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H303" t="n">
         <v>22750</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H304" t="n">
         <v>23100</v>
@@ -9504,7 +9504,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H315" t="n">
         <v>8750</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H316" t="n">
         <v>5600</v>
@@ -9562,7 +9562,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>2.1211998462677</v>
+        <v>2.12120008468628</v>
       </c>
       <c r="H317" t="n">
         <v>6650</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H318" t="n">
         <v>52850</v>
@@ -9620,7 +9620,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179304122925</v>
+        <v>2.11179327964783</v>
       </c>
       <c r="H319" t="n">
         <v>10850</v>
@@ -9649,7 +9649,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H320" t="n">
         <v>21000</v>
@@ -9678,7 +9678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H321" t="n">
         <v>5250</v>
@@ -9707,7 +9707,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H322" t="n">
         <v>3150</v>
@@ -9736,7 +9736,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H323" t="n">
         <v>16100</v>
@@ -9794,7 +9794,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950695991516</v>
+        <v>1.98950672149658</v>
       </c>
       <c r="H325" t="n">
         <v>2800</v>
@@ -9881,7 +9881,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H328" t="n">
         <v>4900</v>
@@ -9910,7 +9910,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G329" t="n">
-        <v>2.1211998462677</v>
+        <v>2.12120008468628</v>
       </c>
       <c r="H329" t="n">
         <v>12250</v>
@@ -9997,7 +9997,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H332" t="n">
         <v>7700</v>
@@ -10055,7 +10055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H334" t="n">
         <v>4550</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10316,7 +10316,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478907585144</v>
+        <v>1.79478919506073</v>
       </c>
       <c r="H343" t="n">
         <v>19600</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10519,7 +10519,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G350" t="n">
-        <v>1.24732208251953</v>
+        <v>1.24732196331024</v>
       </c>
       <c r="H350" t="n">
         <v>36750</v>
@@ -10548,7 +10548,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H351" t="n">
         <v>6650</v>
@@ -10635,7 +10635,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G354" t="n">
-        <v>1.29435539245605</v>
+        <v>1.29435527324677</v>
       </c>
       <c r="H354" t="n">
         <v>3850</v>
@@ -10693,7 +10693,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H356" t="n">
         <v>3850</v>
@@ -10780,7 +10780,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H359" t="n">
         <v>9100</v>
@@ -10838,7 +10838,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H361" t="n">
         <v>33950</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209767818451</v>
+        <v>1.55209755897522</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -10896,7 +10896,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002808094025</v>
+        <v>1.68002796173096</v>
       </c>
       <c r="H363" t="n">
         <v>22050</v>
@@ -11070,7 +11070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H369" t="n">
         <v>55650</v>
@@ -11099,7 +11099,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H370" t="n">
         <v>68600</v>
@@ -11128,7 +11128,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H371" t="n">
         <v>184800</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11273,7 +11273,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.56331253051758</v>
+        <v>2.563312292099</v>
       </c>
       <c r="H376" t="n">
         <v>99050</v>
@@ -11331,7 +11331,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H378" t="n">
         <v>99050</v>
@@ -11389,7 +11389,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H380" t="n">
         <v>15050</v>
@@ -11418,7 +11418,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089580535889</v>
+        <v>2.68089556694031</v>
       </c>
       <c r="H381" t="n">
         <v>12250</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975240707397</v>
+        <v>2.61975264549255</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11505,7 +11505,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H384" t="n">
         <v>5250</v>
@@ -11563,7 +11563,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H386" t="n">
         <v>10150</v>
@@ -11592,7 +11592,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H387" t="n">
         <v>2450</v>
@@ -11766,7 +11766,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H393" t="n">
         <v>10150</v>
@@ -11853,7 +11853,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860924720764</v>
+        <v>2.55860948562622</v>
       </c>
       <c r="H396" t="n">
         <v>2100</v>
@@ -11940,7 +11940,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750955581665</v>
+        <v>2.41750931739807</v>
       </c>
       <c r="H399" t="n">
         <v>4550</v>
@@ -11998,7 +11998,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G401" t="n">
-        <v>2.51627945899963</v>
+        <v>2.51627922058105</v>
       </c>
       <c r="H401" t="n">
         <v>51450</v>
@@ -12056,7 +12056,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.40810298919678</v>
+        <v>2.4081027507782</v>
       </c>
       <c r="H403" t="n">
         <v>14000</v>
@@ -12230,7 +12230,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047600746155</v>
+        <v>2.37047624588013</v>
       </c>
       <c r="H409" t="n">
         <v>6300</v>
@@ -12346,7 +12346,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.31873965263367</v>
+        <v>2.31873989105225</v>
       </c>
       <c r="H413" t="n">
         <v>10150</v>
@@ -12433,7 +12433,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H416" t="n">
         <v>22400</v>
@@ -12665,7 +12665,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H424" t="n">
         <v>3850</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.4269163608551</v>
+        <v>2.42691612243652</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12897,7 +12897,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106944084167</v>
+        <v>2.36106967926025</v>
       </c>
       <c r="H432" t="n">
         <v>6300</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -13042,7 +13042,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H437" t="n">
         <v>2800</v>
@@ -13071,7 +13071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H438" t="n">
         <v>5600</v>
@@ -13129,7 +13129,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H440" t="n">
         <v>8400</v>
@@ -13158,7 +13158,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H441" t="n">
         <v>11200</v>
@@ -13303,7 +13303,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H446" t="n">
         <v>2450</v>
@@ -13332,7 +13332,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H447" t="n">
         <v>2800</v>
@@ -13361,7 +13361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>2.22937655448914</v>
+        <v>2.22937631607056</v>
       </c>
       <c r="H448" t="n">
         <v>1750</v>
@@ -13390,7 +13390,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H449" t="n">
         <v>2800</v>
@@ -13477,7 +13477,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H452" t="n">
         <v>10850</v>
@@ -13622,7 +13622,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H457" t="n">
         <v>21350</v>
@@ -13680,7 +13680,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H459" t="n">
         <v>12250</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H461" t="n">
         <v>1750</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -13999,7 +13999,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H470" t="n">
         <v>3850</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H474" t="n">
         <v>5250</v>
@@ -14231,7 +14231,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H478" t="n">
         <v>6650</v>
@@ -14260,7 +14260,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H479" t="n">
         <v>700</v>
@@ -14289,7 +14289,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H480" t="n">
         <v>5600</v>
@@ -14318,7 +14318,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H481" t="n">
         <v>1400</v>
@@ -14376,7 +14376,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658349990845</v>
+        <v>1.95658361911774</v>
       </c>
       <c r="H483" t="n">
         <v>10500</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H485" t="n">
         <v>4550</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14521,7 +14521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H488" t="n">
         <v>2450</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H489" t="n">
         <v>21700</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14666,7 +14666,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H493" t="n">
         <v>3500</v>
@@ -14695,7 +14695,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H494" t="n">
         <v>6650</v>
@@ -14724,7 +14724,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H496" t="n">
         <v>9100</v>
@@ -14782,7 +14782,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H497" t="n">
         <v>10850</v>
@@ -14811,7 +14811,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H498" t="n">
         <v>350</v>
@@ -14927,7 +14927,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G502" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H502" t="n">
         <v>32900</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -14985,7 +14985,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H504" t="n">
         <v>7350</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15072,7 +15072,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H507" t="n">
         <v>19250</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H513" t="n">
         <v>3850</v>
@@ -15275,7 +15275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H514" t="n">
         <v>2800</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H518" t="n">
         <v>10150</v>
@@ -15420,7 +15420,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H519" t="n">
         <v>7000</v>
@@ -15449,7 +15449,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H520" t="n">
         <v>2100</v>
@@ -15536,7 +15536,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H523" t="n">
         <v>3150</v>
@@ -15565,7 +15565,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H524" t="n">
         <v>3850</v>
@@ -15594,7 +15594,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G526" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H526" t="n">
         <v>9800</v>
@@ -15652,7 +15652,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H537" t="n">
         <v>2800</v>
@@ -16000,7 +16000,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G539" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H539" t="n">
         <v>1750</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16145,7 +16145,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H544" t="n">
         <v>1750</v>
@@ -16232,7 +16232,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G547" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H547" t="n">
         <v>700</v>
@@ -16261,7 +16261,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H548" t="n">
         <v>7000</v>
@@ -16290,7 +16290,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H549" t="n">
         <v>1050</v>
@@ -16348,7 +16348,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H551" t="n">
         <v>140000</v>
@@ -16464,7 +16464,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H555" t="n">
         <v>62650</v>
@@ -16493,7 +16493,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86251699924469</v>
+        <v>1.86251711845398</v>
       </c>
       <c r="H556" t="n">
         <v>11550</v>
@@ -16522,7 +16522,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H557" t="n">
         <v>7000</v>
@@ -16580,7 +16580,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H559" t="n">
         <v>10150</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16638,7 +16638,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H561" t="n">
         <v>8050</v>
@@ -16696,7 +16696,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H563" t="n">
         <v>5600</v>
@@ -16812,7 +16812,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H567" t="n">
         <v>9800</v>
@@ -16841,7 +16841,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H568" t="n">
         <v>10150</v>
@@ -16899,7 +16899,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H570" t="n">
         <v>2100</v>
@@ -16928,7 +16928,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H571" t="n">
         <v>2450</v>
@@ -16957,7 +16957,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G572" t="n">
-        <v>1.85311055183411</v>
+        <v>1.85311043262482</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H573" t="n">
         <v>7000</v>
@@ -17015,7 +17015,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H574" t="n">
         <v>1750</v>
@@ -17044,7 +17044,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17160,7 +17160,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H579" t="n">
         <v>8400</v>
@@ -17189,7 +17189,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17247,7 +17247,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.80137372016907</v>
+        <v>1.80137383937836</v>
       </c>
       <c r="H582" t="n">
         <v>350</v>
@@ -17276,7 +17276,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H583" t="n">
         <v>19950</v>
@@ -17305,7 +17305,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H589" t="n">
         <v>2450</v>
@@ -17537,7 +17537,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.7073073387146</v>
+        <v>1.70730745792389</v>
       </c>
       <c r="H592" t="n">
         <v>2100</v>
@@ -17566,7 +17566,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612071037292</v>
+        <v>1.72612059116364</v>
       </c>
       <c r="H593" t="n">
         <v>4550</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H596" t="n">
         <v>1400</v>
@@ -17740,7 +17740,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H599" t="n">
         <v>5250</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17827,7 +17827,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.6649774312973</v>
+        <v>1.66497731208801</v>
       </c>
       <c r="H602" t="n">
         <v>350</v>
@@ -17914,7 +17914,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H605" t="n">
         <v>350</v>
@@ -17943,7 +17943,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H606" t="n">
         <v>12250</v>
@@ -17972,7 +17972,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H607" t="n">
         <v>5950</v>
@@ -18001,7 +18001,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H608" t="n">
         <v>1050</v>
@@ -18030,7 +18030,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H609" t="n">
         <v>8750</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18320,7 +18320,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H619" t="n">
         <v>2800</v>
@@ -18349,7 +18349,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H620" t="n">
         <v>10150</v>
@@ -18407,7 +18407,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>1.50976765155792</v>
+        <v>1.50976753234863</v>
       </c>
       <c r="H622" t="n">
         <v>9800</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.78726375102997</v>
+        <v>1.78726387023926</v>
       </c>
       <c r="H624" t="n">
         <v>55300</v>
@@ -18552,7 +18552,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264740467072</v>
+        <v>1.62264752388</v>
       </c>
       <c r="H627" t="n">
         <v>23800</v>
@@ -18639,7 +18639,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H630" t="n">
         <v>2100</v>
@@ -18813,7 +18813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55680096149445</v>
+        <v>1.55680084228516</v>
       </c>
       <c r="H636" t="n">
         <v>9800</v>
@@ -18842,7 +18842,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798747062683</v>
+        <v>1.53798758983612</v>
       </c>
       <c r="H637" t="n">
         <v>5950</v>
@@ -18871,7 +18871,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620752811432</v>
+        <v>1.56620740890503</v>
       </c>
       <c r="H638" t="n">
         <v>10500</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447105407715</v>
+        <v>1.51447093486786</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19248,7 +19248,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803093910217</v>
+        <v>1.45803105831146</v>
       </c>
       <c r="H651" t="n">
         <v>17150</v>
@@ -19277,7 +19277,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H652" t="n">
         <v>8050</v>
@@ -19335,7 +19335,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565768241882</v>
+        <v>1.49565756320953</v>
       </c>
       <c r="H654" t="n">
         <v>10150</v>
@@ -19364,7 +19364,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H655" t="n">
         <v>5600</v>
@@ -19393,7 +19393,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H656" t="n">
         <v>5950</v>
@@ -19422,7 +19422,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H657" t="n">
         <v>2800</v>
@@ -19480,7 +19480,7 @@
         <v>1.375</v>
       </c>
       <c r="G659" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H659" t="n">
         <v>8750</v>
@@ -19567,7 +19567,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H662" t="n">
         <v>21700</v>
@@ -19596,7 +19596,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G663" t="n">
-        <v>0.931258499622345</v>
+        <v>0.93125855922699</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378686904907</v>
+        <v>0.818378746509552</v>
       </c>
       <c r="H664" t="n">
         <v>10850</v>
@@ -19654,7 +19654,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G665" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H665" t="n">
         <v>9100</v>
@@ -19683,7 +19683,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G666" t="n">
-        <v>0.893631875514984</v>
+        <v>0.893631935119629</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19712,7 +19712,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775154590607</v>
+        <v>0.954775214195251</v>
       </c>
       <c r="H667" t="n">
         <v>350</v>
@@ -19770,7 +19770,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970571994781</v>
+        <v>0.919970512390137</v>
       </c>
       <c r="H669" t="n">
         <v>2100</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19828,7 +19828,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089270591736</v>
+        <v>0.918089210987091</v>
       </c>
       <c r="H671" t="n">
         <v>3150</v>
@@ -19857,7 +19857,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021221637726</v>
+        <v>0.935021162033081</v>
       </c>
       <c r="H672" t="n">
         <v>5950</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.91432648897171</v>
+        <v>0.914326548576355</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19915,7 +19915,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H674" t="n">
         <v>16800</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -19973,7 +19973,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291749954224</v>
+        <v>0.978291809558868</v>
       </c>
       <c r="H676" t="n">
         <v>8750</v>
@@ -20002,7 +20002,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H677" t="n">
         <v>700</v>
@@ -20031,7 +20031,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885064125061</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20118,7 +20118,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401719093323</v>
+        <v>0.992401778697968</v>
       </c>
       <c r="H681" t="n">
         <v>3500</v>
@@ -20147,7 +20147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591837406158</v>
+        <v>1.01591849327087</v>
       </c>
       <c r="H682" t="n">
         <v>12950</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H684" t="n">
         <v>47250</v>
@@ -20234,7 +20234,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H685" t="n">
         <v>34650</v>
@@ -20466,7 +20466,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H693" t="n">
         <v>17850</v>
@@ -20495,7 +20495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H694" t="n">
         <v>9800</v>
@@ -20524,7 +20524,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H702" t="n">
         <v>3150</v>
@@ -20814,7 +20814,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H705" t="n">
         <v>2450</v>
@@ -20843,7 +20843,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H706" t="n">
         <v>22400</v>
@@ -20959,7 +20959,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H710" t="n">
         <v>1050</v>
@@ -21075,7 +21075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H714" t="n">
         <v>4900</v>
@@ -21104,7 +21104,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H715" t="n">
         <v>128100</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21191,7 +21191,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H718" t="n">
         <v>700</v>
@@ -21220,7 +21220,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H719" t="n">
         <v>1050</v>
@@ -21278,7 +21278,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985435009003</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H721" t="n">
         <v>7700</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21423,7 +21423,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H726" t="n">
         <v>13300</v>
@@ -21684,7 +21684,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875477790833</v>
+        <v>1.20875465869904</v>
       </c>
       <c r="H735" t="n">
         <v>9450</v>
@@ -21771,7 +21771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H738" t="n">
         <v>22750</v>
@@ -21858,7 +21858,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H741" t="n">
         <v>38150</v>
@@ -22003,7 +22003,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H746" t="n">
         <v>2450</v>
@@ -22032,7 +22032,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H747" t="n">
         <v>1050</v>
@@ -22061,7 +22061,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H754" t="n">
         <v>35350</v>
@@ -22293,7 +22293,7 @@
         <v>1.375</v>
       </c>
       <c r="G756" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H756" t="n">
         <v>3500</v>
@@ -22380,7 +22380,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H759" t="n">
         <v>4900</v>
@@ -22409,7 +22409,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H761" t="n">
         <v>7700</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22525,7 +22525,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H764" t="n">
         <v>1050</v>
@@ -22699,7 +22699,7 @@
         <v>1.375</v>
       </c>
       <c r="G770" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H770" t="n">
         <v>8400</v>
@@ -22873,7 +22873,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H776" t="n">
         <v>6300</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345818042755</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.1476114988327</v>
+        <v>1.14761161804199</v>
       </c>
       <c r="H789" t="n">
         <v>5250</v>
@@ -23279,7 +23279,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H790" t="n">
         <v>4200</v>
@@ -23453,7 +23453,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H796" t="n">
         <v>1050</v>
@@ -23656,7 +23656,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H803" t="n">
         <v>17850</v>
@@ -23743,7 +23743,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H806" t="n">
         <v>46550</v>
@@ -23772,7 +23772,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G807" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H807" t="n">
         <v>15750</v>
@@ -23830,7 +23830,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H809" t="n">
         <v>41300</v>
@@ -23888,7 +23888,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H811" t="n">
         <v>12600</v>
@@ -23917,7 +23917,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G812" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H812" t="n">
         <v>6300</v>
@@ -23946,7 +23946,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H813" t="n">
         <v>4200</v>
@@ -24004,7 +24004,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H815" t="n">
         <v>2800</v>
@@ -24439,7 +24439,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H830" t="n">
         <v>81550</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24497,7 +24497,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H832" t="n">
         <v>52500</v>
@@ -24555,7 +24555,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866784095764</v>
+        <v>1.36866796016693</v>
       </c>
       <c r="H834" t="n">
         <v>12600</v>
@@ -24584,7 +24584,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985435009003</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H835" t="n">
         <v>9100</v>
@@ -24642,7 +24642,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H837" t="n">
         <v>60200</v>
@@ -24729,7 +24729,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H840" t="n">
         <v>9450</v>
@@ -24787,7 +24787,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H842" t="n">
         <v>23800</v>
@@ -24903,7 +24903,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G846" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H846" t="n">
         <v>25900</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -25222,7 +25222,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G857" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H857" t="n">
         <v>7700</v>
@@ -25251,7 +25251,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G858" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H858" t="n">
         <v>24500</v>
@@ -25280,7 +25280,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25483,7 +25483,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.35926115512848</v>
+        <v>1.35926127433777</v>
       </c>
       <c r="H866" t="n">
         <v>2800</v>
@@ -25599,7 +25599,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H870" t="n">
         <v>2100</v>
@@ -25628,7 +25628,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H871" t="n">
         <v>2100</v>
@@ -25686,7 +25686,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H873" t="n">
         <v>4550</v>
@@ -25715,7 +25715,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G874" t="n">
-        <v>1.35926115512848</v>
+        <v>1.35926127433777</v>
       </c>
       <c r="H874" t="n">
         <v>7350</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25947,7 +25947,7 @@
         <v>1.375</v>
       </c>
       <c r="G882" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H882" t="n">
         <v>350</v>
@@ -25976,7 +25976,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H883" t="n">
         <v>5950</v>
@@ -26005,7 +26005,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H884" t="n">
         <v>2800</v>
@@ -26034,7 +26034,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H885" t="n">
         <v>8750</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26092,7 +26092,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H887" t="n">
         <v>1400</v>
@@ -26121,7 +26121,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.27460122108459</v>
+        <v>1.27460134029388</v>
       </c>
       <c r="H888" t="n">
         <v>2450</v>
@@ -26208,7 +26208,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H891" t="n">
         <v>11900</v>
@@ -26266,7 +26266,7 @@
         <v>1.375</v>
       </c>
       <c r="G893" t="n">
-        <v>1.29341471195221</v>
+        <v>1.29341459274292</v>
       </c>
       <c r="H893" t="n">
         <v>8400</v>
@@ -26295,7 +26295,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H894" t="n">
         <v>14000</v>
@@ -26324,7 +26324,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H895" t="n">
         <v>10150</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26382,7 +26382,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H897" t="n">
         <v>25200</v>
@@ -26411,7 +26411,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.49095439910889</v>
+        <v>1.4909542798996</v>
       </c>
       <c r="H898" t="n">
         <v>172900</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H899" t="n">
         <v>51450</v>
@@ -26498,7 +26498,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H901" t="n">
         <v>91700</v>
@@ -26643,7 +26643,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H906" t="n">
         <v>33950</v>
@@ -26991,7 +26991,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H918" t="n">
         <v>3150</v>
@@ -27020,7 +27020,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H919" t="n">
         <v>9100</v>
@@ -27049,7 +27049,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662696838379</v>
+        <v>1.87662708759308</v>
       </c>
       <c r="H920" t="n">
         <v>215950</v>
@@ -27078,7 +27078,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H921" t="n">
         <v>352450</v>
@@ -27165,7 +27165,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777012825012</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H924" t="n">
         <v>12250</v>
@@ -27194,7 +27194,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H925" t="n">
         <v>26950</v>
@@ -27281,7 +27281,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H928" t="n">
         <v>17500</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H931" t="n">
         <v>264600</v>
@@ -27397,7 +27397,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H932" t="n">
         <v>82600</v>
@@ -27484,7 +27484,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H935" t="n">
         <v>40950</v>
@@ -27513,7 +27513,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H936" t="n">
         <v>10500</v>
@@ -27542,7 +27542,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H937" t="n">
         <v>8750</v>
@@ -27600,7 +27600,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H939" t="n">
         <v>46200</v>
@@ -27629,7 +27629,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H940" t="n">
         <v>2100</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827686309814</v>
+        <v>2.08827662467957</v>
       </c>
       <c r="H941" t="n">
         <v>39900</v>
@@ -27716,7 +27716,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H943" t="n">
         <v>154700</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -27919,7 +27919,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H950" t="n">
         <v>126350</v>
@@ -28064,7 +28064,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G955" t="n">
-        <v>2.71852231025696</v>
+        <v>2.71852254867554</v>
       </c>
       <c r="H955" t="n">
         <v>15400</v>
@@ -28093,7 +28093,7 @@
         <v>2.75</v>
       </c>
       <c r="G956" t="n">
-        <v>2.58682942390442</v>
+        <v>2.58682918548584</v>
       </c>
       <c r="H956" t="n">
         <v>21700</v>
@@ -28122,7 +28122,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>2.75614929199219</v>
+        <v>2.75614905357361</v>
       </c>
       <c r="H957" t="n">
         <v>51100</v>
@@ -28151,7 +28151,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>2.70911574363708</v>
+        <v>2.70911598205566</v>
       </c>
       <c r="H958" t="n">
         <v>9100</v>
@@ -28180,7 +28180,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H959" t="n">
         <v>13300</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.86902856826782</v>
+        <v>2.86902904510498</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28354,7 +28354,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H965" t="n">
         <v>91700</v>
@@ -28383,7 +28383,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H966" t="n">
         <v>283500</v>
@@ -28412,7 +28412,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224142074585</v>
+        <v>3.45224118232727</v>
       </c>
       <c r="H967" t="n">
         <v>114450</v>
@@ -28644,7 +28644,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H975" t="n">
         <v>25200</v>
@@ -28673,7 +28673,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H976" t="n">
         <v>8050</v>
@@ -28702,7 +28702,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H977" t="n">
         <v>16450</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28760,7 +28760,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H979" t="n">
         <v>12950</v>
@@ -28905,7 +28905,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>3.01953530311584</v>
+        <v>3.01953506469727</v>
       </c>
       <c r="H984" t="n">
         <v>16450</v>
@@ -29079,7 +29079,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H990" t="n">
         <v>30450</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292179107666</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29253,7 +29253,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H996" t="n">
         <v>14700</v>
@@ -29282,7 +29282,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H997" t="n">
         <v>9100</v>
@@ -29311,7 +29311,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H999" t="n">
         <v>2800</v>
@@ -29369,7 +29369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H1000" t="n">
         <v>30100</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29630,7 +29630,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1009" t="n">
         <v>5250</v>
@@ -29659,7 +29659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1010" t="n">
         <v>2100</v>
@@ -29688,7 +29688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1011" t="n">
         <v>2100</v>
@@ -29717,7 +29717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1012" t="n">
         <v>3500</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29891,7 +29891,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1018" t="n">
         <v>108150</v>
@@ -29920,7 +29920,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1019" t="n">
         <v>10500</v>
@@ -29949,7 +29949,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1020" t="n">
         <v>1750</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30036,7 +30036,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1023" t="n">
         <v>6650</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30181,7 +30181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1028" t="n">
         <v>2100</v>
@@ -30239,7 +30239,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1030" t="n">
         <v>6300</v>
@@ -30355,7 +30355,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1034" t="n">
         <v>7000</v>
@@ -30384,7 +30384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1035" t="n">
         <v>7000</v>
@@ -30442,7 +30442,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1037" t="n">
         <v>14700</v>
@@ -30500,7 +30500,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.11360192298889</v>
+        <v>3.11360168457031</v>
       </c>
       <c r="H1039" t="n">
         <v>7350</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30819,7 +30819,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1050" t="n">
         <v>34300</v>
@@ -30848,7 +30848,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.3581748008728</v>
+        <v>3.35817456245422</v>
       </c>
       <c r="H1051" t="n">
         <v>278600</v>
@@ -30877,7 +30877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597494125366</v>
+        <v>3.07597517967224</v>
       </c>
       <c r="H1052" t="n">
         <v>252000</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31225,7 +31225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H1064" t="n">
         <v>9800</v>
@@ -31254,7 +31254,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1065" t="n">
         <v>95550</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31457,7 +31457,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H1072" t="n">
         <v>64750</v>
@@ -31573,7 +31573,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.77206754684448</v>
+        <v>3.77206778526306</v>
       </c>
       <c r="H1076" t="n">
         <v>223300</v>
@@ -31631,7 +31631,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325393676758</v>
+        <v>3.75325417518616</v>
       </c>
       <c r="H1078" t="n">
         <v>55650</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31776,7 +31776,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1083" t="n">
         <v>11200</v>
@@ -31834,7 +31834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1085" t="n">
         <v>15750</v>
@@ -31892,7 +31892,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H1087" t="n">
         <v>16450</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32124,7 +32124,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.57452750205994</v>
+        <v>3.57452774047852</v>
       </c>
       <c r="H1095" t="n">
         <v>16800</v>
@@ -32153,7 +32153,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1096" t="n">
         <v>23800</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292179107666</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -32269,7 +32269,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H1100" t="n">
         <v>28000</v>
@@ -32327,7 +32327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1102" t="n">
         <v>26250</v>
@@ -32385,7 +32385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1104" t="n">
         <v>26600</v>
@@ -32414,7 +32414,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.6250786781311</v>
+        <v>3.62507843971252</v>
       </c>
       <c r="H1105" t="n">
         <v>4900</v>
@@ -32646,7 +32646,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1113" t="n">
         <v>40950</v>
@@ -32675,7 +32675,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794955253601</v>
+        <v>3.54794931411743</v>
       </c>
       <c r="H1114" t="n">
         <v>30100</v>
@@ -32762,7 +32762,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1117" t="n">
         <v>9800</v>
@@ -32849,7 +32849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1120" t="n">
         <v>7350</v>
@@ -32878,7 +32878,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436078071594</v>
+        <v>3.64436101913452</v>
       </c>
       <c r="H1121" t="n">
         <v>74200</v>
@@ -32936,7 +32936,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579633712769</v>
+        <v>3.60579609870911</v>
       </c>
       <c r="H1123" t="n">
         <v>43750</v>
@@ -33226,7 +33226,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1133" t="n">
         <v>7000</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1135" t="n">
         <v>3850</v>
@@ -33371,7 +33371,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1138" t="n">
         <v>3850</v>
@@ -33429,7 +33429,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1140" t="n">
         <v>26950</v>
@@ -33516,7 +33516,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1143" t="n">
         <v>6300</v>
@@ -33632,7 +33632,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687282562256</v>
+        <v>3.57687258720398</v>
       </c>
       <c r="H1147" t="n">
         <v>44100</v>
@@ -33661,7 +33661,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1148" t="n">
         <v>15400</v>
@@ -33806,7 +33806,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1153" t="n">
         <v>350</v>
@@ -33893,7 +33893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32620239257812</v>
+        <v>3.3262026309967</v>
       </c>
       <c r="H1156" t="n">
         <v>3150</v>
@@ -34154,7 +34154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1165" t="n">
         <v>14700</v>
@@ -34270,7 +34270,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31388020515442</v>
+        <v>2.31387996673584</v>
       </c>
       <c r="H1169" t="n">
         <v>30100</v>
@@ -34328,7 +34328,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608016967773</v>
+        <v>1.98608028888702</v>
       </c>
       <c r="H1171" t="n">
         <v>30800</v>
@@ -34415,7 +34415,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029143333435</v>
+        <v>2.41029167175293</v>
       </c>
       <c r="H1174" t="n">
         <v>21350</v>
@@ -34618,7 +34618,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.297278881073</v>
+        <v>3.29727911949158</v>
       </c>
       <c r="H1181" t="n">
         <v>33950</v>
@@ -34647,7 +34647,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1182" t="n">
         <v>13650</v>
@@ -34676,7 +34676,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512590408325</v>
+        <v>3.35512614250183</v>
       </c>
       <c r="H1183" t="n">
         <v>4200</v>
@@ -34705,7 +34705,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871443748474</v>
+        <v>3.25871419906616</v>
       </c>
       <c r="H1184" t="n">
         <v>4900</v>
@@ -34763,7 +34763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1186" t="n">
         <v>17150</v>
@@ -34821,7 +34821,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1188" t="n">
         <v>25900</v>
@@ -34850,7 +34850,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1189" t="n">
         <v>9100</v>
@@ -34879,7 +34879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1190" t="n">
         <v>13650</v>
@@ -35024,7 +35024,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1195" t="n">
         <v>5950</v>
@@ -35111,7 +35111,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1198" t="n">
         <v>18200</v>
@@ -35198,7 +35198,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1201" t="n">
         <v>7700</v>
@@ -35256,7 +35256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1203" t="n">
         <v>10500</v>
@@ -35285,7 +35285,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1204" t="n">
         <v>2450</v>
@@ -35314,7 +35314,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1205" t="n">
         <v>1050</v>
@@ -35488,7 +35488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1211" t="n">
         <v>3150</v>
@@ -35604,7 +35604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1215" t="n">
         <v>6300</v>
@@ -35633,7 +35633,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1216" t="n">
         <v>3500</v>
@@ -68351,6 +68351,35 @@
         <v>1750</v>
       </c>
       <c r="I2344" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2345" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="G2345" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="H2345" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I2345" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249001502991</v>
+        <v>3.03249025344849</v>
       </c>
       <c r="H3" t="n">
         <v>123200</v>
@@ -485,7 +485,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671130180359</v>
+        <v>3.19671106338501</v>
       </c>
       <c r="H4" t="n">
         <v>123200</v>
@@ -572,7 +572,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H7" t="n">
         <v>6650</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058515548706</v>
+        <v>3.17058491706848</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -688,7 +688,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111251831055</v>
+        <v>3.19111275672913</v>
       </c>
       <c r="H11" t="n">
         <v>3150</v>
@@ -746,7 +746,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111251831055</v>
+        <v>3.19111275672913</v>
       </c>
       <c r="H13" t="n">
         <v>1400</v>
@@ -833,7 +833,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H16" t="n">
         <v>17500</v>
@@ -891,7 +891,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389217376709</v>
+        <v>3.26389241218567</v>
       </c>
       <c r="H18" t="n">
         <v>19250</v>
@@ -1065,7 +1065,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>4.01221752166748</v>
+        <v>4.01221799850464</v>
       </c>
       <c r="H24" t="n">
         <v>49000</v>
@@ -1181,7 +1181,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30147075653076</v>
+        <v>4.3014702796936</v>
       </c>
       <c r="H28" t="n">
         <v>25550</v>
@@ -1210,7 +1210,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297533035278</v>
+        <v>4.64297580718994</v>
       </c>
       <c r="H29" t="n">
         <v>126350</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911275863647</v>
       </c>
       <c r="H32" t="n">
         <v>60200</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120553970337</v>
+        <v>7.65120506286621</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1384,7 +1384,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.76478576660156</v>
+        <v>6.7647852897644</v>
       </c>
       <c r="H35" t="n">
         <v>289450</v>
@@ -1471,7 +1471,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830738067627</v>
+        <v>6.08830690383911</v>
       </c>
       <c r="H38" t="n">
         <v>90650</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761827468872</v>
+        <v>6.16761779785156</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1674,7 +1674,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876203536987</v>
+        <v>6.84876251220703</v>
       </c>
       <c r="H45" t="n">
         <v>72450</v>
@@ -1732,7 +1732,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.91407775878906</v>
+        <v>6.9140772819519</v>
       </c>
       <c r="H47" t="n">
         <v>35350</v>
@@ -1761,7 +1761,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939205169678</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H48" t="n">
         <v>25200</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451398849487</v>
+        <v>7.74451351165771</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1906,7 +1906,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>8.02443504333496</v>
+        <v>8.02443599700928</v>
       </c>
       <c r="H53" t="n">
         <v>181300</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435657501221</v>
+        <v>8.30435752868652</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175899505615</v>
+        <v>8.06175804138184</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2109,7 +2109,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866466522217</v>
+        <v>7.19866514205933</v>
       </c>
       <c r="H60" t="n">
         <v>109200</v>
@@ -2167,7 +2167,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061380386353</v>
+        <v>7.38061428070068</v>
       </c>
       <c r="H62" t="n">
         <v>17150</v>
@@ -2225,7 +2225,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>6.64348554611206</v>
+        <v>6.6434850692749</v>
       </c>
       <c r="H64" t="n">
         <v>68950</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.08669567108154</v>
+        <v>7.0866961479187</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2689,7 +2689,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474700927734</v>
+        <v>6.90474653244019</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939205169678</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H81" t="n">
         <v>11200</v>
@@ -2747,7 +2747,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405838012695</v>
+        <v>6.98405790328979</v>
       </c>
       <c r="H82" t="n">
         <v>10500</v>
@@ -2776,7 +2776,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004192352295</v>
+        <v>7.04004240036011</v>
       </c>
       <c r="H83" t="n">
         <v>9100</v>
@@ -2805,7 +2805,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541578292847</v>
+        <v>6.89541530609131</v>
       </c>
       <c r="H84" t="n">
         <v>2800</v>
@@ -2834,7 +2834,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673490524292</v>
+        <v>6.94673442840576</v>
       </c>
       <c r="H85" t="n">
         <v>3500</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145889282227</v>
+        <v>6.74145841598511</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817125320435</v>
+        <v>6.57817077636719</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3356,7 +3356,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287490844727</v>
+        <v>6.44287538528442</v>
       </c>
       <c r="H103" t="n">
         <v>5600</v>
@@ -3414,7 +3414,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.39155626296997</v>
+        <v>6.39155578613281</v>
       </c>
       <c r="H105" t="n">
         <v>2100</v>
@@ -3646,7 +3646,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H113" t="n">
         <v>8400</v>
@@ -3762,7 +3762,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H117" t="n">
         <v>3850</v>
@@ -3849,7 +3849,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561004638672</v>
+        <v>6.19561052322388</v>
       </c>
       <c r="H120" t="n">
         <v>5600</v>
@@ -3907,7 +3907,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.0556492805481</v>
+        <v>6.05564880371094</v>
       </c>
       <c r="H122" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>5.79438877105713</v>
+        <v>5.79438829421997</v>
       </c>
       <c r="H124" t="n">
         <v>13650</v>
@@ -4052,7 +4052,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175100326538</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H127" t="n">
         <v>15750</v>
@@ -4110,7 +4110,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>6.37289428710938</v>
+        <v>6.37289476394653</v>
       </c>
       <c r="H129" t="n">
         <v>52850</v>
@@ -4139,7 +4139,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301103591919</v>
+        <v>5.95301151275635</v>
       </c>
       <c r="H130" t="n">
         <v>22400</v>
@@ -4168,7 +4168,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108127593994</v>
+        <v>5.70108079910278</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175100326538</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H133" t="n">
         <v>16450</v>
@@ -4255,7 +4255,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G134" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H134" t="n">
         <v>16800</v>
@@ -4313,7 +4313,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911228179932</v>
+        <v>5.58911275863647</v>
       </c>
       <c r="H136" t="n">
         <v>8750</v>
@@ -4371,7 +4371,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375875473022</v>
+        <v>5.66375827789307</v>
       </c>
       <c r="H138" t="n">
         <v>3850</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104299545288</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4487,7 +4487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238101959229</v>
+        <v>5.82238054275513</v>
       </c>
       <c r="H142" t="n">
         <v>3850</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104299545288</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H153" t="n">
         <v>7000</v>
@@ -4835,7 +4835,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>5.50513601303101</v>
+        <v>5.50513553619385</v>
       </c>
       <c r="H154" t="n">
         <v>1050</v>
@@ -4893,7 +4893,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517429351807</v>
+        <v>5.36517477035522</v>
       </c>
       <c r="H156" t="n">
         <v>5950</v>
@@ -5038,7 +5038,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5154,7 +5154,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H165" t="n">
         <v>1750</v>
@@ -5183,7 +5183,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651279449463</v>
+        <v>5.34651374816895</v>
       </c>
       <c r="H166" t="n">
         <v>7350</v>
@@ -5212,7 +5212,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253652572632</v>
+        <v>5.26253700256348</v>
       </c>
       <c r="H167" t="n">
         <v>2800</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5444,7 +5444,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H175" t="n">
         <v>17150</v>
@@ -5473,7 +5473,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043087005615</v>
+        <v>5.70043039321899</v>
       </c>
       <c r="H176" t="n">
         <v>3150</v>
@@ -5502,7 +5502,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.78509140014648</v>
+        <v>5.78509092330933</v>
       </c>
       <c r="H177" t="n">
         <v>8050</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.73805809020996</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.73805809020996</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5647,7 +5647,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729030609131</v>
+        <v>6.06729078292847</v>
       </c>
       <c r="H182" t="n">
         <v>62650</v>
@@ -5705,7 +5705,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390405654907</v>
+        <v>5.80390453338623</v>
       </c>
       <c r="H184" t="n">
         <v>16450</v>
@@ -5734,7 +5734,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399147033691</v>
+        <v>5.64399099349976</v>
       </c>
       <c r="H185" t="n">
         <v>4550</v>
@@ -5792,7 +5792,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H187" t="n">
         <v>4900</v>
@@ -5821,7 +5821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>5.54992485046387</v>
+        <v>5.54992437362671</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467184066772</v>
+        <v>5.47467136383057</v>
       </c>
       <c r="H191" t="n">
         <v>2800</v>
@@ -5937,7 +5937,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467184066772</v>
+        <v>5.47467136383057</v>
       </c>
       <c r="H192" t="n">
         <v>5950</v>
@@ -5995,7 +5995,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G194" t="n">
-        <v>5.34297847747803</v>
+        <v>5.34297800064087</v>
       </c>
       <c r="H194" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G195" t="n">
-        <v>5.34297847747803</v>
+        <v>5.34297800064087</v>
       </c>
       <c r="H195" t="n">
         <v>2800</v>
@@ -6053,7 +6053,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891185760498</v>
+        <v>5.24891138076782</v>
       </c>
       <c r="H196" t="n">
         <v>25200</v>
@@ -6169,7 +6169,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H200" t="n">
         <v>5950</v>
@@ -6256,7 +6256,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H203" t="n">
         <v>12950</v>
@@ -6285,7 +6285,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>5.126624584198</v>
+        <v>5.12662506103516</v>
       </c>
       <c r="H204" t="n">
         <v>4900</v>
@@ -6488,7 +6488,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>5.13603210449219</v>
+        <v>5.13603162765503</v>
       </c>
       <c r="H211" t="n">
         <v>4550</v>
@@ -6517,7 +6517,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>5.19247198104858</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H212" t="n">
         <v>28350</v>
@@ -6575,7 +6575,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>5.05137157440186</v>
+        <v>5.05137205123901</v>
       </c>
       <c r="H214" t="n">
         <v>1750</v>
@@ -6604,7 +6604,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>5.13603210449219</v>
+        <v>5.13603162765503</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959222793579</v>
+        <v>5.07959175109863</v>
       </c>
       <c r="H216" t="n">
         <v>2800</v>
@@ -6923,7 +6923,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51048946380615</v>
+        <v>4.51048994064331</v>
       </c>
       <c r="H226" t="n">
         <v>37450</v>
@@ -7155,7 +7155,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>4.20006990432739</v>
+        <v>4.20007038116455</v>
       </c>
       <c r="H234" t="n">
         <v>6650</v>
@@ -7213,7 +7213,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490359306335</v>
+        <v>3.96490383148193</v>
       </c>
       <c r="H236" t="n">
         <v>12600</v>
@@ -7387,7 +7387,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22828960418701</v>
+        <v>4.22829008102417</v>
       </c>
       <c r="H242" t="n">
         <v>7700</v>
@@ -7445,7 +7445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189367294312</v>
+        <v>4.09189319610596</v>
       </c>
       <c r="H244" t="n">
         <v>7700</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312353134155</v>
+        <v>3.99312376976013</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7619,7 +7619,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316723823547</v>
+        <v>3.91316699981689</v>
       </c>
       <c r="H250" t="n">
         <v>16450</v>
@@ -7793,7 +7793,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7880,7 +7880,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.67329740524292</v>
+        <v>3.6732976436615</v>
       </c>
       <c r="H259" t="n">
         <v>77000</v>
@@ -7996,7 +7996,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H263" t="n">
         <v>3850</v>
@@ -8083,7 +8083,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931796073914</v>
+        <v>3.41931772232056</v>
       </c>
       <c r="H266" t="n">
         <v>7350</v>
@@ -8315,7 +8315,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745096206665</v>
+        <v>3.60745120048523</v>
       </c>
       <c r="H274" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.38639450073242</v>
+        <v>3.386394739151</v>
       </c>
       <c r="H281" t="n">
         <v>7000</v>
@@ -8634,7 +8634,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H285" t="n">
         <v>12950</v>
@@ -8924,7 +8924,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092391014099</v>
+        <v>3.71092414855957</v>
       </c>
       <c r="H295" t="n">
         <v>10500</v>
@@ -8953,7 +8953,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H296" t="n">
         <v>39900</v>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H301" t="n">
         <v>67900</v>
@@ -9272,7 +9272,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>2.77496242523193</v>
+        <v>2.77496218681335</v>
       </c>
       <c r="H307" t="n">
         <v>53200</v>
@@ -9301,7 +9301,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>2.77496242523193</v>
+        <v>2.77496218681335</v>
       </c>
       <c r="H308" t="n">
         <v>19250</v>
@@ -9475,7 +9475,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H314" t="n">
         <v>23450</v>
@@ -9504,7 +9504,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H315" t="n">
         <v>8750</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H318" t="n">
         <v>52850</v>
@@ -9620,7 +9620,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179327964783</v>
+        <v>2.11179304122925</v>
       </c>
       <c r="H319" t="n">
         <v>10850</v>
@@ -9736,7 +9736,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H323" t="n">
         <v>16100</v>
@@ -10055,7 +10055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H334" t="n">
         <v>4550</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10316,7 +10316,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478919506073</v>
+        <v>1.79478907585144</v>
       </c>
       <c r="H343" t="n">
         <v>19600</v>
@@ -10374,7 +10374,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G345" t="n">
-        <v>1.68755340576172</v>
+        <v>1.68755328655243</v>
       </c>
       <c r="H345" t="n">
         <v>37800</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10519,7 +10519,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G350" t="n">
-        <v>1.24732196331024</v>
+        <v>1.24732208251953</v>
       </c>
       <c r="H350" t="n">
         <v>36750</v>
@@ -10693,7 +10693,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H356" t="n">
         <v>3850</v>
@@ -10838,7 +10838,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H361" t="n">
         <v>33950</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209755897522</v>
+        <v>1.55209767818451</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -10896,7 +10896,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002796173096</v>
+        <v>1.68002808094025</v>
       </c>
       <c r="H363" t="n">
         <v>22050</v>
@@ -11099,7 +11099,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H370" t="n">
         <v>68600</v>
@@ -11128,7 +11128,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H371" t="n">
         <v>184800</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11273,7 +11273,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.563312292099</v>
+        <v>2.56331253051758</v>
       </c>
       <c r="H376" t="n">
         <v>99050</v>
@@ -11331,7 +11331,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H378" t="n">
         <v>99050</v>
@@ -11389,7 +11389,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733592033386</v>
+        <v>2.73733568191528</v>
       </c>
       <c r="H380" t="n">
         <v>15050</v>
@@ -11505,7 +11505,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H384" t="n">
         <v>5250</v>
@@ -11534,7 +11534,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>2.62915921211243</v>
+        <v>2.62915945053101</v>
       </c>
       <c r="H385" t="n">
         <v>2450</v>
@@ -11563,7 +11563,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H386" t="n">
         <v>10150</v>
@@ -11592,7 +11592,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H387" t="n">
         <v>2450</v>
@@ -11679,7 +11679,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983934402466</v>
+        <v>2.45983958244324</v>
       </c>
       <c r="H390" t="n">
         <v>1750</v>
@@ -11766,7 +11766,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H393" t="n">
         <v>10150</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H402" t="n">
         <v>8750</v>
@@ -12056,7 +12056,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.4081027507782</v>
+        <v>2.40810298919678</v>
       </c>
       <c r="H403" t="n">
         <v>14000</v>
@@ -12230,7 +12230,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047624588013</v>
+        <v>2.37047600746155</v>
       </c>
       <c r="H409" t="n">
         <v>6300</v>
@@ -12346,7 +12346,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.31873989105225</v>
+        <v>2.31873965263367</v>
       </c>
       <c r="H413" t="n">
         <v>10150</v>
@@ -12984,7 +12984,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H435" t="n">
         <v>11200</v>
@@ -13071,7 +13071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H438" t="n">
         <v>5600</v>
@@ -13129,7 +13129,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522323608398</v>
+        <v>2.29522299766541</v>
       </c>
       <c r="H440" t="n">
         <v>8400</v>
@@ -13303,7 +13303,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522323608398</v>
+        <v>2.29522299766541</v>
       </c>
       <c r="H446" t="n">
         <v>2450</v>
@@ -13332,7 +13332,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H447" t="n">
         <v>2800</v>
@@ -13622,7 +13622,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H457" t="n">
         <v>21350</v>
@@ -13680,7 +13680,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H459" t="n">
         <v>12250</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H474" t="n">
         <v>5250</v>
@@ -14376,7 +14376,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658361911774</v>
+        <v>1.95658349990845</v>
       </c>
       <c r="H483" t="n">
         <v>10500</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H485" t="n">
         <v>4550</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H489" t="n">
         <v>21700</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14666,7 +14666,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H493" t="n">
         <v>3500</v>
@@ -14753,7 +14753,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H496" t="n">
         <v>9100</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16290,7 +16290,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H549" t="n">
         <v>1050</v>
@@ -16348,7 +16348,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293643951416</v>
+        <v>2.17293667793274</v>
       </c>
       <c r="H551" t="n">
         <v>140000</v>
@@ -16580,7 +16580,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H559" t="n">
         <v>10150</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16638,7 +16638,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H561" t="n">
         <v>8050</v>
@@ -16812,7 +16812,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H567" t="n">
         <v>9800</v>
@@ -16899,7 +16899,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H570" t="n">
         <v>2100</v>
@@ -16986,7 +16986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H573" t="n">
         <v>7000</v>
@@ -17015,7 +17015,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H574" t="n">
         <v>1750</v>
@@ -17044,7 +17044,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H587" t="n">
         <v>2800</v>
@@ -17421,7 +17421,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315390110016</v>
+        <v>1.77315378189087</v>
       </c>
       <c r="H590" t="n">
         <v>1050</v>
@@ -17595,7 +17595,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G594" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H594" t="n">
         <v>700</v>
@@ -17624,7 +17624,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H595" t="n">
         <v>11200</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H596" t="n">
         <v>1400</v>
@@ -17682,7 +17682,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G597" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H597" t="n">
         <v>2100</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17827,7 +17827,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.66497731208801</v>
+        <v>1.6649774312973</v>
       </c>
       <c r="H602" t="n">
         <v>350</v>
@@ -18030,7 +18030,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H609" t="n">
         <v>8750</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18320,7 +18320,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H619" t="n">
         <v>2800</v>
@@ -18349,7 +18349,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H620" t="n">
         <v>10150</v>
@@ -18407,7 +18407,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>1.50976753234863</v>
+        <v>1.50976765155792</v>
       </c>
       <c r="H622" t="n">
         <v>9800</v>
@@ -18494,7 +18494,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G625" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H625" t="n">
         <v>116200</v>
@@ -18639,7 +18639,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H630" t="n">
         <v>2100</v>
@@ -18668,7 +18668,7 @@
         <v>1.625</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52858090400696</v>
+        <v>1.52858102321625</v>
       </c>
       <c r="H631" t="n">
         <v>7000</v>
@@ -18755,7 +18755,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387750148773</v>
+        <v>1.52387762069702</v>
       </c>
       <c r="H634" t="n">
         <v>2450</v>
@@ -18871,7 +18871,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620740890503</v>
+        <v>1.56620752811432</v>
       </c>
       <c r="H638" t="n">
         <v>10500</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447093486786</v>
+        <v>1.51447105407715</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19190,7 +19190,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H649" t="n">
         <v>56000</v>
@@ -19219,7 +19219,7 @@
         <v>1.625</v>
       </c>
       <c r="G650" t="n">
-        <v>1.52858090400696</v>
+        <v>1.52858102321625</v>
       </c>
       <c r="H650" t="n">
         <v>77700</v>
@@ -19277,7 +19277,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H652" t="n">
         <v>8050</v>
@@ -19335,7 +19335,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565756320953</v>
+        <v>1.49565768241882</v>
       </c>
       <c r="H654" t="n">
         <v>10150</v>
@@ -19364,7 +19364,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H655" t="n">
         <v>5600</v>
@@ -19393,7 +19393,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H656" t="n">
         <v>5950</v>
@@ -19422,7 +19422,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H657" t="n">
         <v>2800</v>
@@ -19712,7 +19712,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775214195251</v>
+        <v>0.954775154590607</v>
       </c>
       <c r="H667" t="n">
         <v>350</v>
@@ -19741,7 +19741,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106610298157</v>
+        <v>0.886106550693512</v>
       </c>
       <c r="H668" t="n">
         <v>2450</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19828,7 +19828,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089210987091</v>
+        <v>0.918089270591736</v>
       </c>
       <c r="H671" t="n">
         <v>3150</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326548576355</v>
+        <v>0.91432648897171</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19915,7 +19915,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H674" t="n">
         <v>16800</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -19973,7 +19973,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291809558868</v>
+        <v>0.978291749954224</v>
       </c>
       <c r="H676" t="n">
         <v>8750</v>
@@ -20002,7 +20002,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H677" t="n">
         <v>700</v>
@@ -20031,7 +20031,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885123729706</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20118,7 +20118,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401778697968</v>
+        <v>0.992401719093323</v>
       </c>
       <c r="H681" t="n">
         <v>3500</v>
@@ -20205,7 +20205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H684" t="n">
         <v>47250</v>
@@ -20292,7 +20292,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G687" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H687" t="n">
         <v>87850</v>
@@ -20350,7 +20350,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>1.28400802612305</v>
+        <v>1.28400790691376</v>
       </c>
       <c r="H689" t="n">
         <v>23450</v>
@@ -20669,7 +20669,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H700" t="n">
         <v>350</v>
@@ -20727,7 +20727,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H702" t="n">
         <v>3150</v>
@@ -20814,7 +20814,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H705" t="n">
         <v>2450</v>
@@ -20959,7 +20959,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.13820481300354</v>
+        <v>1.13820493221283</v>
       </c>
       <c r="H710" t="n">
         <v>1050</v>
@@ -21075,7 +21075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H714" t="n">
         <v>4900</v>
@@ -21104,7 +21104,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H715" t="n">
         <v>128100</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21191,7 +21191,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H718" t="n">
         <v>700</v>
@@ -21220,7 +21220,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H719" t="n">
         <v>1050</v>
@@ -21278,7 +21278,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985458850861</v>
+        <v>1.34985446929932</v>
       </c>
       <c r="H721" t="n">
         <v>7700</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21713,7 +21713,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G736" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H736" t="n">
         <v>9800</v>
@@ -21771,7 +21771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H738" t="n">
         <v>22750</v>
@@ -21800,7 +21800,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G739" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H739" t="n">
         <v>7000</v>
@@ -21829,7 +21829,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G740" t="n">
-        <v>1.28400802612305</v>
+        <v>1.28400790691376</v>
       </c>
       <c r="H740" t="n">
         <v>7350</v>
@@ -22003,7 +22003,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H746" t="n">
         <v>2450</v>
@@ -22235,7 +22235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>1.35455799102783</v>
+        <v>1.35455787181854</v>
       </c>
       <c r="H754" t="n">
         <v>35350</v>
@@ -22322,7 +22322,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H757" t="n">
         <v>8750</v>
@@ -22380,7 +22380,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H759" t="n">
         <v>4900</v>
@@ -22409,7 +22409,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H761" t="n">
         <v>7700</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22525,7 +22525,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H764" t="n">
         <v>1050</v>
@@ -22873,7 +22873,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H776" t="n">
         <v>6300</v>
@@ -23221,7 +23221,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H788" t="n">
         <v>14000</v>
@@ -23250,7 +23250,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.14761161804199</v>
+        <v>1.1476114988327</v>
       </c>
       <c r="H789" t="n">
         <v>5250</v>
@@ -23337,7 +23337,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H792" t="n">
         <v>4900</v>
@@ -23453,7 +23453,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>1.13820481300354</v>
+        <v>1.13820493221283</v>
       </c>
       <c r="H796" t="n">
         <v>1050</v>
@@ -23482,7 +23482,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H797" t="n">
         <v>7700</v>
@@ -23569,7 +23569,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H800" t="n">
         <v>2800</v>
@@ -23598,7 +23598,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H801" t="n">
         <v>5250</v>
@@ -23656,7 +23656,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H803" t="n">
         <v>17850</v>
@@ -23772,7 +23772,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G807" t="n">
-        <v>1.33574461936951</v>
+        <v>1.33574450016022</v>
       </c>
       <c r="H807" t="n">
         <v>15750</v>
@@ -23917,7 +23917,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G812" t="n">
-        <v>1.33574461936951</v>
+        <v>1.33574450016022</v>
       </c>
       <c r="H812" t="n">
         <v>6300</v>
@@ -24004,7 +24004,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H815" t="n">
         <v>2800</v>
@@ -24120,7 +24120,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H819" t="n">
         <v>13650</v>
@@ -24439,7 +24439,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H830" t="n">
         <v>81550</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24497,7 +24497,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>1.35455799102783</v>
+        <v>1.35455787181854</v>
       </c>
       <c r="H832" t="n">
         <v>52500</v>
@@ -24555,7 +24555,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866796016693</v>
+        <v>1.36866784095764</v>
       </c>
       <c r="H834" t="n">
         <v>12600</v>
@@ -24584,7 +24584,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985458850861</v>
+        <v>1.34985446929932</v>
       </c>
       <c r="H835" t="n">
         <v>9100</v>
@@ -24787,7 +24787,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>1.39688789844513</v>
+        <v>1.39688777923584</v>
       </c>
       <c r="H842" t="n">
         <v>23800</v>
@@ -24816,7 +24816,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.38277792930603</v>
+        <v>1.38277781009674</v>
       </c>
       <c r="H843" t="n">
         <v>4550</v>
@@ -24903,7 +24903,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G846" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H846" t="n">
         <v>25900</v>
@@ -24932,7 +24932,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510771751404</v>
+        <v>1.42510759830475</v>
       </c>
       <c r="H847" t="n">
         <v>8750</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -25019,7 +25019,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.38277792930603</v>
+        <v>1.38277781009674</v>
       </c>
       <c r="H850" t="n">
         <v>7350</v>
@@ -25222,7 +25222,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G857" t="n">
-        <v>1.39688789844513</v>
+        <v>1.39688777923584</v>
       </c>
       <c r="H857" t="n">
         <v>7700</v>
@@ -25251,7 +25251,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G858" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H858" t="n">
         <v>24500</v>
@@ -25280,7 +25280,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H873" t="n">
         <v>4550</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25889,7 +25889,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H880" t="n">
         <v>350</v>
@@ -25918,7 +25918,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G881" t="n">
-        <v>1.29811799526215</v>
+        <v>1.29811787605286</v>
       </c>
       <c r="H881" t="n">
         <v>3150</v>
@@ -26034,7 +26034,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H885" t="n">
         <v>8750</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26092,7 +26092,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H887" t="n">
         <v>1400</v>
@@ -26208,7 +26208,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H891" t="n">
         <v>11900</v>
@@ -26295,7 +26295,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H894" t="n">
         <v>14000</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26382,7 +26382,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H897" t="n">
         <v>25200</v>
@@ -26411,7 +26411,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.4909542798996</v>
+        <v>1.49095439910889</v>
       </c>
       <c r="H898" t="n">
         <v>172900</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H899" t="n">
         <v>51450</v>
@@ -26556,7 +26556,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H903" t="n">
         <v>11200</v>
@@ -26701,7 +26701,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G908" t="n">
-        <v>1.68849396705627</v>
+        <v>1.68849384784698</v>
       </c>
       <c r="H908" t="n">
         <v>11200</v>
@@ -26817,7 +26817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>1.69319725036621</v>
+        <v>1.6931973695755</v>
       </c>
       <c r="H912" t="n">
         <v>4900</v>
@@ -26962,7 +26962,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="n">
-        <v>1.67438399791718</v>
+        <v>1.67438387870789</v>
       </c>
       <c r="H917" t="n">
         <v>12950</v>
@@ -26991,7 +26991,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H918" t="n">
         <v>3150</v>
@@ -27049,7 +27049,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662708759308</v>
+        <v>1.87662696838379</v>
       </c>
       <c r="H920" t="n">
         <v>215950</v>
@@ -27078,7 +27078,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H921" t="n">
         <v>352450</v>
@@ -27165,7 +27165,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777024745941</v>
       </c>
       <c r="H924" t="n">
         <v>12250</v>
@@ -27281,7 +27281,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H928" t="n">
         <v>17500</v>
@@ -27310,7 +27310,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946349143982</v>
+        <v>2.06946325302124</v>
       </c>
       <c r="H929" t="n">
         <v>53900</v>
@@ -27484,7 +27484,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H935" t="n">
         <v>40950</v>
@@ -27600,7 +27600,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H939" t="n">
         <v>46200</v>
@@ -27629,7 +27629,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H940" t="n">
         <v>2100</v>
@@ -27716,7 +27716,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293643951416</v>
+        <v>2.17293667793274</v>
       </c>
       <c r="H943" t="n">
         <v>154700</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.02894186973572</v>
+        <v>3.0289421081543</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -27919,7 +27919,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131512641907</v>
+        <v>2.99131536483765</v>
       </c>
       <c r="H950" t="n">
         <v>126350</v>
@@ -28006,7 +28006,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.76555585861206</v>
+        <v>2.76555562019348</v>
       </c>
       <c r="H953" t="n">
         <v>46550</v>
@@ -28151,7 +28151,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>2.70911598205566</v>
+        <v>2.70911574363708</v>
       </c>
       <c r="H958" t="n">
         <v>9100</v>
@@ -28180,7 +28180,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733592033386</v>
+        <v>2.73733568191528</v>
       </c>
       <c r="H959" t="n">
         <v>13300</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.86902904510498</v>
+        <v>2.8690288066864</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28238,7 +28238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H961" t="n">
         <v>175000</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28325,7 +28325,7 @@
         <v>3.25</v>
       </c>
       <c r="G964" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H964" t="n">
         <v>25900</v>
@@ -28354,7 +28354,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.32995462417603</v>
+        <v>3.3299548625946</v>
       </c>
       <c r="H965" t="n">
         <v>91700</v>
@@ -28673,7 +28673,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.32995462417603</v>
+        <v>3.3299548625946</v>
       </c>
       <c r="H976" t="n">
         <v>8050</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.2547013759613</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28876,7 +28876,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.9254686832428</v>
+        <v>2.92546844482422</v>
       </c>
       <c r="H983" t="n">
         <v>78750</v>
@@ -28905,7 +28905,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>3.01953506469727</v>
+        <v>3.01953530311584</v>
       </c>
       <c r="H984" t="n">
         <v>16450</v>
@@ -28992,7 +28992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H987" t="n">
         <v>16800</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.2829213142395</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.2547013759613</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29340,7 +29340,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H999" t="n">
         <v>2800</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29572,7 +29572,7 @@
         <v>3.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1007" t="n">
         <v>15400</v>
@@ -29601,7 +29601,7 @@
         <v>3.25</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1008" t="n">
         <v>6300</v>
@@ -29630,7 +29630,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1009" t="n">
         <v>5250</v>
@@ -29659,7 +29659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H1010" t="n">
         <v>2100</v>
@@ -29688,7 +29688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1011" t="n">
         <v>2100</v>
@@ -29717,7 +29717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1012" t="n">
         <v>3500</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29891,7 +29891,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1018" t="n">
         <v>108150</v>
@@ -29920,7 +29920,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1019" t="n">
         <v>10500</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30036,7 +30036,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1023" t="n">
         <v>6650</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30181,7 +30181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1028" t="n">
         <v>2100</v>
@@ -30239,7 +30239,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1030" t="n">
         <v>6300</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30703,7 +30703,7 @@
         <v>3.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1046" t="n">
         <v>9100</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30848,7 +30848,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.35817456245422</v>
+        <v>3.3581748008728</v>
       </c>
       <c r="H1051" t="n">
         <v>278600</v>
@@ -30935,7 +30935,7 @@
         <v>3.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.05716180801392</v>
+        <v>3.0571620464325</v>
       </c>
       <c r="H1054" t="n">
         <v>47950</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.02894186973572</v>
+        <v>3.0289421081543</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31225,7 +31225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131512641907</v>
+        <v>2.99131536483765</v>
       </c>
       <c r="H1064" t="n">
         <v>9800</v>
@@ -31254,7 +31254,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H1065" t="n">
         <v>95550</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31370,7 +31370,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707487106323</v>
+        <v>3.21707510948181</v>
       </c>
       <c r="H1069" t="n">
         <v>30450</v>
@@ -31515,7 +31515,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.37698793411255</v>
+        <v>3.37698769569397</v>
       </c>
       <c r="H1074" t="n">
         <v>53550</v>
@@ -31544,7 +31544,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630780220032</v>
+        <v>3.54630756378174</v>
       </c>
       <c r="H1075" t="n">
         <v>125650</v>
@@ -31602,7 +31602,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.8473207950592</v>
+        <v>3.84732055664062</v>
       </c>
       <c r="H1077" t="n">
         <v>136500</v>
@@ -31631,7 +31631,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325417518616</v>
+        <v>3.75325393676758</v>
       </c>
       <c r="H1078" t="n">
         <v>55650</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.2829213142395</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -68380,6 +68380,35 @@
         <v>1750</v>
       </c>
       <c r="I2345" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2346" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="G2346" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="H2346" t="n">
+        <v>9450</v>
+      </c>
+      <c r="I2346" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249025344849</v>
+        <v>3.03249001502991</v>
       </c>
       <c r="H3" t="n">
         <v>123200</v>
@@ -659,7 +659,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044350624084</v>
+        <v>3.20044326782227</v>
       </c>
       <c r="H10" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512778282166</v>
+        <v>3.13512825965881</v>
       </c>
       <c r="H12" t="n">
         <v>5950</v>
@@ -775,7 +775,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206506729126</v>
+        <v>3.12206482887268</v>
       </c>
       <c r="H14" t="n">
         <v>8050</v>
@@ -891,7 +891,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389241218567</v>
+        <v>3.26389217376709</v>
       </c>
       <c r="H18" t="n">
         <v>19250</v>
@@ -949,7 +949,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198731422424</v>
+        <v>3.40198707580566</v>
       </c>
       <c r="H20" t="n">
         <v>22050</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.555011510849</v>
+        <v>3.55501127243042</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1007,7 +1007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.881587266922</v>
+        <v>3.88158702850342</v>
       </c>
       <c r="H22" t="n">
         <v>75600</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105966567993</v>
+        <v>3.86105918884277</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1065,7 +1065,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>4.01221799850464</v>
+        <v>4.01221752166748</v>
       </c>
       <c r="H24" t="n">
         <v>49000</v>
@@ -1094,7 +1094,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556401252747</v>
+        <v>3.96556377410889</v>
       </c>
       <c r="H25" t="n">
         <v>38150</v>
@@ -1210,7 +1210,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G29" t="n">
-        <v>4.64297580718994</v>
+        <v>4.64297533035278</v>
       </c>
       <c r="H29" t="n">
         <v>126350</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.58911275863647</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H32" t="n">
         <v>60200</v>
@@ -1326,7 +1326,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>6.39622116088867</v>
+        <v>6.39622068405151</v>
       </c>
       <c r="H33" t="n">
         <v>131600</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120506286621</v>
+        <v>7.65120553970337</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1384,7 +1384,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7647852897644</v>
+        <v>6.76478576660156</v>
       </c>
       <c r="H35" t="n">
         <v>289450</v>
@@ -1413,7 +1413,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>6.41954803466797</v>
+        <v>6.41954851150513</v>
       </c>
       <c r="H36" t="n">
         <v>160650</v>
@@ -1471,7 +1471,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830690383911</v>
+        <v>6.08830738067627</v>
       </c>
       <c r="H38" t="n">
         <v>90650</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761779785156</v>
+        <v>6.16761827468872</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1529,7 +1529,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088701248169</v>
+        <v>6.40088653564453</v>
       </c>
       <c r="H40" t="n">
         <v>82250</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451351165771</v>
+        <v>7.7445125579834</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1906,7 +1906,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>8.02443599700928</v>
+        <v>8.02443504333496</v>
       </c>
       <c r="H53" t="n">
         <v>181300</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750904083252</v>
+        <v>8.95750999450684</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2022,7 +2022,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424030303955</v>
+        <v>8.72424125671387</v>
       </c>
       <c r="H57" t="n">
         <v>169750</v>
@@ -2051,7 +2051,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303840637207</v>
+        <v>8.25303936004639</v>
       </c>
       <c r="H58" t="n">
         <v>105350</v>
@@ -2138,7 +2138,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726802825928</v>
+        <v>7.42726755142212</v>
       </c>
       <c r="H61" t="n">
         <v>87500</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.110023021698</v>
+        <v>7.11002254486084</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2225,7 +2225,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>6.6434850692749</v>
+        <v>6.64348554611206</v>
       </c>
       <c r="H64" t="n">
         <v>68950</v>
@@ -2254,7 +2254,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675428390503</v>
+        <v>6.87675380706787</v>
       </c>
       <c r="H65" t="n">
         <v>99750</v>
@@ -2312,7 +2312,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>7.26864528656006</v>
+        <v>7.2686448097229</v>
       </c>
       <c r="H67" t="n">
         <v>45500</v>
@@ -2341,7 +2341,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>7.52524042129517</v>
+        <v>7.52523994445801</v>
       </c>
       <c r="H68" t="n">
         <v>49000</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252466201782</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2399,7 +2399,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858715057373</v>
+        <v>7.47858762741089</v>
       </c>
       <c r="H70" t="n">
         <v>35350</v>
@@ -2428,7 +2428,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>7.45525979995728</v>
+        <v>7.45526027679443</v>
       </c>
       <c r="H71" t="n">
         <v>10150</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.0866961479187</v>
+        <v>7.08669567108154</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2631,7 +2631,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H78" t="n">
         <v>8750</v>
@@ -2834,7 +2834,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673442840576</v>
+        <v>6.94673538208008</v>
       </c>
       <c r="H85" t="n">
         <v>3500</v>
@@ -2892,7 +2892,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H87" t="n">
         <v>30100</v>
@@ -2921,7 +2921,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H88" t="n">
         <v>7700</v>
@@ -2979,7 +2979,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.96073150634766</v>
+        <v>6.9607310295105</v>
       </c>
       <c r="H90" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.81143951416016</v>
+        <v>6.811439037323</v>
       </c>
       <c r="H93" t="n">
         <v>9800</v>
@@ -3182,7 +3182,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.78344678878784</v>
+        <v>6.783447265625</v>
       </c>
       <c r="H97" t="n">
         <v>5250</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817077636719</v>
+        <v>6.57817029953003</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3269,7 +3269,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419450759888</v>
+        <v>6.49419403076172</v>
       </c>
       <c r="H100" t="n">
         <v>8750</v>
@@ -3298,7 +3298,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094562530518</v>
+        <v>6.19094514846802</v>
       </c>
       <c r="H101" t="n">
         <v>40250</v>
@@ -3327,7 +3327,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H102" t="n">
         <v>24850</v>
@@ -3472,7 +3472,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555191040039</v>
+        <v>6.40555143356323</v>
       </c>
       <c r="H107" t="n">
         <v>2450</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3530,7 +3530,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H109" t="n">
         <v>2800</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3617,7 +3617,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>6.27958679199219</v>
+        <v>6.27958726882935</v>
       </c>
       <c r="H112" t="n">
         <v>18200</v>
@@ -3646,7 +3646,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H113" t="n">
         <v>8400</v>
@@ -3704,7 +3704,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H115" t="n">
         <v>10850</v>
@@ -3733,7 +3733,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694854736328</v>
+        <v>6.17694902420044</v>
       </c>
       <c r="H116" t="n">
         <v>1400</v>
@@ -3762,7 +3762,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H117" t="n">
         <v>3850</v>
@@ -3907,7 +3907,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.05564880371094</v>
+        <v>6.0556492805481</v>
       </c>
       <c r="H122" t="n">
         <v>7000</v>
@@ -3936,7 +3936,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H123" t="n">
         <v>8400</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4110,7 +4110,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>6.37289476394653</v>
+        <v>6.37289428710938</v>
       </c>
       <c r="H129" t="n">
         <v>52850</v>
@@ -4139,7 +4139,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301151275635</v>
+        <v>5.95301103591919</v>
       </c>
       <c r="H130" t="n">
         <v>22400</v>
@@ -4197,7 +4197,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H132" t="n">
         <v>5600</v>
@@ -4255,7 +4255,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G134" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513601303101</v>
       </c>
       <c r="H134" t="n">
         <v>16800</v>
@@ -4284,7 +4284,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245901107788</v>
+        <v>5.54245853424072</v>
       </c>
       <c r="H135" t="n">
         <v>20300</v>
@@ -4313,7 +4313,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>5.58911275863647</v>
+        <v>5.58911228179932</v>
       </c>
       <c r="H136" t="n">
         <v>8750</v>
@@ -4371,7 +4371,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G138" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375875473022</v>
       </c>
       <c r="H138" t="n">
         <v>3850</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81304979324341</v>
+        <v>5.81305074691772</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4458,7 +4458,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H141" t="n">
         <v>1400</v>
@@ -4487,7 +4487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238054275513</v>
+        <v>5.82238101959229</v>
       </c>
       <c r="H142" t="n">
         <v>3850</v>
@@ -4516,7 +4516,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>5.71041202545166</v>
+        <v>5.7104115486145</v>
       </c>
       <c r="H143" t="n">
         <v>1750</v>
@@ -4603,7 +4603,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505802154541</v>
+        <v>5.78505754470825</v>
       </c>
       <c r="H146" t="n">
         <v>8750</v>
@@ -4632,7 +4632,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H147" t="n">
         <v>5600</v>
@@ -4661,7 +4661,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H148" t="n">
         <v>2450</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513601303101</v>
       </c>
       <c r="H153" t="n">
         <v>7000</v>
@@ -4835,7 +4835,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>5.50513553619385</v>
+        <v>5.50513601303101</v>
       </c>
       <c r="H154" t="n">
         <v>1050</v>
@@ -4893,7 +4893,7 @@
         <v>5.75</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36517477035522</v>
+        <v>5.36517429351807</v>
       </c>
       <c r="H156" t="n">
         <v>5950</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052877426147</v>
+        <v>5.29052829742432</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5067,7 +5067,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17855978012085</v>
+        <v>5.17856025695801</v>
       </c>
       <c r="H162" t="n">
         <v>3850</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316701889038</v>
+        <v>5.39316749572754</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5183,7 +5183,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651374816895</v>
+        <v>5.34651327133179</v>
       </c>
       <c r="H166" t="n">
         <v>7350</v>
@@ -5212,7 +5212,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253700256348</v>
+        <v>5.26253652572632</v>
       </c>
       <c r="H167" t="n">
         <v>2800</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5357,7 +5357,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.333571434021</v>
+        <v>5.33357191085815</v>
       </c>
       <c r="H172" t="n">
         <v>4900</v>
@@ -5386,7 +5386,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H173" t="n">
         <v>16100</v>
@@ -5444,7 +5444,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H175" t="n">
         <v>17150</v>
@@ -5473,7 +5473,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043039321899</v>
+        <v>5.70043087005615</v>
       </c>
       <c r="H176" t="n">
         <v>3150</v>
@@ -5560,7 +5560,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212423324585</v>
+        <v>5.83212375640869</v>
       </c>
       <c r="H179" t="n">
         <v>14700</v>
@@ -5618,7 +5618,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102478027344</v>
+        <v>5.69102430343628</v>
       </c>
       <c r="H181" t="n">
         <v>9100</v>
@@ -5647,7 +5647,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729078292847</v>
+        <v>6.06729030609131</v>
       </c>
       <c r="H182" t="n">
         <v>62650</v>
@@ -5705,7 +5705,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390453338623</v>
+        <v>5.80390405654907</v>
       </c>
       <c r="H184" t="n">
         <v>16450</v>
@@ -5734,7 +5734,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399099349976</v>
+        <v>5.64399147033691</v>
       </c>
       <c r="H185" t="n">
         <v>4550</v>
@@ -5792,7 +5792,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H187" t="n">
         <v>4900</v>
@@ -5821,7 +5821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>5.54992437362671</v>
+        <v>5.54992485046387</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H189" t="n">
         <v>2450</v>
@@ -5879,7 +5879,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H190" t="n">
         <v>350</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950529098511</v>
+        <v>5.23950576782227</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6169,7 +6169,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H200" t="n">
         <v>5950</v>
@@ -6198,7 +6198,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H201" t="n">
         <v>32550</v>
@@ -6256,7 +6256,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187902450562</v>
+        <v>5.20187854766846</v>
       </c>
       <c r="H203" t="n">
         <v>12950</v>
@@ -6343,7 +6343,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2206916809082</v>
+        <v>5.22069215774536</v>
       </c>
       <c r="H206" t="n">
         <v>1750</v>
@@ -6488,7 +6488,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H211" t="n">
         <v>4550</v>
@@ -6517,7 +6517,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H212" t="n">
         <v>28350</v>
@@ -6546,7 +6546,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077909469604</v>
+        <v>5.06077861785889</v>
       </c>
       <c r="H213" t="n">
         <v>10150</v>
@@ -6604,7 +6604,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>5.13603162765503</v>
+        <v>5.13603210449219</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959175109863</v>
+        <v>5.07959222793579</v>
       </c>
       <c r="H216" t="n">
         <v>2800</v>
@@ -6749,7 +6749,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.83501863479614</v>
+        <v>4.8350191116333</v>
       </c>
       <c r="H220" t="n">
         <v>10500</v>
@@ -6836,7 +6836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>4.89145851135254</v>
+        <v>4.8914589881897</v>
       </c>
       <c r="H223" t="n">
         <v>4900</v>
@@ -6865,7 +6865,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G224" t="n">
-        <v>4.87264585494995</v>
+        <v>4.87264537811279</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6923,7 +6923,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51048994064331</v>
+        <v>4.51048946380615</v>
       </c>
       <c r="H226" t="n">
         <v>37450</v>
@@ -7039,7 +7039,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985256195068</v>
+        <v>4.59985303878784</v>
       </c>
       <c r="H230" t="n">
         <v>1750</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884052276611</v>
+        <v>4.2988395690918</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7329,7 +7329,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31295013427734</v>
+        <v>4.31294965744019</v>
       </c>
       <c r="H240" t="n">
         <v>9100</v>
@@ -7387,7 +7387,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22829008102417</v>
+        <v>4.22828960418701</v>
       </c>
       <c r="H242" t="n">
         <v>7700</v>
@@ -7503,7 +7503,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H246" t="n">
         <v>1050</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312376976013</v>
+        <v>3.99312329292297</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7590,7 +7590,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842024803162</v>
+        <v>3.98842000961304</v>
       </c>
       <c r="H249" t="n">
         <v>5250</v>
@@ -7648,7 +7648,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147411346436</v>
+        <v>3.78147435188293</v>
       </c>
       <c r="H251" t="n">
         <v>12600</v>
@@ -7793,7 +7793,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7851,7 +7851,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H258" t="n">
         <v>73500</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8083,7 +8083,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931772232056</v>
+        <v>3.41931796073914</v>
       </c>
       <c r="H266" t="n">
         <v>7350</v>
@@ -8286,7 +8286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H273" t="n">
         <v>1050</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.386394739151</v>
+        <v>3.38639450073242</v>
       </c>
       <c r="H281" t="n">
         <v>7000</v>
@@ -8634,7 +8634,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525134086609</v>
+        <v>3.32525157928467</v>
       </c>
       <c r="H285" t="n">
         <v>12950</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H288" t="n">
         <v>17500</v>
@@ -8750,7 +8750,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G289" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H290" t="n">
         <v>8750</v>
@@ -8808,7 +8808,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H291" t="n">
         <v>4900</v>
@@ -8895,7 +8895,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>3.62156081199646</v>
+        <v>3.62156105041504</v>
       </c>
       <c r="H294" t="n">
         <v>1750</v>
@@ -8982,7 +8982,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813133239746</v>
+        <v>3.43813109397888</v>
       </c>
       <c r="H297" t="n">
         <v>29400</v>
@@ -9011,7 +9011,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H298" t="n">
         <v>51800</v>
@@ -9040,7 +9040,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H299" t="n">
         <v>5950</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.95368885993958</v>
+        <v>2.953688621521</v>
       </c>
       <c r="H300" t="n">
         <v>59850</v>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H301" t="n">
         <v>67900</v>
@@ -9156,7 +9156,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H303" t="n">
         <v>22750</v>
@@ -9214,7 +9214,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373208999634</v>
+        <v>2.87373232841492</v>
       </c>
       <c r="H305" t="n">
         <v>23450</v>
@@ -9272,7 +9272,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H307" t="n">
         <v>53200</v>
@@ -9301,7 +9301,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>2.77496218681335</v>
+        <v>2.77496242523193</v>
       </c>
       <c r="H308" t="n">
         <v>19250</v>
@@ -9359,7 +9359,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H310" t="n">
         <v>2450</v>
@@ -9388,7 +9388,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H311" t="n">
         <v>5950</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H313" t="n">
         <v>15400</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H318" t="n">
         <v>52850</v>
@@ -9649,7 +9649,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H320" t="n">
         <v>21000</v>
@@ -9823,7 +9823,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654003143311</v>
+        <v>2.03654026985168</v>
       </c>
       <c r="H326" t="n">
         <v>2450</v>
@@ -9852,7 +9852,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H327" t="n">
         <v>53900</v>
@@ -9881,7 +9881,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H328" t="n">
         <v>4900</v>
@@ -9997,7 +9997,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H332" t="n">
         <v>7700</v>
@@ -10171,7 +10171,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924653053284</v>
+        <v>1.81924641132355</v>
       </c>
       <c r="H338" t="n">
         <v>10150</v>
@@ -10229,7 +10229,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H340" t="n">
         <v>2100</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10345,7 +10345,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80983984470367</v>
+        <v>1.80983996391296</v>
       </c>
       <c r="H344" t="n">
         <v>19600</v>
@@ -10374,7 +10374,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G345" t="n">
-        <v>1.68755328655243</v>
+        <v>1.68755340576172</v>
       </c>
       <c r="H345" t="n">
         <v>37800</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10693,7 +10693,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H356" t="n">
         <v>3850</v>
@@ -10809,7 +10809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H360" t="n">
         <v>9450</v>
@@ -10838,7 +10838,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H361" t="n">
         <v>33950</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209767818451</v>
+        <v>1.55209743976593</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -11012,7 +11012,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928961753845</v>
+        <v>2.38928937911987</v>
       </c>
       <c r="H367" t="n">
         <v>146300</v>
@@ -11070,7 +11070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H369" t="n">
         <v>55650</v>
@@ -11099,7 +11099,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H370" t="n">
         <v>68600</v>
@@ -11128,7 +11128,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H371" t="n">
         <v>184800</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11302,7 +11302,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H377" t="n">
         <v>26600</v>
@@ -11331,7 +11331,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199549674988</v>
+        <v>2.82199573516846</v>
       </c>
       <c r="H378" t="n">
         <v>99050</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975264549255</v>
+        <v>2.61975288391113</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11476,7 +11476,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H383" t="n">
         <v>11200</v>
@@ -11505,7 +11505,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H384" t="n">
         <v>5250</v>
@@ -11534,7 +11534,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>2.62915945053101</v>
+        <v>2.62915921211243</v>
       </c>
       <c r="H385" t="n">
         <v>2450</v>
@@ -11563,7 +11563,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H386" t="n">
         <v>10150</v>
@@ -11592,7 +11592,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H387" t="n">
         <v>2450</v>
@@ -11650,7 +11650,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H389" t="n">
         <v>2800</v>
@@ -11708,7 +11708,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H391" t="n">
         <v>26250</v>
@@ -11737,7 +11737,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G392" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H392" t="n">
         <v>23450</v>
@@ -11766,7 +11766,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.53979587554932</v>
+        <v>2.5397961139679</v>
       </c>
       <c r="H393" t="n">
         <v>10150</v>
@@ -11824,7 +11824,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216960906982</v>
+        <v>2.50216937065125</v>
       </c>
       <c r="H395" t="n">
         <v>4900</v>
@@ -11882,7 +11882,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11940,7 +11940,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750931739807</v>
+        <v>2.41750955581665</v>
       </c>
       <c r="H399" t="n">
         <v>4550</v>
@@ -11969,7 +11969,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H400" t="n">
         <v>3850</v>
@@ -12085,7 +12085,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H404" t="n">
         <v>5950</v>
@@ -12114,7 +12114,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H405" t="n">
         <v>1050</v>
@@ -12143,7 +12143,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H406" t="n">
         <v>7700</v>
@@ -12230,7 +12230,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047600746155</v>
+        <v>2.37047624588013</v>
       </c>
       <c r="H409" t="n">
         <v>6300</v>
@@ -12317,7 +12317,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H412" t="n">
         <v>44100</v>
@@ -12723,7 +12723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056294441223</v>
+        <v>2.21056318283081</v>
       </c>
       <c r="H426" t="n">
         <v>1750</v>
@@ -12752,7 +12752,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H427" t="n">
         <v>21000</v>
@@ -12781,7 +12781,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H428" t="n">
         <v>43400</v>
@@ -12810,7 +12810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H429" t="n">
         <v>20300</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691612243652</v>
+        <v>2.42691588401794</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12897,7 +12897,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106967926025</v>
+        <v>2.36106944084167</v>
       </c>
       <c r="H432" t="n">
         <v>6300</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H439" t="n">
         <v>350</v>
@@ -13129,7 +13129,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H440" t="n">
         <v>8400</v>
@@ -13158,7 +13158,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H441" t="n">
         <v>11200</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H442" t="n">
         <v>4900</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H443" t="n">
         <v>350</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H445" t="n">
         <v>350</v>
@@ -13303,7 +13303,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522299766541</v>
+        <v>2.29522323608398</v>
       </c>
       <c r="H446" t="n">
         <v>2450</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H450" t="n">
         <v>4550</v>
@@ -13477,7 +13477,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H452" t="n">
         <v>10850</v>
@@ -13535,7 +13535,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13530993461609</v>
+        <v>2.13531017303467</v>
       </c>
       <c r="H454" t="n">
         <v>9800</v>
@@ -13622,7 +13622,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H457" t="n">
         <v>21350</v>
@@ -13651,7 +13651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H458" t="n">
         <v>14700</v>
@@ -13680,7 +13680,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H459" t="n">
         <v>12250</v>
@@ -13709,7 +13709,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G460" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H460" t="n">
         <v>5600</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -13999,7 +13999,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H470" t="n">
         <v>3850</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H473" t="n">
         <v>3500</v>
@@ -14115,7 +14115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H474" t="n">
         <v>5250</v>
@@ -14144,7 +14144,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H475" t="n">
         <v>2100</v>
@@ -14173,7 +14173,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H477" t="n">
         <v>25200</v>
@@ -14347,7 +14347,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H482" t="n">
         <v>1400</v>
@@ -14405,7 +14405,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H484" t="n">
         <v>1050</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H485" t="n">
         <v>4550</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14492,7 +14492,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H487" t="n">
         <v>20650</v>
@@ -14521,7 +14521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H488" t="n">
         <v>2450</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H489" t="n">
         <v>21700</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14666,7 +14666,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H493" t="n">
         <v>3500</v>
@@ -14695,7 +14695,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H494" t="n">
         <v>6650</v>
@@ -14724,7 +14724,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H496" t="n">
         <v>9100</v>
@@ -14811,7 +14811,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H498" t="n">
         <v>350</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15072,7 +15072,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H507" t="n">
         <v>19250</v>
@@ -15101,7 +15101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H508" t="n">
         <v>700</v>
@@ -15130,7 +15130,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H509" t="n">
         <v>6650</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H518" t="n">
         <v>10150</v>
@@ -15420,7 +15420,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H519" t="n">
         <v>7000</v>
@@ -15449,7 +15449,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H520" t="n">
         <v>2100</v>
@@ -15478,7 +15478,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H521" t="n">
         <v>1050</v>
@@ -15507,7 +15507,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G522" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H522" t="n">
         <v>9100</v>
@@ -15536,7 +15536,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H523" t="n">
         <v>3150</v>
@@ -15565,7 +15565,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H524" t="n">
         <v>3850</v>
@@ -15594,7 +15594,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434064865112</v>
+        <v>1.75434052944183</v>
       </c>
       <c r="H528" t="n">
         <v>1400</v>
@@ -15710,7 +15710,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H530" t="n">
         <v>3850</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H537" t="n">
         <v>2800</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548392772675</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16319,7 +16319,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H550" t="n">
         <v>141050</v>
@@ -16377,7 +16377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H552" t="n">
         <v>46200</v>
@@ -16406,7 +16406,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G553" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H553" t="n">
         <v>66500</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16551,7 +16551,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H558" t="n">
         <v>9450</v>
@@ -16580,7 +16580,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H559" t="n">
         <v>10150</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16638,7 +16638,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H561" t="n">
         <v>8050</v>
@@ -16667,7 +16667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H562" t="n">
         <v>3500</v>
@@ -16696,7 +16696,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H563" t="n">
         <v>5600</v>
@@ -17102,7 +17102,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H577" t="n">
         <v>4200</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17276,7 +17276,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H583" t="n">
         <v>19950</v>
@@ -17305,7 +17305,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H587" t="n">
         <v>2800</v>
@@ -17421,7 +17421,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H589" t="n">
         <v>2450</v>
@@ -17566,7 +17566,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612059116364</v>
+        <v>1.72612071037292</v>
       </c>
       <c r="H593" t="n">
         <v>4550</v>
@@ -17595,7 +17595,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G594" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H594" t="n">
         <v>700</v>
@@ -17624,7 +17624,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H595" t="n">
         <v>11200</v>
@@ -17682,7 +17682,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G597" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H597" t="n">
         <v>2100</v>
@@ -17740,7 +17740,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H599" t="n">
         <v>5250</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17914,7 +17914,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H605" t="n">
         <v>350</v>
@@ -17943,7 +17943,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H606" t="n">
         <v>12250</v>
@@ -17972,7 +17972,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H607" t="n">
         <v>5950</v>
@@ -18001,7 +18001,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H608" t="n">
         <v>1050</v>
@@ -18059,7 +18059,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379068374634</v>
+        <v>1.68379056453705</v>
       </c>
       <c r="H610" t="n">
         <v>2800</v>
@@ -18088,7 +18088,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H611" t="n">
         <v>11200</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18320,7 +18320,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H619" t="n">
         <v>2800</v>
@@ -18349,7 +18349,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H620" t="n">
         <v>10150</v>
@@ -18378,7 +18378,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5191742181778</v>
+        <v>1.51917433738708</v>
       </c>
       <c r="H621" t="n">
         <v>6300</v>
@@ -18494,7 +18494,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G625" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H625" t="n">
         <v>116200</v>
@@ -18523,7 +18523,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H626" t="n">
         <v>30450</v>
@@ -18639,7 +18639,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031749725342</v>
+        <v>1.58031737804413</v>
       </c>
       <c r="H630" t="n">
         <v>2100</v>
@@ -18668,7 +18668,7 @@
         <v>1.625</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H631" t="n">
         <v>7000</v>
@@ -18726,7 +18726,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091081142426</v>
+        <v>1.57091093063354</v>
       </c>
       <c r="H633" t="n">
         <v>10850</v>
@@ -18929,7 +18929,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H640" t="n">
         <v>8050</v>
@@ -19016,7 +19016,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H643" t="n">
         <v>21000</v>
@@ -19074,7 +19074,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625099658966</v>
+        <v>1.48625111579895</v>
       </c>
       <c r="H646" t="n">
         <v>5600</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447105407715</v>
+        <v>1.51447093486786</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19190,7 +19190,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H649" t="n">
         <v>56000</v>
@@ -19219,7 +19219,7 @@
         <v>1.625</v>
       </c>
       <c r="G650" t="n">
-        <v>1.52858102321625</v>
+        <v>1.52858090400696</v>
       </c>
       <c r="H650" t="n">
         <v>77700</v>
@@ -19248,7 +19248,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803105831146</v>
+        <v>1.45803093910217</v>
       </c>
       <c r="H651" t="n">
         <v>17150</v>
@@ -19277,7 +19277,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H652" t="n">
         <v>8050</v>
@@ -19364,7 +19364,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H655" t="n">
         <v>5600</v>
@@ -19393,7 +19393,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H656" t="n">
         <v>5950</v>
@@ -19422,7 +19422,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H657" t="n">
         <v>2800</v>
@@ -19625,7 +19625,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378746509552</v>
+        <v>0.818378686904907</v>
       </c>
       <c r="H664" t="n">
         <v>10850</v>
@@ -19770,7 +19770,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970512390137</v>
+        <v>0.919970571994781</v>
       </c>
       <c r="H669" t="n">
         <v>2100</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19828,7 +19828,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089270591736</v>
+        <v>0.918089210987091</v>
       </c>
       <c r="H671" t="n">
         <v>3150</v>
@@ -19857,7 +19857,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021162033081</v>
+        <v>0.935021221637726</v>
       </c>
       <c r="H672" t="n">
         <v>5950</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.91432648897171</v>
+        <v>0.914326608181</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19915,7 +19915,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H674" t="n">
         <v>16800</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -20002,7 +20002,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H677" t="n">
         <v>700</v>
@@ -20031,7 +20031,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885123729706</v>
+        <v>0.968885183334351</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20263,7 +20263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H686" t="n">
         <v>6650</v>
@@ -20292,7 +20292,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G687" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H687" t="n">
         <v>87850</v>
@@ -20350,7 +20350,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H689" t="n">
         <v>23450</v>
@@ -20437,7 +20437,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H692" t="n">
         <v>4550</v>
@@ -20611,7 +20611,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H698" t="n">
         <v>3850</v>
@@ -20640,7 +20640,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H699" t="n">
         <v>2450</v>
@@ -20669,7 +20669,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H700" t="n">
         <v>350</v>
@@ -20727,7 +20727,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H702" t="n">
         <v>3150</v>
@@ -20756,7 +20756,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H703" t="n">
         <v>16100</v>
@@ -20785,7 +20785,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H704" t="n">
         <v>2800</v>
@@ -20901,7 +20901,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H708" t="n">
         <v>13650</v>
@@ -20988,7 +20988,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409496307373</v>
+        <v>1.12409508228302</v>
       </c>
       <c r="H711" t="n">
         <v>1750</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H713" t="n">
         <v>2450</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21191,7 +21191,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H718" t="n">
         <v>700</v>
@@ -21220,7 +21220,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H719" t="n">
         <v>1050</v>
@@ -21278,7 +21278,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H721" t="n">
         <v>7700</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21336,7 +21336,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G723" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H723" t="n">
         <v>7350</v>
@@ -21365,7 +21365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H724" t="n">
         <v>21350</v>
@@ -21394,7 +21394,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H727" t="n">
         <v>2450</v>
@@ -21481,7 +21481,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G728" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H728" t="n">
         <v>700</v>
@@ -21510,7 +21510,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H729" t="n">
         <v>1750</v>
@@ -21539,7 +21539,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H731" t="n">
         <v>1050</v>
@@ -21597,7 +21597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G733" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H734" t="n">
         <v>2100</v>
@@ -21684,7 +21684,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875465869904</v>
+        <v>1.20875477790833</v>
       </c>
       <c r="H735" t="n">
         <v>9450</v>
@@ -21713,7 +21713,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G736" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H736" t="n">
         <v>9800</v>
@@ -21742,7 +21742,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G737" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H737" t="n">
         <v>60550</v>
@@ -21800,7 +21800,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G739" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H739" t="n">
         <v>7000</v>
@@ -21829,7 +21829,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G740" t="n">
-        <v>1.28400790691376</v>
+        <v>1.28400802612305</v>
       </c>
       <c r="H740" t="n">
         <v>7350</v>
@@ -21945,7 +21945,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H744" t="n">
         <v>1050</v>
@@ -22003,7 +22003,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H746" t="n">
         <v>2450</v>
@@ -22119,7 +22119,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H750" t="n">
         <v>350</v>
@@ -22148,7 +22148,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H753" t="n">
         <v>8750</v>
@@ -22322,7 +22322,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H757" t="n">
         <v>8750</v>
@@ -22380,7 +22380,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H759" t="n">
         <v>4900</v>
@@ -22409,7 +22409,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H763" t="n">
         <v>700</v>
@@ -22554,7 +22554,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H765" t="n">
         <v>3150</v>
@@ -22612,7 +22612,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H767" t="n">
         <v>350</v>
@@ -22641,7 +22641,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H768" t="n">
         <v>700</v>
@@ -22931,7 +22931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H778" t="n">
         <v>10500</v>
@@ -22960,7 +22960,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G780" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H781" t="n">
         <v>14000</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H787" t="n">
         <v>700</v>
@@ -23250,7 +23250,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.1476114988327</v>
+        <v>1.14761161804199</v>
       </c>
       <c r="H789" t="n">
         <v>5250</v>
@@ -23308,7 +23308,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G791" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H791" t="n">
         <v>3500</v>
@@ -23511,7 +23511,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H798" t="n">
         <v>12600</v>
@@ -23685,7 +23685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H804" t="n">
         <v>12600</v>
@@ -23714,7 +23714,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H805" t="n">
         <v>18550</v>
@@ -23801,7 +23801,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H808" t="n">
         <v>8050</v>
@@ -23888,7 +23888,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H811" t="n">
         <v>12600</v>
@@ -23975,7 +23975,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H814" t="n">
         <v>4550</v>
@@ -24004,7 +24004,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H815" t="n">
         <v>2800</v>
@@ -24033,7 +24033,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G816" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H816" t="n">
         <v>6650</v>
@@ -24062,7 +24062,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H817" t="n">
         <v>8400</v>
@@ -24149,7 +24149,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H820" t="n">
         <v>16100</v>
@@ -24178,7 +24178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H822" t="n">
         <v>3850</v>
@@ -24323,7 +24323,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G826" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H826" t="n">
         <v>700</v>
@@ -24381,7 +24381,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G828" t="n">
-        <v>1.15231490135193</v>
+        <v>1.15231478214264</v>
       </c>
       <c r="H828" t="n">
         <v>3500</v>
@@ -24410,7 +24410,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H829" t="n">
         <v>40600</v>
@@ -24439,7 +24439,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H830" t="n">
         <v>81550</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24584,7 +24584,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985446929932</v>
+        <v>1.34985458850861</v>
       </c>
       <c r="H835" t="n">
         <v>9100</v>
@@ -24642,7 +24642,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H837" t="n">
         <v>60200</v>
@@ -24671,7 +24671,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H838" t="n">
         <v>13300</v>
@@ -24816,7 +24816,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H843" t="n">
         <v>4550</v>
@@ -24845,7 +24845,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H844" t="n">
         <v>129500</v>
@@ -24932,7 +24932,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510759830475</v>
+        <v>1.42510771751404</v>
       </c>
       <c r="H847" t="n">
         <v>8750</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -25019,7 +25019,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.38277781009674</v>
+        <v>1.38277792930603</v>
       </c>
       <c r="H850" t="n">
         <v>7350</v>
@@ -25106,7 +25106,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H853" t="n">
         <v>1750</v>
@@ -25135,7 +25135,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G863" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H863" t="n">
         <v>5250</v>
@@ -25454,7 +25454,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H865" t="n">
         <v>4900</v>
@@ -25570,7 +25570,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H869" t="n">
         <v>3850</v>
@@ -25744,7 +25744,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.33104121685028</v>
+        <v>1.33104133605957</v>
       </c>
       <c r="H875" t="n">
         <v>350</v>
@@ -25773,7 +25773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H876" t="n">
         <v>4200</v>
@@ -25802,7 +25802,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H877" t="n">
         <v>1400</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25860,7 +25860,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H879" t="n">
         <v>3850</v>
@@ -25889,7 +25889,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H880" t="n">
         <v>350</v>
@@ -25918,7 +25918,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G881" t="n">
-        <v>1.29811787605286</v>
+        <v>1.29811799526215</v>
       </c>
       <c r="H881" t="n">
         <v>3150</v>
@@ -26034,7 +26034,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H885" t="n">
         <v>8750</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26092,7 +26092,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989793777466</v>
+        <v>1.26989805698395</v>
       </c>
       <c r="H887" t="n">
         <v>1400</v>
@@ -26150,7 +26150,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H889" t="n">
         <v>6650</v>
@@ -26179,7 +26179,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H890" t="n">
         <v>7350</v>
@@ -26237,7 +26237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H892" t="n">
         <v>7000</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862425327301</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26382,7 +26382,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099774837494</v>
+        <v>1.41099786758423</v>
       </c>
       <c r="H897" t="n">
         <v>25200</v>
@@ -26411,7 +26411,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.49095439910889</v>
+        <v>1.4909542798996</v>
       </c>
       <c r="H898" t="n">
         <v>172900</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H899" t="n">
         <v>51450</v>
@@ -26498,7 +26498,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H901" t="n">
         <v>91700</v>
@@ -26527,7 +26527,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G902" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H902" t="n">
         <v>47600</v>
@@ -26556,7 +26556,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H903" t="n">
         <v>11200</v>
@@ -26643,7 +26643,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H906" t="n">
         <v>33950</v>
@@ -26701,7 +26701,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G908" t="n">
-        <v>1.68849384784698</v>
+        <v>1.68849396705627</v>
       </c>
       <c r="H908" t="n">
         <v>11200</v>
@@ -26817,7 +26817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>1.6931973695755</v>
+        <v>1.69319725036621</v>
       </c>
       <c r="H912" t="n">
         <v>4900</v>
@@ -26846,7 +26846,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G913" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H913" t="n">
         <v>5250</v>
@@ -26904,7 +26904,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -26962,7 +26962,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G917" t="n">
-        <v>1.67438387870789</v>
+        <v>1.67438399791718</v>
       </c>
       <c r="H917" t="n">
         <v>12950</v>
@@ -27020,7 +27020,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H919" t="n">
         <v>9100</v>
@@ -27107,7 +27107,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H922" t="n">
         <v>129500</v>
@@ -27136,7 +27136,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H923" t="n">
         <v>32550</v>
@@ -27165,7 +27165,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.93777024745941</v>
+        <v>1.9377703666687</v>
       </c>
       <c r="H924" t="n">
         <v>12250</v>
@@ -27194,7 +27194,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H925" t="n">
         <v>26950</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27310,7 +27310,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946325302124</v>
+        <v>2.06946349143982</v>
       </c>
       <c r="H929" t="n">
         <v>53900</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H931" t="n">
         <v>264600</v>
@@ -27397,7 +27397,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H932" t="n">
         <v>82600</v>
@@ -27484,7 +27484,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065035820007</v>
+        <v>2.05065011978149</v>
       </c>
       <c r="H935" t="n">
         <v>40950</v>
@@ -27513,7 +27513,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H936" t="n">
         <v>10500</v>
@@ -27542,7 +27542,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H937" t="n">
         <v>8750</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827662467957</v>
+        <v>2.08827686309814</v>
       </c>
       <c r="H941" t="n">
         <v>39900</v>
@@ -27687,7 +27687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.15412330627441</v>
+        <v>2.15412306785583</v>
       </c>
       <c r="H942" t="n">
         <v>109200</v>
@@ -27745,7 +27745,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H944" t="n">
         <v>203700</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -27948,7 +27948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.97250199317932</v>
+        <v>2.9725022315979</v>
       </c>
       <c r="H951" t="n">
         <v>31150</v>
@@ -28006,7 +28006,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.76555562019348</v>
+        <v>2.76555585861206</v>
       </c>
       <c r="H953" t="n">
         <v>46550</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28325,7 +28325,7 @@
         <v>3.25</v>
       </c>
       <c r="G964" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H964" t="n">
         <v>25900</v>
@@ -28383,7 +28383,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H966" t="n">
         <v>283500</v>
@@ -28412,7 +28412,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224118232727</v>
+        <v>3.45224142074585</v>
       </c>
       <c r="H967" t="n">
         <v>114450</v>
@@ -28441,7 +28441,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H968" t="n">
         <v>131250</v>
@@ -28470,7 +28470,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H969" t="n">
         <v>18550</v>
@@ -28557,7 +28557,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H972" t="n">
         <v>29400</v>
@@ -28586,7 +28586,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.31114149093628</v>
+        <v>3.3111412525177</v>
       </c>
       <c r="H973" t="n">
         <v>20300</v>
@@ -28615,7 +28615,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H974" t="n">
         <v>31500</v>
@@ -28644,7 +28644,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H975" t="n">
         <v>25200</v>
@@ -28702,7 +28702,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H977" t="n">
         <v>16450</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470161437988</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28847,7 +28847,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H982" t="n">
         <v>30800</v>
@@ -28876,7 +28876,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.92546844482422</v>
+        <v>2.9254686832428</v>
       </c>
       <c r="H983" t="n">
         <v>78750</v>
@@ -29021,7 +29021,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H988" t="n">
         <v>11550</v>
@@ -29050,7 +29050,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G989" t="n">
-        <v>3.30173468589783</v>
+        <v>3.30173492431641</v>
       </c>
       <c r="H989" t="n">
         <v>43400</v>
@@ -29079,7 +29079,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H990" t="n">
         <v>30450</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470161437988</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29282,7 +29282,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H997" t="n">
         <v>9100</v>
@@ -29311,7 +29311,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29427,7 +29427,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1002" t="n">
         <v>2450</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29485,7 +29485,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1004" t="n">
         <v>2450</v>
@@ -29572,7 +29572,7 @@
         <v>3.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1007" t="n">
         <v>15400</v>
@@ -29601,7 +29601,7 @@
         <v>3.25</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1008" t="n">
         <v>6300</v>
@@ -29630,7 +29630,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1009" t="n">
         <v>5250</v>
@@ -29688,7 +29688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1011" t="n">
         <v>2100</v>
@@ -29717,7 +29717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1012" t="n">
         <v>3500</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29862,7 +29862,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H1017" t="n">
         <v>68950</v>
@@ -29978,7 +29978,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1021" t="n">
         <v>8050</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30094,7 +30094,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1025" t="n">
         <v>9450</v>
@@ -30123,7 +30123,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1026" t="n">
         <v>3500</v>
@@ -30181,7 +30181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063499450684</v>
+        <v>3.16063475608826</v>
       </c>
       <c r="H1028" t="n">
         <v>2100</v>
@@ -30268,7 +30268,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1031" t="n">
         <v>1400</v>
@@ -30297,7 +30297,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1032" t="n">
         <v>14700</v>
@@ -30326,7 +30326,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1033" t="n">
         <v>6300</v>
@@ -30355,7 +30355,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1034" t="n">
         <v>7000</v>
@@ -30413,7 +30413,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1036" t="n">
         <v>45850</v>
@@ -30442,7 +30442,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1037" t="n">
         <v>14700</v>
@@ -30558,7 +30558,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1041" t="n">
         <v>7350</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30616,7 +30616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1043" t="n">
         <v>2800</v>
@@ -30645,7 +30645,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1044" t="n">
         <v>4900</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30703,7 +30703,7 @@
         <v>3.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1046" t="n">
         <v>9100</v>
@@ -30732,7 +30732,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1047" t="n">
         <v>2100</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419535636902</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30819,7 +30819,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1050" t="n">
         <v>34300</v>
@@ -30935,7 +30935,7 @@
         <v>3.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.0571620464325</v>
+        <v>3.05716180801392</v>
       </c>
       <c r="H1054" t="n">
         <v>47950</v>
@@ -30964,7 +30964,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1055" t="n">
         <v>17850</v>
@@ -31022,7 +31022,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1057" t="n">
         <v>9100</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.0289421081543</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31312,7 +31312,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1067" t="n">
         <v>21700</v>
@@ -31341,7 +31341,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1068" t="n">
         <v>42350</v>
@@ -31457,7 +31457,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H1072" t="n">
         <v>64750</v>
@@ -31515,7 +31515,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.37698769569397</v>
+        <v>3.37698793411255</v>
       </c>
       <c r="H1074" t="n">
         <v>53550</v>
@@ -31602,7 +31602,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.84732055664062</v>
+        <v>3.8473207950592</v>
       </c>
       <c r="H1077" t="n">
         <v>136500</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31776,7 +31776,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1083" t="n">
         <v>11200</v>
@@ -31834,7 +31834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1085" t="n">
         <v>15750</v>
@@ -31892,7 +31892,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H1087" t="n">
         <v>16450</v>
@@ -31979,7 +31979,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512093544006</v>
+        <v>3.56512117385864</v>
       </c>
       <c r="H1090" t="n">
         <v>50050</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32066,7 +32066,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562767028809</v>
+        <v>3.71562743186951</v>
       </c>
       <c r="H1093" t="n">
         <v>55300</v>
@@ -32153,7 +32153,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1096" t="n">
         <v>23800</v>
@@ -32269,7 +32269,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H1100" t="n">
         <v>28000</v>
@@ -32298,7 +32298,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046135902405</v>
+        <v>3.48046112060547</v>
       </c>
       <c r="H1101" t="n">
         <v>45850</v>
@@ -32327,7 +32327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1102" t="n">
         <v>26250</v>
@@ -32385,7 +32385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1104" t="n">
         <v>26600</v>
@@ -32414,7 +32414,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.62507843971252</v>
+        <v>3.6250786781311</v>
       </c>
       <c r="H1105" t="n">
         <v>4900</v>
@@ -32646,7 +32646,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1113" t="n">
         <v>40950</v>
@@ -32675,7 +32675,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794931411743</v>
+        <v>3.54794955253601</v>
       </c>
       <c r="H1114" t="n">
         <v>30100</v>
@@ -32762,7 +32762,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1117" t="n">
         <v>9800</v>
@@ -32849,7 +32849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1120" t="n">
         <v>7350</v>
@@ -32878,7 +32878,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436101913452</v>
+        <v>3.64436078071594</v>
       </c>
       <c r="H1121" t="n">
         <v>74200</v>
@@ -32936,7 +32936,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579609870911</v>
+        <v>3.60579633712769</v>
       </c>
       <c r="H1123" t="n">
         <v>43750</v>
@@ -33226,7 +33226,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1133" t="n">
         <v>7000</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1135" t="n">
         <v>3850</v>
@@ -33371,7 +33371,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1138" t="n">
         <v>3850</v>
@@ -33429,7 +33429,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1140" t="n">
         <v>26950</v>
@@ -33516,7 +33516,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1143" t="n">
         <v>6300</v>
@@ -33632,7 +33632,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687258720398</v>
+        <v>3.57687282562256</v>
       </c>
       <c r="H1147" t="n">
         <v>44100</v>
@@ -33661,7 +33661,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1148" t="n">
         <v>15400</v>
@@ -33806,7 +33806,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1153" t="n">
         <v>350</v>
@@ -33893,7 +33893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.3262026309967</v>
+        <v>3.32620239257812</v>
       </c>
       <c r="H1156" t="n">
         <v>3150</v>
@@ -34154,7 +34154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1165" t="n">
         <v>14700</v>
@@ -34270,7 +34270,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31387996673584</v>
+        <v>2.31388020515442</v>
       </c>
       <c r="H1169" t="n">
         <v>30100</v>
@@ -34328,7 +34328,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608028888702</v>
+        <v>1.98608016967773</v>
       </c>
       <c r="H1171" t="n">
         <v>30800</v>
@@ -34415,7 +34415,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029167175293</v>
+        <v>2.41029143333435</v>
       </c>
       <c r="H1174" t="n">
         <v>21350</v>
@@ -34618,7 +34618,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.29727911949158</v>
+        <v>3.297278881073</v>
       </c>
       <c r="H1181" t="n">
         <v>33950</v>
@@ -34647,7 +34647,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1182" t="n">
         <v>13650</v>
@@ -34676,7 +34676,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512614250183</v>
+        <v>3.35512590408325</v>
       </c>
       <c r="H1183" t="n">
         <v>4200</v>
@@ -34705,7 +34705,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871419906616</v>
+        <v>3.25871443748474</v>
       </c>
       <c r="H1184" t="n">
         <v>4900</v>
@@ -34763,7 +34763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1186" t="n">
         <v>17150</v>
@@ -34821,7 +34821,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1188" t="n">
         <v>25900</v>
@@ -34850,7 +34850,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1189" t="n">
         <v>9100</v>
@@ -34879,7 +34879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1190" t="n">
         <v>13650</v>
@@ -35024,7 +35024,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1195" t="n">
         <v>5950</v>
@@ -35111,7 +35111,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1198" t="n">
         <v>18200</v>
@@ -35198,7 +35198,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1201" t="n">
         <v>7700</v>
@@ -35256,7 +35256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1203" t="n">
         <v>10500</v>
@@ -35285,7 +35285,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1204" t="n">
         <v>2450</v>
@@ -35314,7 +35314,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1205" t="n">
         <v>1050</v>
@@ -35488,7 +35488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1211" t="n">
         <v>3150</v>
@@ -35604,7 +35604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1215" t="n">
         <v>6300</v>
@@ -35633,7 +35633,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1216" t="n">
         <v>3500</v>
@@ -68397,7 +68397,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="E2346" t="n">
-        <v>0.579999983310699</v>
+        <v>0.555000007152557</v>
       </c>
       <c r="F2346" t="n">
         <v>0.555000007152557</v>
@@ -68409,6 +68409,35 @@
         <v>9450</v>
       </c>
       <c r="I2346" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2347" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G2347" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="H2347" t="n">
+        <v>19250</v>
+      </c>
+      <c r="I2347" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15378975868225</v>
+        <v>3.15378999710083</v>
       </c>
       <c r="H5" t="n">
         <v>82950</v>
@@ -572,7 +572,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H7" t="n">
         <v>6650</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512825965881</v>
+        <v>3.13512778282166</v>
       </c>
       <c r="H12" t="n">
         <v>5950</v>
@@ -775,7 +775,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206482887268</v>
+        <v>3.12206506729126</v>
       </c>
       <c r="H14" t="n">
         <v>8050</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H15" t="n">
         <v>11200</v>
@@ -833,7 +833,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178200721741</v>
+        <v>3.18178176879883</v>
       </c>
       <c r="H16" t="n">
         <v>17500</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501127243042</v>
+        <v>3.55501103401184</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105918884277</v>
+        <v>3.86105966567993</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615503311157</v>
+        <v>4.23615550994873</v>
       </c>
       <c r="H27" t="n">
         <v>65450</v>
@@ -1181,7 +1181,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3014702796936</v>
+        <v>4.30147075653076</v>
       </c>
       <c r="H28" t="n">
         <v>25550</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1268,7 +1268,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521352767944</v>
+        <v>5.22521305084229</v>
       </c>
       <c r="H31" t="n">
         <v>145250</v>
@@ -1326,7 +1326,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>6.39622068405151</v>
+        <v>6.39622116088867</v>
       </c>
       <c r="H33" t="n">
         <v>131600</v>
@@ -1413,7 +1413,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>6.41954851150513</v>
+        <v>6.41954803466797</v>
       </c>
       <c r="H36" t="n">
         <v>160650</v>
@@ -1442,7 +1442,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092576980591</v>
+        <v>6.26092529296875</v>
       </c>
       <c r="H37" t="n">
         <v>89950</v>
@@ -1471,7 +1471,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830738067627</v>
+        <v>6.08830690383911</v>
       </c>
       <c r="H38" t="n">
         <v>90650</v>
@@ -1645,7 +1645,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401914596558</v>
+        <v>7.12401866912842</v>
       </c>
       <c r="H44" t="n">
         <v>91350</v>
@@ -1703,7 +1703,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080902099609</v>
+        <v>6.68080854415894</v>
       </c>
       <c r="H46" t="n">
         <v>27650</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451303482056</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750999450684</v>
+        <v>8.95750904083252</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2022,7 +2022,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424125671387</v>
+        <v>8.72424030303955</v>
       </c>
       <c r="H57" t="n">
         <v>169750</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2109,7 +2109,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866514205933</v>
+        <v>7.19866466522217</v>
       </c>
       <c r="H60" t="n">
         <v>109200</v>
@@ -2167,7 +2167,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061428070068</v>
+        <v>7.38061380386353</v>
       </c>
       <c r="H62" t="n">
         <v>17150</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002254486084</v>
+        <v>7.11002206802368</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2254,7 +2254,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675380706787</v>
+        <v>6.87675428390503</v>
       </c>
       <c r="H65" t="n">
         <v>99750</v>
@@ -2312,7 +2312,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>7.2686448097229</v>
+        <v>7.26864528656006</v>
       </c>
       <c r="H67" t="n">
         <v>45500</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252466201782</v>
+        <v>7.70252513885498</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2428,7 +2428,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>7.45526027679443</v>
+        <v>7.45525979995728</v>
       </c>
       <c r="H71" t="n">
         <v>10150</v>
@@ -2457,7 +2457,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.57189416885376</v>
+        <v>7.57189464569092</v>
       </c>
       <c r="H72" t="n">
         <v>15750</v>
@@ -2486,7 +2486,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059490203857</v>
+        <v>7.45059442520142</v>
       </c>
       <c r="H73" t="n">
         <v>20650</v>
@@ -2515,7 +2515,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H74" t="n">
         <v>15750</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.08669567108154</v>
+        <v>7.0866961479187</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2602,7 +2602,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H77" t="n">
         <v>12600</v>
@@ -2631,7 +2631,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H78" t="n">
         <v>8750</v>
@@ -2747,7 +2747,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405790328979</v>
+        <v>6.98405838012695</v>
       </c>
       <c r="H82" t="n">
         <v>10500</v>
@@ -2776,7 +2776,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004240036011</v>
+        <v>7.04004192352295</v>
       </c>
       <c r="H83" t="n">
         <v>9100</v>
@@ -2892,7 +2892,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H87" t="n">
         <v>30100</v>
@@ -2921,7 +2921,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>7.0913610458374</v>
+        <v>7.09136152267456</v>
       </c>
       <c r="H88" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H89" t="n">
         <v>7350</v>
@@ -3066,7 +3066,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.811439037323</v>
+        <v>6.81143951416016</v>
       </c>
       <c r="H93" t="n">
         <v>9800</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145841598511</v>
+        <v>6.74145889282227</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3182,7 +3182,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.783447265625</v>
+        <v>6.78344678878784</v>
       </c>
       <c r="H97" t="n">
         <v>5250</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817029953003</v>
+        <v>6.57817077636719</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3298,7 +3298,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094514846802</v>
+        <v>6.19094562530518</v>
       </c>
       <c r="H101" t="n">
         <v>40250</v>
@@ -3414,7 +3414,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.39155578613281</v>
+        <v>6.39155626296997</v>
       </c>
       <c r="H105" t="n">
         <v>2100</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3617,7 +3617,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>6.27958726882935</v>
+        <v>6.27958679199219</v>
       </c>
       <c r="H112" t="n">
         <v>18200</v>
@@ -3646,7 +3646,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H113" t="n">
         <v>8400</v>
@@ -3675,7 +3675,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G114" t="n">
-        <v>6.3075795173645</v>
+        <v>6.30757999420166</v>
       </c>
       <c r="H114" t="n">
         <v>4550</v>
@@ -3704,7 +3704,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H115" t="n">
         <v>10850</v>
@@ -3733,7 +3733,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.17694902420044</v>
+        <v>6.17694854736328</v>
       </c>
       <c r="H116" t="n">
         <v>1400</v>
@@ -3762,7 +3762,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H117" t="n">
         <v>3850</v>
@@ -3791,7 +3791,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962554931641</v>
+        <v>6.13962602615356</v>
       </c>
       <c r="H118" t="n">
         <v>1750</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828704833984</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561052322388</v>
+        <v>6.19561004638672</v>
       </c>
       <c r="H120" t="n">
         <v>5600</v>
@@ -3907,7 +3907,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.0556492805481</v>
+        <v>6.05564880371094</v>
       </c>
       <c r="H122" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>5.79438829421997</v>
+        <v>5.79438877105713</v>
       </c>
       <c r="H124" t="n">
         <v>13650</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4168,7 +4168,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108079910278</v>
+        <v>5.7010817527771</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305074691772</v>
+        <v>5.81305027008057</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4516,7 +4516,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>5.7104115486145</v>
+        <v>5.71041202545166</v>
       </c>
       <c r="H143" t="n">
         <v>1750</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4574,7 +4574,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.98100328445435</v>
+        <v>5.9810037612915</v>
       </c>
       <c r="H145" t="n">
         <v>39200</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052829742432</v>
+        <v>5.29052925109863</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5038,7 +5038,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5096,7 +5096,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789052963257</v>
+        <v>5.18789100646973</v>
       </c>
       <c r="H163" t="n">
         <v>1400</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5154,7 +5154,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718204498291</v>
+        <v>5.33718252182007</v>
       </c>
       <c r="H165" t="n">
         <v>1750</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -68438,6 +68438,35 @@
         <v>19250</v>
       </c>
       <c r="I2347" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2348" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="G2348" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="H2348" t="n">
+        <v>6650</v>
+      </c>
+      <c r="I2348" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15378999710083</v>
+        <v>3.15378975868225</v>
       </c>
       <c r="H5" t="n">
         <v>82950</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058515548706</v>
+        <v>3.17058491706848</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.06981301307678</v>
+        <v>3.0698127746582</v>
       </c>
       <c r="H15" t="n">
         <v>11200</v>
@@ -862,7 +862,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G17" t="n">
-        <v>3.18924641609192</v>
+        <v>3.1892466545105</v>
       </c>
       <c r="H17" t="n">
         <v>2450</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501103401184</v>
+        <v>3.55501127243042</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1007,7 +1007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.88158702850342</v>
+        <v>3.881587266922</v>
       </c>
       <c r="H22" t="n">
         <v>75600</v>
@@ -1094,7 +1094,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556377410889</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H25" t="n">
         <v>38150</v>
@@ -1123,7 +1123,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939910888672</v>
+        <v>4.07939958572388</v>
       </c>
       <c r="H26" t="n">
         <v>28700</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615550994873</v>
+        <v>4.23615503311157</v>
       </c>
       <c r="H27" t="n">
         <v>65450</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1268,7 +1268,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521305084229</v>
+        <v>5.22521352767944</v>
       </c>
       <c r="H31" t="n">
         <v>145250</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120553970337</v>
+        <v>7.65120601654053</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1442,7 +1442,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092529296875</v>
+        <v>6.26092576980591</v>
       </c>
       <c r="H37" t="n">
         <v>89950</v>
@@ -1703,7 +1703,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080854415894</v>
+        <v>6.68080902099609</v>
       </c>
       <c r="H46" t="n">
         <v>27650</v>
@@ -1732,7 +1732,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9140772819519</v>
+        <v>6.91407775878906</v>
       </c>
       <c r="H47" t="n">
         <v>35350</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435657501221</v>
+        <v>8.30435752868652</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750904083252</v>
+        <v>8.95750999450684</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175899505615</v>
+        <v>8.06175804138184</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002206802368</v>
+        <v>7.11002254486084</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2312,7 +2312,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>7.26864528656006</v>
+        <v>7.2686448097229</v>
       </c>
       <c r="H67" t="n">
         <v>45500</v>
@@ -2341,7 +2341,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>7.52523994445801</v>
+        <v>7.52524042129517</v>
       </c>
       <c r="H68" t="n">
         <v>49000</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252466201782</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2457,7 +2457,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.57189464569092</v>
+        <v>7.57189416885376</v>
       </c>
       <c r="H72" t="n">
         <v>15750</v>
@@ -2486,7 +2486,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059442520142</v>
+        <v>7.45059490203857</v>
       </c>
       <c r="H73" t="n">
         <v>20650</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.0866961479187</v>
+        <v>7.08669567108154</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2805,7 +2805,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541530609131</v>
+        <v>6.89541578292847</v>
       </c>
       <c r="H84" t="n">
         <v>2800</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145889282227</v>
+        <v>6.74145841598511</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3182,7 +3182,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.78344678878784</v>
+        <v>6.783447265625</v>
       </c>
       <c r="H97" t="n">
         <v>5250</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817077636719</v>
+        <v>6.57817125320435</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3617,7 +3617,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>6.27958679199219</v>
+        <v>6.27958726882935</v>
       </c>
       <c r="H112" t="n">
         <v>18200</v>
@@ -3646,7 +3646,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H113" t="n">
         <v>8400</v>
@@ -3675,7 +3675,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G114" t="n">
-        <v>6.30757999420166</v>
+        <v>6.3075795173645</v>
       </c>
       <c r="H114" t="n">
         <v>4550</v>
@@ -3762,7 +3762,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159502029419</v>
+        <v>6.25159454345703</v>
       </c>
       <c r="H117" t="n">
         <v>3850</v>
@@ -3791,7 +3791,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962602615356</v>
+        <v>6.13962554931641</v>
       </c>
       <c r="H118" t="n">
         <v>1750</v>
@@ -3878,7 +3878,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G121" t="n">
-        <v>6.14895677566528</v>
+        <v>6.14895725250244</v>
       </c>
       <c r="H121" t="n">
         <v>3150</v>
@@ -3907,7 +3907,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.05564880371094</v>
+        <v>6.0556492805481</v>
       </c>
       <c r="H122" t="n">
         <v>7000</v>
@@ -3936,7 +3936,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H123" t="n">
         <v>8400</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4168,7 +4168,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.7010817527771</v>
+        <v>5.70108127593994</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4197,7 +4197,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H132" t="n">
         <v>5600</v>
@@ -4458,7 +4458,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H141" t="n">
         <v>1400</v>
@@ -4516,7 +4516,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>5.71041202545166</v>
+        <v>5.71041250228882</v>
       </c>
       <c r="H143" t="n">
         <v>1750</v>
@@ -4603,7 +4603,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.78505754470825</v>
+        <v>5.78505802154541</v>
       </c>
       <c r="H146" t="n">
         <v>8750</v>
@@ -4632,7 +4632,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H147" t="n">
         <v>5600</v>
@@ -4661,7 +4661,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H148" t="n">
         <v>2450</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052925109863</v>
+        <v>5.29052877426147</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -5270,7 +5270,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H170" t="n">
         <v>1050</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5357,7 +5357,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.33357191085815</v>
+        <v>5.333571434021</v>
       </c>
       <c r="H172" t="n">
         <v>4900</v>
@@ -5386,7 +5386,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H173" t="n">
         <v>16100</v>
@@ -5415,7 +5415,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>5.45585823059082</v>
+        <v>5.45585870742798</v>
       </c>
       <c r="H174" t="n">
         <v>8750</v>
@@ -5473,7 +5473,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043087005615</v>
+        <v>5.70043134689331</v>
       </c>
       <c r="H176" t="n">
         <v>3150</v>
@@ -5560,7 +5560,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212375640869</v>
+        <v>5.83212423324585</v>
       </c>
       <c r="H179" t="n">
         <v>14700</v>
@@ -5618,7 +5618,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="n">
         <v>9100</v>
@@ -5908,7 +5908,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H191" t="n">
         <v>2800</v>
@@ -5937,7 +5937,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467136383057</v>
+        <v>5.47467184066772</v>
       </c>
       <c r="H192" t="n">
         <v>5950</v>
@@ -5966,7 +5966,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>5.45585823059082</v>
+        <v>5.45585870742798</v>
       </c>
       <c r="H193" t="n">
         <v>4550</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950576782227</v>
+        <v>5.23950529098511</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6198,7 +6198,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H201" t="n">
         <v>32550</v>
@@ -6227,7 +6227,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G202" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H202" t="n">
         <v>14350</v>
@@ -6314,7 +6314,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28653812408447</v>
+        <v>5.28653860092163</v>
       </c>
       <c r="H205" t="n">
         <v>700</v>
@@ -6372,7 +6372,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H207" t="n">
         <v>8050</v>
@@ -6430,7 +6430,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721897125244</v>
+        <v>5.11721849441528</v>
       </c>
       <c r="H209" t="n">
         <v>5600</v>
@@ -6546,7 +6546,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077861785889</v>
+        <v>5.06077909469604</v>
       </c>
       <c r="H213" t="n">
         <v>10150</v>
@@ -6720,7 +6720,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>4.97611904144287</v>
+        <v>4.97611856460571</v>
       </c>
       <c r="H219" t="n">
         <v>5950</v>
@@ -6778,7 +6778,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442567825317</v>
+        <v>4.84442520141602</v>
       </c>
       <c r="H221" t="n">
         <v>4550</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H227" t="n">
         <v>8400</v>
@@ -7097,7 +7097,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472995758057</v>
+        <v>4.28472948074341</v>
       </c>
       <c r="H232" t="n">
         <v>4900</v>
@@ -7213,7 +7213,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490383148193</v>
+        <v>3.96490359306335</v>
       </c>
       <c r="H236" t="n">
         <v>12600</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.2988395690918</v>
+        <v>4.29884004592896</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H238" t="n">
         <v>147350</v>
@@ -7329,7 +7329,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31294965744019</v>
+        <v>4.31295013427734</v>
       </c>
       <c r="H240" t="n">
         <v>9100</v>
@@ -7416,7 +7416,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.185959815979</v>
+        <v>4.18596029281616</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7445,7 +7445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189319610596</v>
+        <v>4.09189367294312</v>
       </c>
       <c r="H244" t="n">
         <v>7700</v>
@@ -7474,7 +7474,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.0636739730835</v>
+        <v>4.06367349624634</v>
       </c>
       <c r="H245" t="n">
         <v>4550</v>
@@ -7503,7 +7503,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="n">
         <v>1050</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312353134155</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7590,7 +7590,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842000961304</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="n">
         <v>5250</v>
@@ -7619,7 +7619,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316699981689</v>
+        <v>3.91316723823547</v>
       </c>
       <c r="H250" t="n">
         <v>16450</v>
@@ -7648,7 +7648,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147435188293</v>
+        <v>3.78147411346436</v>
       </c>
       <c r="H251" t="n">
         <v>12600</v>
@@ -7677,7 +7677,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G252" t="n">
-        <v>3.74855065345764</v>
+        <v>3.74855041503906</v>
       </c>
       <c r="H252" t="n">
         <v>15750</v>
@@ -7851,7 +7851,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="n">
         <v>73500</v>
@@ -7880,7 +7880,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="n">
         <v>77000</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8083,7 +8083,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931796073914</v>
+        <v>3.41931819915771</v>
       </c>
       <c r="H266" t="n">
         <v>7350</v>
@@ -8170,7 +8170,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H269" t="n">
         <v>3500</v>
@@ -8199,7 +8199,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.41461491584778</v>
+        <v>3.4146146774292</v>
       </c>
       <c r="H270" t="n">
         <v>7350</v>
@@ -8286,7 +8286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="n">
         <v>1050</v>
@@ -8315,7 +8315,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745120048523</v>
+        <v>3.60745096206665</v>
       </c>
       <c r="H274" t="n">
         <v>3500</v>
@@ -8663,7 +8663,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H286" t="n">
         <v>10500</v>
@@ -8692,7 +8692,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169145584106</v>
+        <v>3.38169169425964</v>
       </c>
       <c r="H287" t="n">
         <v>2100</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="n">
         <v>17500</v>
@@ -8808,7 +8808,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="n">
         <v>4900</v>
@@ -8924,7 +8924,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092414855957</v>
+        <v>3.71092391014099</v>
       </c>
       <c r="H295" t="n">
         <v>10500</v>
@@ -8982,7 +8982,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="n">
         <v>29400</v>
@@ -9011,7 +9011,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H298" t="n">
         <v>51800</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="n">
         <v>59850</v>
@@ -9156,7 +9156,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H303" t="n">
         <v>22750</v>
@@ -9214,7 +9214,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="n">
         <v>23450</v>
@@ -9243,7 +9243,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>3.01012873649597</v>
+        <v>3.01012849807739</v>
       </c>
       <c r="H306" t="n">
         <v>54950</v>
@@ -9388,7 +9388,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="n">
         <v>5950</v>
@@ -9417,7 +9417,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153270721436</v>
+        <v>2.59153246879578</v>
       </c>
       <c r="H312" t="n">
         <v>6650</v>
@@ -9475,7 +9475,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H314" t="n">
         <v>23450</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H316" t="n">
         <v>5600</v>
@@ -9620,7 +9620,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179304122925</v>
+        <v>2.11179327964783</v>
       </c>
       <c r="H319" t="n">
         <v>10850</v>
@@ -9678,7 +9678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H321" t="n">
         <v>5250</v>
@@ -9707,7 +9707,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H322" t="n">
         <v>3150</v>
@@ -9736,7 +9736,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H323" t="n">
         <v>16100</v>
@@ -9794,7 +9794,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950672149658</v>
+        <v>1.98950695991516</v>
       </c>
       <c r="H325" t="n">
         <v>2800</v>
@@ -9823,7 +9823,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654026985168</v>
+        <v>2.03654003143311</v>
       </c>
       <c r="H326" t="n">
         <v>2450</v>
@@ -9852,7 +9852,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H327" t="n">
         <v>53900</v>
@@ -9881,7 +9881,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H328" t="n">
         <v>4900</v>
@@ -9968,7 +9968,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.0929799079895</v>
+        <v>2.09298014640808</v>
       </c>
       <c r="H331" t="n">
         <v>10150</v>
@@ -10055,7 +10055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H334" t="n">
         <v>4550</v>
@@ -10171,7 +10171,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924641132355</v>
+        <v>1.81924653053284</v>
       </c>
       <c r="H338" t="n">
         <v>10150</v>
@@ -10229,7 +10229,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H340" t="n">
         <v>2100</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10316,7 +10316,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478907585144</v>
+        <v>1.79478919506073</v>
       </c>
       <c r="H343" t="n">
         <v>19600</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10461,7 +10461,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G348" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H348" t="n">
         <v>11550</v>
@@ -10490,7 +10490,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G349" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H349" t="n">
         <v>21700</v>
@@ -10548,7 +10548,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H351" t="n">
         <v>6650</v>
@@ -10606,7 +10606,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G353" t="n">
-        <v>1.29623663425446</v>
+        <v>1.29623651504517</v>
       </c>
       <c r="H353" t="n">
         <v>9450</v>
@@ -10780,7 +10780,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H359" t="n">
         <v>9100</v>
@@ -10809,7 +10809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="n">
         <v>9450</v>
@@ -10896,7 +10896,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002808094025</v>
+        <v>1.68002796173096</v>
       </c>
       <c r="H363" t="n">
         <v>22050</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11389,7 +11389,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H380" t="n">
         <v>15050</v>
@@ -11418,7 +11418,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089556694031</v>
+        <v>2.68089580535889</v>
       </c>
       <c r="H381" t="n">
         <v>12250</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975288391113</v>
+        <v>2.61975264549255</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11476,7 +11476,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="n">
         <v>11200</v>
@@ -11708,7 +11708,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="n">
         <v>26250</v>
@@ -11853,7 +11853,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860948562622</v>
+        <v>2.55860924720764</v>
       </c>
       <c r="H396" t="n">
         <v>2100</v>
@@ -11969,7 +11969,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H400" t="n">
         <v>3850</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H402" t="n">
         <v>8750</v>
@@ -12056,7 +12056,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.40810298919678</v>
+        <v>2.4081027507782</v>
       </c>
       <c r="H403" t="n">
         <v>14000</v>
@@ -12317,7 +12317,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H412" t="n">
         <v>44100</v>
@@ -12752,7 +12752,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="n">
         <v>21000</v>
@@ -12781,7 +12781,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="n">
         <v>43400</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691588401794</v>
+        <v>2.42691612243652</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12897,7 +12897,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106944084167</v>
+        <v>2.36106967926025</v>
       </c>
       <c r="H432" t="n">
         <v>6300</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -12984,7 +12984,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H435" t="n">
         <v>11200</v>
@@ -13042,7 +13042,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H437" t="n">
         <v>2800</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="n">
         <v>350</v>
@@ -13158,7 +13158,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878335952759</v>
+        <v>2.23878312110901</v>
       </c>
       <c r="H441" t="n">
         <v>11200</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="n">
         <v>350</v>
@@ -13390,7 +13390,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H449" t="n">
         <v>2800</v>
@@ -13535,7 +13535,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13531017303467</v>
+        <v>2.13530993461609</v>
       </c>
       <c r="H454" t="n">
         <v>9800</v>
@@ -13651,7 +13651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="n">
         <v>14700</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H461" t="n">
         <v>1750</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13941,7 +13941,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G468" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H468" t="n">
         <v>7000</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H473" t="n">
         <v>3500</v>
@@ -14144,7 +14144,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H475" t="n">
         <v>2100</v>
@@ -14173,7 +14173,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H478" t="n">
         <v>6650</v>
@@ -14260,7 +14260,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H479" t="n">
         <v>700</v>
@@ -14289,7 +14289,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H480" t="n">
         <v>5600</v>
@@ -14318,7 +14318,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H481" t="n">
         <v>1400</v>
@@ -14347,7 +14347,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="n">
         <v>1400</v>
@@ -14376,7 +14376,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658349990845</v>
+        <v>1.95658361911774</v>
       </c>
       <c r="H483" t="n">
         <v>10500</v>
@@ -14405,7 +14405,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="n">
         <v>1050</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14492,7 +14492,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H487" t="n">
         <v>20650</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15101,7 +15101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H508" t="n">
         <v>700</v>
@@ -15130,7 +15130,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H509" t="n">
         <v>6650</v>
@@ -15217,7 +15217,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G512" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H512" t="n">
         <v>700</v>
@@ -15391,7 +15391,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H518" t="n">
         <v>10150</v>
@@ -15420,7 +15420,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H519" t="n">
         <v>7000</v>
@@ -15449,7 +15449,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082411289215</v>
+        <v>1.73082399368286</v>
       </c>
       <c r="H520" t="n">
         <v>2100</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H550" t="n">
         <v>141050</v>
@@ -16348,7 +16348,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H551" t="n">
         <v>140000</v>
@@ -16377,7 +16377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="n">
         <v>46200</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539699077606</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16551,7 +16551,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H558" t="n">
         <v>9450</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16667,7 +16667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H562" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G565" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H565" t="n">
         <v>4200</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17537,7 +17537,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.70730745792389</v>
+        <v>1.7073073387146</v>
       </c>
       <c r="H592" t="n">
         <v>2100</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H596" t="n">
         <v>1400</v>
@@ -17740,7 +17740,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H599" t="n">
         <v>5250</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17827,7 +17827,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.6649774312973</v>
+        <v>1.66497731208801</v>
       </c>
       <c r="H602" t="n">
         <v>350</v>
@@ -17914,7 +17914,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H605" t="n">
         <v>350</v>
@@ -17972,7 +17972,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H607" t="n">
         <v>5950</v>
@@ -18001,7 +18001,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H608" t="n">
         <v>1050</v>
@@ -18030,7 +18030,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H609" t="n">
         <v>8750</v>
@@ -18059,7 +18059,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379056453705</v>
+        <v>1.68379068374634</v>
       </c>
       <c r="H610" t="n">
         <v>2800</v>
@@ -18088,7 +18088,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H611" t="n">
         <v>11200</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18378,7 +18378,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.51917433738708</v>
+        <v>1.5191742181778</v>
       </c>
       <c r="H621" t="n">
         <v>6300</v>
@@ -18523,7 +18523,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H626" t="n">
         <v>30450</v>
@@ -18552,7 +18552,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264752388</v>
+        <v>1.62264740467072</v>
       </c>
       <c r="H627" t="n">
         <v>23800</v>
@@ -18726,7 +18726,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091093063354</v>
+        <v>1.57091081142426</v>
       </c>
       <c r="H633" t="n">
         <v>10850</v>
@@ -18842,7 +18842,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798758983612</v>
+        <v>1.53798747062683</v>
       </c>
       <c r="H637" t="n">
         <v>5950</v>
@@ -18929,7 +18929,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H640" t="n">
         <v>8050</v>
@@ -18958,7 +18958,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H641" t="n">
         <v>3150</v>
@@ -18987,7 +18987,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G642" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H642" t="n">
         <v>3500</v>
@@ -19016,7 +19016,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H643" t="n">
         <v>21000</v>
@@ -19045,7 +19045,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G644" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H644" t="n">
         <v>5950</v>
@@ -19074,7 +19074,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625111579895</v>
+        <v>1.48625099658966</v>
       </c>
       <c r="H646" t="n">
         <v>5600</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447093486786</v>
+        <v>1.51447081565857</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19161,7 +19161,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G648" t="n">
-        <v>1.50506436824799</v>
+        <v>1.5050642490387</v>
       </c>
       <c r="H648" t="n">
         <v>2100</v>
@@ -19248,7 +19248,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803093910217</v>
+        <v>1.45803105831146</v>
       </c>
       <c r="H651" t="n">
         <v>17150</v>
@@ -19335,7 +19335,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565768241882</v>
+        <v>1.49565756320953</v>
       </c>
       <c r="H654" t="n">
         <v>10150</v>
@@ -19712,7 +19712,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775154590607</v>
+        <v>0.954775214195251</v>
       </c>
       <c r="H667" t="n">
         <v>350</v>
@@ -19770,7 +19770,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970571994781</v>
+        <v>0.919970512390137</v>
       </c>
       <c r="H669" t="n">
         <v>2100</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -19973,7 +19973,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291749954224</v>
+        <v>0.978291809558868</v>
       </c>
       <c r="H676" t="n">
         <v>8750</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20118,7 +20118,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401719093323</v>
+        <v>0.992401659488678</v>
       </c>
       <c r="H681" t="n">
         <v>3500</v>
@@ -20147,7 +20147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591849327087</v>
+        <v>1.01591837406158</v>
       </c>
       <c r="H682" t="n">
         <v>12950</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20495,7 +20495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H694" t="n">
         <v>9800</v>
@@ -20524,7 +20524,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H696" t="n">
         <v>18200</v>
@@ -20582,7 +20582,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H697" t="n">
         <v>9800</v>
@@ -20640,7 +20640,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="n">
         <v>2450</v>
@@ -20785,7 +20785,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H704" t="n">
         <v>2800</v>
@@ -20814,7 +20814,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H705" t="n">
         <v>2450</v>
@@ -20843,7 +20843,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H706" t="n">
         <v>22400</v>
@@ -20988,7 +20988,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="n">
         <v>1750</v>
@@ -21075,7 +21075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H714" t="n">
         <v>4900</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21365,7 +21365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="n">
         <v>21350</v>
@@ -21394,7 +21394,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H741" t="n">
         <v>38150</v>
@@ -22032,7 +22032,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H747" t="n">
         <v>1050</v>
@@ -22061,7 +22061,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G755" t="n">
-        <v>1.32163453102112</v>
+        <v>1.32163465023041</v>
       </c>
       <c r="H755" t="n">
         <v>29750</v>
@@ -22438,7 +22438,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H761" t="n">
         <v>7700</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H763" t="n">
         <v>700</v>
@@ -22525,7 +22525,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H764" t="n">
         <v>1050</v>
@@ -22641,7 +22641,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H768" t="n">
         <v>700</v>
@@ -22873,7 +22873,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H776" t="n">
         <v>6300</v>
@@ -23018,7 +23018,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="n">
         <v>14000</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345806121826</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H788" t="n">
         <v>14000</v>
@@ -23279,7 +23279,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H790" t="n">
         <v>4200</v>
@@ -23337,7 +23337,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H792" t="n">
         <v>4900</v>
@@ -23482,7 +23482,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H797" t="n">
         <v>7700</v>
@@ -23569,7 +23569,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H800" t="n">
         <v>2800</v>
@@ -23598,7 +23598,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H801" t="n">
         <v>5250</v>
@@ -23656,7 +23656,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.20405149459839</v>
+        <v>1.2040513753891</v>
       </c>
       <c r="H803" t="n">
         <v>17850</v>
@@ -23743,7 +23743,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H806" t="n">
         <v>46550</v>
@@ -23801,7 +23801,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H808" t="n">
         <v>8050</v>
@@ -23830,7 +23830,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H809" t="n">
         <v>41300</v>
@@ -23888,7 +23888,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H811" t="n">
         <v>12600</v>
@@ -23946,7 +23946,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H813" t="n">
         <v>4200</v>
@@ -24120,7 +24120,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H819" t="n">
         <v>13650</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24555,7 +24555,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866784095764</v>
+        <v>1.36866796016693</v>
       </c>
       <c r="H834" t="n">
         <v>12600</v>
@@ -24642,7 +24642,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519465446472</v>
+        <v>1.26519477367401</v>
       </c>
       <c r="H837" t="n">
         <v>60200</v>
@@ -24671,7 +24671,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="n">
         <v>13300</v>
@@ -24729,7 +24729,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H840" t="n">
         <v>9450</v>
@@ -24758,7 +24758,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G841" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H841" t="n">
         <v>42000</v>
@@ -24845,7 +24845,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="n">
         <v>129500</v>
@@ -24932,7 +24932,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510771751404</v>
+        <v>1.42510783672333</v>
       </c>
       <c r="H847" t="n">
         <v>8750</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -24990,7 +24990,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H849" t="n">
         <v>8050</v>
@@ -25048,7 +25048,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G851" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H851" t="n">
         <v>2450</v>
@@ -25077,7 +25077,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H852" t="n">
         <v>4200</v>
@@ -25106,7 +25106,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H853" t="n">
         <v>1750</v>
@@ -25135,7 +25135,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G860" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H860" t="n">
         <v>15050</v>
@@ -25338,7 +25338,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G861" t="n">
-        <v>1.406294465065</v>
+        <v>1.40629458427429</v>
       </c>
       <c r="H861" t="n">
         <v>5600</v>
@@ -25541,7 +25541,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.36396455764771</v>
+        <v>1.36396467685699</v>
       </c>
       <c r="H868" t="n">
         <v>3150</v>
@@ -25570,7 +25570,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H869" t="n">
         <v>3850</v>
@@ -25599,7 +25599,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H870" t="n">
         <v>2100</v>
@@ -25628,7 +25628,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H871" t="n">
         <v>2100</v>
@@ -25657,7 +25657,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>1.32163453102112</v>
+        <v>1.32163465023041</v>
       </c>
       <c r="H872" t="n">
         <v>6300</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26150,7 +26150,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H889" t="n">
         <v>6650</v>
@@ -26237,7 +26237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="n">
         <v>7000</v>
@@ -26324,7 +26324,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H895" t="n">
         <v>10150</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862449169159</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26469,7 +26469,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G900" t="n">
-        <v>1.86722040176392</v>
+        <v>1.86722052097321</v>
       </c>
       <c r="H900" t="n">
         <v>280000</v>
@@ -26991,7 +26991,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.6790874004364</v>
+        <v>1.67908728122711</v>
       </c>
       <c r="H918" t="n">
         <v>3150</v>
@@ -27020,7 +27020,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616417884827</v>
+        <v>1.64616405963898</v>
       </c>
       <c r="H919" t="n">
         <v>9100</v>
@@ -27049,7 +27049,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662696838379</v>
+        <v>1.87662708759308</v>
       </c>
       <c r="H920" t="n">
         <v>215950</v>
@@ -27078,7 +27078,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H921" t="n">
         <v>352450</v>
@@ -27107,7 +27107,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H922" t="n">
         <v>129500</v>
@@ -27136,7 +27136,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H923" t="n">
         <v>32550</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539699077606</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27281,7 +27281,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480343818665</v>
+        <v>1.98480331897736</v>
       </c>
       <c r="H928" t="n">
         <v>17500</v>
@@ -27310,7 +27310,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946349143982</v>
+        <v>2.06946325302124</v>
       </c>
       <c r="H929" t="n">
         <v>53900</v>
@@ -27600,7 +27600,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H939" t="n">
         <v>46200</v>
@@ -27629,7 +27629,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361704826355</v>
+        <v>2.00361680984497</v>
       </c>
       <c r="H940" t="n">
         <v>2100</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827686309814</v>
+        <v>2.08827662467957</v>
       </c>
       <c r="H941" t="n">
         <v>39900</v>
@@ -27716,7 +27716,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293667793274</v>
+        <v>2.17293643951416</v>
       </c>
       <c r="H943" t="n">
         <v>154700</v>
@@ -27745,7 +27745,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H944" t="n">
         <v>203700</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27803,7 +27803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>2.72792911529541</v>
+        <v>2.72792935371399</v>
       </c>
       <c r="H946" t="n">
         <v>286650</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.02894186973572</v>
+        <v>3.02894163131714</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -27919,7 +27919,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H950" t="n">
         <v>126350</v>
@@ -27948,7 +27948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9725022315979</v>
+        <v>2.97250199317932</v>
       </c>
       <c r="H951" t="n">
         <v>31150</v>
@@ -28180,7 +28180,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733568191528</v>
+        <v>2.73733592033386</v>
       </c>
       <c r="H959" t="n">
         <v>13300</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28354,7 +28354,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H965" t="n">
         <v>91700</v>
@@ -28441,7 +28441,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H968" t="n">
         <v>131250</v>
@@ -28470,7 +28470,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="n">
         <v>18550</v>
@@ -28557,7 +28557,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="n">
         <v>29400</v>
@@ -28615,7 +28615,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H974" t="n">
         <v>31500</v>
@@ -28644,7 +28644,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H975" t="n">
         <v>25200</v>
@@ -28673,7 +28673,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.3299548625946</v>
+        <v>3.32995462417603</v>
       </c>
       <c r="H976" t="n">
         <v>8050</v>
@@ -28702,7 +28702,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H977" t="n">
         <v>16450</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28760,7 +28760,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H979" t="n">
         <v>12950</v>
@@ -28847,7 +28847,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H982" t="n">
         <v>30800</v>
@@ -28934,7 +28934,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>3.01012873649597</v>
+        <v>3.01012849807739</v>
       </c>
       <c r="H985" t="n">
         <v>25900</v>
@@ -29021,7 +29021,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="n">
         <v>11550</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29253,7 +29253,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H996" t="n">
         <v>14700</v>
@@ -29282,7 +29282,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H997" t="n">
         <v>9100</v>
@@ -29311,7 +29311,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232835769653</v>
+        <v>3.29232811927795</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H999" t="n">
         <v>2800</v>
@@ -29369,7 +29369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H1000" t="n">
         <v>30100</v>
@@ -29427,7 +29427,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="n">
         <v>2450</v>
@@ -29485,7 +29485,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1004" t="n">
         <v>2450</v>
@@ -29659,7 +29659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1010" t="n">
         <v>2100</v>
@@ -29862,7 +29862,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H1017" t="n">
         <v>68950</v>
@@ -29978,7 +29978,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1021" t="n">
         <v>8050</v>
@@ -30094,7 +30094,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1025" t="n">
         <v>9450</v>
@@ -30123,7 +30123,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="n">
         <v>3500</v>
@@ -30268,7 +30268,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="n">
         <v>1400</v>
@@ -30297,7 +30297,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1032" t="n">
         <v>14700</v>
@@ -30326,7 +30326,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="n">
         <v>6300</v>
@@ -30355,7 +30355,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1034" t="n">
         <v>7000</v>
@@ -30413,7 +30413,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1036" t="n">
         <v>45850</v>
@@ -30442,7 +30442,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1037" t="n">
         <v>14700</v>
@@ -30558,7 +30558,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1041" t="n">
         <v>7350</v>
@@ -30616,7 +30616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="n">
         <v>2800</v>
@@ -30645,7 +30645,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1044" t="n">
         <v>4900</v>
@@ -30732,7 +30732,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1047" t="n">
         <v>2100</v>
@@ -30819,7 +30819,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944860458374</v>
+        <v>3.17944836616516</v>
       </c>
       <c r="H1050" t="n">
         <v>34300</v>
@@ -30848,7 +30848,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.3581748008728</v>
+        <v>3.35817456245422</v>
       </c>
       <c r="H1051" t="n">
         <v>278600</v>
@@ -30877,7 +30877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597517967224</v>
+        <v>3.07597494125366</v>
       </c>
       <c r="H1052" t="n">
         <v>252000</v>
@@ -30964,7 +30964,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1055" t="n">
         <v>17850</v>
@@ -31022,7 +31022,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1057" t="n">
         <v>9100</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.02894186973572</v>
+        <v>3.02894163131714</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31225,7 +31225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131536483765</v>
+        <v>2.99131512641907</v>
       </c>
       <c r="H1064" t="n">
         <v>9800</v>
@@ -31254,7 +31254,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885517120361</v>
+        <v>3.18885493278503</v>
       </c>
       <c r="H1065" t="n">
         <v>95550</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31312,7 +31312,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="n">
         <v>21700</v>
@@ -31341,7 +31341,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1068" t="n">
         <v>42350</v>
@@ -31631,7 +31631,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325393676758</v>
+        <v>3.75325417518616</v>
       </c>
       <c r="H1078" t="n">
         <v>55650</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31979,7 +31979,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512117385864</v>
+        <v>3.56512093544006</v>
       </c>
       <c r="H1090" t="n">
         <v>50050</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32327,7 +32327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1102" t="n">
         <v>26250</v>
@@ -32385,7 +32385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364312171936</v>
+        <v>3.66364336013794</v>
       </c>
       <c r="H1104" t="n">
         <v>26600</v>
@@ -32414,7 +32414,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.6250786781311</v>
+        <v>3.62507843971252</v>
       </c>
       <c r="H1105" t="n">
         <v>4900</v>
@@ -32646,7 +32646,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1113" t="n">
         <v>40950</v>
@@ -32675,7 +32675,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794955253601</v>
+        <v>3.54794931411743</v>
       </c>
       <c r="H1114" t="n">
         <v>30100</v>
@@ -32762,7 +32762,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1117" t="n">
         <v>9800</v>
@@ -32849,7 +32849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440848350525</v>
+        <v>3.37440824508667</v>
       </c>
       <c r="H1120" t="n">
         <v>7350</v>
@@ -32878,7 +32878,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436078071594</v>
+        <v>3.64436101913452</v>
       </c>
       <c r="H1121" t="n">
         <v>74200</v>
@@ -32936,7 +32936,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579633712769</v>
+        <v>3.60579609870911</v>
       </c>
       <c r="H1123" t="n">
         <v>43750</v>
@@ -33226,7 +33226,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1133" t="n">
         <v>7000</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974346160889</v>
+        <v>3.49974370002747</v>
       </c>
       <c r="H1135" t="n">
         <v>3850</v>
@@ -33371,7 +33371,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1138" t="n">
         <v>3850</v>
@@ -33429,7 +33429,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1140" t="n">
         <v>26950</v>
@@ -33516,7 +33516,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1143" t="n">
         <v>6300</v>
@@ -33632,7 +33632,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687282562256</v>
+        <v>3.57687258720398</v>
       </c>
       <c r="H1147" t="n">
         <v>44100</v>
@@ -33661,7 +33661,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1148" t="n">
         <v>15400</v>
@@ -33806,7 +33806,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081971168518</v>
+        <v>3.47081995010376</v>
       </c>
       <c r="H1153" t="n">
         <v>350</v>
@@ -33893,7 +33893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32620239257812</v>
+        <v>3.3262026309967</v>
       </c>
       <c r="H1156" t="n">
         <v>3150</v>
@@ -34154,7 +34154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1165" t="n">
         <v>14700</v>
@@ -34270,7 +34270,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31388020515442</v>
+        <v>2.31387996673584</v>
       </c>
       <c r="H1169" t="n">
         <v>30100</v>
@@ -34328,7 +34328,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608016967773</v>
+        <v>1.98608028888702</v>
       </c>
       <c r="H1171" t="n">
         <v>30800</v>
@@ -34415,7 +34415,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029143333435</v>
+        <v>2.41029167175293</v>
       </c>
       <c r="H1174" t="n">
         <v>21350</v>
@@ -34618,7 +34618,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.297278881073</v>
+        <v>3.29727911949158</v>
       </c>
       <c r="H1181" t="n">
         <v>33950</v>
@@ -34647,7 +34647,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1182" t="n">
         <v>13650</v>
@@ -34676,7 +34676,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512590408325</v>
+        <v>3.35512614250183</v>
       </c>
       <c r="H1183" t="n">
         <v>4200</v>
@@ -34705,7 +34705,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871443748474</v>
+        <v>3.25871419906616</v>
       </c>
       <c r="H1184" t="n">
         <v>4900</v>
@@ -34763,7 +34763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225526809692</v>
+        <v>3.43225502967834</v>
       </c>
       <c r="H1186" t="n">
         <v>17150</v>
@@ -34821,7 +34821,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1188" t="n">
         <v>25900</v>
@@ -34850,7 +34850,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117877960205</v>
+        <v>3.46117854118347</v>
       </c>
       <c r="H1189" t="n">
         <v>9100</v>
@@ -34879,7 +34879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476731300354</v>
+        <v>3.36476707458496</v>
       </c>
       <c r="H1190" t="n">
         <v>13650</v>
@@ -35024,7 +35024,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1195" t="n">
         <v>5950</v>
@@ -35111,7 +35111,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1198" t="n">
         <v>18200</v>
@@ -35198,7 +35198,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.19122624397278</v>
+        <v>3.1912260055542</v>
       </c>
       <c r="H1201" t="n">
         <v>7700</v>
@@ -35256,7 +35256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373781204224</v>
+        <v>3.12373805046082</v>
       </c>
       <c r="H1203" t="n">
         <v>10500</v>
@@ -35285,7 +35285,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1204" t="n">
         <v>2450</v>
@@ -35314,7 +35314,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266132354736</v>
+        <v>3.15266156196594</v>
       </c>
       <c r="H1205" t="n">
         <v>1050</v>
@@ -35488,7 +35488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876142501831</v>
+        <v>2.98876166343689</v>
       </c>
       <c r="H1211" t="n">
         <v>3150</v>
@@ -35604,7 +35604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1215" t="n">
         <v>6300</v>
@@ -35633,7 +35633,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486200332642</v>
+        <v>2.82486176490784</v>
       </c>
       <c r="H1216" t="n">
         <v>3500</v>
@@ -68467,6 +68467,35 @@
         <v>6650</v>
       </c>
       <c r="I2348" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2349" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="H2349" t="n">
+        <v>24850</v>
+      </c>
+      <c r="I2349" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671106338501</v>
+        <v>3.19671130180359</v>
       </c>
       <c r="H4" t="n">
         <v>123200</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058491706848</v>
+        <v>3.17058515548706</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -659,7 +659,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044326782227</v>
+        <v>3.20044350624084</v>
       </c>
       <c r="H10" t="n">
         <v>7000</v>
@@ -688,7 +688,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H11" t="n">
         <v>3150</v>
@@ -746,7 +746,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111275672913</v>
+        <v>3.19111251831055</v>
       </c>
       <c r="H13" t="n">
         <v>1400</v>
@@ -862,7 +862,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1892466545105</v>
+        <v>3.18924641609192</v>
       </c>
       <c r="H17" t="n">
         <v>2450</v>
@@ -949,7 +949,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198707580566</v>
+        <v>3.40198731422424</v>
       </c>
       <c r="H20" t="n">
         <v>22050</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501127243042</v>
+        <v>3.555011510849</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1123,7 +1123,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.07939958572388</v>
+        <v>4.07939910888672</v>
       </c>
       <c r="H26" t="n">
         <v>28700</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1355,7 +1355,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65120601654053</v>
+        <v>7.65120553970337</v>
       </c>
       <c r="H34" t="n">
         <v>46550</v>
@@ -1471,7 +1471,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830690383911</v>
+        <v>6.08830738067627</v>
       </c>
       <c r="H38" t="n">
         <v>90650</v>
@@ -1529,7 +1529,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088653564453</v>
+        <v>6.40088701248169</v>
       </c>
       <c r="H40" t="n">
         <v>82250</v>
@@ -1645,7 +1645,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401866912842</v>
+        <v>7.12401914596558</v>
       </c>
       <c r="H44" t="n">
         <v>91350</v>
@@ -1674,7 +1674,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876251220703</v>
+        <v>6.84876203536987</v>
       </c>
       <c r="H45" t="n">
         <v>72450</v>
@@ -1761,7 +1761,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H48" t="n">
         <v>25200</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451303482056</v>
+        <v>7.74451398849487</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435752868652</v>
+        <v>8.30435657501221</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750999450684</v>
+        <v>8.95750904083252</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2051,7 +2051,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303936004639</v>
+        <v>8.25303840637207</v>
       </c>
       <c r="H58" t="n">
         <v>105350</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175804138184</v>
+        <v>8.06175899505615</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2138,7 +2138,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726755142212</v>
+        <v>7.42726802825928</v>
       </c>
       <c r="H61" t="n">
         <v>87500</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002254486084</v>
+        <v>7.110023021698</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2312,7 +2312,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>7.2686448097229</v>
+        <v>7.26864528656006</v>
       </c>
       <c r="H67" t="n">
         <v>45500</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252466201782</v>
+        <v>7.70252513885498</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2399,7 +2399,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858762741089</v>
+        <v>7.47858715057373</v>
       </c>
       <c r="H70" t="n">
         <v>35350</v>
@@ -2515,7 +2515,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H74" t="n">
         <v>15750</v>
@@ -2602,7 +2602,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H77" t="n">
         <v>12600</v>
@@ -2689,7 +2689,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474653244019</v>
+        <v>6.90474700927734</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939252853394</v>
+        <v>6.97939205169678</v>
       </c>
       <c r="H81" t="n">
         <v>11200</v>
@@ -2834,7 +2834,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673538208008</v>
+        <v>6.94673490524292</v>
       </c>
       <c r="H85" t="n">
         <v>3500</v>
@@ -2950,7 +2950,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H89" t="n">
         <v>7350</v>
@@ -2979,7 +2979,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.9607310295105</v>
+        <v>6.96073150634766</v>
       </c>
       <c r="H90" t="n">
         <v>14000</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145841598511</v>
+        <v>6.74145889282227</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3182,7 +3182,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.783447265625</v>
+        <v>6.78344678878784</v>
       </c>
       <c r="H97" t="n">
         <v>5250</v>
@@ -3269,7 +3269,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419403076172</v>
+        <v>6.49419450759888</v>
       </c>
       <c r="H100" t="n">
         <v>8750</v>
@@ -3327,7 +3327,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.51285552978516</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H102" t="n">
         <v>24850</v>
@@ -3356,7 +3356,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287490844727</v>
       </c>
       <c r="H103" t="n">
         <v>5600</v>
@@ -3472,7 +3472,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555143356323</v>
+        <v>6.40555191040039</v>
       </c>
       <c r="H107" t="n">
         <v>2450</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3530,7 +3530,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.51285552978516</v>
+        <v>6.512855052948</v>
       </c>
       <c r="H109" t="n">
         <v>2800</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43820953369141</v>
+        <v>6.43821001052856</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3617,7 +3617,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>6.27958726882935</v>
+        <v>6.27958679199219</v>
       </c>
       <c r="H112" t="n">
         <v>18200</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828704833984</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -3878,7 +3878,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G121" t="n">
-        <v>6.14895725250244</v>
+        <v>6.14895677566528</v>
       </c>
       <c r="H121" t="n">
         <v>3150</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4052,7 +4052,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175100326538</v>
       </c>
       <c r="H127" t="n">
         <v>15750</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175100326538</v>
       </c>
       <c r="H133" t="n">
         <v>16450</v>
@@ -4284,7 +4284,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245853424072</v>
+        <v>5.54245901107788</v>
       </c>
       <c r="H135" t="n">
         <v>20300</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104299545288</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305027008057</v>
+        <v>5.81304979324341</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4516,7 +4516,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>5.71041250228882</v>
+        <v>5.71041202545166</v>
       </c>
       <c r="H143" t="n">
         <v>1750</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4574,7 +4574,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.9810037612915</v>
+        <v>5.98100328445435</v>
       </c>
       <c r="H145" t="n">
         <v>39200</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104251861572</v>
+        <v>5.84104299545288</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5067,7 +5067,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17856025695801</v>
+        <v>5.17855978012085</v>
       </c>
       <c r="H162" t="n">
         <v>3850</v>
@@ -5096,7 +5096,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789100646973</v>
+        <v>5.18789052963257</v>
       </c>
       <c r="H163" t="n">
         <v>1400</v>
@@ -5183,7 +5183,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651327133179</v>
+        <v>5.34651279449463</v>
       </c>
       <c r="H166" t="n">
         <v>7350</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852102279663</v>
+        <v>5.31852054595947</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -5270,7 +5270,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>5.28653860092163</v>
+        <v>5.28653812408447</v>
       </c>
       <c r="H170" t="n">
         <v>1050</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484571456909</v>
+        <v>5.15484523773193</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5415,7 +5415,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>5.45585870742798</v>
+        <v>5.45585823059082</v>
       </c>
       <c r="H174" t="n">
         <v>8750</v>
@@ -5473,7 +5473,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G176" t="n">
-        <v>5.70043134689331</v>
+        <v>5.70043087005615</v>
       </c>
       <c r="H176" t="n">
         <v>3150</v>
@@ -5502,7 +5502,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.78509092330933</v>
+        <v>5.78509140014648</v>
       </c>
       <c r="H177" t="n">
         <v>8050</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805809020996</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5850,7 +5850,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H189" t="n">
         <v>2450</v>
@@ -5879,7 +5879,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H190" t="n">
         <v>350</v>
@@ -5966,7 +5966,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>5.45585870742798</v>
+        <v>5.45585823059082</v>
       </c>
       <c r="H193" t="n">
         <v>4550</v>
@@ -5995,7 +5995,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G194" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H194" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G195" t="n">
-        <v>5.34297800064087</v>
+        <v>5.34297847747803</v>
       </c>
       <c r="H195" t="n">
         <v>2800</v>
@@ -6053,7 +6053,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891138076782</v>
+        <v>5.24891185760498</v>
       </c>
       <c r="H196" t="n">
         <v>25200</v>
@@ -6227,7 +6227,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G202" t="n">
-        <v>5.28653860092163</v>
+        <v>5.28653812408447</v>
       </c>
       <c r="H202" t="n">
         <v>14350</v>
@@ -6285,7 +6285,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>5.12662506103516</v>
+        <v>5.126624584198</v>
       </c>
       <c r="H204" t="n">
         <v>4900</v>
@@ -6314,7 +6314,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28653860092163</v>
+        <v>5.28653812408447</v>
       </c>
       <c r="H205" t="n">
         <v>700</v>
@@ -6343,7 +6343,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>5.22069215774536</v>
+        <v>5.2206916809082</v>
       </c>
       <c r="H206" t="n">
         <v>1750</v>
@@ -6372,7 +6372,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179161071777</v>
+        <v>5.36179113388062</v>
       </c>
       <c r="H207" t="n">
         <v>8050</v>
@@ -6430,7 +6430,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721849441528</v>
+        <v>5.11721897125244</v>
       </c>
       <c r="H209" t="n">
         <v>5600</v>
@@ -6575,7 +6575,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>5.05137205123901</v>
+        <v>5.05137157440186</v>
       </c>
       <c r="H214" t="n">
         <v>1750</v>
@@ -6720,7 +6720,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>4.97611856460571</v>
+        <v>4.97611904144287</v>
       </c>
       <c r="H219" t="n">
         <v>5950</v>
@@ -6749,7 +6749,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.8350191116333</v>
+        <v>4.83501863479614</v>
       </c>
       <c r="H220" t="n">
         <v>10500</v>
@@ -6778,7 +6778,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.84442520141602</v>
+        <v>4.84442567825317</v>
       </c>
       <c r="H221" t="n">
         <v>4550</v>
@@ -6836,7 +6836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>4.8914589881897</v>
+        <v>4.89145851135254</v>
       </c>
       <c r="H223" t="n">
         <v>4900</v>
@@ -6865,7 +6865,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G224" t="n">
-        <v>4.87264537811279</v>
+        <v>4.87264585494995</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H227" t="n">
         <v>8400</v>
@@ -7039,7 +7039,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985303878784</v>
+        <v>4.59985256195068</v>
       </c>
       <c r="H230" t="n">
         <v>1750</v>
@@ -7097,7 +7097,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472948074341</v>
+        <v>4.28472995758057</v>
       </c>
       <c r="H232" t="n">
         <v>4900</v>
@@ -7155,7 +7155,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>4.20007038116455</v>
+        <v>4.20006990432739</v>
       </c>
       <c r="H234" t="n">
         <v>6650</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884004592896</v>
+        <v>4.29884052276611</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519346237183</v>
+        <v>4.51519298553467</v>
       </c>
       <c r="H238" t="n">
         <v>147350</v>
@@ -7416,7 +7416,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G243" t="n">
-        <v>4.18596029281616</v>
+        <v>4.185959815979</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7474,7 +7474,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.06367349624634</v>
+        <v>4.0636739730835</v>
       </c>
       <c r="H245" t="n">
         <v>4550</v>
@@ -7677,7 +7677,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G252" t="n">
-        <v>3.74855041503906</v>
+        <v>3.74855065345764</v>
       </c>
       <c r="H252" t="n">
         <v>15750</v>
@@ -7996,7 +7996,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H263" t="n">
         <v>3850</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8083,7 +8083,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G266" t="n">
-        <v>3.41931819915771</v>
+        <v>3.41931796073914</v>
       </c>
       <c r="H266" t="n">
         <v>7350</v>
@@ -8170,7 +8170,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G269" t="n">
-        <v>3.38169169425964</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H269" t="n">
         <v>3500</v>
@@ -8199,7 +8199,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.4146146774292</v>
+        <v>3.41461491584778</v>
       </c>
       <c r="H270" t="n">
         <v>7350</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>3.49927473068237</v>
+        <v>3.49927449226379</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8663,7 +8663,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38169169425964</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H286" t="n">
         <v>10500</v>
@@ -8692,7 +8692,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>3.38169169425964</v>
+        <v>3.38169145584106</v>
       </c>
       <c r="H287" t="n">
         <v>2100</v>
@@ -8750,7 +8750,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G289" t="n">
-        <v>3.49927473068237</v>
+        <v>3.49927449226379</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H290" t="n">
         <v>8750</v>
@@ -8895,7 +8895,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>3.62156105041504</v>
+        <v>3.62156081199646</v>
       </c>
       <c r="H294" t="n">
         <v>1750</v>
@@ -8953,7 +8953,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918779373169</v>
+        <v>3.65918755531311</v>
       </c>
       <c r="H296" t="n">
         <v>39900</v>
@@ -9040,7 +9040,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H299" t="n">
         <v>5950</v>
@@ -9243,7 +9243,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>3.01012849807739</v>
+        <v>3.01012873649597</v>
       </c>
       <c r="H306" t="n">
         <v>54950</v>
@@ -9359,7 +9359,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>2.61504936218262</v>
+        <v>2.61504912376404</v>
       </c>
       <c r="H310" t="n">
         <v>2450</v>
@@ -9417,7 +9417,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>2.59153246879578</v>
+        <v>2.59153270721436</v>
       </c>
       <c r="H312" t="n">
         <v>6650</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44572949409485</v>
+        <v>2.44572925567627</v>
       </c>
       <c r="H313" t="n">
         <v>15400</v>
@@ -9504,7 +9504,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H315" t="n">
         <v>8750</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H316" t="n">
         <v>5600</v>
@@ -9649,7 +9649,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H320" t="n">
         <v>21000</v>
@@ -9678,7 +9678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H321" t="n">
         <v>5250</v>
@@ -9707,7 +9707,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H322" t="n">
         <v>3150</v>
@@ -9736,7 +9736,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480331897736</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H323" t="n">
         <v>16100</v>
@@ -9794,7 +9794,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950695991516</v>
+        <v>1.98950672149658</v>
       </c>
       <c r="H325" t="n">
         <v>2800</v>
@@ -9968,7 +9968,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>2.09298014640808</v>
+        <v>2.0929799079895</v>
       </c>
       <c r="H331" t="n">
         <v>10150</v>
@@ -9997,7 +9997,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H332" t="n">
         <v>7700</v>
@@ -10055,7 +10055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480331897736</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H334" t="n">
         <v>4550</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10345,7 +10345,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80983996391296</v>
+        <v>1.80983984470367</v>
       </c>
       <c r="H344" t="n">
         <v>19600</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10461,7 +10461,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5050642490387</v>
+        <v>1.50506436824799</v>
       </c>
       <c r="H348" t="n">
         <v>11550</v>
@@ -10490,7 +10490,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G349" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H349" t="n">
         <v>21700</v>
@@ -10519,7 +10519,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G350" t="n">
-        <v>1.24732208251953</v>
+        <v>1.24732196331024</v>
       </c>
       <c r="H350" t="n">
         <v>36750</v>
@@ -10548,7 +10548,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H351" t="n">
         <v>6650</v>
@@ -10606,7 +10606,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G353" t="n">
-        <v>1.29623651504517</v>
+        <v>1.29623663425446</v>
       </c>
       <c r="H353" t="n">
         <v>9450</v>
@@ -10780,7 +10780,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H359" t="n">
         <v>9100</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209743976593</v>
+        <v>1.55209755897522</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -11012,7 +11012,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928937911987</v>
+        <v>2.38928961753845</v>
       </c>
       <c r="H367" t="n">
         <v>146300</v>
@@ -11070,7 +11070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H369" t="n">
         <v>55650</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742285728455</v>
+        <v>2.57742261886597</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11273,7 +11273,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.56331253051758</v>
+        <v>2.563312292099</v>
       </c>
       <c r="H376" t="n">
         <v>99050</v>
@@ -11302,7 +11302,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H377" t="n">
         <v>26600</v>
@@ -11418,7 +11418,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089580535889</v>
+        <v>2.68089556694031</v>
       </c>
       <c r="H381" t="n">
         <v>12250</v>
@@ -11650,7 +11650,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H389" t="n">
         <v>2800</v>
@@ -11679,7 +11679,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983958244324</v>
+        <v>2.45983934402466</v>
       </c>
       <c r="H390" t="n">
         <v>1750</v>
@@ -11737,7 +11737,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G392" t="n">
-        <v>2.61504936218262</v>
+        <v>2.61504912376404</v>
       </c>
       <c r="H392" t="n">
         <v>23450</v>
@@ -11824,7 +11824,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216937065125</v>
+        <v>2.50216960906982</v>
       </c>
       <c r="H395" t="n">
         <v>4900</v>
@@ -11853,7 +11853,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860924720764</v>
+        <v>2.55860948562622</v>
       </c>
       <c r="H396" t="n">
         <v>2100</v>
@@ -11882,7 +11882,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11940,7 +11940,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750955581665</v>
+        <v>2.41750931739807</v>
       </c>
       <c r="H399" t="n">
         <v>4550</v>
@@ -12085,7 +12085,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H404" t="n">
         <v>5950</v>
@@ -12114,7 +12114,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H405" t="n">
         <v>1050</v>
@@ -12143,7 +12143,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>2.44572949409485</v>
+        <v>2.44572925567627</v>
       </c>
       <c r="H406" t="n">
         <v>7700</v>
@@ -12346,7 +12346,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.31873965263367</v>
+        <v>2.31873989105225</v>
       </c>
       <c r="H413" t="n">
         <v>10150</v>
@@ -12723,7 +12723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056318283081</v>
+        <v>2.21056294441223</v>
       </c>
       <c r="H426" t="n">
         <v>1750</v>
@@ -12810,7 +12810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H429" t="n">
         <v>20300</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -13042,7 +13042,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H437" t="n">
         <v>2800</v>
@@ -13071,7 +13071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H438" t="n">
         <v>5600</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H442" t="n">
         <v>4900</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H443" t="n">
         <v>350</v>
@@ -13332,7 +13332,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27640986442566</v>
+        <v>2.27640962600708</v>
       </c>
       <c r="H447" t="n">
         <v>2800</v>
@@ -13390,7 +13390,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759673118591</v>
+        <v>2.25759649276733</v>
       </c>
       <c r="H449" t="n">
         <v>2800</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H450" t="n">
         <v>4550</v>
@@ -13477,7 +13477,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H452" t="n">
         <v>10850</v>
@@ -13709,7 +13709,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G460" t="n">
-        <v>2.01302361488342</v>
+        <v>2.01302337646484</v>
       </c>
       <c r="H460" t="n">
         <v>5600</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H461" t="n">
         <v>1750</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -13941,7 +13941,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G468" t="n">
-        <v>1.86722052097321</v>
+        <v>1.86722040176392</v>
       </c>
       <c r="H468" t="n">
         <v>7000</v>
@@ -13999,7 +13999,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H470" t="n">
         <v>3850</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.01302361488342</v>
+        <v>2.01302337646484</v>
       </c>
       <c r="H477" t="n">
         <v>25200</v>
@@ -14231,7 +14231,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H478" t="n">
         <v>6650</v>
@@ -14260,7 +14260,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183674812317</v>
+        <v>2.03183698654175</v>
       </c>
       <c r="H479" t="n">
         <v>700</v>
@@ -14289,7 +14289,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H480" t="n">
         <v>5600</v>
@@ -14318,7 +14318,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124355316162</v>
+        <v>2.04124331474304</v>
       </c>
       <c r="H481" t="n">
         <v>1400</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14521,7 +14521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H488" t="n">
         <v>2450</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14695,7 +14695,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H494" t="n">
         <v>6650</v>
@@ -14724,7 +14724,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192368507385</v>
+        <v>1.87192380428314</v>
       </c>
       <c r="H498" t="n">
         <v>350</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15072,7 +15072,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H507" t="n">
         <v>19250</v>
@@ -15217,7 +15217,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G512" t="n">
-        <v>1.86722052097321</v>
+        <v>1.86722040176392</v>
       </c>
       <c r="H512" t="n">
         <v>700</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H521" t="n">
         <v>1050</v>
@@ -15507,7 +15507,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G522" t="n">
-        <v>1.74963736534119</v>
+        <v>1.7496372461319</v>
       </c>
       <c r="H522" t="n">
         <v>9100</v>
@@ -15536,7 +15536,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H523" t="n">
         <v>3150</v>
@@ -15565,7 +15565,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H524" t="n">
         <v>3850</v>
@@ -15594,7 +15594,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434052944183</v>
+        <v>1.75434064865112</v>
       </c>
       <c r="H528" t="n">
         <v>1400</v>
@@ -15710,7 +15710,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.74963736534119</v>
+        <v>1.7496372461319</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H530" t="n">
         <v>3850</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H537" t="n">
         <v>2800</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548380851746</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16290,7 +16290,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H549" t="n">
         <v>1050</v>
@@ -16406,7 +16406,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G553" t="n">
-        <v>1.81078052520752</v>
+        <v>1.81078040599823</v>
       </c>
       <c r="H553" t="n">
         <v>66500</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539699077606</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836368083954</v>
+        <v>1.92836356163025</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16696,7 +16696,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H563" t="n">
         <v>5600</v>
@@ -16754,7 +16754,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G565" t="n">
-        <v>1.86722052097321</v>
+        <v>1.86722040176392</v>
       </c>
       <c r="H565" t="n">
         <v>4200</v>
@@ -16812,7 +16812,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H567" t="n">
         <v>9800</v>
@@ -16899,7 +16899,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H570" t="n">
         <v>2100</v>
@@ -16986,7 +16986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959389686584</v>
+        <v>1.82959377765656</v>
       </c>
       <c r="H573" t="n">
         <v>7000</v>
@@ -17015,7 +17015,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H574" t="n">
         <v>1750</v>
@@ -17044,7 +17044,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>1.82489049434662</v>
+        <v>1.82489061355591</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.81078052520752</v>
+        <v>1.81078040599823</v>
       </c>
       <c r="H577" t="n">
         <v>4200</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196715354919</v>
+        <v>1.79196727275848</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17276,7 +17276,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H583" t="n">
         <v>19950</v>
@@ -17305,7 +17305,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904393196106</v>
+        <v>1.75904381275177</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H589" t="n">
         <v>2450</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315378189087</v>
+        <v>1.77315390110016</v>
       </c>
       <c r="H590" t="n">
         <v>1050</v>
@@ -17537,7 +17537,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.7073073387146</v>
+        <v>1.70730745792389</v>
       </c>
       <c r="H592" t="n">
         <v>2100</v>
@@ -17566,7 +17566,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612071037292</v>
+        <v>1.72612059116364</v>
       </c>
       <c r="H593" t="n">
         <v>4550</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17943,7 +17943,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845061779022</v>
+        <v>1.76845049858093</v>
       </c>
       <c r="H606" t="n">
         <v>12250</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735080718994</v>
+        <v>1.62735068798065</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18407,7 +18407,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>1.50976765155792</v>
+        <v>1.50976753234863</v>
       </c>
       <c r="H622" t="n">
         <v>9800</v>
@@ -18552,7 +18552,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264740467072</v>
+        <v>1.62264752388</v>
       </c>
       <c r="H627" t="n">
         <v>23800</v>
@@ -18755,7 +18755,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387762069702</v>
+        <v>1.52387750148773</v>
       </c>
       <c r="H634" t="n">
         <v>2450</v>
@@ -18842,7 +18842,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798747062683</v>
+        <v>1.53798758983612</v>
       </c>
       <c r="H637" t="n">
         <v>5950</v>
@@ -18871,7 +18871,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620752811432</v>
+        <v>1.56620740890503</v>
       </c>
       <c r="H638" t="n">
         <v>10500</v>
@@ -18958,7 +18958,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.5050642490387</v>
+        <v>1.50506436824799</v>
       </c>
       <c r="H641" t="n">
         <v>3150</v>
@@ -18987,7 +18987,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G642" t="n">
-        <v>1.5050642490387</v>
+        <v>1.50506436824799</v>
       </c>
       <c r="H642" t="n">
         <v>3500</v>
@@ -19045,7 +19045,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G644" t="n">
-        <v>1.5050642490387</v>
+        <v>1.50506436824799</v>
       </c>
       <c r="H644" t="n">
         <v>5950</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447081565857</v>
+        <v>1.51447093486786</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19161,7 +19161,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G648" t="n">
-        <v>1.5050642490387</v>
+        <v>1.50506436824799</v>
       </c>
       <c r="H648" t="n">
         <v>2100</v>
@@ -19625,7 +19625,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378686904907</v>
+        <v>0.818378746509552</v>
       </c>
       <c r="H664" t="n">
         <v>10850</v>
@@ -19741,7 +19741,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106550693512</v>
+        <v>0.886106610298157</v>
       </c>
       <c r="H668" t="n">
         <v>2450</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19857,7 +19857,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021221637726</v>
+        <v>0.935021162033081</v>
       </c>
       <c r="H672" t="n">
         <v>5950</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326608181</v>
+        <v>0.914326548576355</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181840419769</v>
+        <v>0.964181780815125</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851933002472</v>
+        <v>0.921851873397827</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20118,7 +20118,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401659488678</v>
+        <v>0.992401778697968</v>
       </c>
       <c r="H681" t="n">
         <v>3500</v>
@@ -20147,7 +20147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591837406158</v>
+        <v>1.01591849327087</v>
       </c>
       <c r="H682" t="n">
         <v>12950</v>
@@ -20205,7 +20205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H684" t="n">
         <v>47250</v>
@@ -20263,7 +20263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H686" t="n">
         <v>6650</v>
@@ -20437,7 +20437,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H692" t="n">
         <v>4550</v>
@@ -20495,7 +20495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H694" t="n">
         <v>9800</v>
@@ -20524,7 +20524,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H696" t="n">
         <v>18200</v>
@@ -20582,7 +20582,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H697" t="n">
         <v>9800</v>
@@ -20611,7 +20611,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H698" t="n">
         <v>3850</v>
@@ -20756,7 +20756,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H703" t="n">
         <v>16100</v>
@@ -20843,7 +20843,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H706" t="n">
         <v>22400</v>
@@ -20901,7 +20901,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H708" t="n">
         <v>13650</v>
@@ -20959,7 +20959,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H710" t="n">
         <v>1050</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H713" t="n">
         <v>2450</v>
@@ -21104,7 +21104,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H715" t="n">
         <v>128100</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21336,7 +21336,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G723" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H723" t="n">
         <v>7350</v>
@@ -21452,7 +21452,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H727" t="n">
         <v>2450</v>
@@ -21481,7 +21481,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G728" t="n">
-        <v>1.2181613445282</v>
+        <v>1.21816146373749</v>
       </c>
       <c r="H728" t="n">
         <v>700</v>
@@ -21510,7 +21510,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H729" t="n">
         <v>1750</v>
@@ -21539,7 +21539,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H731" t="n">
         <v>1050</v>
@@ -21597,7 +21597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G733" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H734" t="n">
         <v>2100</v>
@@ -21684,7 +21684,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875477790833</v>
+        <v>1.20875465869904</v>
       </c>
       <c r="H735" t="n">
         <v>9450</v>
@@ -21742,7 +21742,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G737" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H737" t="n">
         <v>60550</v>
@@ -21771,7 +21771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H738" t="n">
         <v>22750</v>
@@ -21858,7 +21858,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H741" t="n">
         <v>38150</v>
@@ -21945,7 +21945,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H744" t="n">
         <v>1050</v>
@@ -22032,7 +22032,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H747" t="n">
         <v>1050</v>
@@ -22061,7 +22061,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H750" t="n">
         <v>350</v>
@@ -22148,7 +22148,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H753" t="n">
         <v>8750</v>
@@ -22235,7 +22235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H754" t="n">
         <v>35350</v>
@@ -22264,7 +22264,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G755" t="n">
-        <v>1.32163465023041</v>
+        <v>1.32163453102112</v>
       </c>
       <c r="H755" t="n">
         <v>29750</v>
@@ -22554,7 +22554,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H765" t="n">
         <v>3150</v>
@@ -22612,7 +22612,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H767" t="n">
         <v>350</v>
@@ -22931,7 +22931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H778" t="n">
         <v>10500</v>
@@ -22960,7 +22960,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G780" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H787" t="n">
         <v>700</v>
@@ -23279,7 +23279,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879836559296</v>
+        <v>1.12879824638367</v>
       </c>
       <c r="H790" t="n">
         <v>4200</v>
@@ -23308,7 +23308,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G791" t="n">
-        <v>1.2181613445282</v>
+        <v>1.21816146373749</v>
       </c>
       <c r="H791" t="n">
         <v>3500</v>
@@ -23453,7 +23453,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>1.13820493221283</v>
+        <v>1.13820481300354</v>
       </c>
       <c r="H796" t="n">
         <v>1050</v>
@@ -23511,7 +23511,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H798" t="n">
         <v>12600</v>
@@ -23685,7 +23685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H804" t="n">
         <v>12600</v>
@@ -23714,7 +23714,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H805" t="n">
         <v>18550</v>
@@ -23743,7 +23743,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H806" t="n">
         <v>46550</v>
@@ -23772,7 +23772,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G807" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H807" t="n">
         <v>15750</v>
@@ -23830,7 +23830,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H809" t="n">
         <v>41300</v>
@@ -23917,7 +23917,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G812" t="n">
-        <v>1.33574450016022</v>
+        <v>1.33574461936951</v>
       </c>
       <c r="H812" t="n">
         <v>6300</v>
@@ -23946,7 +23946,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H813" t="n">
         <v>4200</v>
@@ -23975,7 +23975,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H814" t="n">
         <v>4550</v>
@@ -24033,7 +24033,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G816" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H816" t="n">
         <v>6650</v>
@@ -24062,7 +24062,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H817" t="n">
         <v>8400</v>
@@ -24149,7 +24149,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H820" t="n">
         <v>16100</v>
@@ -24178,7 +24178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H822" t="n">
         <v>3850</v>
@@ -24323,7 +24323,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G826" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H826" t="n">
         <v>700</v>
@@ -24381,7 +24381,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G828" t="n">
-        <v>1.15231478214264</v>
+        <v>1.15231490135193</v>
       </c>
       <c r="H828" t="n">
         <v>3500</v>
@@ -24410,7 +24410,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H829" t="n">
         <v>40600</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44862449169159</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24497,7 +24497,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>1.35455787181854</v>
+        <v>1.35455799102783</v>
       </c>
       <c r="H832" t="n">
         <v>52500</v>
@@ -24729,7 +24729,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H840" t="n">
         <v>9450</v>
@@ -24758,7 +24758,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G841" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H841" t="n">
         <v>42000</v>
@@ -24787,7 +24787,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H842" t="n">
         <v>23800</v>
@@ -24903,7 +24903,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G846" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H846" t="n">
         <v>25900</v>
@@ -24932,7 +24932,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>1.42510783672333</v>
+        <v>1.42510771751404</v>
       </c>
       <c r="H847" t="n">
         <v>8750</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.44862449169159</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -24990,7 +24990,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>1.40629458427429</v>
+        <v>1.406294465065</v>
       </c>
       <c r="H849" t="n">
         <v>8050</v>
@@ -25048,7 +25048,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G851" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H851" t="n">
         <v>2450</v>
@@ -25077,7 +25077,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>1.40629458427429</v>
+        <v>1.406294465065</v>
       </c>
       <c r="H852" t="n">
         <v>4200</v>
@@ -25222,7 +25222,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G857" t="n">
-        <v>1.39688777923584</v>
+        <v>1.39688789844513</v>
       </c>
       <c r="H857" t="n">
         <v>7700</v>
@@ -25251,7 +25251,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G858" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H858" t="n">
         <v>24500</v>
@@ -25280,7 +25280,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.45332765579224</v>
+        <v>1.45332777500153</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G860" t="n">
-        <v>1.40629458427429</v>
+        <v>1.406294465065</v>
       </c>
       <c r="H860" t="n">
         <v>15050</v>
@@ -25338,7 +25338,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G861" t="n">
-        <v>1.40629458427429</v>
+        <v>1.406294465065</v>
       </c>
       <c r="H861" t="n">
         <v>5600</v>
@@ -25396,7 +25396,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G863" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H863" t="n">
         <v>5250</v>
@@ -25454,7 +25454,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H865" t="n">
         <v>4900</v>
@@ -25541,7 +25541,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.36396467685699</v>
+        <v>1.36396455764771</v>
       </c>
       <c r="H868" t="n">
         <v>3150</v>
@@ -25599,7 +25599,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H870" t="n">
         <v>2100</v>
@@ -25628,7 +25628,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044790267944</v>
+        <v>1.34044778347015</v>
       </c>
       <c r="H871" t="n">
         <v>2100</v>
@@ -25657,7 +25657,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>1.32163465023041</v>
+        <v>1.32163453102112</v>
       </c>
       <c r="H872" t="n">
         <v>6300</v>
@@ -25686,7 +25686,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H873" t="n">
         <v>4550</v>
@@ -25744,7 +25744,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.33104133605957</v>
+        <v>1.33104121685028</v>
       </c>
       <c r="H875" t="n">
         <v>350</v>
@@ -25773,7 +25773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H876" t="n">
         <v>4200</v>
@@ -25802,7 +25802,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H877" t="n">
         <v>1400</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25860,7 +25860,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H879" t="n">
         <v>3850</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871142864227</v>
+        <v>1.28871130943298</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26179,7 +26179,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H890" t="n">
         <v>7350</v>
@@ -26208,7 +26208,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H891" t="n">
         <v>11900</v>
@@ -26295,7 +26295,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222784519196</v>
+        <v>1.31222796440125</v>
       </c>
       <c r="H894" t="n">
         <v>14000</v>
@@ -26324,7 +26324,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930462360382</v>
+        <v>1.27930474281311</v>
       </c>
       <c r="H895" t="n">
         <v>10150</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.44862449169159</v>
+        <v>1.4486243724823</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26469,7 +26469,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G900" t="n">
-        <v>1.86722052097321</v>
+        <v>1.86722040176392</v>
       </c>
       <c r="H900" t="n">
         <v>280000</v>
@@ -26498,7 +26498,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H901" t="n">
         <v>91700</v>
@@ -26527,7 +26527,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G902" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H902" t="n">
         <v>47600</v>
@@ -26643,7 +26643,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493396282196</v>
+        <v>1.74493384361267</v>
       </c>
       <c r="H906" t="n">
         <v>33950</v>
@@ -26846,7 +26846,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G913" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H913" t="n">
         <v>5250</v>
@@ -26904,7 +26904,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -27194,7 +27194,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895699501038</v>
+        <v>1.91895687580109</v>
       </c>
       <c r="H925" t="n">
         <v>26950</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539699077606</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27281,7 +27281,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480331897736</v>
+        <v>1.98480355739594</v>
       </c>
       <c r="H928" t="n">
         <v>17500</v>
@@ -27310,7 +27310,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G929" t="n">
-        <v>2.06946325302124</v>
+        <v>2.06946349143982</v>
       </c>
       <c r="H929" t="n">
         <v>53900</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H931" t="n">
         <v>264600</v>
@@ -27397,7 +27397,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115637779236</v>
+        <v>2.20115661621094</v>
       </c>
       <c r="H932" t="n">
         <v>82600</v>
@@ -27513,7 +27513,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H936" t="n">
         <v>10500</v>
@@ -27542,7 +27542,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005692481995</v>
+        <v>2.06005668640137</v>
       </c>
       <c r="H937" t="n">
         <v>8750</v>
@@ -27687,7 +27687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.15412306785583</v>
+        <v>2.15412330627441</v>
       </c>
       <c r="H942" t="n">
         <v>109200</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454262733459</v>
+        <v>2.46454286575317</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27803,7 +27803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>2.72792935371399</v>
+        <v>2.72792911529541</v>
       </c>
       <c r="H946" t="n">
         <v>286650</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.02894163131714</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -28151,7 +28151,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>2.70911574363708</v>
+        <v>2.70911598205566</v>
       </c>
       <c r="H958" t="n">
         <v>9100</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.8690288066864</v>
+        <v>2.86902904510498</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28238,7 +28238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H961" t="n">
         <v>175000</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28383,7 +28383,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H966" t="n">
         <v>283500</v>
@@ -28412,7 +28412,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224142074585</v>
+        <v>3.45224118232727</v>
       </c>
       <c r="H967" t="n">
         <v>114450</v>
@@ -28586,7 +28586,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3111412525177</v>
+        <v>3.31114149093628</v>
       </c>
       <c r="H973" t="n">
         <v>20300</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28760,7 +28760,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H979" t="n">
         <v>12950</v>
@@ -28905,7 +28905,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>3.01953530311584</v>
+        <v>3.01953506469727</v>
       </c>
       <c r="H984" t="n">
         <v>16450</v>
@@ -28934,7 +28934,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>3.01012849807739</v>
+        <v>3.01012873649597</v>
       </c>
       <c r="H985" t="n">
         <v>25900</v>
@@ -28992,7 +28992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H987" t="n">
         <v>16800</v>
@@ -29050,7 +29050,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G989" t="n">
-        <v>3.30173492431641</v>
+        <v>3.30173468589783</v>
       </c>
       <c r="H989" t="n">
         <v>43400</v>
@@ -29079,7 +29079,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H990" t="n">
         <v>30450</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292155265808</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470161437988</v>
+        <v>3.2547013759613</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29253,7 +29253,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H996" t="n">
         <v>14700</v>
@@ -29369,7 +29369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529480934143</v>
+        <v>3.24529504776001</v>
       </c>
       <c r="H1000" t="n">
         <v>30100</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29891,7 +29891,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1018" t="n">
         <v>108150</v>
@@ -29920,7 +29920,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1019" t="n">
         <v>10500</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30036,7 +30036,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1023" t="n">
         <v>6650</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30239,7 +30239,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241505622864</v>
+        <v>3.13241481781006</v>
       </c>
       <c r="H1030" t="n">
         <v>6300</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419511795044</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30877,7 +30877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597494125366</v>
+        <v>3.07597517967224</v>
       </c>
       <c r="H1052" t="n">
         <v>252000</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.02894163131714</v>
+        <v>3.02894186973572</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538174629211</v>
+        <v>3.08538150787354</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31370,7 +31370,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707510948181</v>
+        <v>3.21707487106323</v>
       </c>
       <c r="H1069" t="n">
         <v>30450</v>
@@ -31457,7 +31457,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351474761963</v>
+        <v>3.27351498603821</v>
       </c>
       <c r="H1072" t="n">
         <v>64750</v>
@@ -31544,7 +31544,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630756378174</v>
+        <v>3.54630780220032</v>
       </c>
       <c r="H1075" t="n">
         <v>125650</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393430709839</v>
+        <v>3.58393454551697</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31776,7 +31776,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1083" t="n">
         <v>11200</v>
@@ -31834,7 +31834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1085" t="n">
         <v>15750</v>
@@ -31892,7 +31892,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986792564392</v>
+        <v>3.48986768722534</v>
       </c>
       <c r="H1087" t="n">
         <v>16450</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800092697144</v>
+        <v>3.67800116539001</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32066,7 +32066,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562743186951</v>
+        <v>3.71562767028809</v>
       </c>
       <c r="H1093" t="n">
         <v>55300</v>
@@ -32153,7 +32153,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808786392212</v>
+        <v>3.51808762550354</v>
       </c>
       <c r="H1096" t="n">
         <v>23800</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292155265808</v>
+        <v>3.2829213142395</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -32269,7 +32269,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690123558044</v>
+        <v>3.53690099716187</v>
       </c>
       <c r="H1100" t="n">
         <v>28000</v>
@@ -32298,7 +32298,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046112060547</v>
+        <v>3.48046135902405</v>
       </c>
       <c r="H1101" t="n">
         <v>45850</v>
@@ -68496,6 +68496,35 @@
         <v>24850</v>
       </c>
       <c r="I2349" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2350" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="H2350" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I2350" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.03249001502991</v>
+        <v>3.03249025344849</v>
       </c>
       <c r="H3" t="n">
         <v>123200</v>
@@ -485,7 +485,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G4" t="n">
-        <v>3.19671130180359</v>
+        <v>3.19671106338501</v>
       </c>
       <c r="H4" t="n">
         <v>123200</v>
@@ -572,7 +572,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H7" t="n">
         <v>6650</v>
@@ -601,7 +601,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17058515548706</v>
+        <v>3.17058491706848</v>
       </c>
       <c r="H8" t="n">
         <v>36050</v>
@@ -659,7 +659,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>3.20044350624084</v>
+        <v>3.20044326782227</v>
       </c>
       <c r="H10" t="n">
         <v>7000</v>
@@ -688,7 +688,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.19111251831055</v>
+        <v>3.19111275672913</v>
       </c>
       <c r="H11" t="n">
         <v>3150</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>3.13512778282166</v>
+        <v>3.13512802124023</v>
       </c>
       <c r="H12" t="n">
         <v>5950</v>
@@ -746,7 +746,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.19111251831055</v>
+        <v>3.19111275672913</v>
       </c>
       <c r="H13" t="n">
         <v>1400</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H15" t="n">
         <v>11200</v>
@@ -833,7 +833,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18178176879883</v>
+        <v>3.18178200721741</v>
       </c>
       <c r="H16" t="n">
         <v>17500</v>
@@ -891,7 +891,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G18" t="n">
-        <v>3.26389217376709</v>
+        <v>3.26389241218567</v>
       </c>
       <c r="H18" t="n">
         <v>19250</v>
@@ -949,7 +949,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40198731422424</v>
+        <v>3.40198707580566</v>
       </c>
       <c r="H20" t="n">
         <v>22050</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.555011510849</v>
+        <v>3.55501103401184</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1007,7 +1007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>3.881587266922</v>
+        <v>3.88158702850342</v>
       </c>
       <c r="H22" t="n">
         <v>75600</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105966567993</v>
+        <v>3.86105942726135</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1094,7 +1094,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556401252747</v>
+        <v>3.96556377410889</v>
       </c>
       <c r="H25" t="n">
         <v>38150</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615503311157</v>
+        <v>4.23615550994873</v>
       </c>
       <c r="H27" t="n">
         <v>65450</v>
@@ -1181,7 +1181,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30147075653076</v>
+        <v>4.3014702796936</v>
       </c>
       <c r="H28" t="n">
         <v>25550</v>
@@ -1268,7 +1268,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521352767944</v>
+        <v>5.22521305084229</v>
       </c>
       <c r="H31" t="n">
         <v>145250</v>
@@ -1442,7 +1442,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092576980591</v>
+        <v>6.26092529296875</v>
       </c>
       <c r="H37" t="n">
         <v>89950</v>
@@ -1471,7 +1471,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>6.08830738067627</v>
+        <v>6.08830690383911</v>
       </c>
       <c r="H38" t="n">
         <v>90650</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761827468872</v>
+        <v>6.16761779785156</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1529,7 +1529,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>6.40088701248169</v>
+        <v>6.40088653564453</v>
       </c>
       <c r="H40" t="n">
         <v>82250</v>
@@ -1645,7 +1645,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G44" t="n">
-        <v>7.12401914596558</v>
+        <v>7.12401866912842</v>
       </c>
       <c r="H44" t="n">
         <v>91350</v>
@@ -1674,7 +1674,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876203536987</v>
+        <v>6.84876251220703</v>
       </c>
       <c r="H45" t="n">
         <v>72450</v>
@@ -1703,7 +1703,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080902099609</v>
+        <v>6.68080854415894</v>
       </c>
       <c r="H46" t="n">
         <v>27650</v>
@@ -1732,7 +1732,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.91407775878906</v>
+        <v>6.9140772819519</v>
       </c>
       <c r="H47" t="n">
         <v>35350</v>
@@ -1761,7 +1761,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.97939205169678</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H48" t="n">
         <v>25200</v>
@@ -1790,7 +1790,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000364303589</v>
+        <v>7.18000411987305</v>
       </c>
       <c r="H49" t="n">
         <v>59850</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.74451398849487</v>
+        <v>7.7445125579834</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1964,7 +1964,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>8.36034202575684</v>
+        <v>8.36034107208252</v>
       </c>
       <c r="H55" t="n">
         <v>65100</v>
@@ -1993,7 +1993,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G56" t="n">
-        <v>8.95750904083252</v>
+        <v>8.95750999450684</v>
       </c>
       <c r="H56" t="n">
         <v>139300</v>
@@ -2051,7 +2051,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303840637207</v>
+        <v>8.25303936004639</v>
       </c>
       <c r="H58" t="n">
         <v>105350</v>
@@ -2080,7 +2080,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G59" t="n">
-        <v>8.06175899505615</v>
+        <v>8.06175804138184</v>
       </c>
       <c r="H59" t="n">
         <v>66500</v>
@@ -2138,7 +2138,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42726802825928</v>
+        <v>7.42726755142212</v>
       </c>
       <c r="H61" t="n">
         <v>87500</v>
@@ -2167,7 +2167,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061380386353</v>
+        <v>7.38061428070068</v>
       </c>
       <c r="H62" t="n">
         <v>17150</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.110023021698</v>
+        <v>7.11002206802368</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2341,7 +2341,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>7.52524042129517</v>
+        <v>7.52523994445801</v>
       </c>
       <c r="H68" t="n">
         <v>49000</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252513885498</v>
+        <v>7.70252466201782</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2399,7 +2399,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858715057373</v>
+        <v>7.47858762741089</v>
       </c>
       <c r="H70" t="n">
         <v>35350</v>
@@ -2515,7 +2515,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H74" t="n">
         <v>15750</v>
@@ -2544,7 +2544,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G75" t="n">
-        <v>7.08669567108154</v>
+        <v>7.0866961479187</v>
       </c>
       <c r="H75" t="n">
         <v>5600</v>
@@ -2602,7 +2602,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H77" t="n">
         <v>12600</v>
@@ -2689,7 +2689,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>6.90474700927734</v>
+        <v>6.90474653244019</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>6.97939205169678</v>
+        <v>6.97939252853394</v>
       </c>
       <c r="H81" t="n">
         <v>11200</v>
@@ -2805,7 +2805,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>6.89541578292847</v>
+        <v>6.89541530609131</v>
       </c>
       <c r="H84" t="n">
         <v>2800</v>
@@ -2834,7 +2834,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>6.94673490524292</v>
+        <v>6.94673538208008</v>
       </c>
       <c r="H85" t="n">
         <v>3500</v>
@@ -2950,7 +2950,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466854095459</v>
+        <v>7.18466901779175</v>
       </c>
       <c r="H89" t="n">
         <v>7350</v>
@@ -2979,7 +2979,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>6.96073150634766</v>
+        <v>6.9607310295105</v>
       </c>
       <c r="H90" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>6.81143951416016</v>
+        <v>6.811439037323</v>
       </c>
       <c r="H93" t="n">
         <v>9800</v>
@@ -3124,7 +3124,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>6.74145889282227</v>
+        <v>6.74145841598511</v>
       </c>
       <c r="H95" t="n">
         <v>5950</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817125320435</v>
+        <v>6.57817029953003</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3269,7 +3269,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>6.49419450759888</v>
+        <v>6.49419403076172</v>
       </c>
       <c r="H100" t="n">
         <v>8750</v>
@@ -3298,7 +3298,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094562530518</v>
+        <v>6.19094514846802</v>
       </c>
       <c r="H101" t="n">
         <v>40250</v>
@@ -3327,7 +3327,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H102" t="n">
         <v>24850</v>
@@ -3356,7 +3356,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287490844727</v>
+        <v>6.44287538528442</v>
       </c>
       <c r="H103" t="n">
         <v>5600</v>
@@ -3414,7 +3414,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.39155626296997</v>
+        <v>6.39155578613281</v>
       </c>
       <c r="H105" t="n">
         <v>2100</v>
@@ -3501,7 +3501,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H108" t="n">
         <v>2100</v>
@@ -3530,7 +3530,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.512855052948</v>
+        <v>6.51285552978516</v>
       </c>
       <c r="H109" t="n">
         <v>2800</v>
@@ -3588,7 +3588,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>6.43821001052856</v>
+        <v>6.43820953369141</v>
       </c>
       <c r="H111" t="n">
         <v>1750</v>
@@ -3791,7 +3791,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>6.13962554931641</v>
+        <v>6.13962602615356</v>
       </c>
       <c r="H118" t="n">
         <v>1750</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.158287525177</v>
+        <v>6.15828704833984</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G120" t="n">
-        <v>6.19561004638672</v>
+        <v>6.19561052322388</v>
       </c>
       <c r="H120" t="n">
         <v>5600</v>
@@ -3936,7 +3936,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H123" t="n">
         <v>8400</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4052,7 +4052,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175100326538</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H127" t="n">
         <v>15750</v>
@@ -4081,7 +4081,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75706577301025</v>
+        <v>5.7570652961731</v>
       </c>
       <c r="H128" t="n">
         <v>5250</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175100326538</v>
+        <v>5.69175052642822</v>
       </c>
       <c r="H133" t="n">
         <v>16450</v>
@@ -4284,7 +4284,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245901107788</v>
+        <v>5.54245853424072</v>
       </c>
       <c r="H135" t="n">
         <v>20300</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104299545288</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81304979324341</v>
+        <v>5.81305074691772</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4458,7 +4458,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.9063572883606</v>
+        <v>5.90635776519775</v>
       </c>
       <c r="H141" t="n">
         <v>1400</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4632,7 +4632,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H147" t="n">
         <v>5600</v>
@@ -4661,7 +4661,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037326812744</v>
+        <v>5.85037279129028</v>
       </c>
       <c r="H148" t="n">
         <v>2450</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639652252197</v>
+        <v>5.76639604568481</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104299545288</v>
+        <v>5.84104204177856</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.5797815322876</v>
+        <v>5.57978200912476</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -5038,7 +5038,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5067,7 +5067,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17855978012085</v>
+        <v>5.17856025695801</v>
       </c>
       <c r="H162" t="n">
         <v>3850</v>
@@ -5096,7 +5096,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789052963257</v>
+        <v>5.18789100646973</v>
       </c>
       <c r="H163" t="n">
         <v>1400</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316701889038</v>
+        <v>5.39316749572754</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5154,7 +5154,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G165" t="n">
-        <v>5.33718252182007</v>
+        <v>5.33718204498291</v>
       </c>
       <c r="H165" t="n">
         <v>1750</v>
@@ -5183,7 +5183,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>5.34651279449463</v>
+        <v>5.34651327133179</v>
       </c>
       <c r="H166" t="n">
         <v>7350</v>
@@ -5212,7 +5212,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253652572632</v>
+        <v>5.26253700256348</v>
       </c>
       <c r="H167" t="n">
         <v>2800</v>
@@ -5357,7 +5357,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>5.333571434021</v>
+        <v>5.33357191085815</v>
       </c>
       <c r="H172" t="n">
         <v>4900</v>
@@ -5386,7 +5386,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H173" t="n">
         <v>16100</v>
@@ -5502,7 +5502,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.78509140014648</v>
+        <v>5.78509092330933</v>
       </c>
       <c r="H177" t="n">
         <v>8050</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.73805809020996</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5560,7 +5560,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83212423324585</v>
+        <v>5.83212375640869</v>
       </c>
       <c r="H179" t="n">
         <v>14700</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.73805809020996</v>
+        <v>5.7380576133728</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5618,7 +5618,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102478027344</v>
+        <v>5.69102430343628</v>
       </c>
       <c r="H181" t="n">
         <v>9100</v>
@@ -5850,7 +5850,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H189" t="n">
         <v>2450</v>
@@ -5879,7 +5879,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695720672607</v>
+        <v>5.59695768356323</v>
       </c>
       <c r="H190" t="n">
         <v>350</v>
@@ -5908,7 +5908,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>5.47467184066772</v>
+        <v>5.47467136383057</v>
       </c>
       <c r="H191" t="n">
         <v>2800</v>
@@ -5937,7 +5937,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G192" t="n">
-        <v>5.47467184066772</v>
+        <v>5.47467136383057</v>
       </c>
       <c r="H192" t="n">
         <v>5950</v>
@@ -5995,7 +5995,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G194" t="n">
-        <v>5.34297847747803</v>
+        <v>5.34297800064087</v>
       </c>
       <c r="H194" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G195" t="n">
-        <v>5.34297847747803</v>
+        <v>5.34297800064087</v>
       </c>
       <c r="H195" t="n">
         <v>2800</v>
@@ -6053,7 +6053,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>5.24891185760498</v>
+        <v>5.24891138076782</v>
       </c>
       <c r="H196" t="n">
         <v>25200</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950529098511</v>
+        <v>5.23950576782227</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6198,7 +6198,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348497390747</v>
+        <v>5.49348449707031</v>
       </c>
       <c r="H201" t="n">
         <v>32550</v>
@@ -6285,7 +6285,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>5.126624584198</v>
+        <v>5.12662506103516</v>
       </c>
       <c r="H204" t="n">
         <v>4900</v>
@@ -6343,7 +6343,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2206916809082</v>
+        <v>5.22069215774536</v>
       </c>
       <c r="H206" t="n">
         <v>1750</v>
@@ -6546,7 +6546,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.06077909469604</v>
+        <v>5.06077861785889</v>
       </c>
       <c r="H213" t="n">
         <v>10150</v>
@@ -6575,7 +6575,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>5.05137157440186</v>
+        <v>5.05137205123901</v>
       </c>
       <c r="H214" t="n">
         <v>1750</v>
@@ -6749,7 +6749,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>4.83501863479614</v>
+        <v>4.8350191116333</v>
       </c>
       <c r="H220" t="n">
         <v>10500</v>
@@ -6836,7 +6836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>4.89145851135254</v>
+        <v>4.8914589881897</v>
       </c>
       <c r="H223" t="n">
         <v>4900</v>
@@ -6865,7 +6865,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G224" t="n">
-        <v>4.87264585494995</v>
+        <v>4.87264537811279</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -7039,7 +7039,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.59985256195068</v>
+        <v>4.59985303878784</v>
       </c>
       <c r="H230" t="n">
         <v>1750</v>
@@ -7155,7 +7155,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>4.20006990432739</v>
+        <v>4.20007038116455</v>
       </c>
       <c r="H234" t="n">
         <v>6650</v>
@@ -7213,7 +7213,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>3.96490359306335</v>
+        <v>3.96490383148193</v>
       </c>
       <c r="H236" t="n">
         <v>12600</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29884052276611</v>
+        <v>4.2988395690918</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7329,7 +7329,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>4.31295013427734</v>
+        <v>4.31294965744019</v>
       </c>
       <c r="H240" t="n">
         <v>9100</v>
@@ -7445,7 +7445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>4.09189367294312</v>
+        <v>4.09189319610596</v>
       </c>
       <c r="H244" t="n">
         <v>7700</v>
@@ -7503,7 +7503,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H246" t="n">
         <v>1050</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312353134155</v>
+        <v>3.99312329292297</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7590,7 +7590,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842024803162</v>
+        <v>3.98842000961304</v>
       </c>
       <c r="H249" t="n">
         <v>5250</v>
@@ -7619,7 +7619,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>3.91316723823547</v>
+        <v>3.91316699981689</v>
       </c>
       <c r="H250" t="n">
         <v>16450</v>
@@ -7648,7 +7648,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147411346436</v>
+        <v>3.78147435188293</v>
       </c>
       <c r="H251" t="n">
         <v>12600</v>
@@ -7851,7 +7851,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664066314697</v>
+        <v>4.01664018630981</v>
       </c>
       <c r="H258" t="n">
         <v>73500</v>
@@ -7880,7 +7880,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.67329740524292</v>
+        <v>3.6732976436615</v>
       </c>
       <c r="H259" t="n">
         <v>77000</v>
@@ -7996,7 +7996,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H263" t="n">
         <v>3850</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8286,7 +8286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H273" t="n">
         <v>1050</v>
@@ -8315,7 +8315,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.60745096206665</v>
+        <v>3.60745120048523</v>
       </c>
       <c r="H274" t="n">
         <v>3500</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H288" t="n">
         <v>17500</v>
@@ -8750,7 +8750,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G289" t="n">
-        <v>3.49927449226379</v>
+        <v>3.49927473068237</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G290" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H290" t="n">
         <v>8750</v>
@@ -8808,7 +8808,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.4710545539856</v>
+        <v>3.47105431556702</v>
       </c>
       <c r="H291" t="n">
         <v>4900</v>
@@ -8895,7 +8895,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>3.62156081199646</v>
+        <v>3.62156105041504</v>
       </c>
       <c r="H294" t="n">
         <v>1750</v>
@@ -8924,7 +8924,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G295" t="n">
-        <v>3.71092391014099</v>
+        <v>3.71092414855957</v>
       </c>
       <c r="H295" t="n">
         <v>10500</v>
@@ -8953,7 +8953,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G296" t="n">
-        <v>3.65918755531311</v>
+        <v>3.65918779373169</v>
       </c>
       <c r="H296" t="n">
         <v>39900</v>
@@ -8982,7 +8982,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813133239746</v>
+        <v>3.43813109397888</v>
       </c>
       <c r="H297" t="n">
         <v>29400</v>
@@ -9011,7 +9011,7 @@
         <v>3.5</v>
       </c>
       <c r="G298" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H298" t="n">
         <v>51800</v>
@@ -9040,7 +9040,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H299" t="n">
         <v>5950</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.95368885993958</v>
+        <v>2.953688621521</v>
       </c>
       <c r="H300" t="n">
         <v>59850</v>
@@ -9156,7 +9156,7 @@
         <v>3.5</v>
       </c>
       <c r="G303" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H303" t="n">
         <v>22750</v>
@@ -9214,7 +9214,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373208999634</v>
+        <v>2.87373232841492</v>
       </c>
       <c r="H305" t="n">
         <v>23450</v>
@@ -9359,7 +9359,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H310" t="n">
         <v>2450</v>
@@ -9388,7 +9388,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H311" t="n">
         <v>5950</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H313" t="n">
         <v>15400</v>
@@ -9475,7 +9475,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H314" t="n">
         <v>23450</v>
@@ -9504,7 +9504,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H315" t="n">
         <v>8750</v>
@@ -9620,7 +9620,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>2.11179327964783</v>
+        <v>2.11179304122925</v>
       </c>
       <c r="H319" t="n">
         <v>10850</v>
@@ -9649,7 +9649,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H320" t="n">
         <v>21000</v>
@@ -9736,7 +9736,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H323" t="n">
         <v>16100</v>
@@ -9823,7 +9823,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654003143311</v>
+        <v>2.03654026985168</v>
       </c>
       <c r="H326" t="n">
         <v>2450</v>
@@ -9852,7 +9852,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H327" t="n">
         <v>53900</v>
@@ -9881,7 +9881,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H328" t="n">
         <v>4900</v>
@@ -9997,7 +9997,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H332" t="n">
         <v>7700</v>
@@ -10055,7 +10055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G334" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H334" t="n">
         <v>4550</v>
@@ -10171,7 +10171,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924653053284</v>
+        <v>1.81924641132355</v>
       </c>
       <c r="H338" t="n">
         <v>10150</v>
@@ -10229,7 +10229,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H340" t="n">
         <v>2100</v>
@@ -10316,7 +10316,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G343" t="n">
-        <v>1.79478919506073</v>
+        <v>1.79478907585144</v>
       </c>
       <c r="H343" t="n">
         <v>19600</v>
@@ -10345,7 +10345,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80983984470367</v>
+        <v>1.80983996391296</v>
       </c>
       <c r="H344" t="n">
         <v>19600</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10519,7 +10519,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G350" t="n">
-        <v>1.24732196331024</v>
+        <v>1.24732208251953</v>
       </c>
       <c r="H350" t="n">
         <v>36750</v>
@@ -10809,7 +10809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H360" t="n">
         <v>9450</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209755897522</v>
+        <v>1.55209743976593</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -10896,7 +10896,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.68002796173096</v>
+        <v>1.68002808094025</v>
       </c>
       <c r="H363" t="n">
         <v>22050</v>
@@ -11012,7 +11012,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928961753845</v>
+        <v>2.38928937911987</v>
       </c>
       <c r="H367" t="n">
         <v>146300</v>
@@ -11070,7 +11070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H369" t="n">
         <v>55650</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11273,7 +11273,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.563312292099</v>
+        <v>2.56331253051758</v>
       </c>
       <c r="H376" t="n">
         <v>99050</v>
@@ -11302,7 +11302,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H377" t="n">
         <v>26600</v>
@@ -11389,7 +11389,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G380" t="n">
-        <v>2.73733592033386</v>
+        <v>2.73733568191528</v>
       </c>
       <c r="H380" t="n">
         <v>15050</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975264549255</v>
+        <v>2.61975288391113</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11476,7 +11476,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H383" t="n">
         <v>11200</v>
@@ -11650,7 +11650,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H389" t="n">
         <v>2800</v>
@@ -11679,7 +11679,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983934402466</v>
+        <v>2.45983958244324</v>
       </c>
       <c r="H390" t="n">
         <v>1750</v>
@@ -11708,7 +11708,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386249542236</v>
+        <v>2.63386225700378</v>
       </c>
       <c r="H391" t="n">
         <v>26250</v>
@@ -11737,7 +11737,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G392" t="n">
-        <v>2.61504912376404</v>
+        <v>2.61504936218262</v>
       </c>
       <c r="H392" t="n">
         <v>23450</v>
@@ -11824,7 +11824,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216960906982</v>
+        <v>2.50216937065125</v>
       </c>
       <c r="H395" t="n">
         <v>4900</v>
@@ -11882,7 +11882,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11940,7 +11940,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.41750931739807</v>
+        <v>2.41750955581665</v>
       </c>
       <c r="H399" t="n">
         <v>4550</v>
@@ -11969,7 +11969,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H400" t="n">
         <v>3850</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H402" t="n">
         <v>8750</v>
@@ -12056,7 +12056,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G403" t="n">
-        <v>2.4081027507782</v>
+        <v>2.40810298919678</v>
       </c>
       <c r="H403" t="n">
         <v>14000</v>
@@ -12085,7 +12085,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H404" t="n">
         <v>5950</v>
@@ -12114,7 +12114,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276280403137</v>
+        <v>2.49276304244995</v>
       </c>
       <c r="H405" t="n">
         <v>1050</v>
@@ -12143,7 +12143,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>2.44572925567627</v>
+        <v>2.44572949409485</v>
       </c>
       <c r="H406" t="n">
         <v>7700</v>
@@ -12317,7 +12317,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933308601379</v>
+        <v>2.30933284759521</v>
       </c>
       <c r="H412" t="n">
         <v>44100</v>
@@ -12346,7 +12346,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.31873989105225</v>
+        <v>2.31873965263367</v>
       </c>
       <c r="H413" t="n">
         <v>10150</v>
@@ -12723,7 +12723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056294441223</v>
+        <v>2.21056318283081</v>
       </c>
       <c r="H426" t="n">
         <v>1750</v>
@@ -12752,7 +12752,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H427" t="n">
         <v>21000</v>
@@ -12781,7 +12781,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H428" t="n">
         <v>43400</v>
@@ -12810,7 +12810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H429" t="n">
         <v>20300</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691612243652</v>
+        <v>2.42691588401794</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12897,7 +12897,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G432" t="n">
-        <v>2.36106967926025</v>
+        <v>2.36106944084167</v>
       </c>
       <c r="H432" t="n">
         <v>6300</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -12984,7 +12984,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.3516628742218</v>
+        <v>2.35166311264038</v>
       </c>
       <c r="H435" t="n">
         <v>11200</v>
@@ -13071,7 +13071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H438" t="n">
         <v>5600</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H439" t="n">
         <v>350</v>
@@ -13158,7 +13158,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>2.23878312110901</v>
+        <v>2.23878335952759</v>
       </c>
       <c r="H441" t="n">
         <v>11200</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H442" t="n">
         <v>4900</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H443" t="n">
         <v>350</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24818992614746</v>
+        <v>2.24819016456604</v>
       </c>
       <c r="H445" t="n">
         <v>350</v>
@@ -13332,7 +13332,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27640962600708</v>
+        <v>2.27640986442566</v>
       </c>
       <c r="H447" t="n">
         <v>2800</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.30462980270386</v>
+        <v>2.30462956428528</v>
       </c>
       <c r="H450" t="n">
         <v>4550</v>
@@ -13477,7 +13477,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G452" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H452" t="n">
         <v>10850</v>
@@ -13535,7 +13535,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13530993461609</v>
+        <v>2.13531017303467</v>
       </c>
       <c r="H454" t="n">
         <v>9800</v>
@@ -13651,7 +13651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H458" t="n">
         <v>14700</v>
@@ -13709,7 +13709,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G460" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H460" t="n">
         <v>5600</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -13999,7 +13999,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H470" t="n">
         <v>3850</v>
@@ -14086,7 +14086,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H473" t="n">
         <v>3500</v>
@@ -14144,7 +14144,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H475" t="n">
         <v>2100</v>
@@ -14173,7 +14173,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.01302337646484</v>
+        <v>2.01302361488342</v>
       </c>
       <c r="H477" t="n">
         <v>25200</v>
@@ -14347,7 +14347,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H482" t="n">
         <v>1400</v>
@@ -14376,7 +14376,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>1.95658361911774</v>
+        <v>1.95658349990845</v>
       </c>
       <c r="H483" t="n">
         <v>10500</v>
@@ -14405,7 +14405,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H484" t="n">
         <v>1050</v>
@@ -14492,7 +14492,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H487" t="n">
         <v>20650</v>
@@ -14521,7 +14521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G488" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H488" t="n">
         <v>2450</v>
@@ -14695,7 +14695,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H494" t="n">
         <v>6650</v>
@@ -14724,7 +14724,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G498" t="n">
-        <v>1.87192380428314</v>
+        <v>1.87192368507385</v>
       </c>
       <c r="H498" t="n">
         <v>350</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15072,7 +15072,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H507" t="n">
         <v>19250</v>
@@ -15101,7 +15101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H508" t="n">
         <v>700</v>
@@ -15130,7 +15130,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H509" t="n">
         <v>6650</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H518" t="n">
         <v>10150</v>
@@ -15420,7 +15420,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H519" t="n">
         <v>7000</v>
@@ -15449,7 +15449,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G520" t="n">
-        <v>1.73082399368286</v>
+        <v>1.73082411289215</v>
       </c>
       <c r="H520" t="n">
         <v>2100</v>
@@ -15478,7 +15478,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H521" t="n">
         <v>1050</v>
@@ -15507,7 +15507,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G522" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H522" t="n">
         <v>9100</v>
@@ -15536,7 +15536,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H523" t="n">
         <v>3150</v>
@@ -15565,7 +15565,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H524" t="n">
         <v>3850</v>
@@ -15594,7 +15594,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434064865112</v>
+        <v>1.75434052944183</v>
       </c>
       <c r="H528" t="n">
         <v>1400</v>
@@ -15710,7 +15710,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.7496372461319</v>
+        <v>1.74963736534119</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023067951202</v>
+        <v>1.74023056030273</v>
       </c>
       <c r="H530" t="n">
         <v>3850</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G537" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H537" t="n">
         <v>2800</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548380851746</v>
+        <v>1.81548368930817</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16290,7 +16290,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H549" t="n">
         <v>1050</v>
@@ -16319,7 +16319,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H550" t="n">
         <v>141050</v>
@@ -16348,7 +16348,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17293643951416</v>
+        <v>2.17293667793274</v>
       </c>
       <c r="H551" t="n">
         <v>140000</v>
@@ -16377,7 +16377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421012401581</v>
+        <v>1.99421000480652</v>
       </c>
       <c r="H552" t="n">
         <v>46200</v>
@@ -16406,7 +16406,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G553" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H553" t="n">
         <v>66500</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16551,7 +16551,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H558" t="n">
         <v>9450</v>
@@ -16667,7 +16667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H562" t="n">
         <v>3500</v>
@@ -16696,7 +16696,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H563" t="n">
         <v>5600</v>
@@ -16812,7 +16812,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H567" t="n">
         <v>9800</v>
@@ -16899,7 +16899,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H570" t="n">
         <v>2100</v>
@@ -16986,7 +16986,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.82959377765656</v>
+        <v>1.82959389686584</v>
       </c>
       <c r="H573" t="n">
         <v>7000</v>
@@ -17015,7 +17015,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H574" t="n">
         <v>1750</v>
@@ -17044,7 +17044,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>1.82489061355591</v>
+        <v>1.82489049434662</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.81078040599823</v>
+        <v>1.81078052520752</v>
       </c>
       <c r="H577" t="n">
         <v>4200</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.79196727275848</v>
+        <v>1.7919670343399</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17276,7 +17276,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G583" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H583" t="n">
         <v>19950</v>
@@ -17305,7 +17305,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G584" t="n">
-        <v>1.75904381275177</v>
+        <v>1.75904393196106</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G589" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H589" t="n">
         <v>2450</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315390110016</v>
+        <v>1.77315378189087</v>
       </c>
       <c r="H590" t="n">
         <v>1050</v>
@@ -17566,7 +17566,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72612059116364</v>
+        <v>1.72612071037292</v>
       </c>
       <c r="H593" t="n">
         <v>4550</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H596" t="n">
         <v>1400</v>
@@ -17740,7 +17740,7 @@
         <v>1.75</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H599" t="n">
         <v>5250</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -17827,7 +17827,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>1.66497731208801</v>
+        <v>1.6649774312973</v>
       </c>
       <c r="H602" t="n">
         <v>350</v>
@@ -17914,7 +17914,7 @@
         <v>1.75</v>
       </c>
       <c r="G605" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H605" t="n">
         <v>350</v>
@@ -17943,7 +17943,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G606" t="n">
-        <v>1.76845049858093</v>
+        <v>1.76845061779022</v>
       </c>
       <c r="H606" t="n">
         <v>12250</v>
@@ -17972,7 +17972,7 @@
         <v>1.75</v>
       </c>
       <c r="G607" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H607" t="n">
         <v>5950</v>
@@ -18001,7 +18001,7 @@
         <v>1.75</v>
       </c>
       <c r="G608" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H608" t="n">
         <v>1050</v>
@@ -18030,7 +18030,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G609" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H609" t="n">
         <v>8750</v>
@@ -18059,7 +18059,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379068374634</v>
+        <v>1.68379056453705</v>
       </c>
       <c r="H610" t="n">
         <v>2800</v>
@@ -18088,7 +18088,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H611" t="n">
         <v>11200</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735068798065</v>
+        <v>1.62735092639923</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18378,7 +18378,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5191742181778</v>
+        <v>1.51917433738708</v>
       </c>
       <c r="H621" t="n">
         <v>6300</v>
@@ -18407,7 +18407,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>1.50976753234863</v>
+        <v>1.50976765155792</v>
       </c>
       <c r="H622" t="n">
         <v>9800</v>
@@ -18523,7 +18523,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205409049988</v>
+        <v>1.63205397129059</v>
       </c>
       <c r="H626" t="n">
         <v>30450</v>
@@ -18726,7 +18726,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091081142426</v>
+        <v>1.57091093063354</v>
       </c>
       <c r="H633" t="n">
         <v>10850</v>
@@ -18755,7 +18755,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387750148773</v>
+        <v>1.52387762069702</v>
       </c>
       <c r="H634" t="n">
         <v>2450</v>
@@ -18871,7 +18871,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56620740890503</v>
+        <v>1.56620752811432</v>
       </c>
       <c r="H638" t="n">
         <v>10500</v>
@@ -18929,7 +18929,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H640" t="n">
         <v>8050</v>
@@ -19016,7 +19016,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739415645599</v>
+        <v>1.54739427566528</v>
       </c>
       <c r="H643" t="n">
         <v>21000</v>
@@ -19074,7 +19074,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625099658966</v>
+        <v>1.48625111579895</v>
       </c>
       <c r="H646" t="n">
         <v>5600</v>
@@ -19248,7 +19248,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.45803105831146</v>
+        <v>1.45803093910217</v>
       </c>
       <c r="H651" t="n">
         <v>17150</v>
@@ -19335,7 +19335,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G654" t="n">
-        <v>1.49565756320953</v>
+        <v>1.49565768241882</v>
       </c>
       <c r="H654" t="n">
         <v>10150</v>
@@ -19625,7 +19625,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>0.818378746509552</v>
+        <v>0.818378686904907</v>
       </c>
       <c r="H664" t="n">
         <v>10850</v>
@@ -19712,7 +19712,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>0.954775214195251</v>
+        <v>0.954775154590607</v>
       </c>
       <c r="H667" t="n">
         <v>350</v>
@@ -19741,7 +19741,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106610298157</v>
+        <v>0.886106550693512</v>
       </c>
       <c r="H668" t="n">
         <v>2450</v>
@@ -19770,7 +19770,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G669" t="n">
-        <v>0.919970512390137</v>
+        <v>0.919970571994781</v>
       </c>
       <c r="H669" t="n">
         <v>2100</v>
@@ -19857,7 +19857,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G672" t="n">
-        <v>0.935021162033081</v>
+        <v>0.935021221637726</v>
       </c>
       <c r="H672" t="n">
         <v>5950</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326548576355</v>
+        <v>0.914326608181</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19973,7 +19973,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.978291809558868</v>
+        <v>0.978291749954224</v>
       </c>
       <c r="H676" t="n">
         <v>8750</v>
@@ -20118,7 +20118,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G681" t="n">
-        <v>0.992401778697968</v>
+        <v>0.992401719093323</v>
       </c>
       <c r="H681" t="n">
         <v>3500</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H684" t="n">
         <v>47250</v>
@@ -20263,7 +20263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H686" t="n">
         <v>6650</v>
@@ -20437,7 +20437,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H692" t="n">
         <v>4550</v>
@@ -20611,7 +20611,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H698" t="n">
         <v>3850</v>
@@ -20640,7 +20640,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H699" t="n">
         <v>2450</v>
@@ -20756,7 +20756,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H703" t="n">
         <v>16100</v>
@@ -20785,7 +20785,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H704" t="n">
         <v>2800</v>
@@ -20814,7 +20814,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H705" t="n">
         <v>2450</v>
@@ -20901,7 +20901,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H708" t="n">
         <v>13650</v>
@@ -20959,7 +20959,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.13820481300354</v>
+        <v>1.13820493221283</v>
       </c>
       <c r="H710" t="n">
         <v>1050</v>
@@ -20988,7 +20988,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409496307373</v>
+        <v>1.12409508228302</v>
       </c>
       <c r="H711" t="n">
         <v>1750</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H713" t="n">
         <v>2450</v>
@@ -21075,7 +21075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G714" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H714" t="n">
         <v>4900</v>
@@ -21104,7 +21104,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H715" t="n">
         <v>128100</v>
@@ -21336,7 +21336,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G723" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H723" t="n">
         <v>7350</v>
@@ -21365,7 +21365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H724" t="n">
         <v>21350</v>
@@ -21394,7 +21394,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H727" t="n">
         <v>2450</v>
@@ -21481,7 +21481,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G728" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H728" t="n">
         <v>700</v>
@@ -21510,7 +21510,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H729" t="n">
         <v>1750</v>
@@ -21539,7 +21539,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H731" t="n">
         <v>1050</v>
@@ -21597,7 +21597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G733" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H734" t="n">
         <v>2100</v>
@@ -21684,7 +21684,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G735" t="n">
-        <v>1.20875465869904</v>
+        <v>1.20875477790833</v>
       </c>
       <c r="H735" t="n">
         <v>9450</v>
@@ -21742,7 +21742,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G737" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H737" t="n">
         <v>60550</v>
@@ -21771,7 +21771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H738" t="n">
         <v>22750</v>
@@ -21945,7 +21945,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H744" t="n">
         <v>1050</v>
@@ -22119,7 +22119,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H750" t="n">
         <v>350</v>
@@ -22148,7 +22148,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H753" t="n">
         <v>8750</v>
@@ -22235,7 +22235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G754" t="n">
-        <v>1.35455799102783</v>
+        <v>1.35455787181854</v>
       </c>
       <c r="H754" t="n">
         <v>35350</v>
@@ -22438,7 +22438,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G761" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H761" t="n">
         <v>7700</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H763" t="n">
         <v>700</v>
@@ -22525,7 +22525,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G764" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H764" t="n">
         <v>1050</v>
@@ -22554,7 +22554,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H765" t="n">
         <v>3150</v>
@@ -22612,7 +22612,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H767" t="n">
         <v>350</v>
@@ -22641,7 +22641,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H768" t="n">
         <v>700</v>
@@ -22873,7 +22873,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G776" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H776" t="n">
         <v>6300</v>
@@ -22931,7 +22931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H778" t="n">
         <v>10500</v>
@@ -22960,7 +22960,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G780" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H781" t="n">
         <v>14000</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345806121826</v>
+        <v>1.21345794200897</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H787" t="n">
         <v>700</v>
@@ -23221,7 +23221,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H788" t="n">
         <v>14000</v>
@@ -23308,7 +23308,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G791" t="n">
-        <v>1.21816146373749</v>
+        <v>1.2181613445282</v>
       </c>
       <c r="H791" t="n">
         <v>3500</v>
@@ -23337,7 +23337,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H792" t="n">
         <v>4900</v>
@@ -23453,7 +23453,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>1.13820481300354</v>
+        <v>1.13820493221283</v>
       </c>
       <c r="H796" t="n">
         <v>1050</v>
@@ -23482,7 +23482,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H797" t="n">
         <v>7700</v>
@@ -23511,7 +23511,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H798" t="n">
         <v>12600</v>
@@ -23569,7 +23569,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H800" t="n">
         <v>2800</v>
@@ -23598,7 +23598,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H801" t="n">
         <v>5250</v>
@@ -23656,7 +23656,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.2040513753891</v>
+        <v>1.20405149459839</v>
       </c>
       <c r="H803" t="n">
         <v>17850</v>
@@ -23685,7 +23685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H804" t="n">
         <v>12600</v>
@@ -23714,7 +23714,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108480453491</v>
+        <v>1.25108468532562</v>
       </c>
       <c r="H805" t="n">
         <v>18550</v>
@@ -23772,7 +23772,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G807" t="n">
-        <v>1.33574461936951</v>
+        <v>1.33574450016022</v>
       </c>
       <c r="H807" t="n">
         <v>15750</v>
@@ -23801,7 +23801,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H808" t="n">
         <v>8050</v>
@@ -23888,7 +23888,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H811" t="n">
         <v>12600</v>
@@ -23917,7 +23917,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G812" t="n">
-        <v>1.33574461936951</v>
+        <v>1.33574450016022</v>
       </c>
       <c r="H812" t="n">
         <v>6300</v>
@@ -23975,7 +23975,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638140201569</v>
+        <v>1.24638152122498</v>
       </c>
       <c r="H814" t="n">
         <v>4550</v>
@@ -24033,7 +24033,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G816" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H816" t="n">
         <v>6650</v>
@@ -24062,7 +24062,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H817" t="n">
         <v>8400</v>
@@ -24120,7 +24120,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.1758314371109</v>
+        <v>1.17583155632019</v>
       </c>
       <c r="H819" t="n">
         <v>13650</v>
@@ -24149,7 +24149,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H820" t="n">
         <v>16100</v>
@@ -24178,7 +24178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464480876923</v>
+        <v>1.19464468955994</v>
       </c>
       <c r="H822" t="n">
         <v>3850</v>
@@ -24323,7 +24323,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G826" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H826" t="n">
         <v>700</v>
@@ -24381,7 +24381,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G828" t="n">
-        <v>1.15231490135193</v>
+        <v>1.15231478214264</v>
       </c>
       <c r="H828" t="n">
         <v>3500</v>
@@ -24410,7 +24410,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H829" t="n">
         <v>40600</v>
@@ -24497,7 +24497,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>1.35455799102783</v>
+        <v>1.35455787181854</v>
       </c>
       <c r="H832" t="n">
         <v>52500</v>
@@ -24555,7 +24555,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G834" t="n">
-        <v>1.36866796016693</v>
+        <v>1.36866784095764</v>
       </c>
       <c r="H834" t="n">
         <v>12600</v>
@@ -24642,7 +24642,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.26519477367401</v>
+        <v>1.26519465446472</v>
       </c>
       <c r="H837" t="n">
         <v>60200</v>
@@ -24671,7 +24671,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H838" t="n">
         <v>13300</v>
@@ -24787,7 +24787,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>1.39688789844513</v>
+        <v>1.39688777923584</v>
       </c>
       <c r="H842" t="n">
         <v>23800</v>
@@ -24845,7 +24845,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47684442996979</v>
+        <v>1.4768443107605</v>
       </c>
       <c r="H844" t="n">
         <v>129500</v>
@@ -24903,7 +24903,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G846" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H846" t="n">
         <v>25900</v>
@@ -25106,7 +25106,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H853" t="n">
         <v>1750</v>
@@ -25135,7 +25135,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -25222,7 +25222,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G857" t="n">
-        <v>1.39688789844513</v>
+        <v>1.39688777923584</v>
       </c>
       <c r="H857" t="n">
         <v>7700</v>
@@ -25251,7 +25251,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G858" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H858" t="n">
         <v>24500</v>
@@ -25280,7 +25280,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.45332777500153</v>
+        <v>1.45332765579224</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G863" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H863" t="n">
         <v>5250</v>
@@ -25454,7 +25454,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H865" t="n">
         <v>4900</v>
@@ -25570,7 +25570,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337124347687</v>
+        <v>1.37337112426758</v>
       </c>
       <c r="H869" t="n">
         <v>3850</v>
@@ -25686,7 +25686,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H873" t="n">
         <v>4550</v>
@@ -25744,7 +25744,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.33104121685028</v>
+        <v>1.33104133605957</v>
       </c>
       <c r="H875" t="n">
         <v>350</v>
@@ -25773,7 +25773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H876" t="n">
         <v>4200</v>
@@ -25802,7 +25802,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282139778137</v>
+        <v>1.30282127857208</v>
       </c>
       <c r="H877" t="n">
         <v>1400</v>
@@ -25860,7 +25860,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>1.30752456188202</v>
+        <v>1.30752468109131</v>
       </c>
       <c r="H879" t="n">
         <v>3850</v>
@@ -26150,7 +26150,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H889" t="n">
         <v>6650</v>
@@ -26179,7 +26179,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.22286462783813</v>
+        <v>1.22286474704742</v>
       </c>
       <c r="H890" t="n">
         <v>7350</v>
@@ -26208,7 +26208,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H891" t="n">
         <v>11900</v>
@@ -26237,7 +26237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693124771118</v>
+        <v>1.31693112850189</v>
       </c>
       <c r="H892" t="n">
         <v>7000</v>
@@ -26295,7 +26295,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>1.31222796440125</v>
+        <v>1.31222784519196</v>
       </c>
       <c r="H894" t="n">
         <v>14000</v>
@@ -26498,7 +26498,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H901" t="n">
         <v>91700</v>
@@ -26527,7 +26527,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G902" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H902" t="n">
         <v>47600</v>
@@ -26643,7 +26643,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>1.74493384361267</v>
+        <v>1.74493396282196</v>
       </c>
       <c r="H906" t="n">
         <v>33950</v>
@@ -26846,7 +26846,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G913" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H913" t="n">
         <v>5250</v>
@@ -26904,7 +26904,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.65086734294891</v>
+        <v>1.6508674621582</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -26991,7 +26991,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G918" t="n">
-        <v>1.67908728122711</v>
+        <v>1.6790874004364</v>
       </c>
       <c r="H918" t="n">
         <v>3150</v>
@@ -27020,7 +27020,7 @@
         <v>1.75</v>
       </c>
       <c r="G919" t="n">
-        <v>1.64616405963898</v>
+        <v>1.64616417884827</v>
       </c>
       <c r="H919" t="n">
         <v>9100</v>
@@ -27049,7 +27049,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G920" t="n">
-        <v>1.87662708759308</v>
+        <v>1.87662696838379</v>
       </c>
       <c r="H920" t="n">
         <v>215950</v>
@@ -27078,7 +27078,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G921" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H921" t="n">
         <v>352450</v>
@@ -27107,7 +27107,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073705673218</v>
+        <v>1.89073717594147</v>
       </c>
       <c r="H922" t="n">
         <v>129500</v>
@@ -27136,7 +27136,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717681407928</v>
+        <v>1.94717669487</v>
       </c>
       <c r="H923" t="n">
         <v>32550</v>
@@ -27194,7 +27194,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>1.91895687580109</v>
+        <v>1.91895699501038</v>
       </c>
       <c r="H925" t="n">
         <v>26950</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539675235748</v>
+        <v>1.97539687156677</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27281,7 +27281,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G928" t="n">
-        <v>1.98480355739594</v>
+        <v>1.98480343818665</v>
       </c>
       <c r="H928" t="n">
         <v>17500</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H931" t="n">
         <v>264600</v>
@@ -27397,7 +27397,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.20115661621094</v>
+        <v>2.20115637779236</v>
       </c>
       <c r="H932" t="n">
         <v>82600</v>
@@ -27513,7 +27513,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H936" t="n">
         <v>10500</v>
@@ -27542,7 +27542,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>2.06005668640137</v>
+        <v>2.06005692481995</v>
       </c>
       <c r="H937" t="n">
         <v>8750</v>
@@ -27600,7 +27600,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H939" t="n">
         <v>46200</v>
@@ -27629,7 +27629,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G940" t="n">
-        <v>2.00361680984497</v>
+        <v>2.00361704826355</v>
       </c>
       <c r="H940" t="n">
         <v>2100</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>2.08827662467957</v>
+        <v>2.08827686309814</v>
       </c>
       <c r="H941" t="n">
         <v>39900</v>
@@ -27687,7 +27687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.15412330627441</v>
+        <v>2.15412306785583</v>
       </c>
       <c r="H942" t="n">
         <v>109200</v>
@@ -27716,7 +27716,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>2.17293643951416</v>
+        <v>2.17293667793274</v>
       </c>
       <c r="H943" t="n">
         <v>154700</v>
@@ -27745,7 +27745,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.45513606071472</v>
+        <v>2.4551362991333</v>
       </c>
       <c r="H944" t="n">
         <v>203700</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454286575317</v>
+        <v>2.46454238891602</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27919,7 +27919,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G950" t="n">
-        <v>2.99131512641907</v>
+        <v>2.99131536483765</v>
       </c>
       <c r="H950" t="n">
         <v>126350</v>
@@ -27948,7 +27948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.97250199317932</v>
+        <v>2.9725022315979</v>
       </c>
       <c r="H951" t="n">
         <v>31150</v>
@@ -28151,7 +28151,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>2.70911598205566</v>
+        <v>2.70911574363708</v>
       </c>
       <c r="H958" t="n">
         <v>9100</v>
@@ -28180,7 +28180,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G959" t="n">
-        <v>2.73733592033386</v>
+        <v>2.73733568191528</v>
       </c>
       <c r="H959" t="n">
         <v>13300</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.86902904510498</v>
+        <v>2.8690288066864</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28238,7 +28238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H961" t="n">
         <v>175000</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28354,7 +28354,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>3.32995462417603</v>
+        <v>3.3299548625946</v>
       </c>
       <c r="H965" t="n">
         <v>91700</v>
@@ -28383,7 +28383,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H966" t="n">
         <v>283500</v>
@@ -28412,7 +28412,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>3.45224118232727</v>
+        <v>3.45224142074585</v>
       </c>
       <c r="H967" t="n">
         <v>114450</v>
@@ -28441,7 +28441,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H968" t="n">
         <v>131250</v>
@@ -28470,7 +28470,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H969" t="n">
         <v>18550</v>
@@ -28557,7 +28557,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580106735229</v>
+        <v>3.39580130577087</v>
       </c>
       <c r="H972" t="n">
         <v>29400</v>
@@ -28586,7 +28586,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.31114149093628</v>
+        <v>3.3111412525177</v>
       </c>
       <c r="H973" t="n">
         <v>20300</v>
@@ -28615,7 +28615,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H974" t="n">
         <v>31500</v>
@@ -28644,7 +28644,7 @@
         <v>3.5</v>
       </c>
       <c r="G975" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H975" t="n">
         <v>25200</v>
@@ -28673,7 +28673,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>3.32995462417603</v>
+        <v>3.3299548625946</v>
       </c>
       <c r="H976" t="n">
         <v>8050</v>
@@ -28702,7 +28702,7 @@
         <v>3.5</v>
       </c>
       <c r="G977" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H977" t="n">
         <v>16450</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.2547013759613</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28847,7 +28847,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H982" t="n">
         <v>30800</v>
@@ -28905,7 +28905,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>3.01953506469727</v>
+        <v>3.01953530311584</v>
       </c>
       <c r="H984" t="n">
         <v>16450</v>
@@ -28992,7 +28992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775500297546</v>
+        <v>3.04775524139404</v>
       </c>
       <c r="H987" t="n">
         <v>16800</v>
@@ -29021,7 +29021,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H988" t="n">
         <v>11550</v>
@@ -29050,7 +29050,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G989" t="n">
-        <v>3.30173468589783</v>
+        <v>3.30173492431641</v>
       </c>
       <c r="H989" t="n">
         <v>43400</v>
@@ -29079,7 +29079,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H990" t="n">
         <v>30450</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.2829213142395</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.2547013759613</v>
+        <v>3.25470185279846</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29282,7 +29282,7 @@
         <v>3.5</v>
       </c>
       <c r="G997" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H997" t="n">
         <v>9100</v>
@@ -29311,7 +29311,7 @@
         <v>3.5</v>
       </c>
       <c r="G998" t="n">
-        <v>3.29232811927795</v>
+        <v>3.29232835769653</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H999" t="n">
         <v>2800</v>
@@ -29427,7 +29427,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1002" t="n">
         <v>2450</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29485,7 +29485,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1004" t="n">
         <v>2450</v>
@@ -29659,7 +29659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H1010" t="n">
         <v>2100</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29862,7 +29862,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.36758136749268</v>
+        <v>3.3675811290741</v>
       </c>
       <c r="H1017" t="n">
         <v>68950</v>
@@ -29891,7 +29891,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1018" t="n">
         <v>108150</v>
@@ -29920,7 +29920,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1019" t="n">
         <v>10500</v>
@@ -29978,7 +29978,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1021" t="n">
         <v>8050</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30036,7 +30036,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1023" t="n">
         <v>6650</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30094,7 +30094,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1025" t="n">
         <v>9450</v>
@@ -30123,7 +30123,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1026" t="n">
         <v>3500</v>
@@ -30239,7 +30239,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.13241481781006</v>
+        <v>3.13241505622864</v>
       </c>
       <c r="H1030" t="n">
         <v>6300</v>
@@ -30268,7 +30268,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1031" t="n">
         <v>1400</v>
@@ -30297,7 +30297,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1032" t="n">
         <v>14700</v>
@@ -30326,7 +30326,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1033" t="n">
         <v>6300</v>
@@ -30355,7 +30355,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1034" t="n">
         <v>7000</v>
@@ -30413,7 +30413,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1036" t="n">
         <v>45850</v>
@@ -30442,7 +30442,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1037" t="n">
         <v>14700</v>
@@ -30558,7 +30558,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1041" t="n">
         <v>7350</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30616,7 +30616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1043" t="n">
         <v>2800</v>
@@ -30645,7 +30645,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1044" t="n">
         <v>4900</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30732,7 +30732,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1047" t="n">
         <v>2100</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419511795044</v>
+        <v>3.10419487953186</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30819,7 +30819,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.17944836616516</v>
+        <v>3.17944860458374</v>
       </c>
       <c r="H1050" t="n">
         <v>34300</v>
@@ -30848,7 +30848,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.35817456245422</v>
+        <v>3.3581748008728</v>
       </c>
       <c r="H1051" t="n">
         <v>278600</v>
@@ -30964,7 +30964,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478831291199</v>
+        <v>3.09478855133057</v>
       </c>
       <c r="H1055" t="n">
         <v>17850</v>
@@ -31022,7 +31022,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834843635559</v>
+        <v>3.03834867477417</v>
       </c>
       <c r="H1057" t="n">
         <v>9100</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31225,7 +31225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.99131512641907</v>
+        <v>2.99131536483765</v>
       </c>
       <c r="H1064" t="n">
         <v>9800</v>
@@ -31254,7 +31254,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.18885493278503</v>
+        <v>3.18885517120361</v>
       </c>
       <c r="H1065" t="n">
         <v>95550</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538150787354</v>
+        <v>3.08538198471069</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31312,7 +31312,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122818946838</v>
+        <v>3.15122842788696</v>
       </c>
       <c r="H1067" t="n">
         <v>21700</v>
@@ -31341,7 +31341,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182162284851</v>
+        <v>3.14182186126709</v>
       </c>
       <c r="H1068" t="n">
         <v>42350</v>
@@ -31370,7 +31370,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707487106323</v>
+        <v>3.21707510948181</v>
       </c>
       <c r="H1069" t="n">
         <v>30450</v>
@@ -31457,7 +31457,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.27351498603821</v>
+        <v>3.27351474761963</v>
       </c>
       <c r="H1072" t="n">
         <v>64750</v>
@@ -31544,7 +31544,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630780220032</v>
+        <v>3.54630756378174</v>
       </c>
       <c r="H1075" t="n">
         <v>125650</v>
@@ -31631,7 +31631,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.75325417518616</v>
+        <v>3.75325393676758</v>
       </c>
       <c r="H1078" t="n">
         <v>55650</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393454551697</v>
+        <v>3.58393406867981</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31776,7 +31776,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1083" t="n">
         <v>11200</v>
@@ -31834,7 +31834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1085" t="n">
         <v>15750</v>
@@ -31892,7 +31892,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.48986768722534</v>
+        <v>3.48986792564392</v>
       </c>
       <c r="H1087" t="n">
         <v>16450</v>
@@ -31979,7 +31979,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512093544006</v>
+        <v>3.56512117385864</v>
       </c>
       <c r="H1090" t="n">
         <v>50050</v>
@@ -32066,7 +32066,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562767028809</v>
+        <v>3.71562743186951</v>
       </c>
       <c r="H1093" t="n">
         <v>55300</v>
@@ -32153,7 +32153,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51808762550354</v>
+        <v>3.51808786392212</v>
       </c>
       <c r="H1096" t="n">
         <v>23800</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.2829213142395</v>
+        <v>3.28292155265808</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -32269,7 +32269,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.53690099716187</v>
+        <v>3.53690123558044</v>
       </c>
       <c r="H1100" t="n">
         <v>28000</v>
@@ -32298,7 +32298,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046135902405</v>
+        <v>3.48046112060547</v>
       </c>
       <c r="H1101" t="n">
         <v>45850</v>
@@ -32327,7 +32327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1102" t="n">
         <v>26250</v>
@@ -32385,7 +32385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.66364336013794</v>
+        <v>3.66364312171936</v>
       </c>
       <c r="H1104" t="n">
         <v>26600</v>
@@ -32414,7 +32414,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.62507843971252</v>
+        <v>3.6250786781311</v>
       </c>
       <c r="H1105" t="n">
         <v>4900</v>
@@ -32646,7 +32646,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1113" t="n">
         <v>40950</v>
@@ -32675,7 +32675,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.54794931411743</v>
+        <v>3.54794955253601</v>
       </c>
       <c r="H1114" t="n">
         <v>30100</v>
@@ -32762,7 +32762,7 @@
         <v>3.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1117" t="n">
         <v>9800</v>
@@ -32849,7 +32849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37440824508667</v>
+        <v>3.37440848350525</v>
       </c>
       <c r="H1120" t="n">
         <v>7350</v>
@@ -32878,7 +32878,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.64436101913452</v>
+        <v>3.64436078071594</v>
       </c>
       <c r="H1121" t="n">
         <v>74200</v>
@@ -32936,7 +32936,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.60579609870911</v>
+        <v>3.60579633712769</v>
       </c>
       <c r="H1123" t="n">
         <v>43750</v>
@@ -33226,7 +33226,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1133" t="n">
         <v>7000</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.49974370002747</v>
+        <v>3.49974346160889</v>
       </c>
       <c r="H1135" t="n">
         <v>3850</v>
@@ -33371,7 +33371,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1138" t="n">
         <v>3850</v>
@@ -33429,7 +33429,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1140" t="n">
         <v>26950</v>
@@ -33516,7 +33516,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1143" t="n">
         <v>6300</v>
@@ -33632,7 +33632,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.57687258720398</v>
+        <v>3.57687282562256</v>
       </c>
       <c r="H1147" t="n">
         <v>44100</v>
@@ -33661,7 +33661,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1148" t="n">
         <v>15400</v>
@@ -33806,7 +33806,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.47081995010376</v>
+        <v>3.47081971168518</v>
       </c>
       <c r="H1153" t="n">
         <v>350</v>
@@ -33893,7 +33893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.3262026309967</v>
+        <v>3.32620239257812</v>
       </c>
       <c r="H1156" t="n">
         <v>3150</v>
@@ -34154,7 +34154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1165" t="n">
         <v>14700</v>
@@ -34270,7 +34270,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.31387996673584</v>
+        <v>2.31388020515442</v>
       </c>
       <c r="H1169" t="n">
         <v>30100</v>
@@ -34328,7 +34328,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.98608028888702</v>
+        <v>1.98608016967773</v>
       </c>
       <c r="H1171" t="n">
         <v>30800</v>
@@ -34415,7 +34415,7 @@
         <v>2.5</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.41029167175293</v>
+        <v>2.41029143333435</v>
       </c>
       <c r="H1174" t="n">
         <v>21350</v>
@@ -34618,7 +34618,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.29727911949158</v>
+        <v>3.297278881073</v>
       </c>
       <c r="H1181" t="n">
         <v>33950</v>
@@ -34647,7 +34647,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1182" t="n">
         <v>13650</v>
@@ -34676,7 +34676,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.35512614250183</v>
+        <v>3.35512590408325</v>
       </c>
       <c r="H1183" t="n">
         <v>4200</v>
@@ -34705,7 +34705,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.25871419906616</v>
+        <v>3.25871443748474</v>
       </c>
       <c r="H1184" t="n">
         <v>4900</v>
@@ -34763,7 +34763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.43225502967834</v>
+        <v>3.43225526809692</v>
       </c>
       <c r="H1186" t="n">
         <v>17150</v>
@@ -34821,7 +34821,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1188" t="n">
         <v>25900</v>
@@ -34850,7 +34850,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.46117854118347</v>
+        <v>3.46117877960205</v>
       </c>
       <c r="H1189" t="n">
         <v>9100</v>
@@ -34879,7 +34879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.36476707458496</v>
+        <v>3.36476731300354</v>
       </c>
       <c r="H1190" t="n">
         <v>13650</v>
@@ -35024,7 +35024,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1195" t="n">
         <v>5950</v>
@@ -35111,7 +35111,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1198" t="n">
         <v>18200</v>
@@ -35198,7 +35198,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.1912260055542</v>
+        <v>3.19122624397278</v>
       </c>
       <c r="H1201" t="n">
         <v>7700</v>
@@ -35256,7 +35256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.12373805046082</v>
+        <v>3.12373781204224</v>
       </c>
       <c r="H1203" t="n">
         <v>10500</v>
@@ -35285,7 +35285,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1204" t="n">
         <v>2450</v>
@@ -35314,7 +35314,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.15266156196594</v>
+        <v>3.15266132354736</v>
       </c>
       <c r="H1205" t="n">
         <v>1050</v>
@@ -35488,7 +35488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.98876166343689</v>
+        <v>2.98876142501831</v>
       </c>
       <c r="H1211" t="n">
         <v>3150</v>
@@ -35604,7 +35604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1215" t="n">
         <v>6300</v>
@@ -35633,7 +35633,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.82486176490784</v>
+        <v>2.82486200332642</v>
       </c>
       <c r="H1216" t="n">
         <v>3500</v>
@@ -68510,7 +68510,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="D2350" t="n">
-        <v>0.625</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="E2350" t="n">
         <v>0.615000009536743</v>
@@ -68525,6 +68525,35 @@
         <v>2800</v>
       </c>
       <c r="I2350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2351" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="H2351" t="n">
+        <v>22750</v>
+      </c>
+      <c r="I2351" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABTG.MI.xlsx
+++ b/data/ABTG.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17245125770569</v>
+        <v>3.17245101928711</v>
       </c>
       <c r="H9" t="n">
         <v>5950</v>
@@ -775,7 +775,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12206506729126</v>
+        <v>3.12206530570984</v>
       </c>
       <c r="H14" t="n">
         <v>8050</v>
@@ -862,7 +862,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G17" t="n">
-        <v>3.18924641609192</v>
+        <v>3.1892466545105</v>
       </c>
       <c r="H17" t="n">
         <v>2450</v>
@@ -920,7 +920,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G19" t="n">
-        <v>3.29375076293945</v>
+        <v>3.29375052452087</v>
       </c>
       <c r="H19" t="n">
         <v>6650</v>
@@ -978,7 +978,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55501103401184</v>
+        <v>3.55501127243042</v>
       </c>
       <c r="H21" t="n">
         <v>27300</v>
@@ -1036,7 +1036,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>3.86105942726135</v>
+        <v>3.86105966567993</v>
       </c>
       <c r="H23" t="n">
         <v>58100</v>
@@ -1094,7 +1094,7 @@
         <v>4.25</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96556377410889</v>
+        <v>3.96556448936462</v>
       </c>
       <c r="H25" t="n">
         <v>38150</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.23615550994873</v>
+        <v>4.23615503311157</v>
       </c>
       <c r="H27" t="n">
         <v>65450</v>
@@ -1181,7 +1181,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3014702796936</v>
+        <v>4.30147075653076</v>
       </c>
       <c r="H28" t="n">
         <v>25550</v>
@@ -1239,7 +1239,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H30" t="n">
         <v>76650</v>
@@ -1268,7 +1268,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22521305084229</v>
+        <v>5.22521352767944</v>
       </c>
       <c r="H31" t="n">
         <v>145250</v>
@@ -1384,7 +1384,7 @@
         <v>7.25</v>
       </c>
       <c r="G35" t="n">
-        <v>6.76478576660156</v>
+        <v>6.7647852897644</v>
       </c>
       <c r="H35" t="n">
         <v>289450</v>
@@ -1442,7 +1442,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.26092529296875</v>
+        <v>6.26092576980591</v>
       </c>
       <c r="H37" t="n">
         <v>89950</v>
@@ -1500,7 +1500,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G39" t="n">
-        <v>6.16761779785156</v>
+        <v>6.16761827468872</v>
       </c>
       <c r="H39" t="n">
         <v>19600</v>
@@ -1674,7 +1674,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>6.84876251220703</v>
+        <v>6.84876298904419</v>
       </c>
       <c r="H45" t="n">
         <v>72450</v>
@@ -1703,7 +1703,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.68080854415894</v>
+        <v>6.68080902099609</v>
       </c>
       <c r="H46" t="n">
         <v>27650</v>
@@ -1790,7 +1790,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G49" t="n">
-        <v>7.18000411987305</v>
+        <v>7.18000316619873</v>
       </c>
       <c r="H49" t="n">
         <v>59850</v>
@@ -1819,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>7.46459102630615</v>
+        <v>7.46459054946899</v>
       </c>
       <c r="H50" t="n">
         <v>92050</v>
@@ -1848,7 +1848,7 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>7.46459102630615</v>
+        <v>7.46459054946899</v>
       </c>
       <c r="H51" t="n">
         <v>41650</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.7445125579834</v>
+        <v>7.74451303482056</v>
       </c>
       <c r="H52" t="n">
         <v>76300</v>
@@ -1935,7 +1935,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G54" t="n">
-        <v>8.30435657501221</v>
+        <v>8.30435848236084</v>
       </c>
       <c r="H54" t="n">
         <v>72100</v>
@@ -2022,7 +2022,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G57" t="n">
-        <v>8.72424030303955</v>
+        <v>8.72424125671387</v>
       </c>
       <c r="H57" t="n">
         <v>169750</v>
@@ -2051,7 +2051,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G58" t="n">
-        <v>8.25303936004639</v>
+        <v>8.25303745269775</v>
       </c>
       <c r="H58" t="n">
         <v>105350</v>
@@ -2109,7 +2109,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19866466522217</v>
+        <v>7.19866514205933</v>
       </c>
       <c r="H60" t="n">
         <v>109200</v>
@@ -2167,7 +2167,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>7.38061428070068</v>
+        <v>7.38061475753784</v>
       </c>
       <c r="H62" t="n">
         <v>17150</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>7.11002206802368</v>
+        <v>7.11002254486084</v>
       </c>
       <c r="H63" t="n">
         <v>26950</v>
@@ -2254,7 +2254,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.87675428390503</v>
+        <v>6.87675380706787</v>
       </c>
       <c r="H65" t="n">
         <v>99750</v>
@@ -2283,7 +2283,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>6.83010053634644</v>
+        <v>6.83010101318359</v>
       </c>
       <c r="H66" t="n">
         <v>14350</v>
@@ -2370,7 +2370,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>7.70252466201782</v>
+        <v>7.70252513885498</v>
       </c>
       <c r="H69" t="n">
         <v>29400</v>
@@ -2399,7 +2399,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.47858762741089</v>
+        <v>7.47858715057373</v>
       </c>
       <c r="H70" t="n">
         <v>35350</v>
@@ -2457,7 +2457,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>7.57189416885376</v>
+        <v>7.57189464569092</v>
       </c>
       <c r="H72" t="n">
         <v>15750</v>
@@ -2486,7 +2486,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>7.45059490203857</v>
+        <v>7.45059537887573</v>
       </c>
       <c r="H73" t="n">
         <v>20650</v>
@@ -2515,7 +2515,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H74" t="n">
         <v>15750</v>
@@ -2602,7 +2602,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H77" t="n">
         <v>12600</v>
@@ -2631,7 +2631,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H78" t="n">
         <v>8750</v>
@@ -2660,7 +2660,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.83010053634644</v>
+        <v>6.83010101318359</v>
       </c>
       <c r="H79" t="n">
         <v>5950</v>
@@ -2747,7 +2747,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>6.98405838012695</v>
+        <v>6.98405790328979</v>
       </c>
       <c r="H82" t="n">
         <v>10500</v>
@@ -2776,7 +2776,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>7.04004192352295</v>
+        <v>7.04004240036011</v>
       </c>
       <c r="H83" t="n">
         <v>9100</v>
@@ -2892,7 +2892,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H87" t="n">
         <v>30100</v>
@@ -2921,7 +2921,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>7.09136152267456</v>
+        <v>7.0913610458374</v>
       </c>
       <c r="H88" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>7.18466901779175</v>
+        <v>7.18466854095459</v>
       </c>
       <c r="H89" t="n">
         <v>7350</v>
@@ -3095,7 +3095,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>6.83943128585815</v>
+        <v>6.83943176269531</v>
       </c>
       <c r="H94" t="n">
         <v>23100</v>
@@ -3211,7 +3211,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>6.72279691696167</v>
+        <v>6.72279739379883</v>
       </c>
       <c r="H98" t="n">
         <v>8750</v>
@@ -3240,7 +3240,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G99" t="n">
-        <v>6.57817029953003</v>
+        <v>6.57817077636719</v>
       </c>
       <c r="H99" t="n">
         <v>17850</v>
@@ -3298,7 +3298,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G101" t="n">
-        <v>6.19094514846802</v>
+        <v>6.19094562530518</v>
       </c>
       <c r="H101" t="n">
         <v>40250</v>
@@ -3327,7 +3327,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.51285552978516</v>
+        <v>6.51285600662231</v>
       </c>
       <c r="H102" t="n">
         <v>24850</v>
@@ -3356,7 +3356,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>6.44287538528442</v>
+        <v>6.44287586212158</v>
       </c>
       <c r="H103" t="n">
         <v>5600</v>
@@ -3443,7 +3443,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H106" t="n">
         <v>9800</v>
@@ -3472,7 +3472,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.40555191040039</v>
+        <v>6.40555143356323</v>
       </c>
       <c r="H107" t="n">
         <v>2450</v>
@@ -3530,7 +3530,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>6.51285552978516</v>
+        <v>6.51285600662231</v>
       </c>
       <c r="H109" t="n">
         <v>2800</v>
@@ -3559,7 +3559,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G110" t="n">
-        <v>6.34490251541138</v>
+        <v>6.34490203857422</v>
       </c>
       <c r="H110" t="n">
         <v>1050</v>
@@ -3646,7 +3646,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H113" t="n">
         <v>8400</v>
@@ -3762,7 +3762,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>6.25159454345703</v>
+        <v>6.25159502029419</v>
       </c>
       <c r="H117" t="n">
         <v>3850</v>
@@ -3820,7 +3820,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.15828704833984</v>
+        <v>6.158287525177</v>
       </c>
       <c r="H119" t="n">
         <v>6300</v>
@@ -3907,7 +3907,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G122" t="n">
-        <v>6.0556492805481</v>
+        <v>6.05564880371094</v>
       </c>
       <c r="H122" t="n">
         <v>7000</v>
@@ -3936,7 +3936,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H123" t="n">
         <v>8400</v>
@@ -3994,7 +3994,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H125" t="n">
         <v>51800</v>
@@ -4023,7 +4023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H126" t="n">
         <v>34650</v>
@@ -4052,7 +4052,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175004959106</v>
       </c>
       <c r="H127" t="n">
         <v>15750</v>
@@ -4081,7 +4081,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7570652961731</v>
+        <v>5.75706577301025</v>
       </c>
       <c r="H128" t="n">
         <v>5250</v>
@@ -4139,7 +4139,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>5.95301103591919</v>
+        <v>5.95301151275635</v>
       </c>
       <c r="H130" t="n">
         <v>22400</v>
@@ -4168,7 +4168,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G131" t="n">
-        <v>5.70108127593994</v>
+        <v>5.70108079910278</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.69175052642822</v>
+        <v>5.69175004959106</v>
       </c>
       <c r="H133" t="n">
         <v>16450</v>
@@ -4284,7 +4284,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>5.54245853424072</v>
+        <v>5.54245901107788</v>
       </c>
       <c r="H135" t="n">
         <v>20300</v>
@@ -4342,7 +4342,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>5.6824197769165</v>
+        <v>5.68241930007935</v>
       </c>
       <c r="H137" t="n">
         <v>13300</v>
@@ -4400,7 +4400,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G139" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H139" t="n">
         <v>8400</v>
@@ -4429,7 +4429,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>5.81305074691772</v>
+        <v>5.81305027008057</v>
       </c>
       <c r="H140" t="n">
         <v>6300</v>
@@ -4458,7 +4458,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>5.90635776519775</v>
+        <v>5.9063572883606</v>
       </c>
       <c r="H141" t="n">
         <v>1400</v>
@@ -4487,7 +4487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>5.82238101959229</v>
+        <v>5.82238054275513</v>
       </c>
       <c r="H142" t="n">
         <v>3850</v>
@@ -4545,7 +4545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H144" t="n">
         <v>17850</v>
@@ -4632,7 +4632,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H147" t="n">
         <v>5600</v>
@@ -4661,7 +4661,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>5.85037279129028</v>
+        <v>5.85037326812744</v>
       </c>
       <c r="H148" t="n">
         <v>2450</v>
@@ -4690,7 +4690,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.76639604568481</v>
+        <v>5.76639652252197</v>
       </c>
       <c r="H149" t="n">
         <v>4900</v>
@@ -4719,7 +4719,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G150" t="n">
-        <v>5.84104204177856</v>
+        <v>5.84104251861572</v>
       </c>
       <c r="H150" t="n">
         <v>700</v>
@@ -4777,7 +4777,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>5.57978200912476</v>
+        <v>5.5797815322876</v>
       </c>
       <c r="H152" t="n">
         <v>18550</v>
@@ -4922,7 +4922,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H157" t="n">
         <v>6300</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>5.29052877426147</v>
+        <v>5.29052925109863</v>
       </c>
       <c r="H158" t="n">
         <v>5250</v>
@@ -4980,7 +4980,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H159" t="n">
         <v>3850</v>
@@ -5067,7 +5067,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.17856025695801</v>
+        <v>5.17855978012085</v>
       </c>
       <c r="H162" t="n">
         <v>3850</v>
@@ -5096,7 +5096,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G163" t="n">
-        <v>5.18789100646973</v>
+        <v>5.18789052963257</v>
       </c>
       <c r="H163" t="n">
         <v>1400</v>
@@ -5125,7 +5125,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G164" t="n">
-        <v>5.39316749572754</v>
+        <v>5.39316701889038</v>
       </c>
       <c r="H164" t="n">
         <v>15050</v>
@@ -5212,7 +5212,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>5.26253700256348</v>
+        <v>5.26253652572632</v>
       </c>
       <c r="H167" t="n">
         <v>2800</v>
@@ -5241,7 +5241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>5.31852054595947</v>
+        <v>5.31852102279663</v>
       </c>
       <c r="H168" t="n">
         <v>4550</v>
@@ -5270,7 +5270,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G171" t="n">
-        <v>5.15484523773193</v>
+        <v>5.15484571456909</v>
       </c>
       <c r="H171" t="n">
         <v>5250</v>
@@ -5386,7 +5386,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G173" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H173" t="n">
         <v>16100</v>
@@ -5531,7 +5531,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H178" t="n">
         <v>13300</v>
@@ -5589,7 +5589,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>5.7380576133728</v>
+        <v>5.73805713653564</v>
       </c>
       <c r="H180" t="n">
         <v>6300</v>
@@ -5618,7 +5618,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.69102430343628</v>
+        <v>5.69102478027344</v>
       </c>
       <c r="H181" t="n">
         <v>9100</v>
@@ -5647,7 +5647,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>6.06729030609131</v>
+        <v>6.06729078292847</v>
       </c>
       <c r="H182" t="n">
         <v>62650</v>
@@ -5705,7 +5705,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>5.80390405654907</v>
+        <v>5.80390453338623</v>
       </c>
       <c r="H184" t="n">
         <v>16450</v>
@@ -5734,7 +5734,7 @@
         <v>6</v>
       </c>
       <c r="G185" t="n">
-        <v>5.64399147033691</v>
+        <v>5.64399099349976</v>
       </c>
       <c r="H185" t="n">
         <v>4550</v>
@@ -5850,7 +5850,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H189" t="n">
         <v>2450</v>
@@ -5879,7 +5879,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G190" t="n">
-        <v>5.59695768356323</v>
+        <v>5.59695720672607</v>
       </c>
       <c r="H190" t="n">
         <v>350</v>
@@ -6111,7 +6111,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23950576782227</v>
+        <v>5.23950481414795</v>
       </c>
       <c r="H198" t="n">
         <v>6300</v>
@@ -6140,7 +6140,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" t="n">
-        <v>5.17365837097168</v>
+        <v>5.17365884780884</v>
       </c>
       <c r="H199" t="n">
         <v>1750</v>
@@ -6169,7 +6169,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H200" t="n">
         <v>5950</v>
@@ -6198,7 +6198,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>5.49348449707031</v>
+        <v>5.49348497390747</v>
       </c>
       <c r="H201" t="n">
         <v>32550</v>
@@ -6256,7 +6256,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G203" t="n">
-        <v>5.20187854766846</v>
+        <v>5.20187902450562</v>
       </c>
       <c r="H203" t="n">
         <v>12950</v>
@@ -6343,7 +6343,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>5.22069215774536</v>
+        <v>5.2206916809082</v>
       </c>
       <c r="H206" t="n">
         <v>1750</v>
@@ -6372,7 +6372,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>5.36179113388062</v>
+        <v>5.36179161071777</v>
       </c>
       <c r="H207" t="n">
         <v>8050</v>
@@ -6401,7 +6401,7 @@
         <v>5.5</v>
       </c>
       <c r="G208" t="n">
-        <v>5.17365837097168</v>
+        <v>5.17365884780884</v>
       </c>
       <c r="H208" t="n">
         <v>9450</v>
@@ -6430,7 +6430,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.11721897125244</v>
+        <v>5.11721849441528</v>
       </c>
       <c r="H209" t="n">
         <v>5600</v>
@@ -6633,7 +6633,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>5.07959222793579</v>
+        <v>5.07959175109863</v>
       </c>
       <c r="H216" t="n">
         <v>2800</v>
@@ -6691,7 +6691,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.03255844116211</v>
+        <v>5.03255891799927</v>
       </c>
       <c r="H218" t="n">
         <v>25550</v>
@@ -6836,7 +6836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>4.8914589881897</v>
+        <v>4.89145851135254</v>
       </c>
       <c r="H223" t="n">
         <v>4900</v>
@@ -6865,7 +6865,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G224" t="n">
-        <v>4.87264537811279</v>
+        <v>4.87264585494995</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H227" t="n">
         <v>8400</v>
@@ -7097,7 +7097,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G232" t="n">
-        <v>4.28472995758057</v>
+        <v>4.28472948074341</v>
       </c>
       <c r="H232" t="n">
         <v>4900</v>
@@ -7126,7 +7126,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.24240016937256</v>
+        <v>4.2423996925354</v>
       </c>
       <c r="H233" t="n">
         <v>2450</v>
@@ -7242,7 +7242,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G237" t="n">
-        <v>4.2988395690918</v>
+        <v>4.29884052276611</v>
       </c>
       <c r="H237" t="n">
         <v>23100</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.51519298553467</v>
+        <v>4.51519346237183</v>
       </c>
       <c r="H238" t="n">
         <v>147350</v>
@@ -7387,7 +7387,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>4.22828960418701</v>
+        <v>4.22829008102417</v>
       </c>
       <c r="H242" t="n">
         <v>7700</v>
@@ -7474,7 +7474,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G245" t="n">
-        <v>4.0636739730835</v>
+        <v>4.06367349624634</v>
       </c>
       <c r="H245" t="n">
         <v>4550</v>
@@ -7503,7 +7503,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H246" t="n">
         <v>1050</v>
@@ -7532,7 +7532,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.99312329292297</v>
+        <v>3.99312376976013</v>
       </c>
       <c r="H247" t="n">
         <v>4200</v>
@@ -7590,7 +7590,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.98842000961304</v>
+        <v>3.98842024803162</v>
       </c>
       <c r="H249" t="n">
         <v>5250</v>
@@ -7648,7 +7648,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>3.78147435188293</v>
+        <v>3.78147411346436</v>
       </c>
       <c r="H251" t="n">
         <v>12600</v>
@@ -7735,7 +7735,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G254" t="n">
-        <v>3.54160451889038</v>
+        <v>3.54160475730896</v>
       </c>
       <c r="H254" t="n">
         <v>20300</v>
@@ -7793,7 +7793,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7851,7 +7851,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>4.01664018630981</v>
+        <v>4.01664066314697</v>
       </c>
       <c r="H258" t="n">
         <v>73500</v>
@@ -7880,7 +7880,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6732976436615</v>
+        <v>3.67329740524292</v>
       </c>
       <c r="H259" t="n">
         <v>77000</v>
@@ -8025,7 +8025,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G264" t="n">
-        <v>3.57452774047852</v>
+        <v>3.57452750205994</v>
       </c>
       <c r="H264" t="n">
         <v>2450</v>
@@ -8054,7 +8054,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H265" t="n">
         <v>3850</v>
@@ -8199,7 +8199,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G270" t="n">
-        <v>3.41461491584778</v>
+        <v>3.4146146774292</v>
       </c>
       <c r="H270" t="n">
         <v>7350</v>
@@ -8286,7 +8286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H273" t="n">
         <v>1050</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>3.49927473068237</v>
+        <v>3.49927449226379</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8634,7 +8634,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G285" t="n">
-        <v>3.32525157928467</v>
+        <v>3.32525134086609</v>
       </c>
       <c r="H285" t="n">
         <v>12950</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H288" t="n">
         <v>17500</v>
@@ -8750,7 +8750,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G289" t="n">
-        <v>3.49927473068237</v>
+        <v>3.49927449226379</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8808,7 +8808,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.47105431556702</v>
+        <v>3.4710545539856</v>
       </c>
       <c r="H291" t="n">
         <v>4900</v>
@@ -8895,7 +8895,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>3.62156105041504</v>
+        <v>3.62156081199646</v>
       </c>
       <c r="H294" t="n">
         <v>1750</v>
@@ -8982,7 +8982,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G297" t="n">
-        <v>3.43813109397888</v>
+        <v>3.43813133239746</v>
       </c>
       <c r="H297" t="n">
         <v>29400</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>2.953688621521</v>
+        <v>2.95368885993958</v>
       </c>
       <c r="H300" t="n">
         <v>59850</v>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H301" t="n">
         <v>67900</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H304" t="n">
         <v>23100</v>
@@ -9214,7 +9214,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G305" t="n">
-        <v>2.87373232841492</v>
+        <v>2.87373208999634</v>
       </c>
       <c r="H305" t="n">
         <v>23450</v>
@@ -9359,7 +9359,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>2.61504936218262</v>
+        <v>2.61504912376404</v>
       </c>
       <c r="H310" t="n">
         <v>2450</v>
@@ -9388,7 +9388,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H311" t="n">
         <v>5950</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44572949409485</v>
+        <v>2.44572925567627</v>
       </c>
       <c r="H313" t="n">
         <v>15400</v>
@@ -9475,7 +9475,7 @@
         <v>2.5</v>
       </c>
       <c r="G314" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H314" t="n">
         <v>23450</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H316" t="n">
         <v>5600</v>
@@ -9562,7 +9562,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H317" t="n">
         <v>6650</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H318" t="n">
         <v>52850</v>
@@ -9678,7 +9678,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H321" t="n">
         <v>5250</v>
@@ -9707,7 +9707,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H322" t="n">
         <v>3150</v>
@@ -9794,7 +9794,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.98950672149658</v>
+        <v>1.98950695991516</v>
       </c>
       <c r="H325" t="n">
         <v>2800</v>
@@ -9823,7 +9823,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.03654026985168</v>
+        <v>2.03654003143311</v>
       </c>
       <c r="H326" t="n">
         <v>2450</v>
@@ -9852,7 +9852,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H327" t="n">
         <v>53900</v>
@@ -9910,7 +9910,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G329" t="n">
-        <v>2.12120008468628</v>
+        <v>2.1211998462677</v>
       </c>
       <c r="H329" t="n">
         <v>12250</v>
@@ -10171,7 +10171,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>1.81924641132355</v>
+        <v>1.81924653053284</v>
       </c>
       <c r="H338" t="n">
         <v>10150</v>
@@ -10229,7 +10229,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H340" t="n">
         <v>2100</v>
@@ -10287,7 +10287,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H342" t="n">
         <v>3850</v>
@@ -10345,7 +10345,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80983996391296</v>
+        <v>1.80983984470367</v>
       </c>
       <c r="H344" t="n">
         <v>19600</v>
@@ -10432,7 +10432,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H347" t="n">
         <v>26250</v>
@@ -10548,7 +10548,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G351" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H351" t="n">
         <v>6650</v>
@@ -10635,7 +10635,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G354" t="n">
-        <v>1.29435527324677</v>
+        <v>1.29435539245605</v>
       </c>
       <c r="H354" t="n">
         <v>3850</v>
@@ -10693,7 +10693,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H356" t="n">
         <v>3850</v>
@@ -10780,7 +10780,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G359" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H359" t="n">
         <v>9100</v>
@@ -10809,7 +10809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H360" t="n">
         <v>9450</v>
@@ -10838,7 +10838,7 @@
         <v>1.5</v>
       </c>
       <c r="G361" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H361" t="n">
         <v>33950</v>
@@ -10867,7 +10867,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G362" t="n">
-        <v>1.55209743976593</v>
+        <v>1.55209767818451</v>
       </c>
       <c r="H362" t="n">
         <v>17150</v>
@@ -11012,7 +11012,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>2.38928937911987</v>
+        <v>2.38928961753845</v>
       </c>
       <c r="H367" t="n">
         <v>146300</v>
@@ -11099,7 +11099,7 @@
         <v>3</v>
       </c>
       <c r="G370" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H370" t="n">
         <v>68600</v>
@@ -11128,7 +11128,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H371" t="n">
         <v>184800</v>
@@ -11157,7 +11157,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H372" t="n">
         <v>158200</v>
@@ -11186,7 +11186,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>2.57742261886597</v>
+        <v>2.57742285728455</v>
       </c>
       <c r="H373" t="n">
         <v>161700</v>
@@ -11302,7 +11302,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H377" t="n">
         <v>26600</v>
@@ -11331,7 +11331,7 @@
         <v>3</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82199573516846</v>
+        <v>2.82199549674988</v>
       </c>
       <c r="H378" t="n">
         <v>99050</v>
@@ -11418,7 +11418,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>2.68089556694031</v>
+        <v>2.68089580535889</v>
       </c>
       <c r="H381" t="n">
         <v>12250</v>
@@ -11447,7 +11447,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G382" t="n">
-        <v>2.61975288391113</v>
+        <v>2.61975240707397</v>
       </c>
       <c r="H382" t="n">
         <v>21700</v>
@@ -11476,7 +11476,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H383" t="n">
         <v>11200</v>
@@ -11505,7 +11505,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H384" t="n">
         <v>5250</v>
@@ -11563,7 +11563,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H386" t="n">
         <v>10150</v>
@@ -11592,7 +11592,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H387" t="n">
         <v>2450</v>
@@ -11650,7 +11650,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H389" t="n">
         <v>2800</v>
@@ -11679,7 +11679,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.45983958244324</v>
+        <v>2.45983934402466</v>
       </c>
       <c r="H390" t="n">
         <v>1750</v>
@@ -11708,7 +11708,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>2.63386225700378</v>
+        <v>2.63386249542236</v>
       </c>
       <c r="H391" t="n">
         <v>26250</v>
@@ -11737,7 +11737,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G392" t="n">
-        <v>2.61504936218262</v>
+        <v>2.61504912376404</v>
       </c>
       <c r="H392" t="n">
         <v>23450</v>
@@ -11766,7 +11766,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>2.5397961139679</v>
+        <v>2.53979587554932</v>
       </c>
       <c r="H393" t="n">
         <v>10150</v>
@@ -11824,7 +11824,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G395" t="n">
-        <v>2.50216937065125</v>
+        <v>2.50216960906982</v>
       </c>
       <c r="H395" t="n">
         <v>4900</v>
@@ -11853,7 +11853,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55860948562622</v>
+        <v>2.55860924720764</v>
       </c>
       <c r="H396" t="n">
         <v>2100</v>
@@ -11882,7 +11882,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11969,7 +11969,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H400" t="n">
         <v>3850</v>
@@ -11998,7 +11998,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G401" t="n">
-        <v>2.51627922058105</v>
+        <v>2.51627945899963</v>
       </c>
       <c r="H401" t="n">
         <v>51450</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H402" t="n">
         <v>8750</v>
@@ -12085,7 +12085,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H404" t="n">
         <v>5950</v>
@@ -12114,7 +12114,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.49276304244995</v>
+        <v>2.49276280403137</v>
       </c>
       <c r="H405" t="n">
         <v>1050</v>
@@ -12143,7 +12143,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>2.44572949409485</v>
+        <v>2.44572925567627</v>
       </c>
       <c r="H406" t="n">
         <v>7700</v>
@@ -12230,7 +12230,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>2.37047624588013</v>
+        <v>2.37047600746155</v>
       </c>
       <c r="H409" t="n">
         <v>6300</v>
@@ -12317,7 +12317,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>2.30933284759521</v>
+        <v>2.30933308601379</v>
       </c>
       <c r="H412" t="n">
         <v>44100</v>
@@ -12433,7 +12433,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H416" t="n">
         <v>22400</v>
@@ -12665,7 +12665,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H424" t="n">
         <v>3850</v>
@@ -12723,7 +12723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.21056318283081</v>
+        <v>2.21056294441223</v>
       </c>
       <c r="H426" t="n">
         <v>1750</v>
@@ -12752,7 +12752,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H427" t="n">
         <v>21000</v>
@@ -12781,7 +12781,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H428" t="n">
         <v>43400</v>
@@ -12810,7 +12810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H429" t="n">
         <v>20300</v>
@@ -12839,7 +12839,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>2.42691588401794</v>
+        <v>2.4269163608551</v>
       </c>
       <c r="H430" t="n">
         <v>25900</v>
@@ -12926,7 +12926,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H433" t="n">
         <v>7700</v>
@@ -12984,7 +12984,7 @@
         <v>2.5</v>
       </c>
       <c r="G435" t="n">
-        <v>2.35166311264038</v>
+        <v>2.3516628742218</v>
       </c>
       <c r="H435" t="n">
         <v>11200</v>
@@ -13042,7 +13042,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H437" t="n">
         <v>2800</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H439" t="n">
         <v>350</v>
@@ -13129,7 +13129,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29522323608398</v>
+        <v>2.29522299766541</v>
       </c>
       <c r="H440" t="n">
         <v>8400</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G442" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H442" t="n">
         <v>4900</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H443" t="n">
         <v>350</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.24819016456604</v>
+        <v>2.24818992614746</v>
       </c>
       <c r="H445" t="n">
         <v>350</v>
@@ -13303,7 +13303,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>2.29522323608398</v>
+        <v>2.29522299766541</v>
       </c>
       <c r="H446" t="n">
         <v>2450</v>
@@ -13361,7 +13361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>2.22937631607056</v>
+        <v>2.22937655448914</v>
       </c>
       <c r="H448" t="n">
         <v>1750</v>
@@ -13390,7 +13390,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>2.25759649276733</v>
+        <v>2.25759673118591</v>
       </c>
       <c r="H449" t="n">
         <v>2800</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.30462956428528</v>
+        <v>2.30462980270386</v>
       </c>
       <c r="H450" t="n">
         <v>4550</v>
@@ -13535,7 +13535,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.13531017303467</v>
+        <v>2.13530993461609</v>
       </c>
       <c r="H454" t="n">
         <v>9800</v>
@@ -13622,7 +13622,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H457" t="n">
         <v>21350</v>
@@ -13651,7 +13651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G458" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H458" t="n">
         <v>14700</v>
@@ -13680,7 +13680,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G459" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H459" t="n">
         <v>12250</v>
@@ -13709,7 +13709,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G460" t="n">
-        <v>2.01302361488342</v>
+        <v>2.01302337646484</v>
       </c>
       <c r="H460" t="n">
         <v>5600</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H461" t="n">
         <v>1750</v>
@@ -13796,7 +13796,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G463" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H463" t="n">
         <v>7000</v>
@@ -13912,7 +13912,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G467" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H467" t="n">
         <v>4200</v>
@@ -14028,7 +14028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H471" t="n">
         <v>5250</v>
@@ -14057,7 +14057,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H473" t="n">
         <v>3500</v>
@@ -14115,7 +14115,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H474" t="n">
         <v>5250</v>
@@ -14144,7 +14144,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G475" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H475" t="n">
         <v>2100</v>
@@ -14173,7 +14173,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G476" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.01302361488342</v>
+        <v>2.01302337646484</v>
       </c>
       <c r="H477" t="n">
         <v>25200</v>
@@ -14231,7 +14231,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G478" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H478" t="n">
         <v>6650</v>
@@ -14260,7 +14260,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.03183698654175</v>
+        <v>2.03183674812317</v>
       </c>
       <c r="H479" t="n">
         <v>700</v>
@@ -14289,7 +14289,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H480" t="n">
         <v>5600</v>
@@ -14318,7 +14318,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>2.04124331474304</v>
+        <v>2.04124355316162</v>
       </c>
       <c r="H481" t="n">
         <v>1400</v>
@@ -14347,7 +14347,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H482" t="n">
         <v>1400</v>
@@ -14405,7 +14405,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H484" t="n">
         <v>1050</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H485" t="n">
         <v>4550</v>
@@ -14463,7 +14463,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H486" t="n">
         <v>700</v>
@@ -14492,7 +14492,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G487" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H487" t="n">
         <v>20650</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H489" t="n">
         <v>21700</v>
@@ -14637,7 +14637,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H492" t="n">
         <v>8400</v>
@@ -14666,7 +14666,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H493" t="n">
         <v>3500</v>
@@ -14753,7 +14753,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H496" t="n">
         <v>9100</v>
@@ -14782,7 +14782,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G497" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H497" t="n">
         <v>10850</v>
@@ -14927,7 +14927,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G502" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H502" t="n">
         <v>32900</v>
@@ -14956,7 +14956,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G503" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H503" t="n">
         <v>1400</v>
@@ -14985,7 +14985,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H504" t="n">
         <v>7350</v>
@@ -15014,7 +15014,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H505" t="n">
         <v>3150</v>
@@ -15043,7 +15043,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H506" t="n">
         <v>30450</v>
@@ -15101,7 +15101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G508" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H508" t="n">
         <v>700</v>
@@ -15130,7 +15130,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G509" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H509" t="n">
         <v>6650</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H513" t="n">
         <v>3850</v>
@@ -15275,7 +15275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H514" t="n">
         <v>2800</v>
@@ -15333,7 +15333,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G516" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H516" t="n">
         <v>2450</v>
@@ -15362,7 +15362,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G517" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H521" t="n">
         <v>1050</v>
@@ -15507,7 +15507,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G522" t="n">
-        <v>1.74963736534119</v>
+        <v>1.7496372461319</v>
       </c>
       <c r="H522" t="n">
         <v>9100</v>
@@ -15623,7 +15623,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G526" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H526" t="n">
         <v>9800</v>
@@ -15652,7 +15652,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>1.75434052944183</v>
+        <v>1.75434064865112</v>
       </c>
       <c r="H528" t="n">
         <v>1400</v>
@@ -15710,7 +15710,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.74963736534119</v>
+        <v>1.7496372461319</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G530" t="n">
-        <v>1.74023056030273</v>
+        <v>1.74023067951202</v>
       </c>
       <c r="H530" t="n">
         <v>3850</v>
@@ -15768,7 +15768,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G531" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H531" t="n">
         <v>350</v>
@@ -15797,7 +15797,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G539" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H539" t="n">
         <v>1750</v>
@@ -16029,7 +16029,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G540" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H540" t="n">
         <v>7350</v>
@@ -16058,7 +16058,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G541" t="n">
-        <v>1.81548368930817</v>
+        <v>1.81548392772675</v>
       </c>
       <c r="H541" t="n">
         <v>7700</v>
@@ -16145,7 +16145,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H544" t="n">
         <v>1750</v>
@@ -16232,7 +16232,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G547" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H547" t="n">
         <v>700</v>
@@ -16261,7 +16261,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H548" t="n">
         <v>7000</v>
@@ -16319,7 +16319,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G550" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H550" t="n">
         <v>141050</v>
@@ -16377,7 +16377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>1.99421000480652</v>
+        <v>1.99421012401581</v>
       </c>
       <c r="H552" t="n">
         <v>46200</v>
@@ -16406,7 +16406,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G553" t="n">
-        <v>1.81078052520752</v>
+        <v>1.81078040599823</v>
       </c>
       <c r="H553" t="n">
         <v>66500</v>
@@ -16435,7 +16435,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H554" t="n">
         <v>35700</v>
@@ -16464,7 +16464,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H555" t="n">
         <v>62650</v>
@@ -16493,7 +16493,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86251711845398</v>
+        <v>1.86251699924469</v>
       </c>
       <c r="H556" t="n">
         <v>11550</v>
@@ -16522,7 +16522,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H557" t="n">
         <v>7000</v>
@@ -16551,7 +16551,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G558" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H558" t="n">
         <v>9450</v>
@@ -16580,7 +16580,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H559" t="n">
         <v>10150</v>
@@ -16609,7 +16609,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G560" t="n">
-        <v>1.92836356163025</v>
+        <v>1.92836368083954</v>
       </c>
       <c r="H560" t="n">
         <v>9800</v>
@@ -16638,7 +16638,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H561" t="n">
         <v>8050</v>
@@ -16667,7 +16667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H562" t="n">
         <v>3500</v>
@@ -16841,7 +16841,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H568" t="n">
         <v>10150</v>
@@ -16928,7 +16928,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H571" t="n">
         <v>2450</v>
@@ -16957,7 +16957,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G572" t="n">
-        <v>1.85311043262482</v>
+        <v>1.85311055183411</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.81078052520752</v>
+        <v>1.81078040599823</v>
       </c>
       <c r="H577" t="n">
         <v>4200</v>
@@ -17131,7 +17131,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H578" t="n">
         <v>5250</v>
@@ -17160,7 +17160,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H579" t="n">
         <v>8400</v>
@@ -17189,7 +17189,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>1.7919670343399</v>
+        <v>1.79196715354919</v>
       </c>
       <c r="H581" t="n">
         <v>3150</v>
@@ -17247,7 +17247,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.80137383937836</v>
+        <v>1.80137372016907</v>
       </c>
       <c r="H582" t="n">
         <v>350</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.77315378189087</v>
+        <v>1.77315390110016</v>
       </c>
       <c r="H590" t="n">
         <v>1050</v>
@@ -17537,7 +17537,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>1.70730745792389</v>
+        <v>1.7073073387146</v>
       </c>
       <c r="H592" t="n">
         <v>2100</v>
@@ -17769,7 +17769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H600" t="n">
         <v>1050</v>
@@ -18059,7 +18059,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68379056453705</v>
+        <v>1.68379068374634</v>
       </c>
       <c r="H610" t="n">
         <v>2800</v>
@@ -18088,7 +18088,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G611" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H611" t="n">
         <v>11200</v>
@@ -18117,7 +18117,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>1.62735092639923</v>
+        <v>1.62735080718994</v>
       </c>
       <c r="H612" t="n">
         <v>3850</v>
@@ -18320,7 +18320,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G619" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H619" t="n">
         <v>2800</v>
@@ -18349,7 +18349,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G620" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H620" t="n">
         <v>10150</v>
@@ -18378,7 +18378,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>1.51917433738708</v>
+        <v>1.5191742181778</v>
       </c>
       <c r="H621" t="n">
         <v>6300</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.78726387023926</v>
+        <v>1.78726375102997</v>
       </c>
       <c r="H624" t="n">
         <v>55300</v>
@@ -18523,7 +18523,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G626" t="n">
-        <v>1.63205397129059</v>
+        <v>1.63205409049988</v>
       </c>
       <c r="H626" t="n">
         <v>30450</v>
@@ -18552,7 +18552,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G627" t="n">
-        <v>1.62264752388</v>
+        <v>1.62264740467072</v>
       </c>
       <c r="H627" t="n">
         <v>23800</v>
@@ -18639,7 +18639,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G630" t="n">
-        <v>1.58031737804413</v>
+        <v>1.58031749725342</v>
       </c>
       <c r="H630" t="n">
         <v>2100</v>
@@ -18726,7 +18726,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G633" t="n">
-        <v>1.57091093063354</v>
+        <v>1.57091081142426</v>
       </c>
       <c r="H633" t="n">
         <v>10850</v>
@@ -18755,7 +18755,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G634" t="n">
-        <v>1.52387762069702</v>
+        <v>1.52387750148773</v>
       </c>
       <c r="H634" t="n">
         <v>2450</v>
@@ -18813,7 +18813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55680084228516</v>
+        <v>1.55680096149445</v>
       </c>
       <c r="H636" t="n">
         <v>9800</v>
@@ -18842,7 +18842,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G637" t="n">
-        <v>1.53798758983612</v>
+        <v>1.53798747062683</v>
       </c>
       <c r="H637" t="n">
         <v>5950</v>
@@ -18929,7 +18929,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H640" t="n">
         <v>8050</v>
@@ -19016,7 +19016,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>1.54739427566528</v>
+        <v>1.54739415645599</v>
       </c>
       <c r="H643" t="n">
         <v>21000</v>
@@ -19074,7 +19074,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G645" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G646" t="n">
-        <v>1.48625111579895</v>
+        <v>1.48625099658966</v>
       </c>
       <c r="H646" t="n">
         <v>5600</v>
@@ -19132,7 +19132,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G647" t="n">
-        <v>1.51447093486786</v>
+        <v>1.51447105407715</v>
       </c>
       <c r="H647" t="n">
         <v>3150</v>
@@ -19277,7 +19277,7 @@
         <v>1.5</v>
       </c>
       <c r="G652" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H652" t="n">
         <v>8050</v>
@@ -19364,7 +19364,7 @@
         <v>1.5</v>
       </c>
       <c r="G655" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H655" t="n">
         <v>5600</v>
@@ -19393,7 +19393,7 @@
         <v>1.5</v>
       </c>
       <c r="G656" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H656" t="n">
         <v>5950</v>
@@ -19422,7 +19422,7 @@
         <v>1.5</v>
       </c>
       <c r="G657" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H657" t="n">
         <v>2800</v>
@@ -19480,7 +19480,7 @@
         <v>1.375</v>
       </c>
       <c r="G659" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H659" t="n">
         <v>8750</v>
@@ -19567,7 +19567,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>0.93125855922699</v>
+        <v>0.931258499622345</v>
       </c>
       <c r="H662" t="n">
         <v>21700</v>
@@ -19596,7 +19596,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G663" t="n">
-        <v>0.93125855922699</v>
+        <v>0.931258499622345</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G665" t="n">
-        <v>0.893631935119629</v>
+        <v>0.893631875514984</v>
       </c>
       <c r="H665" t="n">
         <v>9100</v>
@@ -19683,7 +19683,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G666" t="n">
-        <v>0.893631935119629</v>
+        <v>0.893631875514984</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G668" t="n">
-        <v>0.886106550693512</v>
+        <v>0.886106610298157</v>
       </c>
       <c r="H668" t="n">
         <v>2450</v>
@@ -19799,7 +19799,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H670" t="n">
         <v>2450</v>
@@ -19828,7 +19828,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G671" t="n">
-        <v>0.918089210987091</v>
+        <v>0.918089270591736</v>
       </c>
       <c r="H671" t="n">
         <v>3150</v>
@@ -19886,7 +19886,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.914326608181</v>
+        <v>0.91432648897171</v>
       </c>
       <c r="H673" t="n">
         <v>6650</v>
@@ -19915,7 +19915,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H674" t="n">
         <v>16800</v>
@@ -19944,7 +19944,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.964181780815125</v>
+        <v>0.964181840419769</v>
       </c>
       <c r="H675" t="n">
         <v>5600</v>
@@ -20002,7 +20002,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H677" t="n">
         <v>700</v>
@@ -20031,7 +20031,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G679" t="n">
-        <v>0.968885183334351</v>
+        <v>0.968885064125061</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>0.921851873397827</v>
+        <v>0.921851933002472</v>
       </c>
       <c r="H680" t="n">
         <v>12600</v>
@@ -20147,7 +20147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.01591849327087</v>
+        <v>1.01591837406158</v>
       </c>
       <c r="H682" t="n">
         <v>12950</v>
@@ -20176,7 +20176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20234,7 +20234,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H685" t="n">
         <v>34650</v>
@@ -20263,7 +20263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H686" t="n">
         <v>6650</v>
@@ -20437,7 +20437,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G692" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H692" t="n">
         <v>4550</v>
@@ -20466,7 +20466,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H693" t="n">
         <v>17850</v>
@@ -20495,7 +20495,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G694" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H694" t="n">
         <v>9800</v>
@@ -20524,7 +20524,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G695" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20611,7 +20611,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G698" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H698" t="n">
         <v>3850</v>
@@ -20640,7 +20640,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G699" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H699" t="n">
         <v>2450</v>
@@ -20727,7 +20727,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G702" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H702" t="n">
         <v>3150</v>
@@ -20756,7 +20756,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H703" t="n">
         <v>16100</v>
@@ -20785,7 +20785,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H704" t="n">
         <v>2800</v>
@@ -20843,7 +20843,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H706" t="n">
         <v>22400</v>
@@ -20901,7 +20901,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H708" t="n">
         <v>13650</v>
@@ -20988,7 +20988,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.12409508228302</v>
+        <v>1.12409496307373</v>
       </c>
       <c r="H711" t="n">
         <v>1750</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H713" t="n">
         <v>2450</v>
@@ -21133,7 +21133,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G716" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H716" t="n">
         <v>5250</v>
@@ -21191,7 +21191,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H718" t="n">
         <v>700</v>
@@ -21220,7 +21220,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G719" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H719" t="n">
         <v>1050</v>
@@ -21278,7 +21278,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G721" t="n">
-        <v>1.34985458850861</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H721" t="n">
         <v>7700</v>
@@ -21307,7 +21307,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G722" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H722" t="n">
         <v>33950</v>
@@ -21336,7 +21336,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G723" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H723" t="n">
         <v>7350</v>
@@ -21365,7 +21365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G724" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H724" t="n">
         <v>21350</v>
@@ -21394,7 +21394,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H726" t="n">
         <v>13300</v>
@@ -21452,7 +21452,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G727" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H727" t="n">
         <v>2450</v>
@@ -21481,7 +21481,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G728" t="n">
-        <v>1.2181613445282</v>
+        <v>1.21816146373749</v>
       </c>
       <c r="H728" t="n">
         <v>700</v>
@@ -21510,7 +21510,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H729" t="n">
         <v>1750</v>
@@ -21539,7 +21539,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H731" t="n">
         <v>1050</v>
@@ -21597,7 +21597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G733" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H734" t="n">
         <v>2100</v>
@@ -21742,7 +21742,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G737" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H737" t="n">
         <v>60550</v>
@@ -21858,7 +21858,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G741" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H741" t="n">
         <v>38150</v>
@@ -21945,7 +21945,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G744" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H744" t="n">
         <v>1050</v>
@@ -22003,7 +22003,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G746" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H746" t="n">
         <v>2450</v>
@@ -22032,7 +22032,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H747" t="n">
         <v>1050</v>
@@ -22061,7 +22061,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G748" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H750" t="n">
         <v>350</v>
@@ -22148,7 +22148,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H751" t="n">
         <v>2450</v>
@@ -22177,7 +22177,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H753" t="n">
         <v>8750</v>
@@ -22293,7 +22293,7 @@
         <v>1.375</v>
       </c>
       <c r="G756" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H756" t="n">
         <v>3500</v>
@@ -22380,7 +22380,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H759" t="n">
         <v>4900</v>
@@ -22409,7 +22409,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H763" t="n">
         <v>700</v>
@@ -22554,7 +22554,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G765" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H765" t="n">
         <v>3150</v>
@@ -22612,7 +22612,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G767" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H767" t="n">
         <v>350</v>
@@ -22641,7 +22641,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H768" t="n">
         <v>700</v>
@@ -22699,7 +22699,7 @@
         <v>1.375</v>
       </c>
       <c r="G770" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H770" t="n">
         <v>8400</v>
@@ -22931,7 +22931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H778" t="n">
         <v>10500</v>
@@ -22960,7 +22960,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G780" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H781" t="n">
         <v>14000</v>
@@ -23105,7 +23105,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H784" t="n">
         <v>1400</v>
@@ -23134,7 +23134,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H785" t="n">
         <v>700</v>
@@ -23163,7 +23163,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>1.21345794200897</v>
+        <v>1.21345818042755</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H787" t="n">
         <v>700</v>
@@ -23221,7 +23221,7 @@
         <v>1.25</v>
       </c>
       <c r="G788" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H788" t="n">
         <v>14000</v>
@@ -23250,7 +23250,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G789" t="n">
-        <v>1.14761161804199</v>
+        <v>1.1476114988327</v>
       </c>
       <c r="H789" t="n">
         <v>5250</v>
@@ -23279,7 +23279,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>1.12879824638367</v>
+        <v>1.12879836559296</v>
       </c>
       <c r="H790" t="n">
         <v>4200</v>
@@ -23308,7 +23308,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G791" t="n">
-        <v>1.2181613445282</v>
+        <v>1.21816146373749</v>
       </c>
       <c r="H791" t="n">
         <v>3500</v>
@@ -23337,7 +23337,7 @@
         <v>1.25</v>
       </c>
       <c r="G792" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H792" t="n">
         <v>4900</v>
@@ -23482,7 +23482,7 @@
         <v>1.25</v>
       </c>
       <c r="G797" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H797" t="n">
         <v>7700</v>
@@ -23511,7 +23511,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H798" t="n">
         <v>12600</v>
@@ -23569,7 +23569,7 @@
         <v>1.25</v>
       </c>
       <c r="G800" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H800" t="n">
         <v>2800</v>
@@ -23598,7 +23598,7 @@
         <v>1.25</v>
       </c>
       <c r="G801" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H801" t="n">
         <v>5250</v>
@@ -23685,7 +23685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H804" t="n">
         <v>12600</v>
@@ -23714,7 +23714,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25108468532562</v>
+        <v>1.25108480453491</v>
       </c>
       <c r="H805" t="n">
         <v>18550</v>
@@ -23743,7 +23743,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H806" t="n">
         <v>46550</v>
@@ -23801,7 +23801,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H808" t="n">
         <v>8050</v>
@@ -23830,7 +23830,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H809" t="n">
         <v>41300</v>
@@ -23946,7 +23946,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G813" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H813" t="n">
         <v>4200</v>
@@ -23975,7 +23975,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.24638152122498</v>
+        <v>1.24638140201569</v>
       </c>
       <c r="H814" t="n">
         <v>4550</v>
@@ -24004,7 +24004,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G815" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H815" t="n">
         <v>2800</v>
@@ -24033,7 +24033,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G816" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H816" t="n">
         <v>6650</v>
@@ -24062,7 +24062,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H817" t="n">
         <v>8400</v>
@@ -24120,7 +24120,7 @@
         <v>1.25</v>
       </c>
       <c r="G819" t="n">
-        <v>1.17583155632019</v>
+        <v>1.1758314371109</v>
       </c>
       <c r="H819" t="n">
         <v>13650</v>
@@ -24149,7 +24149,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H820" t="n">
         <v>16100</v>
@@ -24178,7 +24178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.19464468955994</v>
+        <v>1.19464480876923</v>
       </c>
       <c r="H822" t="n">
         <v>3850</v>
@@ -24323,7 +24323,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G826" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H826" t="n">
         <v>700</v>
@@ -24381,7 +24381,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G828" t="n">
-        <v>1.15231478214264</v>
+        <v>1.15231490135193</v>
       </c>
       <c r="H828" t="n">
         <v>3500</v>
@@ -24410,7 +24410,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H829" t="n">
         <v>40600</v>
@@ -24439,7 +24439,7 @@
         <v>1.5</v>
       </c>
       <c r="G830" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H830" t="n">
         <v>81550</v>
@@ -24468,7 +24468,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G831" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H831" t="n">
         <v>166950</v>
@@ -24584,7 +24584,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.34985458850861</v>
+        <v>1.34985435009003</v>
       </c>
       <c r="H835" t="n">
         <v>9100</v>
@@ -24671,7 +24671,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G838" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H838" t="n">
         <v>13300</v>
@@ -24729,7 +24729,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H840" t="n">
         <v>9450</v>
@@ -24845,7 +24845,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G844" t="n">
-        <v>1.4768443107605</v>
+        <v>1.47684442996979</v>
       </c>
       <c r="H844" t="n">
         <v>129500</v>
@@ -24961,7 +24961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H848" t="n">
         <v>6650</v>
@@ -25106,7 +25106,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H853" t="n">
         <v>1750</v>
@@ -25135,7 +25135,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G863" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H863" t="n">
         <v>5250</v>
@@ -25454,7 +25454,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H865" t="n">
         <v>4900</v>
@@ -25483,7 +25483,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H866" t="n">
         <v>2800</v>
@@ -25570,7 +25570,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.37337112426758</v>
+        <v>1.37337124347687</v>
       </c>
       <c r="H869" t="n">
         <v>3850</v>
@@ -25599,7 +25599,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G870" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H870" t="n">
         <v>2100</v>
@@ -25628,7 +25628,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>1.34044778347015</v>
+        <v>1.34044790267944</v>
       </c>
       <c r="H871" t="n">
         <v>2100</v>
@@ -25715,7 +25715,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G874" t="n">
-        <v>1.35926127433777</v>
+        <v>1.35926115512848</v>
       </c>
       <c r="H874" t="n">
         <v>7350</v>
@@ -25744,7 +25744,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.33104133605957</v>
+        <v>1.33104121685028</v>
       </c>
       <c r="H875" t="n">
         <v>350</v>
@@ -25773,7 +25773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H876" t="n">
         <v>4200</v>
@@ -25802,7 +25802,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.30282127857208</v>
+        <v>1.30282139778137</v>
       </c>
       <c r="H877" t="n">
         <v>1400</v>
@@ -25831,7 +25831,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H878" t="n">
         <v>8750</v>
@@ -25860,7 +25860,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>1.30752468109131</v>
+        <v>1.30752456188202</v>
       </c>
       <c r="H879" t="n">
         <v>3850</v>
@@ -25947,7 +25947,7 @@
         <v>1.375</v>
       </c>
       <c r="G882" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H882" t="n">
         <v>350</v>
@@ -25976,7 +25976,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H883" t="n">
         <v>5950</v>
@@ -26005,7 +26005,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H884" t="n">
         <v>2800</v>
@@ -26034,7 +26034,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H885" t="n">
         <v>8750</v>
@@ -26063,7 +26063,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>1.28871130943298</v>
+        <v>1.28871142864227</v>
       </c>
       <c r="H886" t="n">
         <v>1750</v>
@@ -26092,7 +26092,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G887" t="n">
-        <v>1.26989805698395</v>
+        <v>1.26989793777466</v>
       </c>
       <c r="H887" t="n">
         <v>1400</v>
@@ -26121,7 +26121,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.27460134029388</v>
+        <v>1.27460122108459</v>
       </c>
       <c r="H888" t="n">
         <v>2450</v>
@@ -26150,7 +26150,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G889" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H889" t="n">
         <v>6650</v>
@@ -26179,7 +26179,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.22286474704742</v>
+        <v>1.22286462783813</v>
       </c>
       <c r="H890" t="n">
         <v>7350</v>
@@ -26237,7 +26237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31693112850189</v>
+        <v>1.31693124771118</v>
       </c>
       <c r="H892" t="n">
         <v>7000</v>
@@ -26266,7 +26266,7 @@
         <v>1.375</v>
       </c>
       <c r="G893" t="n">
-        <v>1.29341459274292</v>
+        <v>1.29341471195221</v>
       </c>
       <c r="H893" t="n">
         <v>8400</v>
@@ -26324,7 +26324,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G895" t="n">
-        <v>1.27930474281311</v>
+        <v>1.27930462360382</v>
       </c>
       <c r="H895" t="n">
         <v>10150</v>
@@ -26353,7 +26353,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>1.4486243724823</v>
+        <v>1.44862425327301</v>
       </c>
       <c r="H896" t="n">
         <v>43400</v>
@@ -26382,7 +26382,7 @@
         <v>1.5</v>
       </c>
       <c r="G897" t="n">
-        <v>1.41099786758423</v>
+        <v>1.41099774837494</v>
       </c>
       <c r="H897" t="n">
         <v>25200</v>
@@ -26411,7 +26411,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G898" t="n">
-        <v>1.4909542798996</v>
+        <v>1.49095439910889</v>
       </c>
       <c r="H898" t="n">
         <v>172900</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H899" t="n">
         <v>51450</v>
@@ -26527,7 +26527,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G902" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H902" t="n">
         <v>47600</v>
@@ -26846,7 +26846,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G913" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H913" t="n">
         <v>5250</v>
@@ -26904,7 +26904,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.6508674621582</v>
+        <v>1.65086734294891</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -27107,7 +27107,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89073717594147</v>
+        <v>1.89073705673218</v>
       </c>
       <c r="H922" t="n">
         <v>129500</v>
@@ -27136,7 +27136,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G923" t="n">
-        <v>1.94717669487</v>
+        <v>1.94717681407928</v>
       </c>
       <c r="H923" t="n">
         <v>32550</v>
@@ -27165,7 +27165,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.9377703666687</v>
+        <v>1.93777012825012</v>
       </c>
       <c r="H924" t="n">
         <v>12250</v>
@@ -27252,7 +27252,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>1.97539687156677</v>
+        <v>1.97539675235748</v>
       </c>
       <c r="H927" t="n">
         <v>112000</v>
@@ -27484,7 +27484,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G935" t="n">
-        <v>2.05065011978149</v>
+        <v>2.05065035820007</v>
       </c>
       <c r="H935" t="n">
         <v>40950</v>
@@ -27687,7 +27687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.15412306785583</v>
+        <v>2.15412330627441</v>
       </c>
       <c r="H942" t="n">
         <v>109200</v>
@@ -27745,7 +27745,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G944" t="n">
-        <v>2.4551362991333</v>
+        <v>2.45513606071472</v>
       </c>
       <c r="H944" t="n">
         <v>203700</v>
@@ -27774,7 +27774,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G945" t="n">
-        <v>2.46454238891602</v>
+        <v>2.46454262733459</v>
       </c>
       <c r="H945" t="n">
         <v>364350</v>
@@ -27861,7 +27861,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G948" t="n">
-        <v>3.02894186973572</v>
+        <v>3.0289421081543</v>
       </c>
       <c r="H948" t="n">
         <v>583450</v>
@@ -27948,7 +27948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9725022315979</v>
+        <v>2.97250199317932</v>
       </c>
       <c r="H951" t="n">
         <v>31150</v>
@@ -28064,7 +28064,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G955" t="n">
-        <v>2.71852254867554</v>
+        <v>2.71852231025696</v>
       </c>
       <c r="H955" t="n">
         <v>15400</v>
@@ -28093,7 +28093,7 @@
         <v>2.75</v>
       </c>
       <c r="G956" t="n">
-        <v>2.58682918548584</v>
+        <v>2.58682942390442</v>
       </c>
       <c r="H956" t="n">
         <v>21700</v>
@@ -28122,7 +28122,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>2.75614905357361</v>
+        <v>2.75614929199219</v>
       </c>
       <c r="H957" t="n">
         <v>51100</v>
@@ -28209,7 +28209,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>2.8690288066864</v>
+        <v>2.86902856826782</v>
       </c>
       <c r="H960" t="n">
         <v>39200</v>
@@ -28238,7 +28238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H961" t="n">
         <v>175000</v>
@@ -28296,7 +28296,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G963" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H963" t="n">
         <v>100100</v>
@@ -28441,7 +28441,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H968" t="n">
         <v>131250</v>
@@ -28470,7 +28470,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G969" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H969" t="n">
         <v>18550</v>
@@ -28557,7 +28557,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G972" t="n">
-        <v>3.39580130577087</v>
+        <v>3.39580106735229</v>
       </c>
       <c r="H972" t="n">
         <v>29400</v>
@@ -28586,7 +28586,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3111412525177</v>
+        <v>3.31114149093628</v>
       </c>
       <c r="H973" t="n">
         <v>20300</v>
@@ -28615,7 +28615,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H974" t="n">
         <v>31500</v>
@@ -28731,7 +28731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H978" t="n">
         <v>15750</v>
@@ -28760,7 +28760,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H979" t="n">
         <v>12950</v>
@@ -28847,7 +28847,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H982" t="n">
         <v>30800</v>
@@ -28992,7 +28992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04775524139404</v>
+        <v>3.04775500297546</v>
       </c>
       <c r="H987" t="n">
         <v>16800</v>
@@ -29021,7 +29021,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G988" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H988" t="n">
         <v>11550</v>
@@ -29050,7 +29050,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G989" t="n">
-        <v>3.30173492431641</v>
+        <v>3.30173468589783</v>
       </c>
       <c r="H989" t="n">
         <v>43400</v>
@@ -29137,7 +29137,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G992" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H992" t="n">
         <v>5250</v>
@@ -29224,7 +29224,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>3.25470185279846</v>
+        <v>3.25470161437988</v>
       </c>
       <c r="H995" t="n">
         <v>24150</v>
@@ -29253,7 +29253,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G996" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H996" t="n">
         <v>14700</v>
@@ -29369,7 +29369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.24529504776001</v>
+        <v>3.24529480934143</v>
       </c>
       <c r="H1000" t="n">
         <v>30100</v>
@@ -29427,7 +29427,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1002" t="n">
         <v>2450</v>
@@ -29456,7 +29456,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1003" t="n">
         <v>10150</v>
@@ -29485,7 +29485,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1004" t="n">
         <v>2450</v>
@@ -29630,7 +29630,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1009" t="n">
         <v>5250</v>
@@ -29688,7 +29688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1011" t="n">
         <v>2100</v>
@@ -29717,7 +29717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1012" t="n">
         <v>3500</v>
@@ -29833,7 +29833,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1016" t="n">
         <v>2800</v>
@@ -29862,7 +29862,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.3675811290741</v>
+        <v>3.36758136749268</v>
       </c>
       <c r="H1017" t="n">
         <v>68950</v>
@@ -29949,7 +29949,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1020" t="n">
         <v>1750</v>
@@ -29978,7 +29978,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1021" t="n">
         <v>8050</v>
@@ -30007,7 +30007,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1022" t="n">
         <v>3150</v>
@@ -30065,7 +30065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1024" t="n">
         <v>350</v>
@@ -30094,7 +30094,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1025" t="n">
         <v>9450</v>
@@ -30123,7 +30123,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1026" t="n">
         <v>3500</v>
@@ -30181,7 +30181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.16063475608826</v>
+        <v>3.16063499450684</v>
       </c>
       <c r="H1028" t="n">
         <v>2100</v>
@@ -30268,7 +30268,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1031" t="n">
         <v>1400</v>
@@ -30297,7 +30297,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1032" t="n">
         <v>14700</v>
@@ -30326,7 +30326,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1033" t="n">
         <v>6300</v>
@@ -30384,7 +30384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1035" t="n">
         <v>7000</v>
@@ -30413,7 +30413,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1036" t="n">
         <v>45850</v>
@@ -30500,7 +30500,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.11360168457031</v>
+        <v>3.11360192298889</v>
       </c>
       <c r="H1039" t="n">
         <v>7350</v>
@@ -30558,7 +30558,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1041" t="n">
         <v>7350</v>
@@ -30587,7 +30587,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1042" t="n">
         <v>9450</v>
@@ -30616,7 +30616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1043" t="n">
         <v>2800</v>
@@ -30645,7 +30645,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1044" t="n">
         <v>4900</v>
@@ -30674,7 +30674,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1045" t="n">
         <v>4200</v>
@@ -30732,7 +30732,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1047" t="n">
         <v>2100</v>
@@ -30761,7 +30761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1048" t="n">
         <v>27650</v>
@@ -30790,7 +30790,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.10419487953186</v>
+        <v>3.10419535636902</v>
       </c>
       <c r="H1049" t="n">
         <v>12600</v>
@@ -30877,7 +30877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.07597517967224</v>
+        <v>3.07597494125366</v>
       </c>
       <c r="H1052" t="n">
         <v>252000</v>
@@ -30964,7 +30964,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.09478855133057</v>
+        <v>3.09478831291199</v>
       </c>
       <c r="H1055" t="n">
         <v>17850</v>
@@ -31022,7 +31022,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.03834867477417</v>
+        <v>3.03834843635559</v>
       </c>
       <c r="H1057" t="n">
         <v>9100</v>
@@ -31167,7 +31167,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.02894186973572</v>
+        <v>3.0289421081543</v>
       </c>
       <c r="H1062" t="n">
         <v>42000</v>
@@ -31196,7 +31196,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1063" t="n">
         <v>11200</v>
@@ -31283,7 +31283,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.08538198471069</v>
+        <v>3.08538174629211</v>
       </c>
       <c r="H1066" t="n">
         <v>44450</v>
@@ -31312,7 +31312,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.15122842788696</v>
+        <v>3.15122818946838</v>
       </c>
       <c r="H1067" t="n">
         <v>21700</v>
@@ -31341,7 +31341,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.14182186126709</v>
+        <v>3.14182162284851</v>
       </c>
       <c r="H1068" t="n">
         <v>42350</v>
@@ -31370,7 +31370,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.21707510948181</v>
+        <v>3.21707487106323</v>
       </c>
       <c r="H1069" t="n">
         <v>30450</v>
@@ -31544,7 +31544,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.54630756378174</v>
+        <v>3.54630780220032</v>
       </c>
       <c r="H1075" t="n">
         <v>125650</v>
@@ -31573,7 +31573,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.77206778526306</v>
+        <v>3.77206754684448</v>
       </c>
       <c r="H1076" t="n">
         <v>223300</v>
@@ -31747,7 +31747,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58393406867981</v>
+        <v>3.58393430709839</v>
       </c>
       <c r="H1082" t="n">
         <v>44100</v>
@@ -31979,7 +31979,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56512117385864</v>
+        <v>3.56512093544006</v>
       </c>
       <c r="H1090" t="n">
         <v>50050</v>
@@ -32008,7 +32008,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.67800116539001</v>
+        <v>3.67800092697144</v>
       </c>
       <c r="H1091" t="n">
         <v>46200</v>
@@ -32066,7 +32066,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.71562743186951</v>
+        <v>3.71562767028809</v>
       </c>
       <c r="H1093" t="n">
         <v>55300</v>
@@ -32124,7 +32124,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.57452774047852</v>
+        <v>3.57452750205994</v>
       </c>
       <c r="H1095" t="n">
         <v>16800</v>
@@ -32211,7 +32211,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28292155265808</v>
+        <v>3.28292179107666</v>
       </c>
       <c r="H1098" t="n">
         <v>39900</v>
@@ -32298,7 +32298,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.48046112060547</v>
+        <v>3.48046135902405</v>
       </c>
       <c r="H1101" t="n">
         <v>45850</v>
@@ -68539,7 +68539,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="D2351" t="n">
-        <v>0.745000004768372</v>
+        <v>0.779999971389771</v>
       </c>
       <c r="E2351" t="n">
         <v>0.634999990463257</v>
@@ -68554,6 +68554,35 @@
         <v>22750</v>
       </c>
       <c r="I2351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2352" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>0.764999985694885</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="H2352" t="n">
+        <v>15050</v>
+      </c>
+      <c r="I2352" t="s">
         <v>9</v>
       </c>
     </row>
